--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -528,7 +528,7 @@
   <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -892,7 +892,7 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="9.5" customWidth="1" min="3" max="3"/>
     <col width="11.5" customWidth="1" min="4" max="4"/>
@@ -1009,9 +1009,9 @@
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="19.5" customWidth="1" min="2" max="2"/>
-    <col width="26.5" customWidth="1" min="3" max="3"/>
+    <col width="29.5" customWidth="1" min="3" max="3"/>
     <col width="8.5" customWidth="1" min="4" max="4"/>
     <col width="11.5" customWidth="1" min="5" max="5"/>
     <col width="10.5" customWidth="1" min="6" max="6"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>ABB (Distributors/Wholes</t>
+          <t>ABB (Distributors/Wholesale</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Orascom Development Hold</t>
+          <t>Orascom Development Holding</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Silicon Motion Technolog</t>
+          <t>Silicon Motion Technology</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -1806,12 +1806,12 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="8.5" customWidth="1" min="2" max="2"/>
     <col width="13.5" customWidth="1" min="3" max="3"/>
     <col width="12.5" customWidth="1" min="4" max="4"/>
-    <col width="32.5" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="50.5" customWidth="1" min="5" max="5"/>
+    <col width="42.5" customWidth="1" min="6" max="6"/>
     <col width="11.5" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1882,7 +1882,7 @@
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Aston Martin Lagonda Global Ho</t>
+          <t>Aston Martin Lagonda Global Holdings</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles,</t>
+          <t>Billionaire/Oligarch Vehicles,Titans &amp; Concentra</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -1999,9 +1999,9 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="46.5" customWidth="1" min="3" max="3"/>
     <col width="30.5" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -2129,7 +2129,7 @@
   <dimension ref="A1:F204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="30.5" customWidth="1" min="2" max="2"/>
     <col width="22.5" customWidth="1" min="3" max="3"/>
     <col width="24.5" customWidth="1" min="4" max="4"/>
@@ -8615,7 +8615,7 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="36.5" customWidth="1" min="2" max="2"/>
     <col width="10.5" customWidth="1" min="3" max="3"/>
     <col width="10.5" customWidth="1" min="4" max="4"/>

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -2052,7 +2052,7 @@
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -2062,26 +2062,26 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>The Greenbrier Companies, Inc.</t>
+          <t>Charter Communications, Inc.</t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>2.1</v>
+        <v>5.9</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>2018</t>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Wendy Teramoto</t>
+          <t>W. Conn</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -2091,26 +2091,28 @@
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K22" s="13" t="n">
-        <v>9.699999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>12.3</v>
+        <v>3</v>
       </c>
       <c r="M22" s="14" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="N22" s="14" t="n">
-        <v>1.09</v>
+        <v>0.83</v>
+      </c>
+      <c r="N22" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -2120,26 +2122,26 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Charter Communications, Inc.</t>
+          <t>The Greenbrier Companies, Inc.</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>2018</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>W. Conn</t>
+          <t>Wendy Teramoto</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
@@ -2149,22 +2151,20 @@
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K23" s="13" t="n">
-        <v>5.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>3</v>
+        <v>12.3</v>
       </c>
       <c r="M23" s="14" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="N23" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>0.84</v>
+      </c>
+      <c r="N23" s="14" t="n">
+        <v>1.09</v>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="E28" s="11" t="n">
         <v>1.4</v>
@@ -7078,7 +7078,7 @@
     <col width="57.5" customWidth="1" min="2" max="2"/>
     <col width="24.5" customWidth="1" min="3" max="3"/>
     <col width="31.5" customWidth="1" min="4" max="4"/>
-    <col width="16.5" customWidth="1" min="5" max="5"/>
+    <col width="10.5" customWidth="1" min="5" max="5"/>
     <col width="11.5" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
@@ -8866,12 +8866,12 @@
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Wendy Teramoto</t>
+          <t>Anthony Williams</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>The Greenbrier Companies</t>
+          <t>Akamai Technologies</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -8886,34 +8886,34 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>AKAM</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>9.699999999999999</v>
+        <v>19.1</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>12.3</v>
+        <v>40.4</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>0.84</v>
+        <v>3.5</v>
       </c>
       <c r="J44" s="14" t="n">
-        <v>1.09</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Anthony Williams</t>
+          <t>Bill Roeschlein</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Akamai Technologies</t>
+          <t>Tigo Energy</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -8928,34 +8928,34 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>AKAM</t>
+          <t>TYGO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>19.1</v>
+        <v>4.7</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>40.4</v>
+        <v>6.7</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>3.5</v>
+        <v>1.65</v>
       </c>
       <c r="J45" s="14" t="n">
-        <v>16.92</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>Bill Roeschlein</t>
+          <t>Thierry Pilenko</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Tigo Energy</t>
+          <t>LanzaTech Global</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -8970,34 +8970,36 @@
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>TYGO</t>
+          <t>LNZA</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
         <v>10.7</v>
       </c>
-      <c r="G46" s="13" t="n">
-        <v>4.7</v>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H46" s="13" t="n">
-        <v>6.7</v>
+        <v>0.1</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>1.65</v>
+        <v>0.05</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>2.38</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>Thierry Pilenko</t>
+          <t>W. Conn</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>LanzaTech Global</t>
+          <t>Charter Communications</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -9012,36 +9014,36 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>LNZA</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
         <v>10.7</v>
       </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G47" s="13" t="n">
+        <v>5.6</v>
       </c>
       <c r="H47" s="13" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J47" s="14" t="n">
-        <v>0.05</v>
+        <v>0.83</v>
+      </c>
+      <c r="J47" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>W. Conn</t>
+          <t>Wendy Teramoto</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Charter Communications</t>
+          <t>The Greenbrier Companies</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -9056,25 +9058,23 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>5.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>3</v>
+        <v>12.3</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="J48" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>0.84</v>
+      </c>
+      <c r="J48" s="14" t="n">
+        <v>1.09</v>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
@@ -9434,12 +9434,12 @@
     <row r="57" ht="14" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Jonathan Christodoro</t>
+          <t>John Campbell</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Xerox</t>
+          <t>Porch Group</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -9454,22 +9454,24 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>XRXDW</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>8.1</v>
+        <v>23.1</v>
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I57" s="14" t="n">
-        <v>0.08</v>
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J57" s="12" t="inlineStr">
         <is>
@@ -9480,12 +9482,12 @@
     <row r="58" ht="14" customHeight="1">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Louis Pastor</t>
+          <t>Chris Siu</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Xerox</t>
+          <t>Aehr Test Systems</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -9500,14 +9502,16 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>XRXDW</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="G58" s="13" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
@@ -9515,23 +9519,21 @@
         </is>
       </c>
       <c r="I58" s="14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J58" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>13.03</v>
+      </c>
+      <c r="J58" s="14" t="n">
+        <v>14.35</v>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>John Campbell</t>
+          <t>Jonathan Christodoro</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Porch Group</t>
+          <t>Xerox</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -9546,24 +9548,22 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>XRXDW</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>23.1</v>
+        <v>8.1</v>
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I59" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I59" s="14" t="n">
+        <v>0.08</v>
       </c>
       <c r="J59" s="12" t="inlineStr">
         <is>
@@ -9574,12 +9574,12 @@
     <row r="60" ht="14" customHeight="1">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Chris Siu</t>
+          <t>Louis Pastor</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Aehr Test Systems</t>
+          <t>Xerox</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -9594,16 +9594,14 @@
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>XRXDW</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="G60" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>7.8</v>
+      </c>
+      <c r="G60" s="13" t="n">
+        <v>8.1</v>
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
@@ -9611,10 +9609,12 @@
         </is>
       </c>
       <c r="I60" s="14" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="J60" s="14" t="n">
-        <v>14.35</v>
+        <v>0.08</v>
+      </c>
+      <c r="J60" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
@@ -12188,12 +12188,12 @@
     <row r="120" ht="14" customHeight="1">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>Vincent Intrieri</t>
+          <t>Charles Searle</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Tencent Holdings</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
@@ -12208,89 +12208,91 @@
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>HTZ 8 07-15-29</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="F120" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G120" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H120" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I120" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J120" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G120" s="13" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H120" s="13" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="I120" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J120" s="14" t="n">
+        <v>3.69</v>
       </c>
     </row>
     <row r="121" ht="14" customHeight="1">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>Charles Searle</t>
+          <t>Abdul Al-Halabi</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>Tencent Holdings</t>
+          <t>Embassy Capital</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
-        </is>
-      </c>
-      <c r="E121" s="9" t="inlineStr">
-        <is>
-          <t>0700.HK</t>
-        </is>
-      </c>
-      <c r="F121" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" s="13" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H121" s="13" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="I121" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="J121" s="14" t="n">
-        <v>3.69</v>
+          <t>Gulf/Royal Family Offices</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I121" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J121" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="122" ht="14" customHeight="1">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>Abdul Al-Halabi</t>
+          <t>Abdulla Binhabtoor</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>Embassy Capital</t>
+          <t>Shamal Holding</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
@@ -12332,17 +12334,17 @@
     <row r="123" ht="14" customHeight="1">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>Abdulla Binhabtoor</t>
+          <t>Abdulmajeed Alhaqbani</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>Shamal Holding</t>
+          <t>Kingdom Holding Company</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -12384,17 +12386,17 @@
     <row r="124" ht="14" customHeight="1">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>Abdulmajeed Alhaqbani</t>
+          <t>Abdulwahab Wazzan</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>Kingdom Holding Company</t>
+          <t>National International Holding Company</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -12436,12 +12438,12 @@
     <row r="125" ht="14" customHeight="1">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>Abdulwahab Wazzan</t>
+          <t>Achporn Charuchinda</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>National International Holding Company</t>
+          <t>Bangchak Corporation</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
@@ -12488,12 +12490,12 @@
     <row r="126" ht="14" customHeight="1">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>Achporn Charuchinda</t>
+          <t>Adam Sierakowski</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>Bangchak Corporation</t>
+          <t>Kinetiko Energy</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
@@ -12503,7 +12505,7 @@
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E126" s="12" t="inlineStr">
@@ -12545,7 +12547,7 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>Kinetiko Energy</t>
+          <t>Raptor Resources (Other Metals, Minerals and Mining</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
@@ -12592,22 +12594,22 @@
     <row r="128" ht="14" customHeight="1">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>Adam Sierakowski</t>
+          <t>Adel Alabdulsalam</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>Raptor Resources (Other Metals, Minerals and Mining</t>
+          <t>Kingdom Holding Company</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr">
@@ -12644,22 +12646,22 @@
     <row r="129" ht="14" customHeight="1">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>Adel Alabdulsalam</t>
+          <t>Adrian Casey</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>Kingdom Holding Company</t>
+          <t>Vulcan Steel (Industrial Supplies and Parts</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
@@ -12696,12 +12698,12 @@
     <row r="130" ht="14" customHeight="1">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>Adrian Casey</t>
+          <t>Adrian Ramos</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Steel (Industrial Supplies and Parts</t>
+          <t>Atlas CON Mining</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
@@ -12748,12 +12750,12 @@
     <row r="131" ht="14" customHeight="1">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>Adrian Ramos</t>
+          <t>Ahmad Al Mujalham</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>Atlas CON Mining</t>
+          <t>Shamal Az-Zour Al-Oula</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
@@ -12763,7 +12765,7 @@
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr">
@@ -12800,17 +12802,17 @@
     <row r="132" ht="14" customHeight="1">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>Ahmad Al Mujalham</t>
+          <t>Ahmed Altanani</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>Shamal Az-Zour Al-Oula</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
@@ -12852,17 +12854,17 @@
     <row r="133" ht="14" customHeight="1">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>Ahmed Altanani</t>
+          <t>Ahmed El Salamouny</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>National International Holding Company</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
@@ -12904,17 +12906,17 @@
     <row r="134" ht="14" customHeight="1">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>Ahmed El Salamouny</t>
+          <t>Ahmed Halawany</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>National International Holding Company</t>
+          <t>SIGMA Capital Holding</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
@@ -12956,17 +12958,17 @@
     <row r="135" ht="14" customHeight="1">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>Ahmed Halawany</t>
+          <t>Al Mawji</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>SIGMA Capital Holding</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
@@ -13008,7 +13010,7 @@
     <row r="136" ht="14" customHeight="1">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>Al Mawji</t>
+          <t>Alain Bacos</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
@@ -13060,22 +13062,22 @@
     <row r="137" ht="14" customHeight="1">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>Alain Bacos</t>
+          <t>Alan Tang</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>Far East Orchard</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E137" s="12" t="inlineStr">
@@ -13112,12 +13114,12 @@
     <row r="138" ht="14" customHeight="1">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>Alan Tang</t>
+          <t>Aleksey Orel</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>Far East Orchard</t>
+          <t>NOVATEK (Russia</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
@@ -13164,12 +13166,12 @@
     <row r="139" ht="14" customHeight="1">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>Aleksey Orel</t>
+          <t>Alessandro Garrone</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>NOVATEK (Russia</t>
+          <t>De Nora</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
@@ -13216,22 +13218,22 @@
     <row r="140" ht="14" customHeight="1">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>Alessandro Garrone</t>
+          <t>Alexander Kempe Cañal de Orozco</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>De Nora</t>
+          <t>37celsius Capital Partners</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E140" s="12" t="inlineStr">
@@ -13268,22 +13270,22 @@
     <row r="141" ht="14" customHeight="1">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>Alexander Kempe Cañal de Orozco</t>
+          <t>Alexander Kurilov</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>37celsius Capital Partners</t>
+          <t>Pharmacy Chain 36.6</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E141" s="12" t="inlineStr">
@@ -13320,12 +13322,12 @@
     <row r="142" ht="14" customHeight="1">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>Alexander Kurilov</t>
+          <t>Alexander Sergeev</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>Pharmacy Chain 36.6</t>
+          <t>En+ Group</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
@@ -13372,22 +13374,22 @@
     <row r="143" ht="14" customHeight="1">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>Alexander Sergeev</t>
+          <t>Alexander Zhuravlev</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>En+ Group</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
@@ -13424,22 +13426,22 @@
     <row r="144" ht="14" customHeight="1">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>Alexander Zhuravlev</t>
+          <t>Alfredo Ramos</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>Atlas CON Mining</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E144" s="12" t="inlineStr">
@@ -13476,12 +13478,12 @@
     <row r="145" ht="14" customHeight="1">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>Alfredo Ramos</t>
+          <t>Alistair Cowden</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>Atlas CON Mining</t>
+          <t>Firefinch</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
@@ -13528,22 +13530,22 @@
     <row r="146" ht="14" customHeight="1">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>Alistair Cowden</t>
+          <t>Alwaleed al Saud</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>Firefinch</t>
+          <t>Kingdom Holding Company</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E146" s="12" t="inlineStr">
@@ -13580,17 +13582,17 @@
     <row r="147" ht="14" customHeight="1">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>Alwaleed al Saud</t>
+          <t>Amnat Jiramanimai</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>Kingdom Holding Company</t>
+          <t>The Crown Property Bureau</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
@@ -13632,17 +13634,17 @@
     <row r="148" ht="14" customHeight="1">
       <c r="A148" s="10" t="inlineStr">
         <is>
-          <t>Amnat Jiramanimai</t>
+          <t>Andre Forsterling</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>The Crown Property Bureau</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>Investor</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
@@ -13684,22 +13686,22 @@
     <row r="149" ht="14" customHeight="1">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>Andre Forsterling</t>
+          <t>Andrea Mangion</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>Trident Estates</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E149" s="12" t="inlineStr">
@@ -13736,12 +13738,12 @@
     <row r="150" ht="14" customHeight="1">
       <c r="A150" s="10" t="inlineStr">
         <is>
-          <t>Andrea Mangion</t>
+          <t>Andres Finkielsztain</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>Trident Estates</t>
+          <t>Menē</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
@@ -13788,12 +13790,12 @@
     <row r="151" ht="14" customHeight="1">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>Andres Finkielsztain</t>
+          <t>Andrew Barron</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>Menē</t>
+          <t>Natcore Technology</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
@@ -13803,7 +13805,7 @@
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E151" s="12" t="inlineStr">
@@ -13840,12 +13842,12 @@
     <row r="152" ht="14" customHeight="1">
       <c r="A152" s="10" t="inlineStr">
         <is>
-          <t>Andrew Barron</t>
+          <t>Andrew Frain</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>Natcore Technology</t>
+          <t>Shamal Az-Zour Al-Oula</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
@@ -13892,17 +13894,17 @@
     <row r="153" ht="14" customHeight="1">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>Andrew Frain</t>
+          <t>André Yché</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>Shamal Az-Zour Al-Oula</t>
+          <t>CDC Habitat</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
@@ -13944,22 +13946,22 @@
     <row r="154" ht="14" customHeight="1">
       <c r="A154" s="10" t="inlineStr">
         <is>
-          <t>André Yché</t>
+          <t>Andy Torrance</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>CDC Habitat</t>
+          <t>Angling Direct</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E154" s="12" t="inlineStr">
@@ -13996,12 +13998,12 @@
     <row r="155" ht="14" customHeight="1">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>Andy Torrance</t>
+          <t>Angela Luger</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>Angling Direct</t>
+          <t>JD Sports Fashion</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
@@ -14048,22 +14050,22 @@
     <row r="156" ht="14" customHeight="1">
       <c r="A156" s="10" t="inlineStr">
         <is>
-          <t>Angela Luger</t>
+          <t>Anke Bridge</t>
         </is>
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>JD Sports Fashion</t>
+          <t>LGT Group</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Family Office (Multi)</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E156" s="12" t="inlineStr">
@@ -14100,22 +14102,22 @@
     <row r="157" ht="14" customHeight="1">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>Anke Bridge</t>
+          <t>Annabel Roedhammer</t>
         </is>
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>LGT Group</t>
+          <t>Vulcan Energy Resources</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Family Office (Multi)</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
@@ -14152,12 +14154,12 @@
     <row r="158" ht="14" customHeight="1">
       <c r="A158" s="10" t="inlineStr">
         <is>
-          <t>Annabel Roedhammer</t>
+          <t>Anne Stevens</t>
         </is>
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Energy Resources</t>
+          <t>Aston Martin Lagonda Global Holdings</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
@@ -14204,12 +14206,12 @@
     <row r="159" ht="14" customHeight="1">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>Anne Stevens</t>
+          <t>Antoine Castro</t>
         </is>
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>Aston Martin Lagonda Global Holdings</t>
+          <t>Paref</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
@@ -14256,12 +14258,12 @@
     <row r="160" ht="14" customHeight="1">
       <c r="A160" s="10" t="inlineStr">
         <is>
-          <t>Antoine Castro</t>
+          <t>Antonio Serrano</t>
         </is>
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>Paref</t>
+          <t>Grupo Dia (Department Stores</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
@@ -14308,12 +14310,12 @@
     <row r="161" ht="14" customHeight="1">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>Antonio Serrano</t>
+          <t>Anu Dhir</t>
         </is>
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>Grupo Dia (Department Stores</t>
+          <t>Capital</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
@@ -14360,22 +14362,22 @@
     <row r="162" ht="14" customHeight="1">
       <c r="A162" s="10" t="inlineStr">
         <is>
-          <t>Anu Dhir</t>
+          <t>Anup Cherian</t>
         </is>
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>Capital</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
@@ -14412,17 +14414,17 @@
     <row r="163" ht="14" customHeight="1">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>Anup Cherian</t>
+          <t>Arada Jaroon-Ek</t>
         </is>
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>Origin Property</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
@@ -14464,12 +14466,12 @@
     <row r="164" ht="14" customHeight="1">
       <c r="A164" s="10" t="inlineStr">
         <is>
-          <t>Arada Jaroon-Ek</t>
+          <t>Arada Vongkusolkit</t>
         </is>
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>Origin Property</t>
+          <t>Erawan Group</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
@@ -14516,12 +14518,12 @@
     <row r="165" ht="14" customHeight="1">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>Arada Vongkusolkit</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>Erawan Group</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
@@ -14531,12 +14533,12 @@
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
-        </is>
-      </c>
-      <c r="E165" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="E165" s="9" t="inlineStr">
+        <is>
+          <t>WOPEF</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
@@ -14544,20 +14546,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G165" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H165" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I165" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G165" s="13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H165" s="13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I165" s="14" t="n">
+        <v>1.15</v>
       </c>
       <c r="J165" s="12" t="inlineStr">
         <is>
@@ -14568,27 +14564,27 @@
     <row r="166" ht="14" customHeight="1">
       <c r="A166" s="10" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Aseem Gupta</t>
         </is>
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
-        </is>
-      </c>
-      <c r="E166" s="9" t="inlineStr">
-        <is>
-          <t>WOPEF</t>
+          <t>Gulf/Royal Family Offices</t>
+        </is>
+      </c>
+      <c r="E166" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F166" s="12" t="inlineStr">
@@ -14596,14 +14592,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G166" s="13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H166" s="13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I166" s="14" t="n">
-        <v>1.15</v>
+      <c r="G166" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H166" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I166" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J166" s="12" t="inlineStr">
         <is>
@@ -14614,22 +14616,22 @@
     <row r="167" ht="14" customHeight="1">
       <c r="A167" s="10" t="inlineStr">
         <is>
-          <t>Aseem Gupta</t>
+          <t>Ashley Paxton</t>
         </is>
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>Ikigai Ventures Limited</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E167" s="12" t="inlineStr">
@@ -14666,22 +14668,22 @@
     <row r="168" ht="14" customHeight="1">
       <c r="A168" s="10" t="inlineStr">
         <is>
-          <t>Ashley Paxton</t>
+          <t>Avinash Mansabdar</t>
         </is>
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>Ikigai Ventures Limited</t>
+          <t>The Private Office of Sheikh Saeed bin Ahmed Al Maktoum</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Family Office (Single)</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E168" s="12" t="inlineStr">
@@ -14718,22 +14720,22 @@
     <row r="169" ht="14" customHeight="1">
       <c r="A169" s="10" t="inlineStr">
         <is>
-          <t>Avinash Mansabdar</t>
+          <t>Bamdad Bastani</t>
         </is>
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>The Private Office of Sheikh Saeed bin Ahmed Al Maktoum</t>
+          <t>IQE</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>Family Office (Single)</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E169" s="12" t="inlineStr">
@@ -14770,12 +14772,12 @@
     <row r="170" ht="14" customHeight="1">
       <c r="A170" s="10" t="inlineStr">
         <is>
-          <t>Bamdad Bastani</t>
+          <t>Basim Alothman</t>
         </is>
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>IQE</t>
+          <t>Coast Investment</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
@@ -14785,7 +14787,7 @@
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E170" s="12" t="inlineStr">
@@ -14822,17 +14824,17 @@
     <row r="171" ht="14" customHeight="1">
       <c r="A171" s="10" t="inlineStr">
         <is>
-          <t>Basim Alothman</t>
+          <t>Bassim Hokimi</t>
         </is>
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>Coast Investment</t>
+          <t>Atlamed</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
@@ -14874,17 +14876,17 @@
     <row r="172" ht="14" customHeight="1">
       <c r="A172" s="10" t="inlineStr">
         <is>
-          <t>Bassim Hokimi</t>
+          <t>Ben Errez</t>
         </is>
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>Atlamed</t>
+          <t>RYVYL</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
@@ -14926,12 +14928,12 @@
     <row r="173" ht="14" customHeight="1">
       <c r="A173" s="10" t="inlineStr">
         <is>
-          <t>Ben Errez</t>
+          <t>Bronwyn Brophy</t>
         </is>
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>RYVYL</t>
+          <t>Vitrolife</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
@@ -14941,7 +14943,7 @@
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E173" s="12" t="inlineStr">
@@ -14978,12 +14980,12 @@
     <row r="174" ht="14" customHeight="1">
       <c r="A174" s="10" t="inlineStr">
         <is>
-          <t>Bronwyn Brophy</t>
+          <t>Bruce Pachkowski</t>
         </is>
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>Vitrolife</t>
+          <t>Total Energy Services</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
@@ -15030,12 +15032,12 @@
     <row r="175" ht="14" customHeight="1">
       <c r="A175" s="10" t="inlineStr">
         <is>
-          <t>Bruce Pachkowski</t>
+          <t>Burckhard Bergmann</t>
         </is>
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>Total Energy Services</t>
+          <t>NOVATEK (Russia</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
@@ -15082,22 +15084,22 @@
     <row r="176" ht="14" customHeight="1">
       <c r="A176" s="10" t="inlineStr">
         <is>
-          <t>Burckhard Bergmann</t>
+          <t>Caesar Maasry</t>
         </is>
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>NOVATEK (Russia</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E176" s="12" t="inlineStr">
@@ -15134,17 +15136,17 @@
     <row r="177" ht="14" customHeight="1">
       <c r="A177" s="10" t="inlineStr">
         <is>
-          <t>Caesar Maasry</t>
+          <t>Carlos Riquelme</t>
         </is>
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>Prince of Wales Country Club</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
@@ -15186,17 +15188,17 @@
     <row r="178" ht="14" customHeight="1">
       <c r="A178" s="10" t="inlineStr">
         <is>
-          <t>Carlos Riquelme</t>
+          <t>Carolyn Ang</t>
         </is>
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>Prince of Wales Country Club</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
@@ -15238,22 +15240,22 @@
     <row r="179" ht="14" customHeight="1">
       <c r="A179" s="10" t="inlineStr">
         <is>
-          <t>Carolyn Ang</t>
+          <t>Carsten Bachg</t>
         </is>
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>Vulcan Energy Resources</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E179" s="12" t="inlineStr">
@@ -15290,12 +15292,12 @@
     <row r="180" ht="14" customHeight="1">
       <c r="A180" s="10" t="inlineStr">
         <is>
-          <t>Carsten Bachg</t>
+          <t>Changxian Beijing</t>
         </is>
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Energy Resources</t>
+          <t>Ares Strategic Mining</t>
         </is>
       </c>
       <c r="C180" s="10" t="inlineStr">
@@ -15342,12 +15344,12 @@
     <row r="181" ht="14" customHeight="1">
       <c r="A181" s="10" t="inlineStr">
         <is>
-          <t>Changxian Beijing</t>
+          <t>Chantelle Collins</t>
         </is>
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>Ares Strategic Mining</t>
+          <t>Trident Resources</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
@@ -15394,12 +15396,12 @@
     <row r="182" ht="14" customHeight="1">
       <c r="A182" s="10" t="inlineStr">
         <is>
-          <t>Chantelle Collins</t>
+          <t>Charles Xuereb</t>
         </is>
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>Trident Resources</t>
+          <t>Trident Estates</t>
         </is>
       </c>
       <c r="C182" s="10" t="inlineStr">
@@ -15446,12 +15448,12 @@
     <row r="183" ht="14" customHeight="1">
       <c r="A183" s="10" t="inlineStr">
         <is>
-          <t>Charles Xuereb</t>
+          <t>Chen Qiuhai</t>
         </is>
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>Trident Estates</t>
+          <t>Yamada Green Resources</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
@@ -15461,7 +15463,7 @@
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E183" s="12" t="inlineStr">
@@ -15498,12 +15500,12 @@
     <row r="184" ht="14" customHeight="1">
       <c r="A184" s="10" t="inlineStr">
         <is>
-          <t>Chen Qiuhai</t>
+          <t>Chi Tung Liu</t>
         </is>
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>Yamada Green Resources</t>
+          <t>Novatek Microelectronics</t>
         </is>
       </c>
       <c r="C184" s="10" t="inlineStr">
@@ -15513,7 +15515,7 @@
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E184" s="12" t="inlineStr">
@@ -15550,12 +15552,12 @@
     <row r="185" ht="14" customHeight="1">
       <c r="A185" s="10" t="inlineStr">
         <is>
-          <t>Chi Tung Liu</t>
+          <t>Chih-Hsien Lo</t>
         </is>
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>Novatek Microelectronics</t>
+          <t>Prince Housing &amp; Development</t>
         </is>
       </c>
       <c r="C185" s="10" t="inlineStr">
@@ -15565,7 +15567,7 @@
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E185" s="12" t="inlineStr">
@@ -15602,12 +15604,12 @@
     <row r="186" ht="14" customHeight="1">
       <c r="A186" s="10" t="inlineStr">
         <is>
-          <t>Chih-Hsien Lo</t>
+          <t>Chris McGinnis</t>
         </is>
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>Prince Housing &amp; Development</t>
+          <t>Playtech</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
@@ -15617,7 +15619,7 @@
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E186" s="12" t="inlineStr">
@@ -15654,22 +15656,22 @@
     <row r="187" ht="14" customHeight="1">
       <c r="A187" s="10" t="inlineStr">
         <is>
-          <t>Chris McGinnis</t>
+          <t>Christian Windfuhr</t>
         </is>
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>Playtech</t>
+          <t>Grand City Properties</t>
         </is>
       </c>
       <c r="C187" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D187" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E187" s="12" t="inlineStr">
@@ -15706,22 +15708,22 @@
     <row r="188" ht="14" customHeight="1">
       <c r="A188" s="10" t="inlineStr">
         <is>
-          <t>Christian Windfuhr</t>
+          <t>Christopher Marshall</t>
         </is>
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>Grand City Properties</t>
+          <t>Payoneer</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E188" s="12" t="inlineStr">
@@ -15758,12 +15760,12 @@
     <row r="189" ht="14" customHeight="1">
       <c r="A189" s="10" t="inlineStr">
         <is>
-          <t>Christopher Marshall</t>
+          <t>Christopher Moreno</t>
         </is>
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>Payoneer</t>
+          <t>Vulcan Energy Resources</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
@@ -15810,22 +15812,22 @@
     <row r="190" ht="14" customHeight="1">
       <c r="A190" s="10" t="inlineStr">
         <is>
-          <t>Christopher Moreno</t>
+          <t>Chye Guan</t>
         </is>
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Energy Resources</t>
+          <t>Quantum Asset Management (Singapore</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E190" s="12" t="inlineStr">
@@ -15862,17 +15864,17 @@
     <row r="191" ht="14" customHeight="1">
       <c r="A191" s="10" t="inlineStr">
         <is>
-          <t>Chye Guan</t>
+          <t>Clemens Gregor</t>
         </is>
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>Quantum Asset Management (Singapore</t>
+          <t>Finad Group</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
@@ -15914,22 +15916,22 @@
     <row r="192" ht="14" customHeight="1">
       <c r="A192" s="10" t="inlineStr">
         <is>
-          <t>Clemens Gregor</t>
+          <t>Craig Hewitt</t>
         </is>
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>Finad Group</t>
+          <t>Delta Seaboard Well Service Inc.</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>Investor</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E192" s="12" t="inlineStr">
@@ -15966,12 +15968,12 @@
     <row r="193" ht="14" customHeight="1">
       <c r="A193" s="10" t="inlineStr">
         <is>
-          <t>Craig Hewitt</t>
+          <t>D. Mark Appleby</t>
         </is>
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>Delta Seaboard Well Service Inc.</t>
+          <t>Tartisan Nickel</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
@@ -16018,12 +16020,12 @@
     <row r="194" ht="14" customHeight="1">
       <c r="A194" s="10" t="inlineStr">
         <is>
-          <t>D. Mark Appleby</t>
+          <t>Dana Codding</t>
         </is>
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>Tartisan Nickel</t>
+          <t>Parkland</t>
         </is>
       </c>
       <c r="C194" s="10" t="inlineStr">
@@ -16070,12 +16072,12 @@
     <row r="195" ht="14" customHeight="1">
       <c r="A195" s="10" t="inlineStr">
         <is>
-          <t>Dana Codding</t>
+          <t>Daniel Halyk</t>
         </is>
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>Parkland</t>
+          <t>Total Energy Services</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
@@ -16122,12 +16124,12 @@
     <row r="196" ht="14" customHeight="1">
       <c r="A196" s="10" t="inlineStr">
         <is>
-          <t>Daniel Halyk</t>
+          <t>Daniel Major</t>
         </is>
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>Total Energy Services</t>
+          <t>GoviEx Uranium</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
@@ -16174,12 +16176,12 @@
     <row r="197" ht="14" customHeight="1">
       <c r="A197" s="10" t="inlineStr">
         <is>
-          <t>Daniel Major</t>
+          <t>Daniel Ninivaggi</t>
         </is>
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>GoviEx Uranium</t>
+          <t>Indivior</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
@@ -16226,12 +16228,12 @@
     <row r="198" ht="14" customHeight="1">
       <c r="A198" s="10" t="inlineStr">
         <is>
-          <t>Daniel Ninivaggi</t>
+          <t>Danny Callow</t>
         </is>
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>Indivior</t>
+          <t>Toubani Resources</t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
@@ -16278,12 +16280,12 @@
     <row r="199" ht="14" customHeight="1">
       <c r="A199" s="10" t="inlineStr">
         <is>
-          <t>Danny Callow</t>
+          <t>Darwin Green</t>
         </is>
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>Toubani Resources</t>
+          <t>Contango ORE</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
@@ -16293,7 +16295,7 @@
       </c>
       <c r="D199" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E199" s="12" t="inlineStr">
@@ -16330,17 +16332,17 @@
     <row r="200" ht="14" customHeight="1">
       <c r="A200" s="10" t="inlineStr">
         <is>
-          <t>Darwin Green</t>
+          <t>David Gibson-Moore</t>
         </is>
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>Contango ORE</t>
+          <t>Dalma Capital</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
@@ -16382,22 +16384,22 @@
     <row r="201" ht="14" customHeight="1">
       <c r="A201" s="10" t="inlineStr">
         <is>
-          <t>David Gibson-Moore</t>
+          <t>David Watkinson</t>
         </is>
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>Dalma Capital</t>
+          <t>Emergent Metals</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>Investor</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E201" s="12" t="inlineStr">
@@ -16434,12 +16436,12 @@
     <row r="202" ht="14" customHeight="1">
       <c r="A202" s="10" t="inlineStr">
         <is>
-          <t>David Watkinson</t>
+          <t>Dean Marks</t>
         </is>
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>Emergent Metals</t>
+          <t>Premier Power Renewable Energy</t>
         </is>
       </c>
       <c r="C202" s="10" t="inlineStr">
@@ -16486,22 +16488,22 @@
     <row r="203" ht="14" customHeight="1">
       <c r="A203" s="10" t="inlineStr">
         <is>
-          <t>Dean Marks</t>
+          <t>Deanna Zhang</t>
         </is>
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>Premier Power Renewable Energy</t>
+          <t>Circularity Capital</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D203" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E203" s="12" t="inlineStr">
@@ -16538,22 +16540,22 @@
     <row r="204" ht="14" customHeight="1">
       <c r="A204" s="10" t="inlineStr">
         <is>
-          <t>Deanna Zhang</t>
+          <t>Deepak Nanda</t>
         </is>
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>Circularity Capital</t>
+          <t>Trident Group</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E204" s="12" t="inlineStr">

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -1034,7 +1034,7 @@
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>SIMO</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -1044,14 +1044,14 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Affirm Holdings, Inc.</t>
+          <t>Silicon Motion Technology Corporation</t>
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>14.8</v>
+        <v>22.3</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>1</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>Keith Rabois</t>
+          <t>Steve Chen</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -1073,26 +1073,26 @@
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K5" s="13" t="n">
-        <v>24.1</v>
+        <v>31</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>11.8</v>
+        <v>7.8</v>
       </c>
       <c r="M5" s="14" t="n">
-        <v>4.17</v>
+        <v>2.18</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>4.63</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>SIMO</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -1102,14 +1102,14 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Silicon Motion Technology Corporation</t>
+          <t>Affirm Holdings, Inc.</t>
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>6.1</v>
+        <v>16.6</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2.1</v>
+        <v>7.7</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>Steve Chen</t>
+          <t>Keith Rabois</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -1131,20 +1131,20 @@
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="K6" s="13" t="n">
-        <v>31</v>
+        <v>24.1</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>7.8</v>
+        <v>11.8</v>
       </c>
       <c r="M6" s="14" t="n">
-        <v>2.18</v>
+        <v>4.17</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>2.18</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>1</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>34.1</v>
+        <v>34.6</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>1</v>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>1</v>
@@ -1632,7 +1632,7 @@
     <row r="15" ht="14" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>SANA</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1642,14 +1642,14 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Sana Biotechnology, Inc.</t>
+          <t>Charter Communications, Inc.</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>16.7</v>
+        <v>19.9</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>2.4</v>
+        <v>8.1</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>1</v>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Richard Mulligan</t>
+          <t>W. Conn</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -1671,21 +1671,17 @@
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="K15" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L15" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>6.05</v>
+        <v>0.83</v>
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
@@ -1696,7 +1692,7 @@
     <row r="16" ht="14" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>TOL</t>
+          <t>SANA</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1706,14 +1702,14 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Toll Brothers, Inc.</t>
+          <t>Sana Biotechnology, Inc.</t>
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>15.9</v>
+        <v>16.7</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>1</v>
@@ -1725,7 +1721,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Derek Kan</t>
+          <t>Richard Mulligan</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -1735,26 +1731,32 @@
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L16" s="13" t="n">
-        <v>10.9</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M16" s="14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="N16" s="14" t="n">
-        <v>1.52</v>
+        <v>6.05</v>
+      </c>
+      <c r="N16" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>UAA</t>
+          <t>TOL</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1764,14 +1766,14 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Under Armour, Inc.</t>
+          <t>Toll Brothers, Inc.</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>14.4</v>
+        <v>15.9</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>1</v>
@@ -1783,7 +1785,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Dawn Fitzpatrick</t>
+          <t>Derek Kan</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -1796,27 +1798,23 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="K17" s="13" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>10.9</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>2.09</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>UAA</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -1826,14 +1824,14 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>IAMGOLD Corporation</t>
+          <t>Under Armour, Inc.</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>13.5</v>
+        <v>14.4</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>1</v>
@@ -1845,36 +1843,40 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Joseph Flaim</t>
+          <t>Dawn Fitzpatrick</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-      <c r="K18" s="13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L18" s="13" t="n">
-        <v>9.9</v>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M18" s="14" t="n">
-        <v>2.61</v>
+        <v>1.36</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>2.61</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>COYA</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -1884,14 +1886,14 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Coya Therapeutics, Inc.</t>
+          <t>IAMGOLD Corporation</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>12.7</v>
+        <v>13.9</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>1</v>
@@ -1903,40 +1905,36 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Wilbur Ross</t>
+          <t>Joseph Flaim</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>9.9</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>COYA</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -1946,26 +1944,26 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>SandRidge Energy, Inc.</t>
+          <t>Coya Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>1999</t>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Nancy Dunlap</t>
+          <t>Wilbur Ross</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -1975,26 +1973,30 @@
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="K20" s="13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L20" s="13" t="n">
-        <v>6.3</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M20" s="14" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -2004,31 +2006,31 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>SandRidge Energy, Inc.</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
         <v>12.1</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>7.5</v>
+        <v>2.6</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>1999</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Sharmila Mulligan</t>
+          <t>Nancy Dunlap</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Managers</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J21" s="10" t="inlineStr">
@@ -2037,22 +2039,22 @@
         </is>
       </c>
       <c r="K21" s="13" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>16.9</v>
+        <v>6.3</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>2.38</v>
+        <v>0.96</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>2.38</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -2062,14 +2064,14 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Charter Communications, Inc.</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>10.7</v>
+        <v>12.1</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5.9</v>
+        <v>7.5</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>1</v>
@@ -2081,32 +2083,30 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>W. Conn</t>
+          <t>Sharmila Mulligan</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Titans &amp; Concentrated Managers</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K22" s="13" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>3</v>
+        <v>16.9</v>
       </c>
       <c r="M22" s="14" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="N22" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>2.38</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="D34" s="11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>1</v>
@@ -2826,7 +2826,7 @@
     <row r="35" ht="14" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>0086.HK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -2836,55 +2836,55 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Sun Hung Kai &amp; Co. Limited</t>
+          <t>Star Bulk Carriers Corp.</t>
         </is>
       </c>
       <c r="D35" s="11" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="F35" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>2010</t>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Jacqueline Leung</t>
+          <t>Raffaele Zagari</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K35" s="13" t="n">
-        <v>5.5</v>
+        <v>7.9</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>5.6</v>
+        <v>11.8</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>0.34</v>
+        <v>1.34</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>0.39</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>AYA</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -2894,55 +2894,55 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Star Bulk Carriers Corp.</t>
+          <t>Aya Gold &amp; Silver Inc.</t>
         </is>
       </c>
       <c r="D36" s="11" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>2021</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>Raffaele Zagari</t>
+          <t>Ghislane Bennouna</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
-        </is>
-      </c>
-      <c r="J36" s="10" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>Gulf/Royal Family Offices</t>
+        </is>
+      </c>
+      <c r="J36" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K36" s="13" t="n">
-        <v>7.9</v>
+        <v>18.9</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>11.8</v>
+        <v>35.9</v>
       </c>
       <c r="M36" s="14" t="n">
-        <v>1.34</v>
+        <v>8.23</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>1.34</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="37" ht="14" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>AYA</t>
+          <t>0086.HK</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -2952,26 +2952,26 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Aya Gold &amp; Silver Inc.</t>
+          <t>Sun Hung Kai &amp; Co. Limited</t>
         </is>
       </c>
       <c r="D37" s="11" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>Ghislane Bennouna</t>
+          <t>Jacqueline Leung</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
@@ -2979,22 +2979,22 @@
           <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
-      <c r="J37" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="K37" s="13" t="n">
-        <v>18.9</v>
+        <v>5.5</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>35.9</v>
+        <v>5.6</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>8.23</v>
+        <v>0.34</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>8.23</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
@@ -3468,7 +3468,7 @@
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>VEON</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -3478,26 +3478,26 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Lindblad Expeditions Holdings, Inc.</t>
+          <t>VEON Ltd.</t>
         </is>
       </c>
       <c r="D46" s="11" t="n">
         <v>24.4</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>Pamala Kaufman</t>
+          <t>Brandon Lewis,Duncan Perry</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
@@ -3507,32 +3507,26 @@
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K46" s="13" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="L46" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M46" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N46" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.1</v>
+      </c>
+      <c r="L46" s="13" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="M46" s="14" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N46" s="14" t="n">
+        <v>167.02</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -3542,59 +3536,61 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Xometry, Inc.</t>
+          <t>Lindblad Expeditions Holdings, Inc.</t>
         </is>
       </c>
       <c r="D47" s="11" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>2022</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>Katharine Weymouth</t>
+          <t>Pamala Kaufman</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="K47" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="n">
+        <v>20.2</v>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M47" s="14" t="n">
-        <v>9.34</v>
-      </c>
-      <c r="N47" s="14" t="n">
-        <v>18.22</v>
+      <c r="M47" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N47" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>UPWK</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -3604,14 +3600,14 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Upwork Inc.</t>
+          <t>Xometry, Inc.</t>
         </is>
       </c>
       <c r="D48" s="11" t="n">
-        <v>21</v>
+        <v>24.1</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="F48" s="12" t="n">
         <v>1</v>
@@ -3623,7 +3619,7 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>Glenn Kelman</t>
+          <t>Katharine Weymouth</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -3633,26 +3629,30 @@
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="K48" s="13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L48" s="13" t="n">
-        <v>10.3</v>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="K48" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L48" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M48" s="14" t="n">
-        <v>1.67</v>
+        <v>9.34</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>2.36</v>
+        <v>18.22</v>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPWK</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -3662,55 +3662,55 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>SLB N.V.</t>
+          <t>Upwork Inc.</t>
         </is>
       </c>
       <c r="D49" s="11" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>10.7</v>
+        <v>3.6</v>
       </c>
       <c r="F49" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="10" t="inlineStr">
-        <is>
-          <t>2011</t>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>Glenn Kelman</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K49" s="13" t="n">
-        <v>12.2</v>
+        <v>5.4</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>25.1</v>
+        <v>10.3</v>
       </c>
       <c r="M49" s="14" t="n">
-        <v>3.01</v>
+        <v>1.67</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>15.23</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -3720,26 +3720,26 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>SLB N.V.</t>
         </is>
       </c>
       <c r="D50" s="11" t="n">
-        <v>19</v>
+        <v>20.8</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>12.8</v>
+        <v>10.7</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1</v>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>2011</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>Cynthia Hostetler,George Willis,Thomas Fanning</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -3749,26 +3749,26 @@
       </c>
       <c r="J50" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K50" s="13" t="n">
-        <v>14.3</v>
+        <v>12.2</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>28.9</v>
+        <v>25.1</v>
       </c>
       <c r="M50" s="14" t="n">
-        <v>3.77</v>
+        <v>3.01</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>9.800000000000001</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>DRIO</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -3778,17 +3778,17 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>DarioHealth Corp.</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="D51" s="11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.6</v>
+        <v>12.8</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -3797,40 +3797,36 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Yoav Shaked</t>
+          <t>Cynthia Hostetler,George Willis,Thomas Fanning</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="n">
+        <v>14.3</v>
       </c>
       <c r="L51" s="13" t="n">
-        <v>9.9</v>
+        <v>28.9</v>
       </c>
       <c r="M51" s="14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N51" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>3.77</v>
+      </c>
+      <c r="N51" s="14" t="n">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>VEON</t>
+          <t>DRIO</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -3840,49 +3836,53 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>VEON Ltd.</t>
+          <t>DarioHealth Corp.</t>
         </is>
       </c>
       <c r="D52" s="11" t="n">
-        <v>16.2</v>
+        <v>17</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G52" s="10" t="inlineStr">
-        <is>
-          <t>2023</t>
+        <v>1</v>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>Brandon Lewis,Duncan Perry</t>
+          <t>Yoav Shaked</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="n">
-        <v>5.1</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L52" s="13" t="n">
-        <v>102.7</v>
+        <v>9.9</v>
       </c>
       <c r="M52" s="14" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="N52" s="14" t="n">
-        <v>167.02</v>
+        <v>1.16</v>
+      </c>
+      <c r="N52" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
@@ -4006,7 +4006,7 @@
     <row r="55" ht="14" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>ALLO</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -4016,26 +4016,26 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>COMPASS Pathways plc</t>
+          <t>Allogene Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="D55" s="11" t="n">
         <v>13.7</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>6.7</v>
+        <v>3.8</v>
       </c>
       <c r="F55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>2012</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>Annalisa Jenkins</t>
+          <t>Franz Humer</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -4059,16 +4059,16 @@
         </is>
       </c>
       <c r="M55" s="14" t="n">
-        <v>15.93</v>
+        <v>1.28</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>15.93</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>ALLO</t>
+          <t>CMPS</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -4078,26 +4078,26 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Allogene Therapeutics, Inc.</t>
+          <t>COMPASS Pathways plc</t>
         </is>
       </c>
       <c r="D56" s="11" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>2.8</v>
+        <v>6.7</v>
       </c>
       <c r="F56" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G56" s="10" t="inlineStr">
-        <is>
-          <t>2012</t>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>Franz Humer</t>
+          <t>Annalisa Jenkins</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="M56" s="14" t="n">
-        <v>1.28</v>
+        <v>15.93</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>1.28</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="57" ht="14" customHeight="1">
@@ -4190,7 +4190,7 @@
     <row r="58" ht="14" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>LNZA</t>
+          <t>NGVT</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -4200,14 +4200,14 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>LanzaTech Global, Inc.</t>
+          <t>Ingevity Corporation</t>
         </is>
       </c>
       <c r="D58" s="11" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="F58" s="12" t="n">
         <v>1</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>Thierry Pilenko</t>
+          <t>Daniel Sansone</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -4229,28 +4229,28 @@
       </c>
       <c r="J58" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="K58" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="n">
+        <v>18.6</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>0.1</v>
+        <v>45.5</v>
       </c>
       <c r="M58" s="14" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N58" s="14" t="n">
-        <v>0.05</v>
+        <v>52.3</v>
+      </c>
+      <c r="N58" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>LNZA</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -4260,14 +4260,14 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Porch Group, Inc.</t>
+          <t>LanzaTech Global, Inc.</t>
         </is>
       </c>
       <c r="D59" s="11" t="n">
-        <v>8</v>
+        <v>10.7</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="F59" s="12" t="n">
         <v>1</v>
@@ -4279,42 +4279,38 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>Amanda Reierson</t>
+          <t>Thierry Pilenko</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="L59" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M59" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N59" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>NGVT</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -4324,14 +4320,14 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Ingevity Corporation</t>
+          <t>Semtech Corporation</t>
         </is>
       </c>
       <c r="D60" s="11" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7</v>
+        <v>6.7</v>
       </c>
       <c r="F60" s="12" t="n">
         <v>1</v>
@@ -4343,7 +4339,7 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>Daniel Sansone</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -4353,28 +4349,26 @@
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K60" s="13" t="n">
-        <v>18.6</v>
+        <v>135</v>
       </c>
       <c r="L60" s="13" t="n">
-        <v>45.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="M60" s="14" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="N60" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>20.63</v>
+      </c>
+      <c r="N60" s="14" t="n">
+        <v>68.36</v>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -4384,14 +4378,14 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Semtech Corporation</t>
+          <t>Amprius Technologies, Inc.</t>
         </is>
       </c>
       <c r="D61" s="11" t="n">
-        <v>7.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="F61" s="12" t="n">
         <v>1</v>
@@ -4403,7 +4397,7 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -4413,26 +4407,30 @@
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="K61" s="13" t="n">
-        <v>135</v>
-      </c>
-      <c r="L61" s="13" t="n">
-        <v>99.90000000000001</v>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="K61" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L61" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M61" s="14" t="n">
-        <v>20.63</v>
+        <v>11.38</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>68.36</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -4442,14 +4440,14 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Republic Services, Inc.</t>
+          <t>Porch Group, Inc.</t>
         </is>
       </c>
       <c r="D62" s="11" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="F62" s="12" t="n">
         <v>1</v>
@@ -4461,7 +4459,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Katharine Weymouth</t>
+          <t>Amanda Reierson</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -4471,17 +4469,21 @@
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="K62" s="13" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="M62" s="14" t="n">
-        <v>5.5</v>
+        <v>23.1</v>
+      </c>
+      <c r="L62" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M62" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N62" s="12" t="inlineStr">
         <is>
@@ -4506,10 +4508,10 @@
         </is>
       </c>
       <c r="D63" s="11" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F63" s="12" t="n">
         <v>1</v>
@@ -4552,7 +4554,7 @@
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -4562,14 +4564,14 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Amprius Technologies, Inc.</t>
+          <t>Republic Services, Inc.</t>
         </is>
       </c>
       <c r="D64" s="11" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="F64" s="12" t="n">
         <v>1</v>
@@ -4581,12 +4583,12 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>Katharine Weymouth</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J64" s="10" t="inlineStr">
@@ -4594,21 +4596,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="K64" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L64" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="K64" s="13" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>30.5</v>
       </c>
       <c r="M64" s="14" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="N64" s="14" t="n">
-        <v>11.38</v>
+        <v>5.5</v>
+      </c>
+      <c r="N64" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
@@ -5090,7 +5090,7 @@
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>HTO</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -5100,14 +5100,14 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>H2O America</t>
+          <t>Guardant Health, Inc.</t>
         </is>
       </c>
       <c r="D73" s="11" t="n">
         <v>3.4</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>1.5</v>
+        <v>8.9</v>
       </c>
       <c r="F73" s="12" t="n">
         <v>1</v>
@@ -5119,36 +5119,44 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>Gregory Landis</t>
+          <t>Aaref Hilaly</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="K73" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="L73" s="13" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="M73" s="14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="N73" s="14" t="n">
-        <v>2.07</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>HTO</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -5158,14 +5166,14 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>MP Materials Corp.</t>
+          <t>H2O America</t>
         </is>
       </c>
       <c r="D74" s="11" t="n">
         <v>3.4</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="F74" s="12" t="n">
         <v>1</v>
@@ -5177,7 +5185,7 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>Randall Weisenburger</t>
+          <t>Gregory Landis</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
@@ -5187,28 +5195,26 @@
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K74" s="13" t="n">
-        <v>150.4</v>
-      </c>
-      <c r="L74" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="L74" s="13" t="n">
+        <v>21.8</v>
       </c>
       <c r="M74" s="14" t="n">
-        <v>4.46</v>
+        <v>1.35</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>4.46</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -5218,14 +5224,14 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Guardant Health, Inc.</t>
+          <t>MP Materials Corp.</t>
         </is>
       </c>
       <c r="D75" s="11" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>6.9</v>
+        <v>3.9</v>
       </c>
       <c r="F75" s="12" t="n">
         <v>1</v>
@@ -5237,38 +5243,32 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>Aaref Hilaly</t>
+          <t>Randall Weisenburger</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="K75" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="n">
+        <v>150.4</v>
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M75" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M75" s="14" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="N75" s="14" t="n">
+        <v>4.46</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
@@ -5632,101 +5632,101 @@
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Yoav Shaked</t>
+          <t>Steve Chen</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Capital</t>
+          <t>tracked principal</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>DarioHealth</t>
+          <t>Silicon Motion Technology</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>DRIO</t>
+          <t>SIMO</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
-        <v>17</v>
+        <v>22.3</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>0.6</v>
+        <v>7.1</v>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Chairman &amp; Board Member</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Board Member</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>31</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>9.9</v>
+        <v>7.8</v>
       </c>
       <c r="J5" s="14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="K5" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>2.18</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>2.18</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Keith Rabois</t>
+          <t>Yoav Shaked</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>tracked principal</t>
+          <t>Sequoia Capital</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>DarioHealth</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>DRIO</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>14.8</v>
+        <v>17</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>6.7</v>
+        <v>0.6</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Board Member</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="n">
-        <v>24.1</v>
+          <t>Chairman &amp; Board Member</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" s="13" t="n">
-        <v>11.8</v>
+        <v>9.9</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="K6" s="14" t="n">
-        <v>4.63</v>
+        <v>1.16</v>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Steve Chen</t>
+          <t>Keith Rabois</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -5736,19 +5736,19 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Silicon Motion Technology</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>SIMO</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="E7" s="12" t="n">
-        <v>6.1</v>
+        <v>16.6</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>2.1</v>
+        <v>7.7</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
@@ -5756,16 +5756,16 @@
         </is>
       </c>
       <c r="H7" s="13" t="n">
-        <v>31</v>
+        <v>24.1</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>7.8</v>
+        <v>11.8</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>2.18</v>
+        <v>4.17</v>
       </c>
       <c r="K7" s="14" t="n">
-        <v>2.18</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
@@ -5790,10 +5790,10 @@
         </is>
       </c>
       <c r="E8" s="12" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>34.1</v>
+        <v>34.6</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>12.6</v>
@@ -7308,12 +7308,12 @@
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Pamala Kaufman</t>
+          <t>Ashok Srivastava</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Lindblad Expeditions Holdings</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -7328,40 +7328,34 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>11.5</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>213.47</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Ashok Srivastava</t>
+          <t>Brandon Lewis</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Veon</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -7376,34 +7370,34 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>VEON</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>22.9</v>
+        <v>24.4</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>17.5</v>
+        <v>102.7</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>4.15</v>
+        <v>3.22</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>213.47</v>
+        <v>167.02</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Ashwini Kumar</t>
+          <t>Duncan Perry</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>PayPal Holdings</t>
+          <t>Veon</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -7418,34 +7412,34 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>VEON</t>
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>22.8</v>
+        <v>24.4</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>9.800000000000001</v>
+        <v>102.7</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>2.35</v>
+        <v>3.22</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>5.35</v>
+        <v>167.02</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Mary Kissel</t>
+          <t>Pamala Kaufman</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>Lindblad Expeditions Holdings</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -7460,38 +7454,40 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>22.6</v>
+        <v>24.4</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>44.3</v>
+        <v>20.2</v>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I11" s="14" t="n">
-        <v>0.93</v>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>neg TBV</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>Ashwini Kumar</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>SLB (Other Energy Services</t>
+          <t>PayPal Holdings</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -7506,34 +7502,34 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>20.8</v>
+        <v>22.7</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>12.2</v>
+        <v>6.8</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>25.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>3.01</v>
+        <v>2.35</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>15.23</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>C. Wes Burton</t>
+          <t>Mary Kissel</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -7548,34 +7544,38 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>19</v>
+        <v>22.6</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>28.9</v>
+        <v>44.3</v>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" s="14" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <v>9.800000000000001</v>
+        <v>0.93</v>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Cynthia Hostetler</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>SLB (Other Energy Services</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -7590,34 +7590,34 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>19</v>
+        <v>20.8</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>14.3</v>
+        <v>12.2</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>28.9</v>
+        <v>25.1</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>3.77</v>
+        <v>3.01</v>
       </c>
       <c r="J14" s="14" t="n">
-        <v>9.800000000000001</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>David Clement</t>
+          <t>Andrew Crowley</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>Markel Group</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -7632,34 +7632,34 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>MKL</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>19</v>
+        <v>20.6</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>14.3</v>
+        <v>6.9</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>28.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>3.77</v>
+        <v>1.05</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>9.800000000000001</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Denson Franklin</t>
+          <t>W. Conn</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>Charter Communications</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -7674,29 +7674,31 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>19</v>
+        <v>19.9</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>14.3</v>
+        <v>5.6</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>28.9</v>
+        <v>3</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>9.800000000000001</v>
+        <v>0.83</v>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>George Willis</t>
+          <t>C. Wes Burton</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -7738,7 +7740,7 @@
     <row r="18" ht="14" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>J. Hill</t>
+          <t>Cynthia Hostetler</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -7780,7 +7782,7 @@
     <row r="19" ht="14" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>J. Thomas Hill</t>
+          <t>David Clement</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -7822,7 +7824,7 @@
     <row r="20" ht="14" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Jerry Perkins</t>
+          <t>Denson Franklin</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -7864,7 +7866,7 @@
     <row r="21" ht="14" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Mark Warren</t>
+          <t>George Willis</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -7906,7 +7908,7 @@
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Mary Carlisle</t>
+          <t>J. Hill</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -7948,7 +7950,7 @@
     <row r="23" ht="14" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Thomas Fanning</t>
+          <t>J. Thomas Hill</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -7990,12 +7992,12 @@
     <row r="24" ht="14" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Andrew Crowley</t>
+          <t>Jerry Perkins</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Markel Group</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -8010,34 +8012,34 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>MKL</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>6.9</v>
+        <v>14.3</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>9.699999999999999</v>
+        <v>28.9</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>1.05</v>
+        <v>3.77</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>1.35</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Richard Mulligan</t>
+          <t>Mark Warren</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Sana Biotechnology</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -8052,40 +8054,34 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>SANA</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>28.9</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="J25" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>3.77</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Brandon Lewis</t>
+          <t>Mary Carlisle</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Veon</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -8100,34 +8096,34 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>VEON</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>16.2</v>
+        <v>19</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>5.1</v>
+        <v>14.3</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>102.7</v>
+        <v>28.9</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>3.22</v>
+        <v>3.77</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>167.02</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Duncan Perry</t>
+          <t>Thomas Fanning</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Veon</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -8142,34 +8138,34 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>VEON</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>16.2</v>
+        <v>19</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>5.1</v>
+        <v>14.3</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>102.7</v>
+        <v>28.9</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>3.22</v>
+        <v>3.77</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>167.02</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Danny Shepherd</t>
+          <t>Richard Mulligan</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Beazer Homes USA</t>
+          <t>Sana Biotechnology</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -8184,14 +8180,16 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>BZH</t>
+          <t>SANA</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="G28" s="13" t="n">
-        <v>39</v>
+        <v>16.7</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
@@ -8199,21 +8197,23 @@
         </is>
       </c>
       <c r="I28" s="14" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="J28" s="14" t="n">
-        <v>0.78</v>
+        <v>6.05</v>
+      </c>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Michael Insulan</t>
+          <t>Danny Shepherd</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Electra Battery Materials</t>
+          <t>Beazer Homes USA</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -8228,14 +8228,14 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>ELBM</t>
+          <t>BZH</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>5.7</v>
+        <v>39</v>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
@@ -8243,21 +8243,21 @@
         </is>
       </c>
       <c r="I29" s="14" t="n">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Derek Kan</t>
+          <t>Michael Insulan</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Toll Brothers</t>
+          <t>Electra Battery Materials</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -8272,34 +8272,36 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>TOL</t>
+          <t>ELBM</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H30" s="13" t="n">
-        <v>10.9</v>
+        <v>5.7</v>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I30" s="14" t="n">
-        <v>1.52</v>
+        <v>0.88</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>1.52</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Meryl Hartzband</t>
+          <t>Derek Kan</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Everest Group (Hamilton</t>
+          <t>Toll Brothers</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -8314,34 +8316,34 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>TOL</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>15.3</v>
+        <v>15.9</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>6.5</v>
+        <v>8.9</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>8</v>
+        <v>10.9</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>0.98</v>
+        <v>1.52</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Dawn Fitzpatrick</t>
+          <t>Meryl Hartzband</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Under Armour</t>
+          <t>Everest Group (Hamilton</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -8356,38 +8358,34 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>UAA</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>15.3</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>1.36</v>
+        <v>0.98</v>
       </c>
       <c r="J32" s="14" t="n">
-        <v>2.09</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="33" ht="14" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>James Nelson</t>
+          <t>Dawn Fitzpatrick</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Global Net Lease</t>
+          <t>Under Armour</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -8402,14 +8400,16 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>GNL</t>
+          <t>UAA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="G33" s="13" t="n">
-        <v>11.9</v>
+        <v>14.4</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
@@ -8417,21 +8417,21 @@
         </is>
       </c>
       <c r="I33" s="14" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Annalisa Jenkins</t>
+          <t>James Nelson</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>COMPASS Pathways</t>
+          <t>Global Net Lease</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -8446,16 +8446,14 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>GNL</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>14.2</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>11.9</v>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
@@ -8463,10 +8461,10 @@
         </is>
       </c>
       <c r="I34" s="14" t="n">
-        <v>15.93</v>
+        <v>1.22</v>
       </c>
       <c r="J34" s="14" t="n">
-        <v>15.93</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
@@ -8496,7 +8494,7 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="G35" s="13" t="n">
         <v>5.3</v>
@@ -8514,12 +8512,12 @@
     <row r="36" ht="14" customHeight="1">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Allan D. Schoening</t>
+          <t>Franz Humer</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Civeo</t>
+          <t>Allogene Therapeutics</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -8534,14 +8532,16 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>CVEO</t>
+          <t>ALLO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="G36" s="13" t="n">
-        <v>6.5</v>
+        <v>13.7</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
@@ -8549,21 +8549,21 @@
         </is>
       </c>
       <c r="I36" s="14" t="n">
-        <v>2.35</v>
+        <v>1.28</v>
       </c>
       <c r="J36" s="14" t="n">
-        <v>4.35</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="37" ht="14" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Franz Humer</t>
+          <t>Annalisa Jenkins</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Allogene Therapeutics</t>
+          <t>COMPASS Pathways</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -8578,11 +8578,11 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>ALLO</t>
+          <t>CMPS</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -8595,21 +8595,21 @@
         </is>
       </c>
       <c r="I37" s="14" t="n">
-        <v>1.28</v>
+        <v>15.93</v>
       </c>
       <c r="J37" s="14" t="n">
-        <v>1.28</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Wilbur Ross</t>
+          <t>Allan D. Schoening</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Coya Therapeutics</t>
+          <t>Civeo</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -8624,16 +8624,14 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>COYA</t>
+          <t>CVEO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>13.3</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>6.5</v>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
@@ -8641,21 +8639,21 @@
         </is>
       </c>
       <c r="I38" s="14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="J38" s="14" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Jonathan Frates</t>
+          <t>Wilbur Ross</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>SandRidge Energy</t>
+          <t>Coya Therapeutics</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -8670,34 +8668,38 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>COYA</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="G39" s="13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H39" s="13" t="n">
-        <v>6.3</v>
+        <v>12.7</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I39" s="14" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="J39" s="14" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Nancy Dunlap</t>
+          <t>Kathleen Quirk</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>SandRidge Energy</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -8712,34 +8714,34 @@
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>3.1</v>
+        <v>12.2</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>6.3</v>
+        <v>35.3</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>0.96</v>
+        <v>5.14</v>
       </c>
       <c r="J40" s="14" t="n">
-        <v>0.96</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>Kathleen Quirk</t>
+          <t>Jonathan Frates</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>SandRidge Energy</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -8754,34 +8756,34 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>12.2</v>
+        <v>3.1</v>
       </c>
       <c r="H41" s="13" t="n">
-        <v>35.3</v>
+        <v>6.3</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>5.14</v>
+        <v>0.96</v>
       </c>
       <c r="J41" s="14" t="n">
-        <v>5.14</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>Stephen Gunther</t>
+          <t>Nancy Dunlap</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Shoulder Innovations</t>
+          <t>SandRidge Energy</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -8791,43 +8793,39 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>12.1</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H42" s="13" t="n">
+        <v>6.3</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>2.96</v>
+        <v>0.96</v>
       </c>
       <c r="J42" s="14" t="n">
-        <v>2.96</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>Bryan Murphy</t>
+          <t>Anthony Williams</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Greenlight Capital Re</t>
+          <t>Akamai Technologies</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -8842,36 +8840,34 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>GLRE</t>
+          <t>AKAM</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>11.8</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>19.1</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>10</v>
+        <v>40.4</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>0.71</v>
+        <v>3.5</v>
       </c>
       <c r="J43" s="14" t="n">
-        <v>0.82</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Anthony Williams</t>
+          <t>Stephen Gunther</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Akamai Technologies</t>
+          <t>Shoulder Innovations</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -8881,39 +8877,43 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>AKAM</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="G44" s="13" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="H44" s="13" t="n">
-        <v>40.4</v>
+        <v>11.3</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I44" s="14" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="J44" s="14" t="n">
-        <v>16.92</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Bill Roeschlein</t>
+          <t>Bryan Murphy</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Tigo Energy</t>
+          <t>Greenlight Capital Re</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -8928,34 +8928,36 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>TYGO</t>
+          <t>GLRE</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="G45" s="13" t="n">
-        <v>4.7</v>
+        <v>11.1</v>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H45" s="13" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>1.65</v>
+        <v>0.71</v>
       </c>
       <c r="J45" s="14" t="n">
-        <v>2.38</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>Thierry Pilenko</t>
+          <t>Daniel Sansone</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>LanzaTech Global</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -8970,36 +8972,36 @@
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>LNZA</t>
+          <t>NGVT</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>10.9</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>18.6</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>0.1</v>
+        <v>45.5</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J46" s="14" t="n">
-        <v>0.05</v>
+        <v>52.3</v>
+      </c>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>W. Conn</t>
+          <t>Kenneth Gunderman</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Charter Communications</t>
+          <t>Uniti Group (Financial Services</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -9014,20 +9016,20 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="H47" s="13" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>0.83</v>
+        <v>14.41</v>
       </c>
       <c r="J47" s="12" t="inlineStr">
         <is>
@@ -9038,12 +9040,12 @@
     <row r="48" ht="14" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Wendy Teramoto</t>
+          <t>Bill Roeschlein</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>The Greenbrier Companies</t>
+          <t>Tigo Energy</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -9058,34 +9060,34 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>TYGO</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>9.699999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>12.3</v>
+        <v>6.7</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>0.84</v>
+        <v>1.65</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>1.09</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Sandra Bell</t>
+          <t>Thierry Pilenko</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Dye &amp; Durham</t>
+          <t>LanzaTech Global</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -9095,87 +9097,83 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>DYNDF</t>
+          <t>LNZA</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="G49" s="13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>10.7</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="13" t="n">
+        <v>0.1</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J49" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>0.05</v>
+      </c>
+      <c r="J49" s="14" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>Kenneth Gunderman</t>
+          <t>Viral Patel</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Uniti Group (Financial Services</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>4.5</v>
+        <v>18.6</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>1.8</v>
+        <v>26.6</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>14.41</v>
-      </c>
-      <c r="J50" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>10.41</v>
+      </c>
+      <c r="J50" s="14" t="n">
+        <v>11.43</v>
       </c>
     </row>
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Richard Russell</t>
+          <t>Wendy Teramoto</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>LM Funding America</t>
+          <t>The Greenbrier Companies</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -9190,40 +9188,34 @@
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>LMFA</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>10.6</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H51" s="13" t="n">
+        <v>12.3</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.84</v>
+      </c>
+      <c r="J51" s="14" t="n">
+        <v>1.09</v>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Jeffrey Fox</t>
+          <t>Sandra Bell</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Westrock Coffee</t>
+          <t>Dye &amp; Durham</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -9233,19 +9225,19 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>WEST</t>
+          <t>DYNDF</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>9.6</v>
+        <v>10.6</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>24.2</v>
+        <v>8.4</v>
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
@@ -9253,21 +9245,23 @@
         </is>
       </c>
       <c r="I52" s="14" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="J52" s="14" t="n">
-        <v>34.55</v>
+        <v>0.12</v>
+      </c>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>Brian Corvese</t>
+          <t>Michael Dougherty</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Agenus</t>
+          <t>Polaris (Automotive</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -9282,38 +9276,36 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H53" s="13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I53" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J53" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="J53" s="14" t="n">
+        <v>59.92</v>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Josephine Linden</t>
+          <t>Richard Russell</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Lands' End</t>
+          <t>LM Funding America</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -9323,39 +9315,45 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LMFA</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G54" s="13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H54" s="13" t="n">
-        <v>0.9</v>
+        <v>10.1</v>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I54" s="14" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="J54" s="14" t="n">
-        <v>0.63</v>
+        <v>2.02</v>
+      </c>
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Robert Colligan</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Dynex Capital</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -9365,81 +9363,83 @@
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>DX</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>32.4</v>
+        <v>135</v>
       </c>
       <c r="H55" s="13" t="n">
-        <v>4.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>0.83</v>
+        <v>20.63</v>
       </c>
       <c r="J55" s="14" t="n">
-        <v>0.83</v>
+        <v>68.36</v>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Dominic Picone</t>
+          <t>Jeffrey Fox</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>Westrock Coffee</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>WEST</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="H56" s="13" t="n">
-        <v>37.3</v>
+        <v>24.2</v>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I56" s="14" t="n">
-        <v>6.07</v>
+        <v>3.24</v>
       </c>
       <c r="J56" s="14" t="n">
-        <v>8.550000000000001</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="57" ht="14" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>John Campbell</t>
+          <t>Brian Corvese</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Porch Group</t>
+          <t>Agenus</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -9454,19 +9454,17 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>AGEN</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="H57" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2.4</v>
+      </c>
+      <c r="H57" s="13" t="n">
+        <v>3.1</v>
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
@@ -9475,19 +9473,19 @@
       </c>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>neg TBV</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Chris Siu</t>
+          <t>Rebecca Grossman-Cohen</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Aehr Test Systems</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -9502,38 +9500,34 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="G58" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G58" s="13" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H58" s="13" t="n">
+        <v>26.3</v>
       </c>
       <c r="I58" s="14" t="n">
-        <v>13.03</v>
+        <v>5.03</v>
       </c>
       <c r="J58" s="14" t="n">
-        <v>14.35</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Jonathan Christodoro</t>
+          <t>Josephine Linden</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Xerox</t>
+          <t>Lands' End</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -9543,43 +9537,39 @@
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>XRXDW</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="H59" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.7</v>
+      </c>
+      <c r="H59" s="13" t="n">
+        <v>0.9</v>
       </c>
       <c r="I59" s="14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J59" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>0.63</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v>0.63</v>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Louis Pastor</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Xerox</t>
+          <t>Amprius Technologies</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -9594,14 +9584,16 @@
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>XRXDW</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="G60" s="13" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
@@ -9609,23 +9601,21 @@
         </is>
       </c>
       <c r="I60" s="14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J60" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>11.38</v>
+      </c>
+      <c r="J60" s="14" t="n">
+        <v>11.38</v>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Daniel Sansone</t>
+          <t>Robert Colligan</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>Dynex Capital</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -9635,87 +9625,81 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>NGVT</t>
+          <t>DX</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>18.6</v>
+        <v>32.4</v>
       </c>
       <c r="H61" s="13" t="n">
-        <v>45.5</v>
+        <v>4.5</v>
       </c>
       <c r="I61" s="14" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="J61" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>0.83</v>
+      </c>
+      <c r="J61" s="14" t="n">
+        <v>0.83</v>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>Richard Massey</t>
+          <t>Dominic Picone</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Jena Acquisition II</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>JENA-UN</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>52</v>
+        <v>19.3</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="I62" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J62" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>37.3</v>
+      </c>
+      <c r="I62" s="14" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="J62" s="14" t="n">
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Randle Reece</t>
+          <t>John Campbell</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>AMN Healthcare Services</t>
+          <t>Porch Group</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -9730,20 +9714,24 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>AMN</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H63" s="13" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="I63" s="14" t="n">
-        <v>1.81</v>
+        <v>23.1</v>
+      </c>
+      <c r="H63" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I63" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J63" s="12" t="inlineStr">
         <is>
@@ -9754,12 +9742,12 @@
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>Chris Siu</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>Aehr Test Systems</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -9774,34 +9762,38 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G64" s="13" t="n">
-        <v>135</v>
-      </c>
-      <c r="H64" s="13" t="n">
-        <v>99.90000000000001</v>
+        <v>7.9</v>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I64" s="14" t="n">
-        <v>20.63</v>
+        <v>13.03</v>
       </c>
       <c r="J64" s="14" t="n">
-        <v>68.36</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>David Allen</t>
+          <t>Jonathan Christodoro</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Xerox</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -9816,20 +9808,22 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>XRXDW</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="H65" s="13" t="n">
-        <v>22.1</v>
+        <v>8.1</v>
+      </c>
+      <c r="H65" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I65" s="14" t="n">
-        <v>2.3</v>
+        <v>0.08</v>
       </c>
       <c r="J65" s="12" t="inlineStr">
         <is>
@@ -9840,12 +9834,12 @@
     <row r="66" ht="14" customHeight="1">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>Pam Kaufman</t>
+          <t>Louis Pastor</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Paramount Skydance</t>
+          <t>Xerox</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -9860,16 +9854,14 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>XRXDW</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="G66" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>7.8</v>
+      </c>
+      <c r="G66" s="13" t="n">
+        <v>8.1</v>
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
@@ -9877,21 +9869,23 @@
         </is>
       </c>
       <c r="I66" s="14" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="J66" s="14" t="n">
-        <v>2.34</v>
+        <v>0.08</v>
+      </c>
+      <c r="J66" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Mark DiPaolo</t>
+          <t>Richard Massey</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Innoviva</t>
+          <t>Jena Acquisition II</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -9906,34 +9900,38 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>INVA</t>
+          <t>JENA-UN</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>1.5</v>
+        <v>52</v>
       </c>
       <c r="H67" s="13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I67" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J67" s="14" t="n">
-        <v>1.48</v>
+        <v>20.7</v>
+      </c>
+      <c r="I67" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J67" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>Tim Cahill</t>
+          <t>Pam Kaufman</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Paramount Skydance</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -9948,36 +9946,38 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G68" s="13" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H68" s="13" t="n">
-        <v>19.6</v>
+        <v>7.3</v>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I68" s="14" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="J68" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J68" s="14" t="n">
+        <v>2.34</v>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>David Moradi</t>
+          <t>Randle Reece</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>AudioEye</t>
+          <t>AMN Healthcare Services</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -9992,22 +9992,20 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>AMN</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="H69" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="H69" s="13" t="n">
+        <v>12.7</v>
       </c>
       <c r="I69" s="14" t="n">
-        <v>27.93</v>
+        <v>1.81</v>
       </c>
       <c r="J69" s="12" t="inlineStr">
         <is>
@@ -10018,12 +10016,12 @@
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>David Habachy</t>
+          <t>David Allen</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Ring Energy</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -10038,36 +10036,36 @@
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>REI</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H70" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>15.1</v>
+      </c>
+      <c r="H70" s="13" t="n">
+        <v>22.1</v>
       </c>
       <c r="I70" s="14" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="J70" s="14" t="n">
-        <v>0.42</v>
+        <v>2.3</v>
+      </c>
+      <c r="J70" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>David Habachy</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Amprius Technologies</t>
+          <t>Ring Energy</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -10082,16 +10080,14 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>REI</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G71" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="G71" s="13" t="n">
+        <v>3.8</v>
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
@@ -10099,21 +10095,21 @@
         </is>
       </c>
       <c r="I71" s="14" t="n">
-        <v>11.38</v>
+        <v>0.42</v>
       </c>
       <c r="J71" s="14" t="n">
-        <v>11.38</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>Tiago Miranda</t>
+          <t>Mark DiPaolo</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Atlas Lithium</t>
+          <t>Innoviva</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -10128,38 +10124,34 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>ATLX</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G72" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>6.7</v>
+      </c>
+      <c r="G72" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H72" s="13" t="n">
+        <v>4.3</v>
       </c>
       <c r="I72" s="14" t="n">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="J72" s="14" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>Martin Bork</t>
+          <t>Tim Cahill</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Navigator Holdings</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -10174,34 +10166,36 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>NVGS</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>6.2</v>
+        <v>14.1</v>
       </c>
       <c r="H73" s="13" t="n">
-        <v>10.6</v>
+        <v>19.6</v>
       </c>
       <c r="I73" s="14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="J73" s="14" t="n">
-        <v>1.15</v>
+        <v>14.01</v>
+      </c>
+      <c r="J73" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>Charles Leykum</t>
+          <t>David Moradi</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Talon Capital (SPAC</t>
+          <t>AudioEye</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -10216,36 +10210,38 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>TLNC</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="G74" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="13" t="n">
-        <v>51.9</v>
+        <v>6.4</v>
+      </c>
+      <c r="G74" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I74" s="14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="J74" s="14" t="n">
-        <v>1.06</v>
+        <v>27.93</v>
+      </c>
+      <c r="J74" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>Tony Buffin</t>
+          <t>Tiago Miranda</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>DFS Furniture</t>
+          <t>Atlas Lithium</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
@@ -10260,36 +10256,38 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>DFS.L</t>
+          <t>ATLX</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G75" s="13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H75" s="13" t="n">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I75" s="14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="J75" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>1.76</v>
+      </c>
+      <c r="J75" s="14" t="n">
+        <v>1.77</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Nicholas Zangler</t>
+          <t>Martin Bork</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>Viant Technology</t>
+          <t>Navigator Holdings</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -10304,34 +10302,34 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>NVGS</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>23.8</v>
+        <v>6.2</v>
       </c>
       <c r="H76" s="13" t="n">
-        <v>28.7</v>
+        <v>10.6</v>
       </c>
       <c r="I76" s="14" t="n">
-        <v>2.11</v>
+        <v>1.15</v>
       </c>
       <c r="J76" s="14" t="n">
-        <v>2.48</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>Oscar Iglesias</t>
+          <t>Charles Leykum</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>Codere Online Luxembourg</t>
+          <t>Talon Capital (SPAC</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
@@ -10346,34 +10344,36 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>CDROW</t>
+          <t>TLNC</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G77" s="13" t="n">
-        <v>4.2</v>
+        <v>6</v>
+      </c>
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H77" s="13" t="n">
-        <v>251.9</v>
+        <v>51.9</v>
       </c>
       <c r="I77" s="14" t="n">
-        <v>9.52</v>
+        <v>1.06</v>
       </c>
       <c r="J77" s="14" t="n">
-        <v>9.52</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>Laura Duda</t>
+          <t>Tony Buffin</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>The Goodyear Tire &amp; Rubber</t>
+          <t>DFS Furniture</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -10388,36 +10388,36 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>DFS.L</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="H78" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.4</v>
+      </c>
+      <c r="H78" s="13" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="I78" s="14" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="J78" s="14" t="n">
-        <v>0.7</v>
+        <v>1.23</v>
+      </c>
+      <c r="J78" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="14" customHeight="1">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>Rebecca Grossman-Cohen</t>
+          <t>Nicholas Zangler</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>Viant Technology</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
@@ -10432,34 +10432,34 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>16.6</v>
+        <v>23.8</v>
       </c>
       <c r="H79" s="13" t="n">
-        <v>26.3</v>
+        <v>28.7</v>
       </c>
       <c r="I79" s="14" t="n">
-        <v>5.03</v>
+        <v>2.11</v>
       </c>
       <c r="J79" s="14" t="n">
-        <v>7.23</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="80" ht="14" customHeight="1">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>Schroeder Norman</t>
+          <t>Oscar Iglesias</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>Simpple (Automation/Workflow Software</t>
+          <t>Codere Online Luxembourg</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -10474,38 +10474,34 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>SPPL</t>
+          <t>CDROW</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G80" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.5</v>
+      </c>
+      <c r="G80" s="13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H80" s="13" t="n">
+        <v>251.9</v>
       </c>
       <c r="I80" s="14" t="n">
-        <v>4.75</v>
+        <v>9.52</v>
       </c>
       <c r="J80" s="14" t="n">
-        <v>103.28</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="81" ht="14" customHeight="1">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>Paul Allen</t>
+          <t>Laura Duda</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Airship AI Holdings</t>
+          <t>The Goodyear Tire &amp; Rubber</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -10520,40 +10516,36 @@
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G81" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I81" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J81" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.4</v>
+      </c>
+      <c r="G81" s="13" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="H81" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="14" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J81" s="14" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="82" ht="14" customHeight="1">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>Aris Kekedjian</t>
+          <t>Schroeder Norman</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>Stratasys (Printing Services (B2B</t>
+          <t>Simpple (Automation/Workflow Software</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
@@ -10568,11 +10560,11 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>SPPL</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -10585,21 +10577,21 @@
         </is>
       </c>
       <c r="I82" s="14" t="n">
-        <v>0.85</v>
+        <v>4.75</v>
       </c>
       <c r="J82" s="14" t="n">
-        <v>1.1</v>
+        <v>103.28</v>
       </c>
     </row>
     <row r="83" ht="14" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>V. Sardo</t>
+          <t>Paul Allen</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Currency Exchange International</t>
+          <t>Airship AI Holdings</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
@@ -10609,39 +10601,45 @@
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>CURN</t>
+          <t>AISP</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G83" s="13" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H83" s="13" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="I83" s="14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="J83" s="14" t="n">
-        <v>1.08</v>
+        <v>2.4</v>
+      </c>
+      <c r="I83" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J83" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="84" ht="14" customHeight="1">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>Haiyan Huang</t>
+          <t>Aris Kekedjian</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holdings</t>
+          <t>Stratasys (Printing Services (B2B</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
@@ -10656,7 +10654,7 @@
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>SSYS</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
@@ -10672,26 +10670,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I84" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J84" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I84" s="14" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J84" s="14" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="85" ht="14" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Poh Kiong Tan</t>
+          <t>V. Sardo</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holdings</t>
+          <t>Currency Exchange International</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
@@ -10701,42 +10695,34 @@
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>CURN</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G85" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H85" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I85" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J85" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G85" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H85" s="13" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I85" s="14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J85" s="14" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="86" ht="14" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Soon Huat Lim</t>
+          <t>Haiyan Huang</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
@@ -10786,12 +10772,12 @@
     <row r="87" ht="14" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>John Baker</t>
+          <t>Poh Kiong Tan</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>FRP Holdings</t>
+          <t>Trident Digital Tech Holdings</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
@@ -10806,34 +10792,42 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>FRPH</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G87" s="13" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="H87" s="13" t="n">
-        <v>4000.5</v>
-      </c>
-      <c r="I87" s="14" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="J87" s="14" t="n">
-        <v>0.96</v>
+        <v>5</v>
+      </c>
+      <c r="G87" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H87" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I87" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J87" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="88" ht="14" customHeight="1">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>Hock Goh</t>
+          <t>Soon Huat Lim</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>SKF</t>
+          <t>Trident Digital Tech Holdings</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
@@ -10848,34 +10842,42 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>SKF-B.ST</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G88" s="13" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H88" s="13" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="I88" s="14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J88" s="14" t="n">
-        <v>2.85</v>
+        <v>5</v>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J88" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="89" ht="14" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>R. Cox</t>
+          <t>John Baker</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Terex</t>
+          <t>FRP Holdings</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
@@ -10890,78 +10892,76 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>FRPH</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>20.2</v>
+        <v>40.6</v>
       </c>
       <c r="H89" s="13" t="n">
-        <v>29.5</v>
+        <v>4000.5</v>
       </c>
       <c r="I89" s="14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="J89" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J89" s="14" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="90" ht="14" customHeight="1">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>Viral Patel</t>
+          <t>Hock Goh</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>SKF</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>SKF-B.ST</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>18.6</v>
+        <v>11.7</v>
       </c>
       <c r="H90" s="13" t="n">
-        <v>26.6</v>
+        <v>27.4</v>
       </c>
       <c r="I90" s="14" t="n">
-        <v>10.41</v>
+        <v>2.14</v>
       </c>
       <c r="J90" s="14" t="n">
-        <v>11.43</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="91" ht="14" customHeight="1">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>Andrew Michelmore</t>
+          <t>R. Cox</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Century Aluminum</t>
+          <t>Terex</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
@@ -10976,34 +10976,36 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>CENX</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>5.6</v>
+        <v>20.2</v>
       </c>
       <c r="H91" s="13" t="n">
-        <v>6.4</v>
+        <v>29.5</v>
       </c>
       <c r="I91" s="14" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J91" s="14" t="n">
-        <v>2.74</v>
+        <v>1.36</v>
+      </c>
+      <c r="J91" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="92" ht="14" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>David Wright</t>
+          <t>Andrew Michelmore</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Rezolve Ai</t>
+          <t>Century Aluminum</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
@@ -11013,45 +11015,39 @@
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>RZLVW</t>
+          <t>CENX</t>
         </is>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G92" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H92" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.6</v>
+      </c>
+      <c r="G92" s="13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H92" s="13" t="n">
+        <v>6.4</v>
       </c>
       <c r="I92" s="14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="J92" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>2.74</v>
+      </c>
+      <c r="J92" s="14" t="n">
+        <v>2.74</v>
       </c>
     </row>
     <row r="93" ht="14" customHeight="1">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>Miliana Pineda</t>
+          <t>David Wright</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Dutch Bros</t>
+          <t>Rezolve Ai</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
@@ -11061,39 +11057,45 @@
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>RZLVW</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G93" s="13" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H93" s="13" t="n">
-        <v>53</v>
+        <v>4.2</v>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I93" s="14" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="J93" s="14" t="n">
-        <v>6.59</v>
+        <v>2.33</v>
+      </c>
+      <c r="J93" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="94" ht="14" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>John McPherson</t>
+          <t>Miliana Pineda</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Commercial Metals</t>
+          <t>Dutch Bros</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
@@ -11108,34 +11110,34 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="F94" s="12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>8.699999999999999</v>
+        <v>25.5</v>
       </c>
       <c r="H94" s="13" t="n">
-        <v>12.1</v>
+        <v>53</v>
       </c>
       <c r="I94" s="14" t="n">
-        <v>1.58</v>
+        <v>6.44</v>
       </c>
       <c r="J94" s="14" t="n">
-        <v>3.72</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="95" ht="14" customHeight="1">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>Douglas Rauch</t>
+          <t>Raffaele Zagari</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market</t>
+          <t>Star Bulk Carriers</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
@@ -11150,34 +11152,34 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>SFM</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="F95" s="12" t="n">
         <v>3.9</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="H95" s="13" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="I95" s="14" t="n">
-        <v>4.23</v>
+        <v>1.34</v>
       </c>
       <c r="J95" s="14" t="n">
-        <v>6.97</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="96" ht="14" customHeight="1">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>Anelise Lara</t>
+          <t>John McPherson</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Commercial Metals</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
@@ -11192,34 +11194,34 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="F96" s="12" t="n">
         <v>3.9</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>5.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H96" s="13" t="n">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="I96" s="14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="J96" s="14" t="n">
-        <v>2.16</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>Gregory Landis</t>
+          <t>Douglas Rauch</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>H2O America</t>
+          <t>Sprouts Farmers Market</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
@@ -11234,34 +11236,34 @@
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>HTO</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="F97" s="12" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H97" s="13" t="n">
-        <v>21.8</v>
+        <v>12.8</v>
       </c>
       <c r="I97" s="14" t="n">
-        <v>1.35</v>
+        <v>4.23</v>
       </c>
       <c r="J97" s="14" t="n">
-        <v>2.07</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="98" ht="14" customHeight="1">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>Michael Denham</t>
+          <t>Anelise Lara</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>National Bank of Canada (Montreall</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
@@ -11276,34 +11278,34 @@
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>NBHC</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="F98" s="12" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>11.1</v>
+        <v>5.1</v>
       </c>
       <c r="H98" s="13" t="n">
-        <v>15.7</v>
+        <v>11.3</v>
       </c>
       <c r="I98" s="14" t="n">
-        <v>0.92</v>
+        <v>1.57</v>
       </c>
       <c r="J98" s="14" t="n">
-        <v>1.34</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="99" ht="14" customHeight="1">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>Randall Weisenburger</t>
+          <t>Gregory Landis</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>MP Materials</t>
+          <t>H2O America</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
@@ -11318,36 +11320,34 @@
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>HTO</t>
         </is>
       </c>
       <c r="F99" s="12" t="n">
         <v>3.4</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>150.4</v>
-      </c>
-      <c r="H99" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H99" s="13" t="n">
+        <v>21.8</v>
       </c>
       <c r="I99" s="14" t="n">
-        <v>4.46</v>
+        <v>1.35</v>
       </c>
       <c r="J99" s="14" t="n">
-        <v>4.46</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="100" ht="14" customHeight="1">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>Michael Dougherty</t>
+          <t>Michael Denham</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>Polaris (Automotive</t>
+          <t>National Bank of Canada (Montreall</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
@@ -11362,36 +11362,34 @@
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>PII</t>
+          <t>NBHC</t>
         </is>
       </c>
       <c r="F100" s="12" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="H100" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>11.1</v>
+      </c>
+      <c r="H100" s="13" t="n">
+        <v>15.7</v>
       </c>
       <c r="I100" s="14" t="n">
-        <v>3.62</v>
+        <v>0.92</v>
       </c>
       <c r="J100" s="14" t="n">
-        <v>59.92</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="101" ht="14" customHeight="1">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>Raffaele Zagari</t>
+          <t>Randall Weisenburger</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>Star Bulk Carriers</t>
+          <t>MP Materials</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
@@ -11406,34 +11404,36 @@
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="F101" s="12" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="H101" s="13" t="n">
-        <v>11.8</v>
+        <v>150.4</v>
+      </c>
+      <c r="H101" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I101" s="14" t="n">
-        <v>1.34</v>
+        <v>4.46</v>
       </c>
       <c r="J101" s="14" t="n">
-        <v>1.34</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="102" ht="14" customHeight="1">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>Len Blavatnik</t>
+          <t>Ghislane Bennouna</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>Warner Music Group</t>
+          <t>Aya Gold &amp; Silver</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
@@ -11443,41 +11443,39 @@
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>AYA</t>
         </is>
       </c>
       <c r="F102" s="12" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>12.1</v>
+        <v>18.9</v>
       </c>
       <c r="H102" s="13" t="n">
-        <v>21.2</v>
+        <v>35.9</v>
       </c>
       <c r="I102" s="14" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="J102" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>8.23</v>
+      </c>
+      <c r="J102" s="14" t="n">
+        <v>8.23</v>
       </c>
     </row>
     <row r="103" ht="14" customHeight="1">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>Ghislane Bennouna</t>
+          <t>Len Blavatnik</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>Aya Gold &amp; Silver</t>
+          <t>Warner Music Group</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
@@ -11487,28 +11485,30 @@
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>AYA</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="F103" s="12" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>18.9</v>
+        <v>12.1</v>
       </c>
       <c r="H103" s="13" t="n">
-        <v>35.9</v>
+        <v>21.2</v>
       </c>
       <c r="I103" s="14" t="n">
-        <v>8.23</v>
-      </c>
-      <c r="J103" s="14" t="n">
-        <v>8.23</v>
+        <v>16.7</v>
+      </c>
+      <c r="J103" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="104" ht="14" customHeight="1">

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -1254,12 +1254,12 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M8" s="14" t="n">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M12" s="14" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M14" s="14" t="n">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M17" s="14" t="n">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M20" s="14" t="n">
@@ -2036,12 +2036,12 @@
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M21" s="14" t="n">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SPAC</t>
         </is>
       </c>
       <c r="L25" s="13" t="n">
@@ -2281,8 +2281,10 @@
       <c r="M25" s="14" t="n">
         <v>1.06</v>
       </c>
-      <c r="N25" s="14" t="n">
-        <v>1.06</v>
+      <c r="N25" s="12" t="inlineStr">
+        <is>
+          <t>SPAC</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
@@ -2335,7 +2337,7 @@
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M26" s="14" t="n">
@@ -2398,12 +2400,12 @@
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
       <c r="N27" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2517,7 @@
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M29" s="14" t="n">
@@ -2634,12 +2636,12 @@
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M31" s="14" t="n">
@@ -3392,12 +3394,12 @@
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M44" s="14" t="n">
@@ -3454,12 +3456,12 @@
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M45" s="14" t="n">
@@ -3577,17 +3579,17 @@
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M47" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
       <c r="N47" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3814,7 @@
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="L51" s="13" t="n">
@@ -3877,7 +3879,7 @@
       </c>
       <c r="L52" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M52" s="14" t="n">
@@ -3934,12 +3936,12 @@
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="L53" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M53" s="14" t="n">
@@ -3996,12 +3998,12 @@
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="L54" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M54" s="14" t="n">
@@ -4116,7 +4118,7 @@
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>net cash</t>
         </is>
       </c>
       <c r="L56" s="13" t="n">
@@ -4176,7 +4178,7 @@
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>net cash</t>
         </is>
       </c>
       <c r="L57" s="13" t="n">
@@ -4354,12 +4356,12 @@
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="L60" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M60" s="14" t="n">
@@ -4419,12 +4421,12 @@
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M61" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
       <c r="N61" s="12" t="inlineStr">
@@ -4543,7 +4545,7 @@
       </c>
       <c r="L63" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M63" s="14" t="n">
@@ -4600,12 +4602,12 @@
       </c>
       <c r="K64" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="L64" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M64" s="14" t="n">
@@ -4723,7 +4725,7 @@
       </c>
       <c r="L66" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M66" s="14" t="n">
@@ -5128,22 +5130,22 @@
       </c>
       <c r="K73" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
       <c r="N73" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5631,7 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="I7" s="13" t="n">
@@ -5725,12 +5727,12 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="J9" s="14" t="n">
@@ -7122,12 +7124,12 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I6" s="14" t="n">
@@ -7299,17 +7301,17 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7391,7 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I12" s="14" t="n">
@@ -8106,12 +8108,12 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I29" s="14" t="n">
@@ -8157,7 +8159,7 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I30" s="14" t="n">
@@ -8240,12 +8242,12 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I32" s="14" t="n">
@@ -8289,7 +8291,7 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I33" s="14" t="n">
@@ -8330,12 +8332,12 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I34" s="14" t="n">
@@ -8460,12 +8462,12 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I37" s="14" t="n">
@@ -8509,7 +8511,7 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I38" s="14" t="n">
@@ -8553,7 +8555,7 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I39" s="14" t="n">
@@ -8594,12 +8596,12 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I40" s="14" t="n">
@@ -8766,7 +8768,7 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>net cash</t>
         </is>
       </c>
       <c r="H44" s="13" t="n">
@@ -8810,7 +8812,7 @@
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>net cash</t>
         </is>
       </c>
       <c r="H45" s="13" t="n">
@@ -9027,7 +9029,7 @@
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I50" s="14" t="n">
@@ -9070,12 +9072,12 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I51" s="14" t="n">
@@ -9119,7 +9121,7 @@
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I52" s="14" t="n">
@@ -9202,20 +9204,22 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>delisted</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I54" s="14" t="n">
-        <v>2.02</v>
+          <t>delisted</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>delisted</t>
+        </is>
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>delisted</t>
         </is>
       </c>
     </row>
@@ -9253,7 +9257,7 @@
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I55" s="14" t="n">
@@ -9342,12 +9346,12 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9554,12 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I62" s="14" t="n">
@@ -9599,12 +9603,12 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
       <c r="J63" s="12" t="inlineStr">
@@ -9647,7 +9651,7 @@
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I64" s="14" t="n">
@@ -9693,7 +9697,7 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I65" s="14" t="n">
@@ -9736,12 +9740,12 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I66" s="14" t="n">
@@ -9868,20 +9872,24 @@
       <c r="F69" s="12" t="n">
         <v>7.2</v>
       </c>
-      <c r="G69" s="13" t="n">
-        <v>52</v>
-      </c>
-      <c r="H69" s="13" t="n">
-        <v>20.7</v>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H69" s="12" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="J69" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>unit</t>
         </is>
       </c>
     </row>
@@ -9916,12 +9924,12 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="H70" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I70" s="14" t="n">
@@ -10009,7 +10017,7 @@
       </c>
       <c r="H72" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I72" s="14" t="n">
@@ -10053,7 +10061,7 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I73" s="14" t="n">
@@ -10143,7 +10151,7 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I75" s="14" t="n">
@@ -10226,12 +10234,12 @@
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I77" s="14" t="n">
@@ -10316,12 +10324,12 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I79" s="14" t="n">
@@ -10362,7 +10370,7 @@
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SPAC</t>
         </is>
       </c>
       <c r="H80" s="13" t="n">
@@ -10371,8 +10379,10 @@
       <c r="I80" s="14" t="n">
         <v>1.06</v>
       </c>
-      <c r="J80" s="14" t="n">
-        <v>1.06</v>
+      <c r="J80" s="12" t="inlineStr">
+        <is>
+          <t>SPAC</t>
+        </is>
       </c>
     </row>
     <row r="81" ht="14" customHeight="1">
@@ -10532,17 +10542,25 @@
       <c r="F84" s="12" t="n">
         <v>5.5</v>
       </c>
-      <c r="G84" s="13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H84" s="13" t="n">
-        <v>251.9</v>
-      </c>
-      <c r="I84" s="14" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="J84" s="14" t="n">
-        <v>9.52</v>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
+      </c>
+      <c r="H84" s="12" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
+      </c>
+      <c r="I84" s="12" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
+      </c>
+      <c r="J84" s="12" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
       </c>
     </row>
     <row r="85" ht="14" customHeight="1">
@@ -10576,12 +10594,12 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg EBITDA</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I85" s="14" t="n">
@@ -10622,7 +10640,7 @@
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>net cash</t>
         </is>
       </c>
       <c r="H86" s="13" t="n">
@@ -10630,12 +10648,12 @@
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
       <c r="J86" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10861,7 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="I91" s="14" t="n">
@@ -10884,20 +10902,22 @@
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>warrant</t>
         </is>
       </c>
       <c r="H92" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I92" s="14" t="n">
-        <v>2.33</v>
+          <t>warrant</t>
+        </is>
+      </c>
+      <c r="I92" s="12" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
       </c>
       <c r="J92" s="12" t="inlineStr">
         <is>
-          <t>neg TBV</t>
+          <t>warrant</t>
         </is>
       </c>
     </row>

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'README'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Board Signal — In Universe'!$A$4:$N$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Board Signal — In Universe'!$A$4:$N$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Board Signal — In Universe'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Investor Board Seats'!$A$4:$K$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Investor Board Seats'!$1:$4</definedName>
@@ -629,7 +629,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>73 land on companies inside our tradeable universe and carry a live smart-money score.</t>
+          <t>72 land on companies inside our tradeable universe and carry a live smart-money score.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>22.4</v>
+        <v>21.9</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>7.3</v>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>22.2</v>
+        <v>20.4</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>7.6</v>
@@ -1210,7 +1210,7 @@
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>BLSH</t>
+          <t>ADDYY</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -1220,14 +1220,14 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>adidas AG</t>
         </is>
       </c>
       <c r="D8" s="11" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>1</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>Alan Howard</t>
+          <t>Nassef Sawiris</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -1249,30 +1249,26 @@
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>18.6</v>
       </c>
       <c r="M8" s="14" t="n">
-        <v>2.5</v>
+        <v>4.59</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>2.6</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>ADDYY</t>
+          <t>ABBN.SW</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -1282,14 +1278,14 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>adidas AG</t>
+          <t>ABB Ltd</t>
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>1</v>
@@ -1301,7 +1297,7 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Nassef Sawiris</t>
+          <t>Jacob Wallenberg</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -1311,26 +1307,26 @@
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>9</v>
+        <v>24.2</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>18.6</v>
+        <v>36.3</v>
       </c>
       <c r="M9" s="14" t="n">
-        <v>4.59</v>
+        <v>11.46</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>6.21</v>
+        <v>33.03</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>ABBN.SW</t>
+          <t>BLSH</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -1340,14 +1336,14 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>ABB Ltd</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>0</v>
+        <v>-4.5</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>1</v>
@@ -1359,7 +1355,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Jacob Wallenberg</t>
+          <t>Alan Howard</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -1369,20 +1365,24 @@
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>36.3</v>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="M10" s="14" t="n">
-        <v>11.46</v>
+        <v>2.5</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>33.03</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>8.199999999999999</v>
@@ -1510,7 +1510,7 @@
     <row r="13" ht="14" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -1520,26 +1520,26 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Monro, Inc.</t>
+          <t>Star Bulk Carriers Corp.</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>25.6</v>
+        <v>30.6</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>2012</t>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Hope Woodhouse</t>
+          <t>Raffaele Zagari</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
@@ -1549,28 +1549,26 @@
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>12.6</v>
+        <v>7.9</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>56.3</v>
+        <v>11.8</v>
       </c>
       <c r="M13" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N13" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>1.34</v>
+      </c>
+      <c r="N13" s="14" t="n">
+        <v>1.34</v>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -1580,26 +1578,26 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>QXO, Inc.</t>
+          <t>Monro, Inc.</t>
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>22.9</v>
+        <v>25.6</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>11.4</v>
+        <v>3</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>2012</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Mary Kissel</t>
+          <t>Hope Woodhouse</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
@@ -1609,19 +1607,17 @@
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="L14" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>12.6</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>56.3</v>
       </c>
       <c r="M14" s="14" t="n">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="N14" s="12" t="inlineStr">
         <is>
@@ -1632,7 +1628,7 @@
     <row r="15" ht="14" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>INVA</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1642,14 +1638,14 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Innoviva, Inc.</t>
+          <t>QXO, Inc.</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>2.6</v>
+        <v>11.4</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>1</v>
@@ -1661,7 +1657,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Mark DiPaolo</t>
+          <t>Mary Kissel</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -1671,26 +1667,30 @@
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L15" s="13" t="n">
-        <v>4.3</v>
+        <v>44.3</v>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="M15" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="N15" s="14" t="n">
-        <v>1.48</v>
+        <v>0.93</v>
+      </c>
+      <c r="N15" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1700,14 +1700,14 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Charter Communications, Inc.</t>
+          <t>Innoviva, Inc.</t>
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>21.8</v>
+        <v>22.5</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>1</v>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>W. Conn</t>
+          <t>Mark DiPaolo</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -1729,28 +1729,26 @@
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="K16" s="13" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="M16" s="14" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="N16" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>1.25</v>
+      </c>
+      <c r="N16" s="14" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>SANA</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1760,14 +1758,14 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Sana Biotechnology, Inc.</t>
+          <t>Charter Communications, Inc.</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>17.1</v>
+        <v>21.8</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>1</v>
@@ -1779,7 +1777,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Richard Mulligan</t>
+          <t>W. Conn</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -1789,21 +1787,17 @@
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>6.05</v>
+        <v>0.83</v>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
@@ -1814,7 +1808,7 @@
     <row r="18" ht="14" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>TOL</t>
+          <t>SANA</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -1824,14 +1818,14 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Toll Brothers, Inc.</t>
+          <t>Sana Biotechnology, Inc.</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>16.2</v>
+        <v>17.1</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>1</v>
@@ -1843,7 +1837,7 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Derek Kan</t>
+          <t>Richard Mulligan</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -1853,26 +1847,32 @@
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="K18" s="13" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L18" s="13" t="n">
-        <v>10.9</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="M18" s="14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="N18" s="14" t="n">
-        <v>1.52</v>
+        <v>6.05</v>
+      </c>
+      <c r="N18" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>TOL</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -1882,14 +1882,14 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>IAMGOLD Corporation</t>
+          <t>Toll Brothers, Inc.</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>14.1</v>
+        <v>16.2</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>1</v>
@@ -1901,36 +1901,36 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Joseph Flaim</t>
+          <t>Derek Kan</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="K19" s="13" t="n">
-        <v>5.3</v>
+        <v>8.9</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>9.9</v>
+        <v>10.9</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>2.61</v>
+        <v>1.52</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>2.61</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>UAA</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -1940,14 +1940,14 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Under Armour, Inc.</t>
+          <t>IAMGOLD Corporation</t>
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>1</v>
@@ -1959,40 +1959,36 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Dawn Fitzpatrick</t>
+          <t>Joseph Flaim</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="K20" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="L20" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>9.9</v>
       </c>
       <c r="M20" s="14" t="n">
-        <v>1.36</v>
+        <v>2.61</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>COYA</t>
+          <t>UAA</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -2002,14 +1998,14 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Coya Therapeutics, Inc.</t>
+          <t>Under Armour, Inc.</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>12.7</v>
+        <v>13.9</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>1</v>
@@ -2021,7 +2017,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Wilbur Ross</t>
+          <t>Dawn Fitzpatrick</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
@@ -2031,7 +2027,7 @@
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
@@ -2045,16 +2041,16 @@
         </is>
       </c>
       <c r="M21" s="14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>COYA</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -2064,14 +2060,14 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Coya Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>12.2</v>
+        <v>12.7</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>7.7</v>
+        <v>1.1</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>1</v>
@@ -2083,30 +2079,34 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Sharmila Mulligan</t>
+          <t>Wilbur Ross</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Managers</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L22" s="13" t="n">
-        <v>16.9</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="M22" s="14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="D24" s="11" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="E24" s="11" t="n">
         <v>2.2</v>
@@ -2290,7 +2290,7 @@
     <row r="26" ht="14" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>WEST</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -2300,14 +2300,14 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Westrock Coffee Company</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="D26" s="11" t="n">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.4</v>
+        <v>7.7</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>1</v>
@@ -2319,38 +2319,36 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Jeffrey Fox</t>
+          <t>Sharmila Mulligan</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Titans &amp; Concentrated Managers</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K26" s="13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="L26" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>6.2</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>16.9</v>
       </c>
       <c r="M26" s="14" t="n">
-        <v>3.24</v>
+        <v>2.38</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>34.55</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>WEST</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -2360,14 +2358,14 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Agenus Inc.</t>
+          <t>Westrock Coffee Company</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>1</v>
@@ -2379,7 +2377,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Brian Corvese</t>
+          <t>Jeffrey Fox</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
@@ -2389,30 +2387,28 @@
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="K27" s="13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L27" s="13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M27" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
-      </c>
-      <c r="N27" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
+        <v>24.2</v>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N27" s="14" t="n">
+        <v>34.55</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>AGEN</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -2422,14 +2418,14 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Lands' End, Inc.</t>
+          <t>Agenus Inc.</t>
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>1</v>
@@ -2441,36 +2437,40 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Josephine Linden</t>
+          <t>Brian Corvese</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="K28" s="13" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M28" s="14" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="N28" s="14" t="n">
-        <v>0.63</v>
+        <v>3.1</v>
+      </c>
+      <c r="M28" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+      <c r="N28" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>XRXDW</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -2480,14 +2480,14 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Xerox Holdings Corporation</t>
+          <t>Lands' End, Inc.</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>1</v>
@@ -2499,34 +2499,30 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Jonathan Christodoro</t>
+          <t>Josephine Linden</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
-        </is>
-      </c>
-      <c r="J29" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Gulf/Royal Family Offices</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="K29" s="13" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="L29" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>0.7</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>0.9</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="N29" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>0.63</v>
+      </c>
+      <c r="N29" s="14" t="n">
+        <v>0.63</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
@@ -2828,7 +2824,7 @@
     <row r="35" ht="14" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>AYA</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -2838,55 +2834,55 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Star Bulk Carriers Corp.</t>
+          <t>Aya Gold &amp; Silver Inc.</t>
         </is>
       </c>
       <c r="D35" s="11" t="n">
         <v>3.3</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="F35" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>2021</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Raffaele Zagari</t>
+          <t>Ghislane Bennouna</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
-        </is>
-      </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>Gulf/Royal Family Offices</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K35" s="13" t="n">
-        <v>7.9</v>
+        <v>18.9</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>11.8</v>
+        <v>35.9</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>1.34</v>
+        <v>8.23</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>1.34</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>AYA</t>
+          <t>0086.HK</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -2896,26 +2892,26 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Aya Gold &amp; Silver Inc.</t>
+          <t>Sun Hung Kai &amp; Co. Limited</t>
         </is>
       </c>
       <c r="D36" s="11" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>Ghislane Bennouna</t>
+          <t>Jacqueline Leung</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -2923,28 +2919,28 @@
           <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
-      <c r="J36" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="K36" s="13" t="n">
-        <v>18.9</v>
+        <v>5.5</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>35.9</v>
+        <v>5.6</v>
       </c>
       <c r="M36" s="14" t="n">
-        <v>8.23</v>
+        <v>0.34</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>8.23</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="37" ht="14" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>0086.HK</t>
+          <t>EVR</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -2954,26 +2950,26 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Sun Hung Kai &amp; Co. Limited</t>
+          <t>Evercore Inc.</t>
         </is>
       </c>
       <c r="D37" s="11" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>2010</t>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>Jacqueline Leung</t>
+          <t>Jonathan Knee</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
@@ -2987,22 +2983,22 @@
         </is>
       </c>
       <c r="K37" s="13" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>5.6</v>
+        <v>13.7</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>0.34</v>
+        <v>5.45</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>0.39</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>EVR</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -3012,14 +3008,14 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Evercore Inc.</t>
+          <t>Telefônica Brasil S.A.</t>
         </is>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>1</v>
@@ -3031,36 +3027,36 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>Jonathan Knee</t>
+          <t>Peter Loscher</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K38" s="13" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>13.7</v>
+        <v>14.7</v>
       </c>
       <c r="M38" s="14" t="n">
-        <v>5.45</v>
+        <v>1.49</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>6.16</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -3070,14 +3066,14 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Telefônica Brasil S.A.</t>
+          <t>Kenon Holdings Ltd.</t>
         </is>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F39" s="12" t="n">
         <v>1</v>
@@ -3089,7 +3085,7 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Peter Loscher</t>
+          <t>Aviad Kaufman</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
@@ -3099,26 +3095,26 @@
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K39" s="13" t="n">
-        <v>4.3</v>
+        <v>12.8</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>14.7</v>
+        <v>29.5</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>1.49</v>
+        <v>2.22</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>5.31</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>0001.HK</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -3128,14 +3124,14 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Kenon Holdings Ltd.</t>
+          <t>CK Hutchison Holdings Limited</t>
         </is>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
         <v>1</v>
@@ -3147,36 +3143,36 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>Aviad Kaufman</t>
+          <t>Kwai Wong</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K40" s="13" t="n">
-        <v>12.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>29.5</v>
+        <v>6.8</v>
       </c>
       <c r="M40" s="14" t="n">
-        <v>2.22</v>
+        <v>0.45</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>0001.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -3186,7 +3182,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>CK Hutchison Holdings Limited</t>
+          <t>Tencent Holdings Limited</t>
         </is>
       </c>
       <c r="D41" s="11" t="n">
@@ -3205,36 +3201,36 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>Kwai Wong</t>
+          <t>Charles Searle</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K41" s="13" t="n">
-        <v>8.300000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>6.8</v>
+        <v>14.6</v>
       </c>
       <c r="M41" s="14" t="n">
-        <v>0.45</v>
+        <v>3</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>1.01</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>360ONE.NS</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -3244,7 +3240,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Tencent Holdings Limited</t>
+          <t>360 One Wam Limited</t>
         </is>
       </c>
       <c r="D42" s="11" t="n">
@@ -3263,36 +3259,36 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>Charles Searle</t>
+          <t>Akhil Gupta</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Sequoia Network,Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="K42" s="13" t="n">
-        <v>10.8</v>
+        <v>18.5</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>14.6</v>
+        <v>35.6</v>
       </c>
       <c r="M42" s="14" t="n">
-        <v>3</v>
+        <v>4.58</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>3.69</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>360ONE.NS</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
@@ -3302,14 +3298,14 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>360 One Wam Limited</t>
+          <t>Oklo Inc.</t>
         </is>
       </c>
       <c r="D43" s="11" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>1</v>
@@ -3321,53 +3317,57 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>Akhil Gupta</t>
+          <t>Samuel Altman</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network,Gulf/Royal Family Offices</t>
+          <t>Titans &amp; Concentrated Managers</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="L43" s="13" t="n">
-        <v>35.6</v>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="K43" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="M43" s="14" t="n">
-        <v>4.58</v>
+        <v>2.11</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>4.58</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Oklo Inc.</t>
+          <t>Republic Services, Inc.</t>
         </is>
       </c>
       <c r="D44" s="11" t="n">
-        <v>-1.1</v>
+        <v>61.2</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="F44" s="12" t="n">
         <v>1</v>
@@ -3379,40 +3379,38 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>Samuel Altman</t>
+          <t>Katharine Weymouth</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Managers</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L44" s="13" t="n">
+        <v>30.5</v>
       </c>
       <c r="M44" s="14" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="N44" s="14" t="n">
-        <v>2.17</v>
+        <v>5.5</v>
+      </c>
+      <c r="N44" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>VEON</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -3422,59 +3420,55 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Xometry, Inc.</t>
+          <t>VEON Ltd.</t>
         </is>
       </c>
       <c r="D45" s="11" t="n">
-        <v>27.4</v>
+        <v>25.9</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>2</v>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>2023</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>Katharine Weymouth</t>
+          <t>Brandon Lewis,Duncan Perry</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>102.7</v>
       </c>
       <c r="M45" s="14" t="n">
-        <v>9.34</v>
+        <v>3.22</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>18.22</v>
+        <v>167.02</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>VEON</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -3484,49 +3478,53 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>VEON Ltd.</t>
+          <t>Xometry, Inc.</t>
         </is>
       </c>
       <c r="D46" s="11" t="n">
-        <v>24.9</v>
+        <v>25.3</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>2023</t>
+        <v>1</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>Brandon Lewis,Duncan Perry</t>
+          <t>Katharine Weymouth</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="K46" s="13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L46" s="13" t="n">
-        <v>102.7</v>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="K46" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="L46" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="M46" s="14" t="n">
-        <v>3.22</v>
+        <v>9.34</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>167.02</v>
+        <v>18.22</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
@@ -3596,7 +3594,7 @@
     <row r="48" ht="14" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>UPWK</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -3606,17 +3604,17 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Upwork Inc.</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="D48" s="11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>3.6</v>
+        <v>13.2</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -3625,36 +3623,36 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>Glenn Kelman</t>
+          <t>Cynthia Hostetler,George Willis,Thomas Fanning</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="K48" s="13" t="n">
-        <v>5.4</v>
+        <v>14.3</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>10.3</v>
+        <v>28.9</v>
       </c>
       <c r="M48" s="14" t="n">
-        <v>1.67</v>
+        <v>3.77</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>2.36</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>UPWK</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -3664,17 +3662,17 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>Upwork Inc.</t>
         </is>
       </c>
       <c r="D49" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>13.2</v>
+        <v>3.6</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -3683,36 +3681,36 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>Cynthia Hostetler,George Willis,Thomas Fanning</t>
+          <t>Glenn Kelman</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K49" s="13" t="n">
-        <v>14.3</v>
+        <v>5.4</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>28.9</v>
+        <v>10.3</v>
       </c>
       <c r="M49" s="14" t="n">
-        <v>3.77</v>
+        <v>1.67</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>9.800000000000001</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>DRIO</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -3722,55 +3720,59 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>SLB N.V.</t>
+          <t>DarioHealth Corp.</t>
         </is>
       </c>
       <c r="D50" s="11" t="n">
-        <v>18.3</v>
+        <v>17.1</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>10.1</v>
+        <v>0.6</v>
       </c>
       <c r="F50" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="10" t="inlineStr">
-        <is>
-          <t>2011</t>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>Yoav Shaked</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J50" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="n">
-        <v>12.2</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="K50" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
       </c>
       <c r="L50" s="13" t="n">
-        <v>25.1</v>
+        <v>9.9</v>
       </c>
       <c r="M50" s="14" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="N50" s="14" t="n">
-        <v>15.23</v>
+        <v>1.16</v>
+      </c>
+      <c r="N50" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>DRIO</t>
+          <t>BZH</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -3780,14 +3782,14 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>DarioHealth Corp.</t>
+          <t>Beazer Homes USA, Inc.</t>
         </is>
       </c>
       <c r="D51" s="11" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="F51" s="12" t="n">
         <v>1</v>
@@ -3799,40 +3801,38 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Yoav Shaked</t>
+          <t>Danny Shepherd</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="L51" s="13" t="n">
-        <v>9.9</v>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="n">
+        <v>39</v>
+      </c>
+      <c r="L51" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="M51" s="14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N51" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>0.77</v>
+      </c>
+      <c r="N51" s="14" t="n">
+        <v>0.78</v>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>BZH</t>
+          <t>CMPS</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -3842,14 +3842,14 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Beazer Homes USA, Inc.</t>
+          <t>COMPASS Pathways plc</t>
         </is>
       </c>
       <c r="D52" s="11" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="F52" s="12" t="n">
         <v>1</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>Danny Shepherd</t>
+          <t>Annalisa Jenkins</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -3871,11 +3871,13 @@
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="n">
-        <v>39</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
       </c>
       <c r="L52" s="12" t="inlineStr">
         <is>
@@ -3883,16 +3885,16 @@
         </is>
       </c>
       <c r="M52" s="14" t="n">
-        <v>0.77</v>
+        <v>15.93</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>0.78</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>ALLO</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -3902,26 +3904,26 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>COMPASS Pathways plc</t>
+          <t>Allogene Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="D53" s="11" t="n">
-        <v>16.2</v>
+        <v>15.7</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="F53" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>2012</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>Annalisa Jenkins</t>
+          <t>Franz Humer</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -3945,16 +3947,16 @@
         </is>
       </c>
       <c r="M53" s="14" t="n">
-        <v>15.93</v>
+        <v>1.28</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>15.93</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>ALLO</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -3964,26 +3966,26 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Allogene Therapeutics, Inc.</t>
+          <t>Everest Group, Ltd.</t>
         </is>
       </c>
       <c r="D54" s="11" t="n">
-        <v>15.7</v>
+        <v>15.2</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="F54" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="10" t="inlineStr">
-        <is>
-          <t>2012</t>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>Franz Humer</t>
+          <t>Meryl Hartzband</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -3993,30 +3995,26 @@
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="K54" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="L54" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L54" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="M54" s="14" t="n">
-        <v>1.28</v>
+        <v>0.98</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -4026,26 +4024,26 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Everest Group, Ltd.</t>
+          <t>SLB N.V.</t>
         </is>
       </c>
       <c r="D55" s="11" t="n">
-        <v>15.2</v>
+        <v>13.4</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>3.4</v>
+        <v>10.1</v>
       </c>
       <c r="F55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>2011</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>Meryl Hartzband</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -4055,20 +4053,20 @@
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K55" s="13" t="n">
-        <v>6.5</v>
+        <v>12.2</v>
       </c>
       <c r="L55" s="13" t="n">
-        <v>8</v>
+        <v>25.1</v>
       </c>
       <c r="M55" s="14" t="n">
-        <v>0.98</v>
+        <v>3.01</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>1.08</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
@@ -4088,10 +4086,10 @@
         </is>
       </c>
       <c r="D56" s="11" t="n">
-        <v>11.2</v>
+        <v>10.7</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="F56" s="12" t="n">
         <v>1</v>
@@ -4148,7 +4146,7 @@
         </is>
       </c>
       <c r="D57" s="11" t="n">
-        <v>11.1</v>
+        <v>10.2</v>
       </c>
       <c r="E57" s="11" t="n">
         <v>1.2</v>
@@ -4208,7 +4206,7 @@
         </is>
       </c>
       <c r="D58" s="11" t="n">
-        <v>10.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E58" s="11" t="n">
         <v>2.7</v>
@@ -4268,7 +4266,7 @@
         </is>
       </c>
       <c r="D59" s="11" t="n">
-        <v>9.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="E59" s="11" t="n">
         <v>7.3</v>
@@ -4326,7 +4324,7 @@
         </is>
       </c>
       <c r="D60" s="11" t="n">
-        <v>8.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="E60" s="11" t="n">
         <v>2.8</v>
@@ -4374,7 +4372,7 @@
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>REI</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -4384,14 +4382,14 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Porch Group, Inc.</t>
+          <t>Ring Energy, Inc.</t>
         </is>
       </c>
       <c r="D61" s="11" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F61" s="12" t="n">
         <v>1</v>
@@ -4403,42 +4401,38 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>Amanda Reierson</t>
+          <t>David Habachy</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K61" s="13" t="n">
-        <v>23.1</v>
+        <v>3.8</v>
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="M61" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
-      </c>
-      <c r="N61" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+      <c r="M61" s="14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N61" s="14" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>ADAG</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -4448,14 +4442,14 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Republic Services, Inc.</t>
+          <t>Adagene Inc.</t>
         </is>
       </c>
       <c r="D62" s="11" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="F62" s="12" t="n">
         <v>1</v>
@@ -4467,7 +4461,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Katharine Weymouth</t>
+          <t>Li Li</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -4477,28 +4471,30 @@
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>30.5</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="K62" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="L62" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="M62" s="14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N62" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>1.32</v>
+      </c>
+      <c r="N62" s="14" t="n">
+        <v>1.32</v>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>REI</t>
+          <t>FRPH</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -4508,14 +4504,14 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Ring Energy, Inc.</t>
+          <t>FRP Holdings, Inc.</t>
         </is>
       </c>
       <c r="D63" s="11" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F63" s="12" t="n">
         <v>1</v>
@@ -4527,7 +4523,7 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>David Habachy</t>
+          <t>John Baker</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
@@ -4537,28 +4533,26 @@
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K63" s="13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L63" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>40.6</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>4000.5</v>
       </c>
       <c r="M63" s="14" t="n">
-        <v>0.42</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>0.42</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>ADAG</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -4568,14 +4562,14 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Adagene Inc.</t>
+          <t>Porch Group, Inc.</t>
         </is>
       </c>
       <c r="D64" s="11" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="F64" s="12" t="n">
         <v>1</v>
@@ -4587,7 +4581,7 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>Li Li</t>
+          <t>Amanda Reierson</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
@@ -4597,30 +4591,32 @@
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="K64" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>23.1</v>
       </c>
       <c r="L64" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="M64" s="14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="N64" s="14" t="n">
-        <v>1.32</v>
+      <c r="M64" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+      <c r="N64" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>FRPH</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -4630,14 +4626,14 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>FRP Holdings, Inc.</t>
+          <t>MP Materials Corp.</t>
         </is>
       </c>
       <c r="D65" s="11" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="F65" s="12" t="n">
         <v>1</v>
@@ -4649,7 +4645,7 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>John Baker</t>
+          <t>Randall Weisenburger</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
@@ -4659,26 +4655,28 @@
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="K65" s="13" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="L65" s="13" t="n">
-        <v>4000.5</v>
+        <v>150.4</v>
+      </c>
+      <c r="L65" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="M65" s="14" t="n">
-        <v>0.9399999999999999</v>
+        <v>4.46</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>0.96</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>BSRR</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -4688,14 +4686,14 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>MP Materials Corp.</t>
+          <t>Sierra Bancorp</t>
         </is>
       </c>
       <c r="D66" s="11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>3.9</v>
+        <v>0.2</v>
       </c>
       <c r="F66" s="12" t="n">
         <v>1</v>
@@ -4707,38 +4705,36 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>Randall Weisenburger</t>
+          <t>Laurence Dutto</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="K66" s="13" t="n">
-        <v>150.4</v>
-      </c>
-      <c r="L66" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>9.4</v>
+      </c>
+      <c r="L66" s="13" t="n">
+        <v>11.6</v>
       </c>
       <c r="M66" s="14" t="n">
-        <v>4.46</v>
+        <v>1.41</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>4.46</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>BSRR</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -4748,14 +4744,14 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Sierra Bancorp</t>
+          <t>Dutch Bros Inc.</t>
         </is>
       </c>
       <c r="D67" s="11" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2</v>
+        <v>4.1</v>
       </c>
       <c r="F67" s="12" t="n">
         <v>1</v>
@@ -4767,36 +4763,36 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>Laurence Dutto</t>
+          <t>Miliana Pineda</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="K67" s="13" t="n">
-        <v>9.4</v>
+        <v>25.5</v>
       </c>
       <c r="L67" s="13" t="n">
-        <v>11.6</v>
+        <v>53</v>
       </c>
       <c r="M67" s="14" t="n">
-        <v>1.41</v>
+        <v>6.44</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>1.52</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -4806,14 +4802,14 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc.</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="D68" s="11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="F68" s="12" t="n">
         <v>1</v>
@@ -4825,7 +4821,7 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>Miliana Pineda</t>
+          <t>Anelise Lara</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
@@ -4835,26 +4831,26 @@
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K68" s="13" t="n">
-        <v>25.5</v>
+        <v>5.1</v>
       </c>
       <c r="L68" s="13" t="n">
-        <v>53</v>
+        <v>11.3</v>
       </c>
       <c r="M68" s="14" t="n">
-        <v>6.44</v>
+        <v>1.57</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>6.59</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>SFM</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -4864,26 +4860,26 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market, Inc.</t>
+          <t>Commercial Metals Company</t>
         </is>
       </c>
       <c r="D69" s="11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="F69" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G69" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>2014</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>Douglas Rauch</t>
+          <t>John McPherson</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
@@ -4893,26 +4889,26 @@
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K69" s="13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L69" s="13" t="n">
-        <v>12.8</v>
+        <v>12.1</v>
       </c>
       <c r="M69" s="14" t="n">
-        <v>4.23</v>
+        <v>1.58</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>6.97</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>HTO</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -4922,14 +4918,14 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>H2O America</t>
         </is>
       </c>
       <c r="D70" s="11" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="F70" s="12" t="n">
         <v>1</v>
@@ -4941,7 +4937,7 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>Anelise Lara</t>
+          <t>Gregory Landis</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -4951,26 +4947,26 @@
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K70" s="13" t="n">
-        <v>5.1</v>
+        <v>14</v>
       </c>
       <c r="L70" s="13" t="n">
-        <v>11.3</v>
+        <v>21.8</v>
       </c>
       <c r="M70" s="14" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -4980,55 +4976,63 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Commercial Metals Company</t>
+          <t>Guardant Health, Inc.</t>
         </is>
       </c>
       <c r="D71" s="11" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>2.1</v>
+        <v>9.4</v>
       </c>
       <c r="F71" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G71" s="10" t="inlineStr">
-        <is>
-          <t>2014</t>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>John McPherson</t>
+          <t>Aaref Hilaly</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="K71" s="13" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="L71" s="13" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M71" s="14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="N71" s="14" t="n">
-        <v>3.72</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="K71" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="L71" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="M71" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+      <c r="N71" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>HTO</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -5038,26 +5042,26 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>H2O America</t>
+          <t>Harbour Energy plc</t>
         </is>
       </c>
       <c r="D72" s="11" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="F72" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G72" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>2018</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>Gregory Landis</t>
+          <t>Alan Ferguson</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -5067,26 +5071,26 @@
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K72" s="13" t="n">
-        <v>14</v>
+        <v>1.5</v>
       </c>
       <c r="L72" s="13" t="n">
-        <v>21.8</v>
+        <v>20.9</v>
       </c>
       <c r="M72" s="14" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>2.07</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -5096,63 +5100,55 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Guardant Health, Inc.</t>
+          <t>Danaos Corporation</t>
         </is>
       </c>
       <c r="D73" s="11" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>9.4</v>
+        <v>1</v>
       </c>
       <c r="F73" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G73" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>2005</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>Aaref Hilaly</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="K73" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="L73" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="M73" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
-      </c>
-      <c r="N73" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L73" s="13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M73" s="14" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N73" s="14" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -5162,26 +5158,26 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy plc</t>
+          <t>United Microelectronics Corporation</t>
         </is>
       </c>
       <c r="D74" s="11" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F74" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G74" s="10" t="inlineStr">
-        <is>
-          <t>2018</t>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>Alan Ferguson</t>
+          <t>Jason Wang</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
@@ -5191,26 +5187,26 @@
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K74" s="13" t="n">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>20.9</v>
+        <v>23.9</v>
       </c>
       <c r="M74" s="14" t="n">
-        <v>1.42</v>
+        <v>4.5</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>6.74</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>UBSI</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -5220,55 +5216,55 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Danaos Corporation</t>
+          <t>United Bankshares, Inc.</t>
         </is>
       </c>
       <c r="D75" s="11" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>J. Mcnamara,Michael Fitzgerald</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="K75" s="13" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="L75" s="13" t="n">
-        <v>5.2</v>
+        <v>12.7</v>
       </c>
       <c r="M75" s="14" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -5278,14 +5274,14 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>United Microelectronics Corporation</t>
+          <t>Sprouts Farmers Market, Inc.</t>
         </is>
       </c>
       <c r="D76" s="11" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="F76" s="12" t="n">
         <v>1</v>
@@ -5297,7 +5293,7 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>Jason Wang</t>
+          <t>Douglas Rauch</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
@@ -5307,82 +5303,24 @@
       </c>
       <c r="J76" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="K76" s="13" t="n">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>23.9</v>
+        <v>12.8</v>
       </c>
       <c r="M76" s="14" t="n">
-        <v>4.5</v>
+        <v>4.23</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>4.54</v>
-      </c>
-    </row>
-    <row r="77" ht="14" customHeight="1">
-      <c r="A77" s="9" t="inlineStr">
-        <is>
-          <t>UBSI</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>United Bankshares, Inc.</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E77" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F77" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>J. Mcnamara,Michael Fitzgerald</t>
-        </is>
-      </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>Sequoia Network</t>
-        </is>
-      </c>
-      <c r="J77" s="10" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="K77" s="13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L77" s="13" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="M77" s="14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N77" s="14" t="n">
-        <v>1.88</v>
+        <v>6.97</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N77"/>
+  <autoFilter ref="A4:N76"/>
   <mergeCells count="2">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
@@ -5529,7 +5467,7 @@
         </is>
       </c>
       <c r="E5" s="12" t="n">
-        <v>22.4</v>
+        <v>21.9</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>7.3</v>
@@ -5574,7 +5512,7 @@
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>22.2</v>
+        <v>20.4</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>7.6</v>
@@ -5619,7 +5557,7 @@
         </is>
       </c>
       <c r="E7" s="12" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>0.6</v>
@@ -5696,7 +5634,7 @@
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Alan Howard</t>
+          <t>Nassef Sawiris</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -5706,46 +5644,42 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Bullish (GI</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>BLSH</t>
+          <t>ADDYY</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Senior Advisor</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+          <t>Board Member</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>18.6</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>2.5</v>
+        <v>4.59</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>2.6</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Nassef Sawiris</t>
+          <t>Jacob Wallenberg</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -5755,42 +5689,42 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>ABB (Distributors/Wholesale</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>ADDYY</t>
+          <t>ABBN.SW</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Board Member</t>
+          <t>Vice Chairman of the Board &amp; Member of the Governance &amp; Nomination Committee</t>
         </is>
       </c>
       <c r="H10" s="13" t="n">
-        <v>9</v>
+        <v>24.2</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>18.6</v>
+        <v>36.3</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>4.59</v>
+        <v>11.46</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>6.21</v>
+        <v>33.03</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Jacob Wallenberg</t>
+          <t>Alan Howard</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -5800,36 +5734,40 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>ABB (Distributors/Wholesale</t>
+          <t>Bullish (GI</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>ABBN.SW</t>
+          <t>BLSH</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>0</v>
+        <v>-4.5</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>Vice Chairman of the Board &amp; Member of the Governance &amp; Nomination Committee</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>36.3</v>
+          <t>Senior Advisor</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="J11" s="14" t="n">
-        <v>11.46</v>
+        <v>2.5</v>
       </c>
       <c r="K11" s="14" t="n">
-        <v>33.03</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -7120,7 +7058,7 @@
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -7142,12 +7080,12 @@
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Hope Woodhouse</t>
+          <t>Raffaele Zagari</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Monro</t>
+          <t>Star Bulk Carriers</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -7162,25 +7100,23 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>25.6</v>
+        <v>30.6</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>12.6</v>
+        <v>7.9</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>56.3</v>
+        <v>11.8</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J7" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>1.34</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>1.34</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
@@ -7210,7 +7146,7 @@
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>24.9</v>
+        <v>25.9</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>5.1</v>
@@ -7252,7 +7188,7 @@
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>24.9</v>
+        <v>25.9</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>5.1</v>
@@ -7270,12 +7206,12 @@
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Pamala Kaufman</t>
+          <t>Hope Woodhouse</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Lindblad Expeditions Holdings</t>
+          <t>Monro</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -7290,40 +7226,36 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>24.5</v>
+        <v>25.6</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
+        <v>12.6</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>0.7</v>
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>neg equity</t>
+          <t>neg TBV</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Ashok Srivastava</t>
+          <t>Pamala Kaufman</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Lindblad Expeditions Holdings</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -7338,23 +7270,29 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>23.3</v>
+        <v>24.5</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>213.47</v>
+        <v>20.2</v>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -7406,12 +7344,12 @@
     <row r="13" ht="14" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Ashwini Kumar</t>
+          <t>Mark DiPaolo</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>PayPal Holdings</t>
+          <t>Innoviva</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -7426,34 +7364,34 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>9.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>2.35</v>
+        <v>1.25</v>
       </c>
       <c r="J13" s="14" t="n">
-        <v>5.35</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Mark DiPaolo</t>
+          <t>Ashwini Kumar</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Innoviva</t>
+          <t>PayPal Holdings</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -7468,34 +7406,34 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>INVA</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>4.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>1.25</v>
+        <v>2.35</v>
       </c>
       <c r="J14" s="14" t="n">
-        <v>1.48</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>W. Conn</t>
+          <t>Ashok Srivastava</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Charter Communications</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -7510,78 +7448,76 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>21.8</v>
+        <v>22.2</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>3</v>
+        <v>17.5</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="J15" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>4.15</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>213.47</v>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>C. Wes Burton</t>
+          <t>Viral Patel</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>20</v>
+        <v>22.1</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>14.3</v>
+        <v>18.6</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>28.9</v>
+        <v>26.6</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>3.77</v>
+        <v>10.41</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>9.800000000000001</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Cynthia Hostetler</t>
+          <t>W. Conn</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>Charter Communications</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -7596,29 +7532,31 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>20</v>
+        <v>21.8</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>14.3</v>
+        <v>5.6</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>28.9</v>
+        <v>3</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <v>9.800000000000001</v>
+        <v>0.83</v>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>David Clement</t>
+          <t>C. Wes Burton</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -7660,7 +7598,7 @@
     <row r="19" ht="14" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Denson Franklin</t>
+          <t>Cynthia Hostetler</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -7702,7 +7640,7 @@
     <row r="20" ht="14" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>George Willis</t>
+          <t>David Clement</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -7744,7 +7682,7 @@
     <row r="21" ht="14" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>J. Hill</t>
+          <t>Denson Franklin</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -7786,7 +7724,7 @@
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>J. Thomas Hill</t>
+          <t>George Willis</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -7828,7 +7766,7 @@
     <row r="23" ht="14" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Jerry Perkins</t>
+          <t>J. Hill</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -7870,7 +7808,7 @@
     <row r="24" ht="14" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Mark Warren</t>
+          <t>J. Thomas Hill</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -7912,7 +7850,7 @@
     <row r="25" ht="14" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Mary Carlisle</t>
+          <t>Jerry Perkins</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -7954,7 +7892,7 @@
     <row r="26" ht="14" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Thomas Fanning</t>
+          <t>Mark Warren</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -7996,12 +7934,12 @@
     <row r="27" ht="14" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Andrew Crowley</t>
+          <t>Mary Carlisle</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Markel Group</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -8016,34 +7954,34 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>MKL</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>6.9</v>
+        <v>14.3</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>9.699999999999999</v>
+        <v>28.9</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>1.05</v>
+        <v>3.77</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>1.35</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>Thomas Fanning</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>SLB (Other Energy Services</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -8058,34 +7996,34 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>18.3</v>
+        <v>20</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>12.2</v>
+        <v>14.3</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>25.1</v>
+        <v>28.9</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>3.01</v>
+        <v>3.77</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>15.23</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Richard Mulligan</t>
+          <t>Andrew Crowley</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Sana Biotechnology</t>
+          <t>Markel Group</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -8100,40 +8038,34 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>SANA</t>
+          <t>MKL</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>19.7</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="J29" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>1.05</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>1.35</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Danny Shepherd</t>
+          <t>Richard Mulligan</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Beazer Homes USA</t>
+          <t>Sana Biotechnology</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -8148,14 +8080,16 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>BZH</t>
+          <t>SANA</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="G30" s="13" t="n">
-        <v>39</v>
+        <v>17.1</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
@@ -8163,21 +8097,23 @@
         </is>
       </c>
       <c r="I30" s="14" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="J30" s="14" t="n">
-        <v>0.78</v>
+        <v>6.05</v>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Derek Kan</t>
+          <t>Danny Shepherd</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Toll Brothers</t>
+          <t>Beazer Homes USA</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -8192,34 +8128,36 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>TOL</t>
+          <t>BZH</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H31" s="13" t="n">
-        <v>10.9</v>
+        <v>39</v>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="I31" s="14" t="n">
-        <v>1.52</v>
+        <v>0.77</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>1.52</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Annalisa Jenkins</t>
+          <t>Derek Kan</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>COMPASS Pathways</t>
+          <t>Toll Brothers</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -8234,38 +8172,34 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>TOL</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
         <v>16.2</v>
       </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+      <c r="G32" s="13" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>10.9</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>15.93</v>
+        <v>1.52</v>
       </c>
       <c r="J32" s="14" t="n">
-        <v>15.93</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="33" ht="14" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>Michael Insulan</t>
+          <t>Annalisa Jenkins</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Electra Battery Materials</t>
+          <t>COMPASS Pathways</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -8280,14 +8214,16 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>ELBM</t>
+          <t>CMPS</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="G33" s="13" t="n">
-        <v>5.7</v>
+        <v>16.2</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
@@ -8295,21 +8231,21 @@
         </is>
       </c>
       <c r="I33" s="14" t="n">
-        <v>0.88</v>
+        <v>15.93</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>0.88</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Franz Humer</t>
+          <t>Michael Insulan</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Allogene Therapeutics</t>
+          <t>Electra Battery Materials</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -8324,16 +8260,14 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>ALLO</t>
+          <t>ELBM</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
         <v>15.7</v>
       </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
+      <c r="G34" s="13" t="n">
+        <v>5.7</v>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
@@ -8341,21 +8275,21 @@
         </is>
       </c>
       <c r="I34" s="14" t="n">
-        <v>1.28</v>
+        <v>0.88</v>
       </c>
       <c r="J34" s="14" t="n">
-        <v>1.28</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Meryl Hartzband</t>
+          <t>Franz Humer</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Everest Group (Hamilton</t>
+          <t>Allogene Therapeutics</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -8370,34 +8304,38 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>ALLO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="G35" s="13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H35" s="13" t="n">
-        <v>8</v>
+        <v>15.7</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="I35" s="14" t="n">
-        <v>0.98</v>
+        <v>1.28</v>
       </c>
       <c r="J35" s="14" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Joseph Flaim</t>
+          <t>Meryl Hartzband</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Iamgold</t>
+          <t>Everest Group (Hamilton</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -8407,39 +8345,39 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>14.1</v>
+        <v>15.2</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>9.9</v>
+        <v>8</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>2.61</v>
+        <v>0.98</v>
       </c>
       <c r="J36" s="14" t="n">
-        <v>2.61</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="37" ht="14" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Dawn Fitzpatrick</t>
+          <t>Joseph Flaim</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Under Armour</t>
+          <t>Iamgold</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -8449,43 +8387,39 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>UAA</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>14.1</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H37" s="13" t="n">
+        <v>9.9</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>1.36</v>
+        <v>2.61</v>
       </c>
       <c r="J37" s="14" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>James Nelson</t>
+          <t>Dawn Fitzpatrick</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Global Net Lease</t>
+          <t>Under Armour</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -8500,14 +8434,16 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>GNL</t>
+          <t>UAA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="G38" s="13" t="n">
-        <v>11.9</v>
+        <v>13.9</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
@@ -8515,21 +8451,21 @@
         </is>
       </c>
       <c r="I38" s="14" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="J38" s="14" t="n">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Allan D. Schoening</t>
+          <t>James Nelson</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Civeo</t>
+          <t>Global Net Lease</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -8544,14 +8480,14 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>CVEO</t>
+          <t>GNL</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>6.5</v>
+        <v>11.9</v>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
@@ -8559,21 +8495,21 @@
         </is>
       </c>
       <c r="I39" s="14" t="n">
-        <v>2.35</v>
+        <v>1.22</v>
       </c>
       <c r="J39" s="14" t="n">
-        <v>4.35</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Wilbur Ross</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Coya Therapeutics</t>
+          <t>SLB (Other Energy Services</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -8588,38 +8524,34 @@
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>COYA</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>13.4</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H40" s="13" t="n">
+        <v>25.1</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="J40" s="14" t="n">
-        <v>0</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>Kathleen Quirk</t>
+          <t>Allan D. Schoening</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>Civeo</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -8634,34 +8566,36 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>CVEO</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="H41" s="13" t="n">
-        <v>35.3</v>
+        <v>6.5</v>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="I41" s="14" t="n">
-        <v>5.14</v>
+        <v>2.35</v>
       </c>
       <c r="J41" s="14" t="n">
-        <v>5.14</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>Jonathan Frates</t>
+          <t>Wilbur Ross</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>SandRidge Energy</t>
+          <t>Coya Therapeutics</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -8676,29 +8610,33 @@
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>COYA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="G42" s="13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H42" s="13" t="n">
-        <v>6.3</v>
+        <v>12.7</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="I42" s="14" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="J42" s="14" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>Nancy Dunlap</t>
+          <t>Jonathan Frates</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
@@ -8740,12 +8678,12 @@
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Thierry Pilenko</t>
+          <t>Nancy Dunlap</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>LanzaTech Global</t>
+          <t>SandRidge Energy</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -8760,36 +8698,34 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>LNZA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>net cash</t>
-        </is>
+        <v>12.1</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>3.1</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>0.1</v>
+        <v>6.3</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>0.05</v>
+        <v>0.96</v>
       </c>
       <c r="J44" s="14" t="n">
-        <v>0.05</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Bryan Murphy</t>
+          <t>Anthony Williams</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Greenlight Capital Re</t>
+          <t>Akamai Technologies</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -8804,36 +8740,34 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>GLRE</t>
+          <t>AKAM</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>net cash</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>19.1</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>10</v>
+        <v>40.4</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>0.71</v>
+        <v>3.5</v>
       </c>
       <c r="J45" s="14" t="n">
-        <v>0.82</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>Anthony Williams</t>
+          <t>Thierry Pilenko</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Akamai Technologies</t>
+          <t>LanzaTech Global</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -8848,34 +8782,36 @@
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>AKAM</t>
+          <t>LNZA</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="G46" s="13" t="n">
-        <v>19.1</v>
+        <v>10.7</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>net cash</t>
+        </is>
       </c>
       <c r="H46" s="13" t="n">
-        <v>40.4</v>
+        <v>0.1</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>3.5</v>
+        <v>0.05</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>16.92</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>Daniel Sansone</t>
+          <t>Sandra Bell</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>Dye &amp; Durham</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -8885,25 +8821,27 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>NGVT</t>
+          <t>DYNDF</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H47" s="13" t="n">
-        <v>45.5</v>
+        <v>8.4</v>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="I47" s="14" t="n">
-        <v>52.3</v>
+        <v>0.12</v>
       </c>
       <c r="J47" s="12" t="inlineStr">
         <is>
@@ -8938,7 +8876,7 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="G48" s="13" t="n">
         <v>9.699999999999999</v>
@@ -8956,54 +8894,56 @@
     <row r="49" ht="14" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Viral Patel</t>
+          <t>Michael Dougherty</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>Polaris (Automotive</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H49" s="13" t="n">
-        <v>26.6</v>
+        <v>40</v>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="I49" s="14" t="n">
-        <v>10.41</v>
+        <v>3.62</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>11.43</v>
+        <v>59.92</v>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>Sandra Bell</t>
+          <t>Bill Roeschlein</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Dye &amp; Durham</t>
+          <t>Tigo Energy</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -9013,43 +8953,39 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>DYNDF</t>
+          <t>TYGO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>4.7</v>
+      </c>
+      <c r="H50" s="13" t="n">
+        <v>6.7</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J50" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>1.65</v>
+      </c>
+      <c r="J50" s="14" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Stephen Gunther</t>
+          <t>Bryan Murphy</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Shoulder Innovations</t>
+          <t>Greenlight Capital Re</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -9059,43 +8995,41 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>GLRE</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+          <t>net cash</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>2.96</v>
+        <v>0.71</v>
       </c>
       <c r="J51" s="14" t="n">
-        <v>2.96</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Michael Dougherty</t>
+          <t>Richard Russell</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Polaris (Automotive</t>
+          <t>LM Funding America</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -9110,36 +9044,42 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>PII</t>
+          <t>LMFA</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="G52" s="13" t="n">
-        <v>40</v>
+        <v>10.1</v>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>delisted</t>
+        </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="I52" s="14" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="J52" s="14" t="n">
-        <v>59.92</v>
+          <t>delisted</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>delisted</t>
+        </is>
+      </c>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>delisted</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>Bill Roeschlein</t>
+          <t>Daniel Sansone</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Tigo Energy</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -9154,34 +9094,36 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>TYGO</t>
+          <t>NGVT</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>4.7</v>
+        <v>18.6</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>6.7</v>
+        <v>45.5</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J53" s="14" t="n">
-        <v>2.38</v>
+        <v>52.3</v>
+      </c>
+      <c r="J53" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Richard Russell</t>
+          <t>Jeffrey Fox</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>LM Funding America</t>
+          <t>Westrock Coffee</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -9196,42 +9138,36 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>LMFA</t>
+          <t>WEST</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="G54" s="12" t="inlineStr">
-        <is>
-          <t>delisted</t>
-        </is>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>24.2</v>
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>delisted</t>
-        </is>
-      </c>
-      <c r="I54" s="12" t="inlineStr">
-        <is>
-          <t>delisted</t>
-        </is>
-      </c>
-      <c r="J54" s="12" t="inlineStr">
-        <is>
-          <t>delisted</t>
-        </is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="I54" s="14" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="J54" s="14" t="n">
+        <v>34.55</v>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Jeffrey Fox</t>
+          <t>Kathleen Quirk</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Westrock Coffee</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -9246,36 +9182,34 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>WEST</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="H55" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>12.2</v>
+      </c>
+      <c r="H55" s="13" t="n">
+        <v>35.3</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>3.24</v>
+        <v>5.14</v>
       </c>
       <c r="J55" s="14" t="n">
-        <v>34.55</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>Brian Corvese</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>Agenus</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -9290,34 +9224,38 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>AGEN</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>135</v>
+        <v>2.4</v>
       </c>
       <c r="H56" s="13" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="I56" s="14" t="n">
-        <v>20.63</v>
-      </c>
-      <c r="J56" s="14" t="n">
-        <v>68.36</v>
+        <v>3.1</v>
+      </c>
+      <c r="I56" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+      <c r="J56" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="14" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Brian Corvese</t>
+          <t>Rebecca Grossman-Cohen</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Agenus</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -9332,38 +9270,34 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>2.4</v>
+        <v>16.6</v>
       </c>
       <c r="H57" s="13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I57" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
-      </c>
-      <c r="J57" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
+        <v>26.3</v>
+      </c>
+      <c r="I57" s="14" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="J57" s="14" t="n">
+        <v>7.23</v>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Rebecca Grossman-Cohen</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -9378,23 +9312,23 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>16.6</v>
+        <v>135</v>
       </c>
       <c r="H58" s="13" t="n">
-        <v>26.3</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I58" s="14" t="n">
-        <v>5.03</v>
+        <v>20.63</v>
       </c>
       <c r="J58" s="14" t="n">
-        <v>7.23</v>
+        <v>68.36</v>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
@@ -9526,12 +9460,12 @@
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>Stephen Gunther</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Amprius Technologies</t>
+          <t>Shoulder Innovations</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -9541,16 +9475,16 @@
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -9563,21 +9497,21 @@
         </is>
       </c>
       <c r="I62" s="14" t="n">
-        <v>11.38</v>
+        <v>2.96</v>
       </c>
       <c r="J62" s="14" t="n">
-        <v>11.38</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>John Campbell</t>
+          <t>Jonathan Christodoro</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Porch Group</t>
+          <t>Xerox</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -9592,35 +9526,37 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>XRXDW</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="G63" s="13" t="n">
-        <v>23.1</v>
+        <v>8.1</v>
+      </c>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>warrant</t>
         </is>
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>neg equity</t>
+          <t>warrant</t>
         </is>
       </c>
       <c r="J63" s="12" t="inlineStr">
         <is>
-          <t>neg TBV</t>
+          <t>warrant</t>
         </is>
       </c>
     </row>
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>Jonathan Christodoro</t>
+          <t>Louis Pastor</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -9646,32 +9582,36 @@
       <c r="F64" s="12" t="n">
         <v>8.1</v>
       </c>
-      <c r="G64" s="13" t="n">
-        <v>8.1</v>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="I64" s="14" t="n">
-        <v>0.08</v>
+          <t>warrant</t>
+        </is>
+      </c>
+      <c r="I64" s="12" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
       </c>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>neg TBV</t>
+          <t>warrant</t>
         </is>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>Louis Pastor</t>
+          <t>Randle Reece</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Xerox</t>
+          <t>AMN Healthcare Services</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -9686,22 +9626,20 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>XRXDW</t>
+          <t>AMN</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="H65" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="H65" s="13" t="n">
+        <v>12.7</v>
       </c>
       <c r="I65" s="14" t="n">
-        <v>0.08</v>
+        <v>1.81</v>
       </c>
       <c r="J65" s="12" t="inlineStr">
         <is>
@@ -9712,12 +9650,12 @@
     <row r="66" ht="14" customHeight="1">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>Chris Siu</t>
+          <t>Kenneth Gunderman</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Aehr Test Systems</t>
+          <t>Uniti Group (Financial Services</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -9732,38 +9670,36 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G66" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="H66" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>7.2</v>
+      </c>
+      <c r="G66" s="13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H66" s="13" t="n">
+        <v>1.8</v>
       </c>
       <c r="I66" s="14" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="J66" s="14" t="n">
-        <v>14.35</v>
+        <v>14.41</v>
+      </c>
+      <c r="J66" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Randle Reece</t>
+          <t>Pam Kaufman</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>AMN Healthcare Services</t>
+          <t>Paramount Skydance</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -9778,36 +9714,38 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>AMN</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="G67" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H67" s="13" t="n">
-        <v>12.7</v>
+        <v>7.1</v>
+      </c>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="H67" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="I67" s="14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="J67" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J67" s="14" t="n">
+        <v>2.34</v>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>Kenneth Gunderman</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Uniti Group (Financial Services</t>
+          <t>Amprius Technologies</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -9822,36 +9760,38 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G68" s="13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H68" s="13" t="n">
-        <v>1.8</v>
+        <v>7.1</v>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="H68" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="I68" s="14" t="n">
-        <v>14.41</v>
-      </c>
-      <c r="J68" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>11.38</v>
+      </c>
+      <c r="J68" s="14" t="n">
+        <v>11.38</v>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>Richard Massey</t>
+          <t>David Habachy</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Jena Acquisition II</t>
+          <t>Ring Energy</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -9866,42 +9806,36 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>JENA-UN</t>
+          <t>REI</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G69" s="12" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="G69" s="13" t="n">
+        <v>3.8</v>
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I69" s="12" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="J69" s="12" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="I69" s="14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J69" s="14" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>Pam Kaufman</t>
+          <t>David Moradi</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Paramount Skydance</t>
+          <t>AudioEye</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -9916,16 +9850,14 @@
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="G70" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
+        <v>6.5</v>
+      </c>
+      <c r="G70" s="13" t="n">
+        <v>50</v>
       </c>
       <c r="H70" s="12" t="inlineStr">
         <is>
@@ -9933,10 +9865,12 @@
         </is>
       </c>
       <c r="I70" s="14" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="J70" s="14" t="n">
-        <v>2.34</v>
+        <v>27.93</v>
+      </c>
+      <c r="J70" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
@@ -9966,7 +9900,7 @@
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="G71" s="13" t="n">
         <v>15.1</v>
@@ -9986,12 +9920,12 @@
     <row r="72" ht="14" customHeight="1">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>David Habachy</t>
+          <t>Laura Duda</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Ring Energy</t>
+          <t>The Goodyear Tire &amp; Rubber</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -10006,14 +9940,14 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>REI</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>3.8</v>
+        <v>34.2</v>
       </c>
       <c r="H72" s="12" t="inlineStr">
         <is>
@@ -10021,21 +9955,21 @@
         </is>
       </c>
       <c r="I72" s="14" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="J72" s="14" t="n">
-        <v>0.42</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>David Moradi</t>
+          <t>Tim Cahill</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>AudioEye</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -10050,22 +9984,20 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="H73" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>14.1</v>
+      </c>
+      <c r="H73" s="13" t="n">
+        <v>19.6</v>
       </c>
       <c r="I73" s="14" t="n">
-        <v>27.93</v>
+        <v>14.01</v>
       </c>
       <c r="J73" s="12" t="inlineStr">
         <is>
@@ -10076,12 +10008,12 @@
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>Tim Cahill</t>
+          <t>Tiago Miranda</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Atlas Lithium</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -10096,36 +10028,38 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>ATLX</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G74" s="13" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H74" s="13" t="n">
-        <v>19.6</v>
+        <v>6.2</v>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="I74" s="14" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="J74" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>1.76</v>
+      </c>
+      <c r="J74" s="14" t="n">
+        <v>1.77</v>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>Laura Duda</t>
+          <t>Martin Bork</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>The Goodyear Tire &amp; Rubber</t>
+          <t>Navigator Holdings</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
@@ -10140,36 +10074,34 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>NVGS</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="H75" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>6.2</v>
+      </c>
+      <c r="H75" s="13" t="n">
+        <v>10.6</v>
       </c>
       <c r="I75" s="14" t="n">
-        <v>0.54</v>
+        <v>1.15</v>
       </c>
       <c r="J75" s="14" t="n">
-        <v>0.7</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Martin Bork</t>
+          <t>John Baker</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>Navigator Holdings</t>
+          <t>FRP Holdings</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -10184,34 +10116,34 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>NVGS</t>
+          <t>FRPH</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>6.2</v>
+        <v>40.6</v>
       </c>
       <c r="H76" s="13" t="n">
-        <v>10.6</v>
+        <v>4000.5</v>
       </c>
       <c r="I76" s="14" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J76" s="14" t="n">
-        <v>1.15</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>Tiago Miranda</t>
+          <t>Tony Buffin</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>Atlas Lithium</t>
+          <t>DFS Furniture</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
@@ -10226,38 +10158,36 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>ATLX</t>
+          <t>DFS.L</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G77" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="H77" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>5.8</v>
+      </c>
+      <c r="G77" s="13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H77" s="13" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="I77" s="14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="J77" s="14" t="n">
-        <v>1.77</v>
+        <v>1.23</v>
+      </c>
+      <c r="J77" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>Tony Buffin</t>
+          <t>Aris Kekedjian</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>DFS Furniture</t>
+          <t>Stratasys (Printing Services (B2B</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -10272,36 +10202,38 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>DFS.L</t>
+          <t>SSYS</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
         <v>5.8</v>
       </c>
-      <c r="G78" s="13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H78" s="13" t="n">
-        <v>9.800000000000001</v>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="I78" s="14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="J78" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>0.85</v>
+      </c>
+      <c r="J78" s="14" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="79" ht="14" customHeight="1">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>Aris Kekedjian</t>
+          <t>Charles Leykum</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>Stratasys (Printing Services (B2B</t>
+          <t>Talon Capital (SPAC</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
@@ -10316,7 +10248,7 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>TLNC</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
@@ -10324,30 +10256,30 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="H79" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+          <t>SPAC</t>
+        </is>
+      </c>
+      <c r="H79" s="13" t="n">
+        <v>51.9</v>
       </c>
       <c r="I79" s="14" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J79" s="14" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
+      </c>
+      <c r="J79" s="12" t="inlineStr">
+        <is>
+          <t>SPAC</t>
+        </is>
       </c>
     </row>
     <row r="80" ht="14" customHeight="1">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>Charles Leykum</t>
+          <t>R. Cox</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>Talon Capital (SPAC</t>
+          <t>Terex</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -10362,38 +10294,36 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>TLNC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G80" s="12" t="inlineStr">
-        <is>
-          <t>SPAC</t>
-        </is>
+        <v>5.7</v>
+      </c>
+      <c r="G80" s="13" t="n">
+        <v>20.2</v>
       </c>
       <c r="H80" s="13" t="n">
-        <v>51.9</v>
+        <v>29.5</v>
       </c>
       <c r="I80" s="14" t="n">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="J80" s="12" t="inlineStr">
         <is>
-          <t>SPAC</t>
+          <t>neg TBV</t>
         </is>
       </c>
     </row>
     <row r="81" ht="14" customHeight="1">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>R. Cox</t>
+          <t>Oscar Iglesias</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Terex</t>
+          <t>Codere Online Luxembourg</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -10408,36 +10338,42 @@
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CDROW</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="G81" s="13" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="H81" s="13" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="I81" s="14" t="n">
-        <v>1.36</v>
+        <v>5.5</v>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
+      </c>
+      <c r="H81" s="12" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
+      </c>
+      <c r="I81" s="12" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
       </c>
       <c r="J81" s="12" t="inlineStr">
         <is>
-          <t>neg TBV</t>
+          <t>warrant</t>
         </is>
       </c>
     </row>
     <row r="82" ht="14" customHeight="1">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>Nicholas Zangler</t>
+          <t>John Campbell</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>Viant Technology</t>
+          <t>Porch Group</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
@@ -10452,34 +10388,40 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="H82" s="13" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="I82" s="14" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="J82" s="14" t="n">
-        <v>2.48</v>
+        <v>23.1</v>
+      </c>
+      <c r="H82" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="I82" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+      <c r="J82" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="83" ht="14" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>John Baker</t>
+          <t>Schroeder Norman</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>FRP Holdings</t>
+          <t>Simpple (Automation/Workflow Software</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
@@ -10494,34 +10436,38 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>FRPH</t>
+          <t>SPPL</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G83" s="13" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="H83" s="13" t="n">
-        <v>4000.5</v>
+        <v>5.2</v>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="I83" s="14" t="n">
-        <v>0.9399999999999999</v>
+        <v>4.75</v>
       </c>
       <c r="J83" s="14" t="n">
-        <v>0.96</v>
+        <v>103.28</v>
       </c>
     </row>
     <row r="84" ht="14" customHeight="1">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>Oscar Iglesias</t>
+          <t>Paul Allen</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>Codere Online Luxembourg</t>
+          <t>Airship AI Holdings</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
@@ -10536,42 +10482,40 @@
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>CDROW</t>
+          <t>AISP</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>warrant</t>
-        </is>
-      </c>
-      <c r="H84" s="12" t="inlineStr">
-        <is>
-          <t>warrant</t>
-        </is>
+          <t>net cash</t>
+        </is>
+      </c>
+      <c r="H84" s="13" t="n">
+        <v>2.4</v>
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
-          <t>warrant</t>
+          <t>neg equity</t>
         </is>
       </c>
       <c r="J84" s="12" t="inlineStr">
         <is>
-          <t>warrant</t>
+          <t>neg equity</t>
         </is>
       </c>
     </row>
     <row r="85" ht="14" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Schroeder Norman</t>
+          <t>V. Sardo</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Simpple (Automation/Workflow Software</t>
+          <t>Currency Exchange International</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
@@ -10581,43 +10525,39 @@
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>SPPL</t>
+          <t>CURN</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
         <v>5.2</v>
       </c>
-      <c r="G85" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="H85" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+      <c r="G85" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H85" s="13" t="n">
+        <v>29.6</v>
       </c>
       <c r="I85" s="14" t="n">
-        <v>4.75</v>
+        <v>1.03</v>
       </c>
       <c r="J85" s="14" t="n">
-        <v>103.28</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="86" ht="14" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Paul Allen</t>
+          <t>Richard Massey</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>Airship AI Holdings</t>
+          <t>Jena Acquisition II</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
@@ -10632,40 +10572,42 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>JENA-UN</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>net cash</t>
-        </is>
-      </c>
-      <c r="H86" s="13" t="n">
-        <v>2.4</v>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H86" s="12" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
-          <t>neg equity</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="J86" s="12" t="inlineStr">
         <is>
-          <t>neg equity</t>
+          <t>unit</t>
         </is>
       </c>
     </row>
     <row r="87" ht="14" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>V. Sardo</t>
+          <t>Len Blavatnik</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Currency Exchange International</t>
+          <t>Warner Music Group</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
@@ -10675,39 +10617,41 @@
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>CURN</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>1.4</v>
+        <v>12.1</v>
       </c>
       <c r="H87" s="13" t="n">
-        <v>29.6</v>
+        <v>21.2</v>
       </c>
       <c r="I87" s="14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="J87" s="14" t="n">
-        <v>1.08</v>
+        <v>16.7</v>
+      </c>
+      <c r="J87" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="88" ht="14" customHeight="1">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>Len Blavatnik</t>
+          <t>Hock Goh</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Warner Music Group</t>
+          <t>SKF</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
@@ -10722,36 +10666,34 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>SKF-B.ST</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
         <v>4.9</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="H88" s="13" t="n">
-        <v>21.2</v>
+        <v>27.4</v>
       </c>
       <c r="I88" s="14" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="J88" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>2.14</v>
+      </c>
+      <c r="J88" s="14" t="n">
+        <v>2.85</v>
       </c>
     </row>
     <row r="89" ht="14" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>Hock Goh</t>
+          <t>Andrew Michelmore</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>SKF</t>
+          <t>Century Aluminum</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
@@ -10766,34 +10708,34 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>SKF-B.ST</t>
+          <t>CENX</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>11.7</v>
+        <v>5.6</v>
       </c>
       <c r="H89" s="13" t="n">
-        <v>27.4</v>
+        <v>6.4</v>
       </c>
       <c r="I89" s="14" t="n">
-        <v>2.14</v>
+        <v>2.74</v>
       </c>
       <c r="J89" s="14" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="90" ht="14" customHeight="1">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>Andrew Michelmore</t>
+          <t>Randall Weisenburger</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Century Aluminum</t>
+          <t>MP Materials</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
@@ -10808,34 +10750,36 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>CENX</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H90" s="13" t="n">
-        <v>6.4</v>
+        <v>150.4</v>
+      </c>
+      <c r="H90" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="I90" s="14" t="n">
-        <v>2.74</v>
+        <v>4.46</v>
       </c>
       <c r="J90" s="14" t="n">
-        <v>2.74</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="91" ht="14" customHeight="1">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>Randall Weisenburger</t>
+          <t>Chris Siu</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>MP Materials</t>
+          <t>Aehr Test Systems</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
@@ -10850,14 +10794,16 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
         <v>4.4</v>
       </c>
-      <c r="G91" s="13" t="n">
-        <v>150.4</v>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
@@ -10865,10 +10811,10 @@
         </is>
       </c>
       <c r="I91" s="14" t="n">
-        <v>4.46</v>
+        <v>13.03</v>
       </c>
       <c r="J91" s="14" t="n">
-        <v>4.46</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="92" ht="14" customHeight="1">
@@ -10948,7 +10894,7 @@
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G93" s="13" t="n">
         <v>25.5</v>
@@ -10966,12 +10912,12 @@
     <row r="94" ht="14" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>Douglas Rauch</t>
+          <t>Nicholas Zangler</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market</t>
+          <t>Viant Technology</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
@@ -10986,23 +10932,23 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>SFM</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="F94" s="12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>8.199999999999999</v>
+        <v>23.8</v>
       </c>
       <c r="H94" s="13" t="n">
-        <v>12.8</v>
+        <v>28.7</v>
       </c>
       <c r="I94" s="14" t="n">
-        <v>4.23</v>
+        <v>2.11</v>
       </c>
       <c r="J94" s="14" t="n">
-        <v>6.97</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="95" ht="14" customHeight="1">
@@ -11050,12 +10996,12 @@
     <row r="96" ht="14" customHeight="1">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>Michael Denham</t>
+          <t>John McPherson</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>National Bank of Canada (Montreall</t>
+          <t>Commercial Metals</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
@@ -11070,34 +11016,34 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>NBHC</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="F96" s="12" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>11.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H96" s="13" t="n">
-        <v>15.7</v>
+        <v>12.1</v>
       </c>
       <c r="I96" s="14" t="n">
-        <v>0.92</v>
+        <v>1.58</v>
       </c>
       <c r="J96" s="14" t="n">
-        <v>1.34</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>John McPherson</t>
+          <t>Michael Denham</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Commercial Metals</t>
+          <t>National Bank of Canada (Montreall</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
@@ -11112,23 +11058,23 @@
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>NBHC</t>
         </is>
       </c>
       <c r="F97" s="12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>8.699999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="H97" s="13" t="n">
-        <v>12.1</v>
+        <v>15.7</v>
       </c>
       <c r="I97" s="14" t="n">
-        <v>1.58</v>
+        <v>0.92</v>
       </c>
       <c r="J97" s="14" t="n">
-        <v>3.72</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="98" ht="14" customHeight="1">
@@ -11158,7 +11104,7 @@
         </is>
       </c>
       <c r="F98" s="12" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G98" s="13" t="n">
         <v>14</v>
@@ -11176,12 +11122,12 @@
     <row r="99" ht="14" customHeight="1">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>Raffaele Zagari</t>
+          <t>Ghislane Bennouna</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>Star Bulk Carriers</t>
+          <t>Aya Gold &amp; Silver</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
@@ -11191,39 +11137,39 @@
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>AYA</t>
         </is>
       </c>
       <c r="F99" s="12" t="n">
         <v>3.3</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>7.9</v>
+        <v>18.9</v>
       </c>
       <c r="H99" s="13" t="n">
-        <v>11.8</v>
+        <v>35.9</v>
       </c>
       <c r="I99" s="14" t="n">
-        <v>1.34</v>
+        <v>8.23</v>
       </c>
       <c r="J99" s="14" t="n">
-        <v>1.34</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="100" ht="14" customHeight="1">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>Ghislane Bennouna</t>
+          <t>Alan Ferguson</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>Aya Gold &amp; Silver</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
@@ -11233,34 +11179,34 @@
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>AYA</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F100" s="12" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>18.9</v>
+        <v>1.5</v>
       </c>
       <c r="H100" s="13" t="n">
-        <v>35.9</v>
+        <v>20.9</v>
       </c>
       <c r="I100" s="14" t="n">
-        <v>8.23</v>
+        <v>1.42</v>
       </c>
       <c r="J100" s="14" t="n">
-        <v>8.23</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="101" ht="14" customHeight="1">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>Alan Ferguson</t>
+          <t>Alexander Krane</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -11302,7 +11248,7 @@
     <row r="102" ht="14" customHeight="1">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>Alexander Krane</t>
+          <t>Andrea Pinarel</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -11344,7 +11290,7 @@
     <row r="103" ht="14" customHeight="1">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>Andrea Pinarel</t>
+          <t>David Kennedy</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
@@ -11386,7 +11332,7 @@
     <row r="104" ht="14" customHeight="1">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>David Kennedy</t>
+          <t>Feyyaz Etiz</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -11428,7 +11374,7 @@
     <row r="105" ht="14" customHeight="1">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Feyyaz Etiz</t>
+          <t>Gustavo Baquero</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
@@ -11470,7 +11416,7 @@
     <row r="106" ht="14" customHeight="1">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Gustavo Baquero</t>
+          <t>Linda Cook</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -11512,7 +11458,7 @@
     <row r="107" ht="14" customHeight="1">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>Linda Cook</t>
+          <t>Michael Tuffin</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
@@ -11554,7 +11500,7 @@
     <row r="108" ht="14" customHeight="1">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>Michael Tuffin</t>
+          <t>Nathan Mauzy</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
@@ -11596,12 +11542,12 @@
     <row r="109" ht="14" customHeight="1">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>Nathan Mauzy</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>Danaos</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
@@ -11611,39 +11557,39 @@
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F109" s="12" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="H109" s="13" t="n">
-        <v>20.9</v>
+        <v>5.2</v>
       </c>
       <c r="I109" s="14" t="n">
-        <v>1.42</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J109" s="14" t="n">
-        <v>6.74</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="110" ht="14" customHeight="1">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>Chi-Tung Liu</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>Danaos</t>
+          <t>United Microelectronics</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
@@ -11653,34 +11599,34 @@
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="H110" s="13" t="n">
-        <v>5.2</v>
+        <v>23.9</v>
       </c>
       <c r="I110" s="14" t="n">
-        <v>0.6899999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="J110" s="14" t="n">
-        <v>0.6899999999999999</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="111" ht="14" customHeight="1">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>Chi-Tung Liu</t>
+          <t>Jason Wang</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
@@ -11722,12 +11668,12 @@
     <row r="112" ht="14" customHeight="1">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>Jason Wang</t>
+          <t>Peter Loscher</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>United Microelectronics</t>
+          <t>Telefónica</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
@@ -11742,34 +11688,34 @@
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="F112" s="12" t="n">
         <v>1.2</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="H112" s="13" t="n">
-        <v>23.9</v>
+        <v>14.7</v>
       </c>
       <c r="I112" s="14" t="n">
-        <v>4.5</v>
+        <v>1.49</v>
       </c>
       <c r="J112" s="14" t="n">
-        <v>4.54</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="113" ht="14" customHeight="1">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>Peter Loscher</t>
+          <t>Kent Yee</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>Telefónica</t>
+          <t>DXP Enterprises</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
@@ -11784,34 +11730,36 @@
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="F113" s="12" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>4.3</v>
+        <v>16</v>
       </c>
       <c r="H113" s="13" t="n">
-        <v>14.7</v>
+        <v>31.7</v>
       </c>
       <c r="I113" s="14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="J113" s="14" t="n">
-        <v>5.31</v>
+        <v>5.43</v>
+      </c>
+      <c r="J113" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="114" ht="14" customHeight="1">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>Kent Yee</t>
+          <t>Aviad Kaufman</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>DXP Enterprises</t>
+          <t>Kenon Holdings</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
@@ -11826,31 +11774,29 @@
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="F114" s="12" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>16</v>
+        <v>12.8</v>
       </c>
       <c r="H114" s="13" t="n">
-        <v>31.7</v>
+        <v>29.5</v>
       </c>
       <c r="I114" s="14" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="J114" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>2.22</v>
+      </c>
+      <c r="J114" s="14" t="n">
+        <v>2.28</v>
       </c>
     </row>
     <row r="115" ht="14" customHeight="1">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>Aviad Kaufman</t>
+          <t>Idan Ofer</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -11892,12 +11838,12 @@
     <row r="116" ht="14" customHeight="1">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>Idan Ofer</t>
+          <t>Douglas Rauch</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>Kenon Holdings</t>
+          <t>Sprouts Farmers Market</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
@@ -11912,23 +11858,23 @@
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="F116" s="12" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="G116" s="13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H116" s="13" t="n">
         <v>12.8</v>
       </c>
-      <c r="H116" s="13" t="n">
-        <v>29.5</v>
-      </c>
       <c r="I116" s="14" t="n">
-        <v>2.22</v>
+        <v>4.23</v>
       </c>
       <c r="J116" s="14" t="n">
-        <v>2.28</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="117" ht="14" customHeight="1">

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -1168,16 +1168,16 @@
         </is>
       </c>
       <c r="N5" s="14" t="n">
-        <v>31</v>
+        <v>31.4</v>
       </c>
       <c r="O5" s="14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="P5" s="15" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="Q5" s="15" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="N6" s="14" t="n">
-        <v>24.1</v>
+        <v>24.7</v>
       </c>
       <c r="O6" s="14" t="n">
-        <v>11.8</v>
+        <v>12.2</v>
       </c>
       <c r="P6" s="15" t="n">
-        <v>4.17</v>
+        <v>4.29</v>
       </c>
       <c r="Q6" s="15" t="n">
-        <v>4.63</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -1314,16 +1314,16 @@
         </is>
       </c>
       <c r="N7" s="14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O7" s="14" t="n">
-        <v>30.4</v>
+        <v>29.9</v>
       </c>
       <c r="P7" s="15" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="Q7" s="15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="N8" s="14" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="O8" s="14" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="P8" s="15" t="n">
-        <v>16.7</v>
+        <v>16.53</v>
       </c>
       <c r="Q8" s="12" t="inlineStr">
         <is>
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="N9" s="14" t="n">
-        <v>24.2</v>
+        <v>23.7</v>
       </c>
       <c r="O9" s="14" t="n">
-        <v>36.3</v>
+        <v>35.4</v>
       </c>
       <c r="P9" s="15" t="n">
-        <v>11.46</v>
+        <v>11.19</v>
       </c>
       <c r="Q9" s="15" t="n">
-        <v>33.03</v>
+        <v>32.24</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
@@ -1538,13 +1538,13 @@
         <v>9</v>
       </c>
       <c r="O10" s="14" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="P10" s="15" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
       <c r="Q10" s="15" t="n">
-        <v>6.21</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="P11" s="15" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q11" s="15" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="N12" s="14" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="O12" s="14" t="n">
-        <v>16.6</v>
+        <v>16.2</v>
       </c>
       <c r="P12" s="15" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="Q12" s="12" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="N14" s="14" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="O14" s="14" t="n">
         <v>11.8</v>
@@ -1912,7 +1912,7 @@
         <v>3</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="Q15" s="12" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="N16" s="14" t="n">
-        <v>44.3</v>
+        <v>43.1</v>
       </c>
       <c r="O16" s="12" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="P16" s="15" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="Q16" s="12" t="inlineStr">
         <is>
@@ -2061,13 +2061,13 @@
         <v>1.5</v>
       </c>
       <c r="O17" s="14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="N18" s="14" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="O18" s="14" t="n">
-        <v>56.3</v>
+        <v>59.1</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="Q18" s="12" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="P19" s="15" t="n">
-        <v>6.05</v>
+        <v>5.64</v>
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
@@ -2285,16 +2285,16 @@
         </is>
       </c>
       <c r="N20" s="14" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O20" s="14" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="P20" s="15" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q20" s="15" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
@@ -2358,16 +2358,16 @@
         </is>
       </c>
       <c r="N21" s="14" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O21" s="14" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="P21" s="15" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="Q21" s="15" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="P22" s="15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Q22" s="15" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
@@ -2508,16 +2508,16 @@
         </is>
       </c>
       <c r="N23" s="14" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="O23" s="14" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="P23" s="15" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="Q23" s="15" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="D26" s="11" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>1</v>
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="P27" s="15" t="n">
-        <v>4.66</v>
+        <v>4.64</v>
       </c>
       <c r="Q27" s="15" t="n">
-        <v>170.42</v>
+        <v>169.78</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
@@ -2885,16 +2885,16 @@
         </is>
       </c>
       <c r="N28" s="14" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="O28" s="14" t="n">
-        <v>16.9</v>
+        <v>17.2</v>
       </c>
       <c r="P28" s="15" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q28" s="15" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="N29" s="14" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="P29" s="15" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="Q29" s="15" t="n">
-        <v>34.55</v>
+        <v>34.77</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="N30" s="14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O30" s="14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="P31" s="15" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="Q31" s="15" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
@@ -3191,10 +3191,10 @@
         <v>0.9</v>
       </c>
       <c r="P32" s="15" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="Q32" s="15" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="33" ht="14" customHeight="1">
@@ -3258,16 +3258,16 @@
         </is>
       </c>
       <c r="N33" s="14" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="O33" s="14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="P33" s="15" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="Q33" s="15" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
@@ -3334,10 +3334,10 @@
         <v>4.4</v>
       </c>
       <c r="O34" s="14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="P34" s="15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Q34" s="12" t="inlineStr">
         <is>
@@ -3556,16 +3556,16 @@
         </is>
       </c>
       <c r="N37" s="14" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="O37" s="14" t="n">
-        <v>27.4</v>
+        <v>27.1</v>
       </c>
       <c r="P37" s="15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q37" s="15" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
@@ -3706,16 +3706,16 @@
         </is>
       </c>
       <c r="N39" s="14" t="n">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="O39" s="14" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="P39" s="15" t="n">
-        <v>8.23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q39" s="15" t="n">
-        <v>8.23</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="P41" s="15" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" s="12" t="inlineStr">
         <is>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="D42" s="11" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>1</v>
@@ -3931,16 +3931,16 @@
         </is>
       </c>
       <c r="N42" s="14" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="O42" s="14" t="n">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="P42" s="15" t="n">
-        <v>4.36</v>
+        <v>4.31</v>
       </c>
       <c r="Q42" s="15" t="n">
-        <v>6.11</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
@@ -4004,16 +4004,16 @@
         </is>
       </c>
       <c r="N43" s="14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O43" s="14" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="P43" s="15" t="n">
-        <v>5.45</v>
+        <v>5.32</v>
       </c>
       <c r="Q43" s="15" t="n">
-        <v>6.16</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
@@ -4077,16 +4077,16 @@
         </is>
       </c>
       <c r="N44" s="14" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="O44" s="14" t="n">
-        <v>29.5</v>
+        <v>28.5</v>
       </c>
       <c r="P44" s="15" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="Q44" s="15" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
@@ -4153,13 +4153,13 @@
         <v>10.8</v>
       </c>
       <c r="O45" s="14" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="P45" s="15" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="Q45" s="15" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="P46" s="15" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="Q46" s="12" t="inlineStr">
         <is>
@@ -4303,13 +4303,13 @@
         <v>8.300000000000001</v>
       </c>
       <c r="O47" s="14" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="P47" s="15" t="n">
         <v>0.45</v>
       </c>
       <c r="Q47" s="15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1">
@@ -4373,16 +4373,16 @@
         </is>
       </c>
       <c r="N48" s="14" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="O48" s="14" t="n">
-        <v>35.6</v>
+        <v>34.7</v>
       </c>
       <c r="P48" s="15" t="n">
-        <v>4.58</v>
+        <v>4.47</v>
       </c>
       <c r="Q48" s="15" t="n">
-        <v>4.58</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="P49" s="15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q49" s="15" t="n">
         <v>2.11</v>
-      </c>
-      <c r="Q49" s="15" t="n">
-        <v>2.17</v>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
@@ -4526,10 +4526,10 @@
         <v>14.2</v>
       </c>
       <c r="O50" s="14" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="P50" s="15" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="Q50" s="12" t="inlineStr">
         <is>
@@ -4598,16 +4598,16 @@
         </is>
       </c>
       <c r="N51" s="14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O51" s="14" t="n">
-        <v>102.7</v>
+        <v>105.1</v>
       </c>
       <c r="P51" s="15" t="n">
-        <v>3.22</v>
+        <v>3.29</v>
       </c>
       <c r="Q51" s="15" t="n">
-        <v>167.02</v>
+        <v>170.85</v>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="D52" s="11" t="n">
-        <v>21.9</v>
+        <v>20.4</v>
       </c>
       <c r="E52" s="11" t="n">
         <v>4.6</v>
@@ -4671,16 +4671,16 @@
         </is>
       </c>
       <c r="N52" s="14" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="O52" s="14" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="P52" s="15" t="n">
-        <v>3.39</v>
+        <v>3.06</v>
       </c>
       <c r="Q52" s="15" t="n">
-        <v>3.39</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="P53" s="15" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Q53" s="15" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="P54" s="15" t="n">
-        <v>9.34</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="Q54" s="15" t="n">
-        <v>18.22</v>
+        <v>18.74</v>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="N55" s="14" t="n">
-        <v>20.2</v>
+        <v>20.7</v>
       </c>
       <c r="O55" s="12" t="inlineStr">
         <is>
@@ -5050,16 +5050,16 @@
         </is>
       </c>
       <c r="N57" s="14" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="O57" s="14" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="P57" s="15" t="n">
         <v>3.77</v>
       </c>
       <c r="Q57" s="15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
@@ -5123,16 +5123,16 @@
         </is>
       </c>
       <c r="N58" s="14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O58" s="14" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="P58" s="15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q58" s="15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="O59" s="14" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P59" s="15" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Q59" s="12" t="inlineStr">
         <is>
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="P60" s="15" t="n">
-        <v>15.93</v>
+        <v>14.72</v>
       </c>
       <c r="Q60" s="15" t="n">
-        <v>15.93</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
@@ -5429,10 +5429,10 @@
         <v>25.1</v>
       </c>
       <c r="P62" s="15" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="Q62" s="15" t="n">
-        <v>15.23</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
@@ -5582,7 +5582,7 @@
         <v>0.71</v>
       </c>
       <c r="Q64" s="15" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
@@ -5654,10 +5654,10 @@
         </is>
       </c>
       <c r="P65" s="15" t="n">
-        <v>11.38</v>
+        <v>10.82</v>
       </c>
       <c r="Q65" s="15" t="n">
-        <v>11.38</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
@@ -5796,13 +5796,13 @@
         </is>
       </c>
       <c r="N67" s="14" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="O67" s="14" t="n">
-        <v>45.5</v>
+        <v>46.3</v>
       </c>
       <c r="P67" s="15" t="n">
-        <v>52.3</v>
+        <v>53.17</v>
       </c>
       <c r="Q67" s="12" t="inlineStr">
         <is>
@@ -5871,16 +5871,16 @@
         </is>
       </c>
       <c r="N68" s="14" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="O68" s="14" t="n">
-        <v>53</v>
+        <v>53.3</v>
       </c>
       <c r="P68" s="15" t="n">
-        <v>6.44</v>
+        <v>6.47</v>
       </c>
       <c r="Q68" s="15" t="n">
-        <v>6.59</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
@@ -5944,16 +5944,16 @@
         </is>
       </c>
       <c r="N69" s="14" t="n">
-        <v>135</v>
+        <v>134.4</v>
       </c>
       <c r="O69" s="14" t="n">
-        <v>99.90000000000001</v>
+        <v>102</v>
       </c>
       <c r="P69" s="15" t="n">
-        <v>20.63</v>
+        <v>21.07</v>
       </c>
       <c r="Q69" s="15" t="n">
-        <v>68.36</v>
+        <v>69.81</v>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
@@ -6027,10 +6027,10 @@
         </is>
       </c>
       <c r="P70" s="15" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="Q70" s="15" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
@@ -6113,7 +6113,7 @@
     <row r="72" ht="14" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>FRPH</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -6123,14 +6123,14 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>FRP Holdings, Inc.</t>
+          <t>United Microelectronics Corporation</t>
         </is>
       </c>
       <c r="D72" s="11" t="n">
         <v>6</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="F72" s="12" t="n">
         <v>1</v>
@@ -6142,20 +6142,22 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>John Baker</t>
-        </is>
-      </c>
-      <c r="I72" s="13" t="n">
-        <v>349924</v>
+          <t>Jason Wang</t>
+        </is>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J72" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K72" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-18 (Purchase)</t>
+      <c r="K72" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L72" s="10" t="inlineStr">
@@ -6165,26 +6167,26 @@
       </c>
       <c r="M72" s="10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N72" s="14" t="n">
-        <v>40.6</v>
+        <v>12</v>
       </c>
       <c r="O72" s="14" t="n">
-        <v>4000.5</v>
+        <v>23</v>
       </c>
       <c r="P72" s="15" t="n">
-        <v>0.9399999999999999</v>
+        <v>4.33</v>
       </c>
       <c r="Q72" s="15" t="n">
-        <v>0.96</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>FRPH</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -6194,14 +6196,14 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Guardant Health, Inc.</t>
+          <t>FRP Holdings, Inc.</t>
         </is>
       </c>
       <c r="D73" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>9.4</v>
+        <v>2.2</v>
       </c>
       <c r="F73" s="12" t="n">
         <v>1</v>
@@ -6213,59 +6215,49 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>Aaref Hilaly</t>
-        </is>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>John Baker</t>
+        </is>
+      </c>
+      <c r="I73" s="13" t="n">
+        <v>349924</v>
       </c>
       <c r="J73" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K73" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-18 (Purchase)</t>
         </is>
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="M73" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="N73" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="O73" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="P73" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
-      </c>
-      <c r="Q73" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="N73" s="14" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="O73" s="14" t="n">
+        <v>3987.7</v>
+      </c>
+      <c r="P73" s="15" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="Q73" s="15" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -6275,14 +6267,14 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>MP Materials Corp.</t>
+          <t>Guardant Health, Inc.</t>
         </is>
       </c>
       <c r="D74" s="11" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>3.9</v>
+        <v>9.4</v>
       </c>
       <c r="F74" s="12" t="n">
         <v>1</v>
@@ -6294,7 +6286,7 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>Randall Weisenburger</t>
+          <t>Aaref Hilaly</t>
         </is>
       </c>
       <c r="I74" s="13" t="inlineStr">
@@ -6314,33 +6306,39 @@
       </c>
       <c r="L74" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="M74" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-      <c r="N74" s="14" t="n">
-        <v>150.4</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N74" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
       </c>
       <c r="O74" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P74" s="15" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="Q74" s="15" t="n">
-        <v>4.46</v>
+      <c r="P74" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+      <c r="Q74" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>BSRR</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -6350,14 +6348,14 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Sierra Bancorp</t>
+          <t>MP Materials Corp.</t>
         </is>
       </c>
       <c r="D75" s="11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
       <c r="F75" s="12" t="n">
         <v>1</v>
@@ -6369,7 +6367,7 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>Laurence Dutto</t>
+          <t>Randall Weisenburger</t>
         </is>
       </c>
       <c r="I75" s="13" t="inlineStr">
@@ -6389,31 +6387,33 @@
       </c>
       <c r="L75" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="M75" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N75" s="14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="O75" s="14" t="n">
-        <v>11.6</v>
+        <v>149.2</v>
+      </c>
+      <c r="O75" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="P75" s="15" t="n">
-        <v>1.41</v>
+        <v>4.44</v>
       </c>
       <c r="Q75" s="15" t="n">
-        <v>1.52</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>BSRR</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -6423,14 +6423,14 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Sierra Bancorp</t>
         </is>
       </c>
       <c r="D76" s="11" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="F76" s="12" t="n">
         <v>1</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>Anelise Lara</t>
+          <t>Laurence Dutto</t>
         </is>
       </c>
       <c r="I76" s="13" t="inlineStr">
@@ -6462,31 +6462,31 @@
       </c>
       <c r="L76" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="M76" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N76" s="14" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="O76" s="14" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="P76" s="15" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="Q76" s="15" t="n">
-        <v>2.16</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -6496,39 +6496,41 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Commercial Metals Company</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="D77" s="11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="F77" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>2014</t>
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>John McPherson</t>
-        </is>
-      </c>
-      <c r="I77" s="13" t="n">
-        <v>99969</v>
+          <t>Anelise Lara</t>
+        </is>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J77" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K77" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-13 (Purchase)</t>
+      <c r="K77" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L77" s="10" t="inlineStr">
@@ -6538,26 +6540,26 @@
       </c>
       <c r="M77" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N77" s="14" t="n">
-        <v>8.699999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="O77" s="14" t="n">
-        <v>12.1</v>
+        <v>11.5</v>
       </c>
       <c r="P77" s="15" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q77" s="15" t="n">
-        <v>3.72</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>HTO</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -6567,41 +6569,39 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>H2O America</t>
+          <t>Commercial Metals Company</t>
         </is>
       </c>
       <c r="D78" s="11" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="F78" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G78" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>2014</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>Gregory Landis</t>
-        </is>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>John McPherson</t>
+        </is>
+      </c>
+      <c r="I78" s="13" t="n">
+        <v>99969</v>
       </c>
       <c r="J78" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K78" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-13 (Purchase)</t>
         </is>
       </c>
       <c r="L78" s="10" t="inlineStr">
@@ -6611,26 +6611,26 @@
       </c>
       <c r="M78" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N78" s="14" t="n">
-        <v>14</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O78" s="14" t="n">
-        <v>21.8</v>
+        <v>12.1</v>
       </c>
       <c r="P78" s="15" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="Q78" s="15" t="n">
-        <v>2.07</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="79" ht="14" customHeight="1">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>RELX</t>
+          <t>HTO</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
@@ -6640,14 +6640,14 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>RELX Plc</t>
+          <t>H2O America</t>
         </is>
       </c>
       <c r="D79" s="11" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="F79" s="12" t="n">
         <v>1</v>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>Suzanne Wood</t>
+          <t>Gregory Landis</t>
         </is>
       </c>
       <c r="I79" s="13" t="inlineStr">
@@ -6682,30 +6682,28 @@
           <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
-      <c r="M79" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M79" s="10" t="inlineStr">
+        <is>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N79" s="14" t="n">
-        <v>12.9</v>
+        <v>14</v>
       </c>
       <c r="O79" s="14" t="n">
-        <v>19.8</v>
+        <v>21.8</v>
       </c>
       <c r="P79" s="15" t="n">
-        <v>35.98</v>
-      </c>
-      <c r="Q79" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>1.35</v>
+      </c>
+      <c r="Q79" s="15" t="n">
+        <v>2.07</v>
       </c>
     </row>
     <row r="80" ht="14" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>RELX</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
@@ -6715,26 +6713,26 @@
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy plc</t>
+          <t>RELX Plc</t>
         </is>
       </c>
       <c r="D80" s="11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="F80" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G80" s="10" t="inlineStr">
-        <is>
-          <t>2018</t>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>Alan Ferguson</t>
+          <t>Suzanne Wood</t>
         </is>
       </c>
       <c r="I80" s="13" t="inlineStr">
@@ -6757,28 +6755,30 @@
           <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
-      <c r="M80" s="10" t="inlineStr">
-        <is>
-          <t>Energy</t>
+      <c r="M80" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N80" s="14" t="n">
-        <v>1.5</v>
+        <v>13</v>
       </c>
       <c r="O80" s="14" t="n">
-        <v>20.9</v>
+        <v>19.9</v>
       </c>
       <c r="P80" s="15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Q80" s="15" t="n">
-        <v>6.74</v>
+        <v>36.24</v>
+      </c>
+      <c r="Q80" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="81" ht="14" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
@@ -6788,26 +6788,26 @@
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Harbour Energy plc</t>
         </is>
       </c>
       <c r="D81" s="11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F81" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G81" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>2018</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>Massimo Belcredi</t>
+          <t>Alan Ferguson</t>
         </is>
       </c>
       <c r="I81" s="13" t="inlineStr">
@@ -6830,28 +6830,28 @@
           <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
-      <c r="M81" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M81" s="10" t="inlineStr">
+        <is>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N81" s="14" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="O81" s="14" t="n">
-        <v>13.5</v>
+        <v>21.5</v>
       </c>
       <c r="P81" s="15" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="Q81" s="15" t="n">
-        <v>1.38</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="82" ht="14" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -6861,26 +6861,26 @@
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group Ltd</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="D82" s="11" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="F82" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G82" s="10" t="inlineStr">
-        <is>
-          <t>2022</t>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Massimo Belcredi</t>
         </is>
       </c>
       <c r="I82" s="13" t="inlineStr">
@@ -6909,22 +6909,22 @@
         </is>
       </c>
       <c r="N82" s="14" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="O82" s="14" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="P82" s="15" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="Q82" s="15" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="83" ht="14" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -6934,26 +6934,26 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Danaos Corporation</t>
+          <t>Woodside Energy Group Ltd</t>
         </is>
       </c>
       <c r="D83" s="11" t="n">
         <v>1.4</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F83" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="I83" s="13" t="inlineStr">
@@ -6973,31 +6973,31 @@
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
-        </is>
-      </c>
-      <c r="M83" s="10" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="M83" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N83" s="14" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="O83" s="14" t="n">
-        <v>5.2</v>
+        <v>13.7</v>
       </c>
       <c r="P83" s="15" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="Q83" s="15" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="84" ht="14" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -7007,26 +7007,26 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>United Microelectronics Corporation</t>
+          <t>Danaos Corporation</t>
         </is>
       </c>
       <c r="D84" s="11" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F84" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G84" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>2005</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>Jason Wang</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="I84" s="13" t="inlineStr">
@@ -7046,25 +7046,25 @@
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="M84" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N84" s="14" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="O84" s="14" t="n">
-        <v>23.9</v>
+        <v>5.2</v>
       </c>
       <c r="P84" s="15" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q84" s="15" t="n">
-        <v>4.54</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="85" ht="14" customHeight="1">
@@ -7128,16 +7128,16 @@
         </is>
       </c>
       <c r="N85" s="14" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O85" s="14" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="P85" s="15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Q85" s="15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="86" ht="14" customHeight="1">
@@ -7157,10 +7157,10 @@
         </is>
       </c>
       <c r="D86" s="11" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="F86" s="12" t="n">
         <v>1</v>
@@ -7201,16 +7201,16 @@
         </is>
       </c>
       <c r="N86" s="14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="O86" s="14" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="P86" s="15" t="n">
-        <v>4.23</v>
+        <v>4.16</v>
       </c>
       <c r="Q86" s="15" t="n">
-        <v>6.97</v>
+        <v>6.85</v>
       </c>
     </row>
   </sheetData>
@@ -7411,16 +7411,16 @@
         </is>
       </c>
       <c r="K5" s="14" t="n">
-        <v>31</v>
+        <v>31.4</v>
       </c>
       <c r="L5" s="14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="M5" s="15" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="N5" s="15" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -7471,16 +7471,16 @@
         </is>
       </c>
       <c r="K6" s="14" t="n">
-        <v>24.1</v>
+        <v>24.7</v>
       </c>
       <c r="L6" s="14" t="n">
-        <v>11.8</v>
+        <v>12.2</v>
       </c>
       <c r="M6" s="15" t="n">
-        <v>4.17</v>
+        <v>4.29</v>
       </c>
       <c r="N6" s="15" t="n">
-        <v>4.63</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="L7" s="14" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M7" s="15" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N7" s="12" t="inlineStr">
         <is>
@@ -7595,16 +7595,16 @@
         </is>
       </c>
       <c r="K8" s="14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L8" s="14" t="n">
-        <v>30.4</v>
+        <v>29.9</v>
       </c>
       <c r="M8" s="15" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="N8" s="15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
@@ -7655,13 +7655,13 @@
         </is>
       </c>
       <c r="K9" s="14" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="M9" s="15" t="n">
-        <v>16.7</v>
+        <v>16.53</v>
       </c>
       <c r="N9" s="12" t="inlineStr">
         <is>
@@ -7717,16 +7717,16 @@
         </is>
       </c>
       <c r="K10" s="14" t="n">
-        <v>24.2</v>
+        <v>23.7</v>
       </c>
       <c r="L10" s="14" t="n">
-        <v>36.3</v>
+        <v>35.4</v>
       </c>
       <c r="M10" s="15" t="n">
-        <v>11.46</v>
+        <v>11.19</v>
       </c>
       <c r="N10" s="15" t="n">
-        <v>33.03</v>
+        <v>32.24</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
@@ -7780,13 +7780,13 @@
         <v>9</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="M11" s="15" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
       <c r="N11" s="15" t="n">
-        <v>6.21</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="M12" s="15" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="N12" s="15" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
@@ -8265,16 +8265,16 @@
         </is>
       </c>
       <c r="K18" s="14" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="L18" s="14" t="n">
-        <v>22.6</v>
+        <v>22.1</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>4.53</v>
+        <v>4.44</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>4.6</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
@@ -8404,7 +8404,7 @@
         <v>12</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="M20" s="15" t="n">
         <v>0.75</v>
@@ -8465,16 +8465,16 @@
         </is>
       </c>
       <c r="K21" s="14" t="n">
-        <v>29.2</v>
+        <v>29.5</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>42.4</v>
+        <v>42.9</v>
       </c>
       <c r="M21" s="15" t="n">
-        <v>8.82</v>
+        <v>8.91</v>
       </c>
       <c r="N21" s="15" t="n">
-        <v>8.83</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -8529,16 +8529,16 @@
         </is>
       </c>
       <c r="K22" s="14" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L22" s="14" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="M22" s="15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="N22" s="15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
@@ -8596,7 +8596,7 @@
         <v>12</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="M23" s="15" t="n">
         <v>0.75</v>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="I5" s="14" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="K5" s="15" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>12</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="K6" s="15" t="n">
         <v>0.75</v>
@@ -8884,13 +8884,13 @@
         <v>17.7</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="L7" s="15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
     </row>
   </sheetData>
@@ -9218,13 +9218,13 @@
         </is>
       </c>
       <c r="I5" s="14" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J5" s="14" t="n">
-        <v>16.6</v>
+        <v>16.2</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="I7" s="14" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J7" s="14" t="n">
         <v>11.8</v>
@@ -9386,7 +9386,7 @@
         <v>3</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="I9" s="14" t="n">
-        <v>44.3</v>
+        <v>43.1</v>
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         </is>
       </c>
       <c r="K9" s="15" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
@@ -9490,27 +9490,27 @@
         </is>
       </c>
       <c r="I10" s="14" t="n">
-        <v>18.6</v>
+        <v>18.1</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>26.6</v>
+        <v>25.9</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>10.41</v>
+        <v>10.12</v>
       </c>
       <c r="L10" s="15" t="n">
-        <v>11.43</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Mark DiPaolo</t>
+          <t>Andrew Crowley</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Innoviva</t>
+          <t>Markel Group</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -9525,11 +9525,11 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>INVA</t>
+          <t>MKL</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
@@ -9542,27 +9542,27 @@
         </is>
       </c>
       <c r="I11" s="14" t="n">
-        <v>1.5</v>
+        <v>6.9</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Andrew Crowley</t>
+          <t>Mark DiPaolo</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Markel Group</t>
+          <t>Innoviva</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -9577,11 +9577,11 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>MKL</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>21.2</v>
+        <v>22.5</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
@@ -9594,16 +9594,16 @@
         </is>
       </c>
       <c r="I12" s="14" t="n">
-        <v>6.9</v>
+        <v>1.5</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>9.699999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
@@ -9646,13 +9646,13 @@
         </is>
       </c>
       <c r="I13" s="14" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="J13" s="14" t="n">
-        <v>56.3</v>
+        <v>59.1</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="K14" s="15" t="n">
-        <v>6.05</v>
+        <v>5.64</v>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
@@ -9758,16 +9758,16 @@
         </is>
       </c>
       <c r="I15" s="14" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="I16" s="14" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="K16" s="15" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
@@ -9864,16 +9864,16 @@
         </is>
       </c>
       <c r="I17" s="14" t="n">
-        <v>19.3</v>
+        <v>18.5</v>
       </c>
       <c r="J17" s="14" t="n">
-        <v>37.3</v>
+        <v>35.6</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>6.07</v>
+        <v>5.79</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>8.550000000000001</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
@@ -9916,16 +9916,16 @@
         </is>
       </c>
       <c r="I18" s="14" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
@@ -9978,10 +9978,10 @@
         </is>
       </c>
       <c r="K19" s="15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="K20" s="15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
@@ -10078,16 +10078,16 @@
         </is>
       </c>
       <c r="I21" s="14" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J21" s="14" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="K21" s="15" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="L21" s="15" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="I22" s="14" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="K22" s="15" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="L22" s="15" t="n">
-        <v>4.35</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
@@ -10344,16 +10344,16 @@
         </is>
       </c>
       <c r="I26" s="14" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K26" s="15" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L26" s="15" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
@@ -10452,7 +10452,7 @@
         </is>
       </c>
       <c r="I28" s="14" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="K28" s="15" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="L28" s="15" t="n">
-        <v>34.55</v>
+        <v>34.77</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
@@ -10506,13 +10506,13 @@
         </is>
       </c>
       <c r="I29" s="14" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="I30" s="14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
@@ -10624,10 +10624,10 @@
         </is>
       </c>
       <c r="K31" s="15" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="L31" s="15" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
@@ -10676,10 +10676,10 @@
         <v>0.9</v>
       </c>
       <c r="K32" s="15" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="L32" s="15" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="33" ht="14" customHeight="1">
@@ -10722,13 +10722,13 @@
         </is>
       </c>
       <c r="I33" s="14" t="n">
-        <v>20.2</v>
+        <v>19.6</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>29.5</v>
+        <v>28.4</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
@@ -10786,10 +10786,10 @@
         </is>
       </c>
       <c r="K34" s="15" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="L34" s="15" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
@@ -10835,10 +10835,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="14" t="n">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="K35" s="15" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>1.8</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>14.41</v>
+        <v>14.16</v>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         </is>
       </c>
       <c r="K38" s="15" t="n">
-        <v>27.93</v>
+        <v>27.92</v>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
@@ -11064,10 +11064,10 @@
         </is>
       </c>
       <c r="K39" s="15" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="L39" s="15" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
@@ -11110,27 +11110,27 @@
         </is>
       </c>
       <c r="I40" s="14" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J40" s="14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K40" s="15" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="L40" s="15" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>Tony Buffin</t>
+          <t>Richard Massey</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>DFS Furniture</t>
+          <t>Jena Acquisition II</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -11145,11 +11145,11 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>DFS.L</t>
+          <t>JENA</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
@@ -11162,29 +11162,31 @@
         </is>
       </c>
       <c r="I41" s="14" t="n">
-        <v>4.4</v>
+        <v>52</v>
       </c>
       <c r="J41" s="14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K41" s="15" t="n">
-        <v>1.23</v>
+        <v>20.6</v>
+      </c>
+      <c r="K41" s="12" t="inlineStr">
+        <is>
+          <t>SPAC</t>
+        </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>neg TBV</t>
+          <t>SPAC</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>Aris Kekedjian</t>
+          <t>Charles Leykum</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Stratasys (Printing Services (B2B</t>
+          <t>Talon Capital (SPAC</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -11199,11 +11201,11 @@
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>TLNC</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
@@ -11217,30 +11219,30 @@
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="J42" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+          <t>SPAC</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="n">
+        <v>51.8</v>
       </c>
       <c r="K42" s="15" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="L42" s="15" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
+      </c>
+      <c r="L42" s="12" t="inlineStr">
+        <is>
+          <t>SPAC</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>Charles Leykum</t>
+          <t>Tony Buffin</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Talon Capital (SPAC</t>
+          <t>DFS Furniture</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -11255,7 +11257,7 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>TLNC</t>
+          <t>DFS.L</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
@@ -11271,32 +11273,30 @@
           <t>biography names the network</t>
         </is>
       </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>SPAC</t>
-        </is>
+      <c r="I43" s="14" t="n">
+        <v>4.4</v>
       </c>
       <c r="J43" s="14" t="n">
-        <v>51.9</v>
+        <v>9.6</v>
       </c>
       <c r="K43" s="15" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>SPAC</t>
+          <t>neg TBV</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Richard Massey</t>
+          <t>Aris Kekedjian</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Jena Acquisition II</t>
+          <t>Stratasys (Printing Services (B2B</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -11311,11 +11311,11 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>JENA</t>
+          <t>SSYS</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
@@ -11327,21 +11327,21 @@
           <t>biography names the network</t>
         </is>
       </c>
-      <c r="I44" s="14" t="n">
-        <v>52</v>
-      </c>
-      <c r="J44" s="14" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>SPAC</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
-        <is>
-          <t>SPAC</t>
-        </is>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="K44" s="15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L44" s="15" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
@@ -11494,13 +11494,13 @@
         </is>
       </c>
       <c r="I47" s="14" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>16.7</v>
+        <v>16.53</v>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
@@ -11548,16 +11548,16 @@
         </is>
       </c>
       <c r="I48" s="14" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>27.4</v>
+        <v>27.1</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="L48" s="15" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
@@ -11600,16 +11600,16 @@
         </is>
       </c>
       <c r="I49" s="14" t="n">
-        <v>23.8</v>
+        <v>24.2</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="K49" s="15" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="L49" s="15" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
@@ -11764,16 +11764,16 @@
         </is>
       </c>
       <c r="I52" s="14" t="n">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="J52" s="14" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="K52" s="15" t="n">
-        <v>8.23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L52" s="15" t="n">
-        <v>8.23</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
@@ -11816,16 +11816,16 @@
         </is>
       </c>
       <c r="I53" s="14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J53" s="14" t="n">
-        <v>251.9</v>
+        <v>259</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>9.52</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="L53" s="15" t="n">
-        <v>9.52</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="K54" s="15" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="L54" s="12" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
@@ -11926,16 +11926,16 @@
         </is>
       </c>
       <c r="I55" s="14" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="J55" s="14" t="n">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="K55" s="15" t="n">
-        <v>4.36</v>
+        <v>4.31</v>
       </c>
       <c r="L55" s="15" t="n">
-        <v>6.11</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="I57" s="14" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="J57" s="14" t="n">
-        <v>31.7</v>
+        <v>32.1</v>
       </c>
       <c r="K57" s="15" t="n">
-        <v>5.43</v>
+        <v>5.49</v>
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
@@ -12084,16 +12084,16 @@
         </is>
       </c>
       <c r="I58" s="14" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="J58" s="14" t="n">
-        <v>29.5</v>
+        <v>28.5</v>
       </c>
       <c r="K58" s="15" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="L58" s="15" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
@@ -12136,16 +12136,16 @@
         </is>
       </c>
       <c r="I59" s="14" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>29.5</v>
+        <v>28.5</v>
       </c>
       <c r="K59" s="15" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="L59" s="15" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1">
@@ -12191,13 +12191,13 @@
         <v>10.8</v>
       </c>
       <c r="J60" s="14" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="K60" s="15" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L60" s="15" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
@@ -12248,7 +12248,7 @@
         </is>
       </c>
       <c r="K61" s="15" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
@@ -12422,16 +12422,16 @@
         </is>
       </c>
       <c r="I64" s="14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J64" s="14" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="L64" s="15" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
@@ -12857,7 +12857,7 @@
         <v>1.05</v>
       </c>
       <c r="L71" s="15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
@@ -12902,16 +12902,16 @@
         </is>
       </c>
       <c r="I72" s="14" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J72" s="14" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="L72" s="15" t="n">
-        <v>3.29</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="I73" s="14" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="J73" s="12" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         </is>
       </c>
       <c r="K73" s="15" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="K74" s="15" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="L74" s="15" t="n">
         <v>0.37</v>
@@ -13143,7 +13143,7 @@
         <v>0.9</v>
       </c>
       <c r="L76" s="15" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
@@ -13748,10 +13748,10 @@
         </is>
       </c>
       <c r="K86" s="15" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="L86" s="15" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="87" ht="14" customHeight="1">
@@ -14057,7 +14057,7 @@
         <v>1.85</v>
       </c>
       <c r="L91" s="15" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="92" ht="14" customHeight="1">
@@ -14350,16 +14350,16 @@
         </is>
       </c>
       <c r="I96" s="14" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="J96" s="14" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="L96" s="15" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
@@ -14524,16 +14524,16 @@
         </is>
       </c>
       <c r="I99" s="14" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="J99" s="14" t="n">
-        <v>35.6</v>
+        <v>35.9</v>
       </c>
       <c r="K99" s="15" t="n">
-        <v>32.66</v>
+        <v>32.9</v>
       </c>
       <c r="L99" s="15" t="n">
-        <v>98.7</v>
+        <v>99.41</v>
       </c>
     </row>
     <row r="100" ht="14" customHeight="1">
@@ -14896,10 +14896,10 @@
         </is>
       </c>
       <c r="K105" s="15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="L105" s="15" t="n">
         <v>1.79</v>
-      </c>
-      <c r="L105" s="15" t="n">
-        <v>1.81</v>
       </c>
     </row>
     <row r="106" ht="14" customHeight="1">
@@ -15130,7 +15130,7 @@
         </is>
       </c>
       <c r="I109" s="14" t="n">
-        <v>204.5</v>
+        <v>202.5</v>
       </c>
       <c r="J109" s="12" t="inlineStr">
         <is>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="K109" s="15" t="n">
-        <v>5.67</v>
+        <v>5.61</v>
       </c>
       <c r="L109" s="15" t="n">
-        <v>5.68</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="110" ht="14" customHeight="1">
@@ -15186,13 +15186,13 @@
         </is>
       </c>
       <c r="I110" s="14" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J110" s="14" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="L110" s="12" t="inlineStr">
         <is>
@@ -15314,10 +15314,10 @@
         </is>
       </c>
       <c r="K112" s="15" t="n">
-        <v>5.76</v>
+        <v>5.67</v>
       </c>
       <c r="L112" s="15" t="n">
-        <v>5.76</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="113" ht="14" customHeight="1">
@@ -15675,13 +15675,13 @@
         <v>17.7</v>
       </c>
       <c r="J118" s="14" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="L118" s="15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="119" ht="14" customHeight="1">
@@ -15974,7 +15974,7 @@
         </is>
       </c>
       <c r="I123" s="14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J123" s="12" t="inlineStr">
         <is>
@@ -16216,16 +16216,16 @@
         </is>
       </c>
       <c r="I127" s="14" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J127" s="14" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="K127" s="15" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="L127" s="15" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="128" ht="14" customHeight="1">
@@ -16280,7 +16280,7 @@
         </is>
       </c>
       <c r="K128" s="15" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="L128" s="12" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         </is>
       </c>
       <c r="I141" s="14" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J141" s="14" t="n">
         <v>9.6</v>
@@ -17249,13 +17249,13 @@
         <v>4.5</v>
       </c>
       <c r="J144" s="14" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="L144" s="15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="145" ht="14" customHeight="1">
@@ -17737,13 +17737,13 @@
         <v>9.9</v>
       </c>
       <c r="J152" s="14" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="L152" s="15" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="153" ht="14" customHeight="1">
@@ -17788,7 +17788,7 @@
         </is>
       </c>
       <c r="I153" s="14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J153" s="14" t="n">
         <v>10.1</v>
@@ -17797,7 +17797,7 @@
         <v>0.86</v>
       </c>
       <c r="L153" s="15" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="154" ht="14" customHeight="1">
@@ -18278,10 +18278,10 @@
         </is>
       </c>
       <c r="K161" s="15" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="L161" s="15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="162" ht="14" customHeight="1">
@@ -19070,16 +19070,16 @@
         </is>
       </c>
       <c r="I174" s="14" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="J174" s="14" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="K174" s="15" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="L174" s="15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="175" ht="14" customHeight="1">
@@ -19313,13 +19313,13 @@
         <v>17.7</v>
       </c>
       <c r="J178" s="14" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="K178" s="15" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="L178" s="15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="179" ht="14" customHeight="1">
@@ -19426,16 +19426,16 @@
         </is>
       </c>
       <c r="I180" s="14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J180" s="14" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="K180" s="15" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="L180" s="15" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="181" ht="14" customHeight="1">
@@ -19604,16 +19604,16 @@
         </is>
       </c>
       <c r="I183" s="14" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="J183" s="14" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="K183" s="15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="L183" s="15" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="184" ht="14" customHeight="1">
@@ -19724,10 +19724,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="K185" s="15" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="L185" s="15" t="n">
-        <v>5.35</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="186" ht="14" customHeight="1">
@@ -19757,7 +19757,7 @@
         </is>
       </c>
       <c r="F186" s="12" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="G186" s="10" t="inlineStr">
         <is>
@@ -19770,16 +19770,16 @@
         </is>
       </c>
       <c r="I186" s="14" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="J186" s="14" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="K186" s="15" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="L186" s="15" t="n">
-        <v>213.47</v>
+        <v>211.22</v>
       </c>
     </row>
     <row r="187" ht="14" customHeight="1">
@@ -19822,16 +19822,16 @@
         </is>
       </c>
       <c r="I187" s="14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J187" s="14" t="n">
-        <v>102.7</v>
+        <v>105.1</v>
       </c>
       <c r="K187" s="15" t="n">
-        <v>3.22</v>
+        <v>3.29</v>
       </c>
       <c r="L187" s="15" t="n">
-        <v>167.02</v>
+        <v>170.85</v>
       </c>
     </row>
     <row r="188" ht="14" customHeight="1">
@@ -19874,16 +19874,16 @@
         </is>
       </c>
       <c r="I188" s="14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J188" s="14" t="n">
-        <v>102.7</v>
+        <v>105.1</v>
       </c>
       <c r="K188" s="15" t="n">
-        <v>3.22</v>
+        <v>3.29</v>
       </c>
       <c r="L188" s="15" t="n">
-        <v>167.02</v>
+        <v>170.85</v>
       </c>
     </row>
     <row r="189" ht="14" customHeight="1">
@@ -19913,7 +19913,7 @@
         </is>
       </c>
       <c r="F189" s="12" t="n">
-        <v>21.9</v>
+        <v>20.4</v>
       </c>
       <c r="G189" s="10" t="inlineStr">
         <is>
@@ -19926,16 +19926,16 @@
         </is>
       </c>
       <c r="I189" s="14" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="J189" s="14" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="K189" s="15" t="n">
-        <v>3.39</v>
+        <v>3.06</v>
       </c>
       <c r="L189" s="15" t="n">
-        <v>3.39</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="190" ht="14" customHeight="1">
@@ -19988,10 +19988,10 @@
         </is>
       </c>
       <c r="K190" s="15" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="L190" s="15" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="191" ht="14" customHeight="1">
@@ -20034,7 +20034,7 @@
         </is>
       </c>
       <c r="I191" s="14" t="n">
-        <v>20.2</v>
+        <v>20.7</v>
       </c>
       <c r="J191" s="12" t="inlineStr">
         <is>
@@ -20146,16 +20146,16 @@
         </is>
       </c>
       <c r="I193" s="14" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J193" s="14" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="K193" s="15" t="n">
         <v>3.77</v>
       </c>
       <c r="L193" s="15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="194" ht="14" customHeight="1">
@@ -20198,16 +20198,16 @@
         </is>
       </c>
       <c r="I194" s="14" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J194" s="14" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="K194" s="15" t="n">
         <v>3.77</v>
       </c>
       <c r="L194" s="15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="195" ht="14" customHeight="1">
@@ -20250,16 +20250,16 @@
         </is>
       </c>
       <c r="I195" s="14" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J195" s="14" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="K195" s="15" t="n">
         <v>3.77</v>
       </c>
       <c r="L195" s="15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="196" ht="14" customHeight="1">
@@ -20302,16 +20302,16 @@
         </is>
       </c>
       <c r="I196" s="14" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J196" s="14" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="K196" s="15" t="n">
         <v>3.77</v>
       </c>
       <c r="L196" s="15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="197" ht="14" customHeight="1">
@@ -20354,16 +20354,16 @@
         </is>
       </c>
       <c r="I197" s="14" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J197" s="14" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="K197" s="15" t="n">
         <v>3.77</v>
       </c>
       <c r="L197" s="15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="198" ht="14" customHeight="1">
@@ -20406,16 +20406,16 @@
         </is>
       </c>
       <c r="I198" s="14" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J198" s="14" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="K198" s="15" t="n">
         <v>3.77</v>
       </c>
       <c r="L198" s="15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="199" ht="14" customHeight="1">
@@ -20458,16 +20458,16 @@
         </is>
       </c>
       <c r="I199" s="14" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J199" s="14" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="K199" s="15" t="n">
         <v>3.77</v>
       </c>
       <c r="L199" s="15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="200" ht="14" customHeight="1">
@@ -20510,16 +20510,16 @@
         </is>
       </c>
       <c r="I200" s="14" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J200" s="14" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="K200" s="15" t="n">
         <v>3.77</v>
       </c>
       <c r="L200" s="15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="201" ht="14" customHeight="1">
@@ -20562,16 +20562,16 @@
         </is>
       </c>
       <c r="I201" s="14" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J201" s="14" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="K201" s="15" t="n">
         <v>3.77</v>
       </c>
       <c r="L201" s="15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="202" ht="14" customHeight="1">
@@ -20614,16 +20614,16 @@
         </is>
       </c>
       <c r="I202" s="14" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J202" s="14" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="K202" s="15" t="n">
         <v>3.77</v>
       </c>
       <c r="L202" s="15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="203" ht="14" customHeight="1">
@@ -20666,16 +20666,16 @@
         </is>
       </c>
       <c r="I203" s="14" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J203" s="14" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="K203" s="15" t="n">
         <v>3.77</v>
       </c>
       <c r="L203" s="15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="204" ht="14" customHeight="1">
@@ -20728,10 +20728,10 @@
         </is>
       </c>
       <c r="K204" s="15" t="n">
-        <v>15.93</v>
+        <v>14.72</v>
       </c>
       <c r="L204" s="15" t="n">
-        <v>15.93</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="205" ht="14" customHeight="1">
@@ -20774,16 +20774,16 @@
         </is>
       </c>
       <c r="I205" s="14" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="J205" s="14" t="n">
-        <v>40.4</v>
+        <v>39.8</v>
       </c>
       <c r="K205" s="15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L205" s="15" t="n">
-        <v>16.92</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="206" ht="14" customHeight="1">
@@ -20826,7 +20826,7 @@
         </is>
       </c>
       <c r="I206" s="14" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="J206" s="12" t="inlineStr">
         <is>
@@ -20834,10 +20834,10 @@
         </is>
       </c>
       <c r="K206" s="15" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="L206" s="15" t="n">
-        <v>59.92</v>
+        <v>58.99</v>
       </c>
     </row>
     <row r="207" ht="14" customHeight="1">
@@ -20883,13 +20883,13 @@
         <v>12.2</v>
       </c>
       <c r="J207" s="14" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="K207" s="15" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="L207" s="15" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="208" ht="14" customHeight="1">
@@ -20990,10 +20990,10 @@
         <v>25.1</v>
       </c>
       <c r="K209" s="15" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="L209" s="15" t="n">
-        <v>15.23</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="210" ht="14" customHeight="1">
@@ -21090,16 +21090,16 @@
         </is>
       </c>
       <c r="I211" s="14" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J211" s="14" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="K211" s="15" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="L211" s="15" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="212" ht="14" customHeight="1">
@@ -21153,7 +21153,7 @@
         <v>0.71</v>
       </c>
       <c r="L212" s="15" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="213" ht="14" customHeight="1">
@@ -21206,10 +21206,10 @@
         </is>
       </c>
       <c r="K213" s="15" t="n">
-        <v>11.38</v>
+        <v>10.82</v>
       </c>
       <c r="L213" s="15" t="n">
-        <v>11.38</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="214" ht="14" customHeight="1">
@@ -21366,13 +21366,13 @@
         </is>
       </c>
       <c r="I216" s="14" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="J216" s="14" t="n">
-        <v>45.5</v>
+        <v>46.3</v>
       </c>
       <c r="K216" s="15" t="n">
-        <v>52.3</v>
+        <v>53.17</v>
       </c>
       <c r="L216" s="12" t="inlineStr">
         <is>
@@ -21420,16 +21420,16 @@
         </is>
       </c>
       <c r="I217" s="14" t="n">
-        <v>16.6</v>
+        <v>16.2</v>
       </c>
       <c r="J217" s="14" t="n">
-        <v>26.3</v>
+        <v>25.9</v>
       </c>
       <c r="K217" s="15" t="n">
-        <v>5.03</v>
+        <v>4.95</v>
       </c>
       <c r="L217" s="15" t="n">
-        <v>7.23</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="218" ht="14" customHeight="1">
@@ -21472,16 +21472,16 @@
         </is>
       </c>
       <c r="I218" s="14" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="J218" s="14" t="n">
-        <v>53</v>
+        <v>53.3</v>
       </c>
       <c r="K218" s="15" t="n">
-        <v>6.44</v>
+        <v>6.47</v>
       </c>
       <c r="L218" s="15" t="n">
-        <v>6.59</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="219" ht="14" customHeight="1">
@@ -21524,16 +21524,16 @@
         </is>
       </c>
       <c r="I219" s="14" t="n">
-        <v>135</v>
+        <v>134.4</v>
       </c>
       <c r="J219" s="14" t="n">
-        <v>99.90000000000001</v>
+        <v>102</v>
       </c>
       <c r="K219" s="15" t="n">
-        <v>20.63</v>
+        <v>21.07</v>
       </c>
       <c r="L219" s="15" t="n">
-        <v>68.36</v>
+        <v>69.81</v>
       </c>
     </row>
     <row r="220" ht="14" customHeight="1">
@@ -21586,21 +21586,21 @@
         </is>
       </c>
       <c r="K220" s="15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="L220" s="15" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="221" ht="14" customHeight="1">
       <c r="A221" s="10" t="inlineStr">
         <is>
-          <t>Laura Duda</t>
+          <t>Tim Cahill</t>
         </is>
       </c>
       <c r="B221" s="10" t="inlineStr">
         <is>
-          <t>The Goodyear Tire &amp; Rubber</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
@@ -21615,11 +21615,11 @@
       </c>
       <c r="E221" s="9" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="F221" s="12" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="G221" s="10" t="inlineStr">
         <is>
@@ -21632,29 +21632,29 @@
         </is>
       </c>
       <c r="I221" s="14" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="J221" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="J221" s="14" t="n">
+        <v>19.4</v>
       </c>
       <c r="K221" s="15" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="L221" s="15" t="n">
-        <v>0.7</v>
+        <v>13.86</v>
+      </c>
+      <c r="L221" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="222" ht="14" customHeight="1">
       <c r="A222" s="10" t="inlineStr">
         <is>
-          <t>Tim Cahill</t>
+          <t>Laura Duda</t>
         </is>
       </c>
       <c r="B222" s="10" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>The Goodyear Tire &amp; Rubber</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
@@ -21669,7 +21669,7 @@
       </c>
       <c r="E222" s="9" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="F222" s="12" t="n">
@@ -21686,18 +21686,18 @@
         </is>
       </c>
       <c r="I222" s="14" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="J222" s="14" t="n">
-        <v>19.6</v>
+        <v>34</v>
+      </c>
+      <c r="J222" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="K222" s="15" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="L222" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>0.52</v>
+      </c>
+      <c r="L222" s="15" t="n">
+        <v>0.68</v>
       </c>
     </row>
     <row r="223" ht="14" customHeight="1">
@@ -21743,24 +21743,24 @@
         <v>6.2</v>
       </c>
       <c r="J223" s="14" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="K223" s="15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="L223" s="15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="224" ht="14" customHeight="1">
       <c r="A224" s="10" t="inlineStr">
         <is>
-          <t>John Baker</t>
+          <t>Chi-Tung Liu</t>
         </is>
       </c>
       <c r="B224" s="10" t="inlineStr">
         <is>
-          <t>FRP Holdings</t>
+          <t>United Microelectronics</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
@@ -21775,7 +21775,7 @@
       </c>
       <c r="E224" s="9" t="inlineStr">
         <is>
-          <t>FRPH</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="F224" s="12" t="n">
@@ -21792,27 +21792,27 @@
         </is>
       </c>
       <c r="I224" s="14" t="n">
-        <v>40.6</v>
+        <v>12</v>
       </c>
       <c r="J224" s="14" t="n">
-        <v>4000.5</v>
+        <v>23</v>
       </c>
       <c r="K224" s="15" t="n">
-        <v>0.9399999999999999</v>
+        <v>4.33</v>
       </c>
       <c r="L224" s="15" t="n">
-        <v>0.96</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="225" ht="14" customHeight="1">
       <c r="A225" s="10" t="inlineStr">
         <is>
-          <t>Schroeder Norman</t>
+          <t>Jason Wang</t>
         </is>
       </c>
       <c r="B225" s="10" t="inlineStr">
         <is>
-          <t>Simpple (Automation/Workflow Software</t>
+          <t>United Microelectronics</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
@@ -21827,11 +21827,11 @@
       </c>
       <c r="E225" s="9" t="inlineStr">
         <is>
-          <t>SPPL</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="F225" s="12" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="G225" s="10" t="inlineStr">
         <is>
@@ -21843,32 +21843,28 @@
           <t>matched another way, usually an employer-name collision: not signal</t>
         </is>
       </c>
-      <c r="I225" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="J225" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+      <c r="I225" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="J225" s="14" t="n">
+        <v>23</v>
       </c>
       <c r="K225" s="15" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="L225" s="15" t="n">
-        <v>103.28</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="226" ht="14" customHeight="1">
       <c r="A226" s="10" t="inlineStr">
         <is>
-          <t>Randall Weisenburger</t>
+          <t>John Baker</t>
         </is>
       </c>
       <c r="B226" s="10" t="inlineStr">
         <is>
-          <t>MP Materials</t>
+          <t>FRP Holdings</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
@@ -21883,11 +21879,11 @@
       </c>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>FRPH</t>
         </is>
       </c>
       <c r="F226" s="12" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="G226" s="10" t="inlineStr">
         <is>
@@ -21900,29 +21896,27 @@
         </is>
       </c>
       <c r="I226" s="14" t="n">
-        <v>150.4</v>
-      </c>
-      <c r="J226" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>40.5</v>
+      </c>
+      <c r="J226" s="14" t="n">
+        <v>3987.7</v>
       </c>
       <c r="K226" s="15" t="n">
-        <v>4.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L226" s="15" t="n">
-        <v>4.46</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="227" ht="14" customHeight="1">
       <c r="A227" s="10" t="inlineStr">
         <is>
-          <t>Chris Siu</t>
+          <t>Schroeder Norman</t>
         </is>
       </c>
       <c r="B227" s="10" t="inlineStr">
         <is>
-          <t>Aehr Test Systems</t>
+          <t>Simpple (Automation/Workflow Software</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
@@ -21937,11 +21931,11 @@
       </c>
       <c r="E227" s="9" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>SPPL</t>
         </is>
       </c>
       <c r="F227" s="12" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="G227" s="10" t="inlineStr">
         <is>
@@ -21964,21 +21958,21 @@
         </is>
       </c>
       <c r="K227" s="15" t="n">
-        <v>13.03</v>
+        <v>4.47</v>
       </c>
       <c r="L227" s="15" t="n">
-        <v>14.35</v>
+        <v>97.22</v>
       </c>
     </row>
     <row r="228" ht="14" customHeight="1">
       <c r="A228" s="10" t="inlineStr">
         <is>
-          <t>Anelise Lara</t>
+          <t>Randall Weisenburger</t>
         </is>
       </c>
       <c r="B228" s="10" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>MP Materials</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
@@ -21993,11 +21987,11 @@
       </c>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="F228" s="12" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="G228" s="10" t="inlineStr">
         <is>
@@ -22010,27 +22004,29 @@
         </is>
       </c>
       <c r="I228" s="14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J228" s="14" t="n">
-        <v>11.3</v>
+        <v>149.2</v>
+      </c>
+      <c r="J228" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="K228" s="15" t="n">
-        <v>1.57</v>
+        <v>4.44</v>
       </c>
       <c r="L228" s="15" t="n">
-        <v>2.16</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="229" ht="14" customHeight="1">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>John McPherson</t>
+          <t>Chris Siu</t>
         </is>
       </c>
       <c r="B229" s="10" t="inlineStr">
         <is>
-          <t>Commercial Metals</t>
+          <t>Aehr Test Systems</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
@@ -22045,11 +22041,11 @@
       </c>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="F229" s="12" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="G229" s="10" t="inlineStr">
         <is>
@@ -22061,28 +22057,32 @@
           <t>matched another way, usually an employer-name collision: not signal</t>
         </is>
       </c>
-      <c r="I229" s="14" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J229" s="14" t="n">
-        <v>12.1</v>
+      <c r="I229" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="J229" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="K229" s="15" t="n">
-        <v>1.58</v>
+        <v>13.35</v>
       </c>
       <c r="L229" s="15" t="n">
-        <v>3.72</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="230" ht="14" customHeight="1">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>Phillip Kardis</t>
+          <t>Anelise Lara</t>
         </is>
       </c>
       <c r="B230" s="10" t="inlineStr">
         <is>
-          <t>Chimera Investment</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
@@ -22092,16 +22092,16 @@
       </c>
       <c r="D230" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>CIM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="F230" s="12" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G230" s="10" t="inlineStr">
         <is>
@@ -22114,29 +22114,27 @@
         </is>
       </c>
       <c r="I230" s="14" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="J230" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>5.2</v>
+      </c>
+      <c r="J230" s="14" t="n">
+        <v>11.5</v>
       </c>
       <c r="K230" s="15" t="n">
-        <v>0.38</v>
+        <v>1.6</v>
       </c>
       <c r="L230" s="15" t="n">
-        <v>0.38</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="231" ht="14" customHeight="1">
       <c r="A231" s="10" t="inlineStr">
         <is>
-          <t>Subramaniam Viswanathan</t>
+          <t>John McPherson</t>
         </is>
       </c>
       <c r="B231" s="10" t="inlineStr">
         <is>
-          <t>Chimera Investment</t>
+          <t>Commercial Metals</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
@@ -22146,16 +22144,16 @@
       </c>
       <c r="D231" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>CIM</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="F231" s="12" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="G231" s="10" t="inlineStr">
         <is>
@@ -22168,29 +22166,27 @@
         </is>
       </c>
       <c r="I231" s="14" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="J231" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J231" s="14" t="n">
+        <v>12.1</v>
       </c>
       <c r="K231" s="15" t="n">
-        <v>0.38</v>
+        <v>1.58</v>
       </c>
       <c r="L231" s="15" t="n">
-        <v>0.38</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="232" ht="14" customHeight="1">
       <c r="A232" s="10" t="inlineStr">
         <is>
-          <t>Gregory Landis</t>
+          <t>Phillip Kardis</t>
         </is>
       </c>
       <c r="B232" s="10" t="inlineStr">
         <is>
-          <t>H2O America</t>
+          <t>Chimera Investment</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
@@ -22200,12 +22196,12 @@
       </c>
       <c r="D232" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>HTO</t>
+          <t>CIM</t>
         </is>
       </c>
       <c r="F232" s="12" t="n">
@@ -22222,27 +22218,29 @@
         </is>
       </c>
       <c r="I232" s="14" t="n">
-        <v>14</v>
-      </c>
-      <c r="J232" s="14" t="n">
-        <v>21.8</v>
+        <v>82.09999999999999</v>
+      </c>
+      <c r="J232" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="K232" s="15" t="n">
-        <v>1.35</v>
+        <v>0.37</v>
       </c>
       <c r="L232" s="15" t="n">
-        <v>2.07</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="233" ht="14" customHeight="1">
       <c r="A233" s="10" t="inlineStr">
         <is>
-          <t>Suzanne Wood</t>
+          <t>Subramaniam Viswanathan</t>
         </is>
       </c>
       <c r="B233" s="10" t="inlineStr">
         <is>
-          <t>RELX (Information Technology</t>
+          <t>Chimera Investment</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
@@ -22252,16 +22250,16 @@
       </c>
       <c r="D233" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>RELX</t>
+          <t>CIM</t>
         </is>
       </c>
       <c r="F233" s="12" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="G233" s="10" t="inlineStr">
         <is>
@@ -22274,29 +22272,29 @@
         </is>
       </c>
       <c r="I233" s="14" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J233" s="14" t="n">
-        <v>19.8</v>
+        <v>82.09999999999999</v>
+      </c>
+      <c r="J233" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="K233" s="15" t="n">
-        <v>35.98</v>
-      </c>
-      <c r="L233" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>0.37</v>
+      </c>
+      <c r="L233" s="15" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="234" ht="14" customHeight="1">
       <c r="A234" s="10" t="inlineStr">
         <is>
-          <t>Alan Ferguson</t>
+          <t>Gregory Landis</t>
         </is>
       </c>
       <c r="B234" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>H2O America</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
@@ -22311,11 +22309,11 @@
       </c>
       <c r="E234" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>HTO</t>
         </is>
       </c>
       <c r="F234" s="12" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G234" s="10" t="inlineStr">
         <is>
@@ -22328,27 +22326,27 @@
         </is>
       </c>
       <c r="I234" s="14" t="n">
-        <v>1.5</v>
+        <v>14</v>
       </c>
       <c r="J234" s="14" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="K234" s="15" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="L234" s="15" t="n">
-        <v>6.74</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="235" ht="14" customHeight="1">
       <c r="A235" s="10" t="inlineStr">
         <is>
-          <t>Alexander Krane</t>
+          <t>Suzanne Wood</t>
         </is>
       </c>
       <c r="B235" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>RELX (Information Technology</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
@@ -22363,11 +22361,11 @@
       </c>
       <c r="E235" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>RELX</t>
         </is>
       </c>
       <c r="F235" s="12" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="G235" s="10" t="inlineStr">
         <is>
@@ -22380,22 +22378,24 @@
         </is>
       </c>
       <c r="I235" s="14" t="n">
-        <v>1.5</v>
+        <v>13</v>
       </c>
       <c r="J235" s="14" t="n">
-        <v>20.9</v>
+        <v>19.9</v>
       </c>
       <c r="K235" s="15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="L235" s="15" t="n">
-        <v>6.74</v>
+        <v>36.24</v>
+      </c>
+      <c r="L235" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="236" ht="14" customHeight="1">
       <c r="A236" s="10" t="inlineStr">
         <is>
-          <t>Andrea Pinarel</t>
+          <t>Alan Ferguson</t>
         </is>
       </c>
       <c r="B236" s="10" t="inlineStr">
@@ -22435,19 +22435,19 @@
         <v>1.5</v>
       </c>
       <c r="J236" s="14" t="n">
-        <v>20.9</v>
+        <v>21.5</v>
       </c>
       <c r="K236" s="15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="L236" s="15" t="n">
-        <v>6.74</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="237" ht="14" customHeight="1">
       <c r="A237" s="10" t="inlineStr">
         <is>
-          <t>David Kennedy</t>
+          <t>Alexander Krane</t>
         </is>
       </c>
       <c r="B237" s="10" t="inlineStr">
@@ -22487,19 +22487,19 @@
         <v>1.5</v>
       </c>
       <c r="J237" s="14" t="n">
-        <v>20.9</v>
+        <v>21.5</v>
       </c>
       <c r="K237" s="15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="L237" s="15" t="n">
-        <v>6.74</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="238" ht="14" customHeight="1">
       <c r="A238" s="10" t="inlineStr">
         <is>
-          <t>Feyyaz Etiz</t>
+          <t>Andrea Pinarel</t>
         </is>
       </c>
       <c r="B238" s="10" t="inlineStr">
@@ -22539,19 +22539,19 @@
         <v>1.5</v>
       </c>
       <c r="J238" s="14" t="n">
-        <v>20.9</v>
+        <v>21.5</v>
       </c>
       <c r="K238" s="15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="L238" s="15" t="n">
-        <v>6.74</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="239" ht="14" customHeight="1">
       <c r="A239" s="10" t="inlineStr">
         <is>
-          <t>Gustavo Baquero</t>
+          <t>David Kennedy</t>
         </is>
       </c>
       <c r="B239" s="10" t="inlineStr">
@@ -22591,19 +22591,19 @@
         <v>1.5</v>
       </c>
       <c r="J239" s="14" t="n">
-        <v>20.9</v>
+        <v>21.5</v>
       </c>
       <c r="K239" s="15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="L239" s="15" t="n">
-        <v>6.74</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="240" ht="14" customHeight="1">
       <c r="A240" s="10" t="inlineStr">
         <is>
-          <t>Linda Cook</t>
+          <t>Feyyaz Etiz</t>
         </is>
       </c>
       <c r="B240" s="10" t="inlineStr">
@@ -22643,19 +22643,19 @@
         <v>1.5</v>
       </c>
       <c r="J240" s="14" t="n">
-        <v>20.9</v>
+        <v>21.5</v>
       </c>
       <c r="K240" s="15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="L240" s="15" t="n">
-        <v>6.74</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="241" ht="14" customHeight="1">
       <c r="A241" s="10" t="inlineStr">
         <is>
-          <t>Michael Tuffin</t>
+          <t>Gustavo Baquero</t>
         </is>
       </c>
       <c r="B241" s="10" t="inlineStr">
@@ -22695,19 +22695,19 @@
         <v>1.5</v>
       </c>
       <c r="J241" s="14" t="n">
-        <v>20.9</v>
+        <v>21.5</v>
       </c>
       <c r="K241" s="15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="L241" s="15" t="n">
-        <v>6.74</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="242" ht="14" customHeight="1">
       <c r="A242" s="10" t="inlineStr">
         <is>
-          <t>Nathan Mauzy</t>
+          <t>Linda Cook</t>
         </is>
       </c>
       <c r="B242" s="10" t="inlineStr">
@@ -22747,24 +22747,24 @@
         <v>1.5</v>
       </c>
       <c r="J242" s="14" t="n">
-        <v>20.9</v>
+        <v>21.5</v>
       </c>
       <c r="K242" s="15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="L242" s="15" t="n">
-        <v>6.74</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="243" ht="14" customHeight="1">
       <c r="A243" s="10" t="inlineStr">
         <is>
-          <t>Massimo Belcredi</t>
+          <t>Michael Tuffin</t>
         </is>
       </c>
       <c r="B243" s="10" t="inlineStr">
         <is>
-          <t>Eni</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
@@ -22779,11 +22779,11 @@
       </c>
       <c r="E243" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F243" s="12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G243" s="10" t="inlineStr">
         <is>
@@ -22796,27 +22796,27 @@
         </is>
       </c>
       <c r="I243" s="14" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J243" s="14" t="n">
-        <v>13.5</v>
+        <v>21.5</v>
       </c>
       <c r="K243" s="15" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="L243" s="15" t="n">
-        <v>1.38</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="244" ht="14" customHeight="1">
       <c r="A244" s="10" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Nathan Mauzy</t>
         </is>
       </c>
       <c r="B244" s="10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C244" s="10" t="inlineStr">
@@ -22831,11 +22831,11 @@
       </c>
       <c r="E244" s="9" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F244" s="12" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="G244" s="10" t="inlineStr">
         <is>
@@ -22848,27 +22848,27 @@
         </is>
       </c>
       <c r="I244" s="14" t="n">
-        <v>5.7</v>
+        <v>1.5</v>
       </c>
       <c r="J244" s="14" t="n">
-        <v>13.5</v>
+        <v>21.5</v>
       </c>
       <c r="K244" s="15" t="n">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="L244" s="15" t="n">
-        <v>1.3</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="245" ht="14" customHeight="1">
       <c r="A245" s="10" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>Massimo Belcredi</t>
         </is>
       </c>
       <c r="B245" s="10" t="inlineStr">
         <is>
-          <t>Danaos</t>
+          <t>Eni</t>
         </is>
       </c>
       <c r="C245" s="10" t="inlineStr">
@@ -22878,16 +22878,16 @@
       </c>
       <c r="D245" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E245" s="9" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F245" s="12" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="G245" s="10" t="inlineStr">
         <is>
@@ -22900,27 +22900,27 @@
         </is>
       </c>
       <c r="I245" s="14" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="J245" s="14" t="n">
-        <v>5.2</v>
+        <v>13.7</v>
       </c>
       <c r="K245" s="15" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.37</v>
       </c>
       <c r="L245" s="15" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="246" ht="14" customHeight="1">
       <c r="A246" s="10" t="inlineStr">
         <is>
-          <t>Chi-Tung Liu</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="B246" s="10" t="inlineStr">
         <is>
-          <t>United Microelectronics</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
@@ -22935,11 +22935,11 @@
       </c>
       <c r="E246" s="9" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="F246" s="12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G246" s="10" t="inlineStr">
         <is>
@@ -22952,27 +22952,27 @@
         </is>
       </c>
       <c r="I246" s="14" t="n">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
       <c r="J246" s="14" t="n">
-        <v>23.9</v>
+        <v>13.7</v>
       </c>
       <c r="K246" s="15" t="n">
-        <v>4.5</v>
+        <v>1.17</v>
       </c>
       <c r="L246" s="15" t="n">
-        <v>4.54</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="247" ht="14" customHeight="1">
       <c r="A247" s="10" t="inlineStr">
         <is>
-          <t>Jason Wang</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="B247" s="10" t="inlineStr">
         <is>
-          <t>United Microelectronics</t>
+          <t>Danaos</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
@@ -22982,16 +22982,16 @@
       </c>
       <c r="D247" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F247" s="12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G247" s="10" t="inlineStr">
         <is>
@@ -23004,16 +23004,16 @@
         </is>
       </c>
       <c r="I247" s="14" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="J247" s="14" t="n">
-        <v>23.9</v>
+        <v>5.2</v>
       </c>
       <c r="K247" s="15" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="L247" s="15" t="n">
-        <v>4.54</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="248" ht="14" customHeight="1">
@@ -23043,7 +23043,7 @@
         </is>
       </c>
       <c r="F248" s="12" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="G248" s="10" t="inlineStr">
         <is>
@@ -23056,16 +23056,16 @@
         </is>
       </c>
       <c r="I248" s="14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J248" s="14" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="K248" s="15" t="n">
-        <v>4.23</v>
+        <v>4.16</v>
       </c>
       <c r="L248" s="15" t="n">
-        <v>6.97</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="249" ht="14" customHeight="1">
@@ -23244,10 +23244,10 @@
         </is>
       </c>
       <c r="K251" s="15" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="L251" s="15" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="252" ht="14" customHeight="1">
@@ -23416,16 +23416,16 @@
         </is>
       </c>
       <c r="I254" s="14" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="J254" s="14" t="n">
-        <v>47.8</v>
+        <v>45.9</v>
       </c>
       <c r="K254" s="15" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="L254" s="15" t="n">
-        <v>4.07</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="255" ht="14" customHeight="1">
@@ -24650,10 +24650,10 @@
         </is>
       </c>
       <c r="K274" s="15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="L274" s="15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="275" ht="14" customHeight="1">
@@ -24760,10 +24760,10 @@
         </is>
       </c>
       <c r="I276" s="14" t="n">
-        <v>117.6</v>
+        <v>117.7</v>
       </c>
       <c r="J276" s="14" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K276" s="15" t="n">
         <v>0.22</v>
@@ -24814,16 +24814,16 @@
         </is>
       </c>
       <c r="I277" s="14" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="J277" s="14" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="K277" s="15" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="L277" s="15" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="278" ht="14" customHeight="1">
@@ -25188,7 +25188,7 @@
         </is>
       </c>
       <c r="K283" s="15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="L283" s="12" t="inlineStr">
         <is>
@@ -25238,16 +25238,16 @@
         </is>
       </c>
       <c r="I284" s="14" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J284" s="14" t="n">
-        <v>15.1</v>
+        <v>15.4</v>
       </c>
       <c r="K284" s="15" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="L284" s="15" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="285" ht="14" customHeight="1">
@@ -25550,10 +25550,10 @@
         </is>
       </c>
       <c r="K289" s="15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="L289" s="15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="290" ht="14" customHeight="1">
@@ -25608,10 +25608,10 @@
         </is>
       </c>
       <c r="K290" s="15" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="L290" s="15" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="291" ht="14" customHeight="1">
@@ -25661,13 +25661,13 @@
         </is>
       </c>
       <c r="J291" s="14" t="n">
-        <v>49.1</v>
+        <v>48.1</v>
       </c>
       <c r="K291" s="15" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="L291" s="15" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="292" ht="14" customHeight="1">
@@ -25774,16 +25774,16 @@
         </is>
       </c>
       <c r="I293" s="14" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="J293" s="14" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="K293" s="15" t="n">
-        <v>4.81</v>
+        <v>4.79</v>
       </c>
       <c r="L293" s="15" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294" ht="14" customHeight="1">
@@ -25828,16 +25828,16 @@
         </is>
       </c>
       <c r="I294" s="14" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="J294" s="14" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="K294" s="15" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="L294" s="15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="295" ht="14" customHeight="1">
@@ -25954,10 +25954,10 @@
         </is>
       </c>
       <c r="K296" s="15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="L296" s="15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="297" ht="14" customHeight="1">
@@ -26184,16 +26184,16 @@
         </is>
       </c>
       <c r="I300" s="14" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J300" s="14" t="n">
-        <v>15.1</v>
+        <v>15.4</v>
       </c>
       <c r="K300" s="15" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="L300" s="15" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="301" ht="14" customHeight="1">
@@ -26243,13 +26243,13 @@
         </is>
       </c>
       <c r="J301" s="14" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="K301" s="15" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="L301" s="15" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="302" ht="14" customHeight="1">
@@ -26354,16 +26354,16 @@
         </is>
       </c>
       <c r="I303" s="14" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="J303" s="14" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="K303" s="15" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="L303" s="15" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="304" ht="14" customHeight="1">
@@ -26470,16 +26470,16 @@
         </is>
       </c>
       <c r="I305" s="14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J305" s="14" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="K305" s="15" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="L305" s="15" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="306" ht="14" customHeight="1">
@@ -27026,10 +27026,10 @@
         </is>
       </c>
       <c r="K314" s="15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="L314" s="15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="315" ht="14" customHeight="1">
@@ -27074,16 +27074,16 @@
         </is>
       </c>
       <c r="I315" s="14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J315" s="14" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="K315" s="15" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="L315" s="15" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="316" ht="14" customHeight="1">
@@ -27138,10 +27138,10 @@
         </is>
       </c>
       <c r="K316" s="15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="L316" s="15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="317" ht="14" customHeight="1">
@@ -27258,10 +27258,10 @@
         </is>
       </c>
       <c r="K318" s="15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="L318" s="15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="319" ht="14" customHeight="1">
@@ -27364,16 +27364,16 @@
         </is>
       </c>
       <c r="I320" s="14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J320" s="14" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="K320" s="15" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="L320" s="15" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="321" ht="14" customHeight="1">
@@ -27790,16 +27790,16 @@
         </is>
       </c>
       <c r="I327" s="14" t="n">
-        <v>12.7</v>
+        <v>12</v>
       </c>
       <c r="J327" s="14" t="n">
-        <v>22.4</v>
+        <v>21.1</v>
       </c>
       <c r="K327" s="15" t="n">
-        <v>4.45</v>
+        <v>4.19</v>
       </c>
       <c r="L327" s="15" t="n">
-        <v>4.45</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="328" ht="14" customHeight="1">
@@ -27916,10 +27916,10 @@
         </is>
       </c>
       <c r="K329" s="15" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="L329" s="15" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="330" ht="14" customHeight="1">
@@ -28150,16 +28150,16 @@
         </is>
       </c>
       <c r="I333" s="14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J333" s="14" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="K333" s="15" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="L333" s="15" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="334" ht="14" customHeight="1">
@@ -28204,16 +28204,16 @@
         </is>
       </c>
       <c r="I334" s="14" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="J334" s="14" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="K334" s="15" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="L334" s="15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="335" ht="14" customHeight="1">
@@ -28754,16 +28754,16 @@
         </is>
       </c>
       <c r="I343" s="14" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J343" s="14" t="n">
-        <v>105.6</v>
+        <v>103.5</v>
       </c>
       <c r="K343" s="15" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L343" s="15" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="344" ht="14" customHeight="1">
@@ -28870,16 +28870,16 @@
         </is>
       </c>
       <c r="I345" s="14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J345" s="14" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="K345" s="15" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="L345" s="15" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="346" ht="14" customHeight="1">
@@ -28986,16 +28986,16 @@
         </is>
       </c>
       <c r="I347" s="14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J347" s="14" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="K347" s="15" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="L347" s="15" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="348" ht="14" customHeight="1">
@@ -29164,16 +29164,16 @@
         </is>
       </c>
       <c r="I350" s="14" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="J350" s="14" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="K350" s="15" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="L350" s="15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="351" ht="14" customHeight="1">
@@ -29223,13 +29223,13 @@
         </is>
       </c>
       <c r="J351" s="14" t="n">
-        <v>49.1</v>
+        <v>48.1</v>
       </c>
       <c r="K351" s="15" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="L351" s="15" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="352" ht="14" customHeight="1">
@@ -29460,16 +29460,16 @@
         </is>
       </c>
       <c r="I355" s="14" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="J355" s="14" t="n">
-        <v>47.8</v>
+        <v>45.9</v>
       </c>
       <c r="K355" s="15" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="L355" s="15" t="n">
-        <v>4.07</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="356" ht="14" customHeight="1">
@@ -29638,7 +29638,7 @@
         </is>
       </c>
       <c r="I358" s="14" t="n">
-        <v>109.7</v>
+        <v>110.6</v>
       </c>
       <c r="J358" s="12" t="inlineStr">
         <is>
@@ -29646,10 +29646,10 @@
         </is>
       </c>
       <c r="K358" s="15" t="n">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="L358" s="15" t="n">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="359" ht="14" customHeight="1">
@@ -30614,16 +30614,16 @@
         </is>
       </c>
       <c r="I374" s="14" t="n">
-        <v>16.3</v>
+        <v>17</v>
       </c>
       <c r="J374" s="14" t="n">
-        <v>48.3</v>
+        <v>50</v>
       </c>
       <c r="K374" s="15" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="L374" s="15" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="375" ht="14" customHeight="1">
@@ -30668,16 +30668,16 @@
         </is>
       </c>
       <c r="I375" s="14" t="n">
-        <v>93.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="J375" s="14" t="n">
-        <v>85.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K375" s="15" t="n">
-        <v>12.56</v>
+        <v>12.06</v>
       </c>
       <c r="L375" s="15" t="n">
-        <v>12.62</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="376" ht="14" customHeight="1">
@@ -30908,16 +30908,16 @@
         </is>
       </c>
       <c r="I379" s="14" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="J379" s="14" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="K379" s="15" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="L379" s="15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="380" ht="14" customHeight="1">
@@ -31086,16 +31086,16 @@
         </is>
       </c>
       <c r="I382" s="14" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="J382" s="14" t="n">
-        <v>80.5</v>
+        <v>80.3</v>
       </c>
       <c r="K382" s="15" t="n">
-        <v>11.57</v>
+        <v>11.55</v>
       </c>
       <c r="L382" s="15" t="n">
-        <v>11.57</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="383" ht="14" customHeight="1">
@@ -31202,16 +31202,16 @@
         </is>
       </c>
       <c r="I384" s="14" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J384" s="14" t="n">
-        <v>105.6</v>
+        <v>103.5</v>
       </c>
       <c r="K384" s="15" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L384" s="15" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="385" ht="14" customHeight="1">
@@ -31804,16 +31804,16 @@
         </is>
       </c>
       <c r="I394" s="14" t="n">
-        <v>12.7</v>
+        <v>12</v>
       </c>
       <c r="J394" s="14" t="n">
-        <v>22.4</v>
+        <v>21.1</v>
       </c>
       <c r="K394" s="15" t="n">
-        <v>4.45</v>
+        <v>4.19</v>
       </c>
       <c r="L394" s="15" t="n">
-        <v>4.45</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="395" ht="14" customHeight="1">
@@ -31861,13 +31861,13 @@
         <v>3.1</v>
       </c>
       <c r="J395" s="14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K395" s="15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="L395" s="15" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="396" ht="14" customHeight="1">
@@ -31912,16 +31912,16 @@
         </is>
       </c>
       <c r="I396" s="14" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="J396" s="14" t="n">
-        <v>17.6</v>
+        <v>17.3</v>
       </c>
       <c r="K396" s="15" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="L396" s="15" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="397" ht="14" customHeight="1">
@@ -32400,16 +32400,16 @@
         </is>
       </c>
       <c r="I404" s="14" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="J404" s="14" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="K404" s="15" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="L404" s="15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="405" ht="14" customHeight="1">
@@ -33194,7 +33194,7 @@
         </is>
       </c>
       <c r="I417" s="14" t="n">
-        <v>109.7</v>
+        <v>110.6</v>
       </c>
       <c r="J417" s="12" t="inlineStr">
         <is>
@@ -33202,10 +33202,10 @@
         </is>
       </c>
       <c r="K417" s="15" t="n">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="L417" s="15" t="n">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="418" ht="14" customHeight="1">
@@ -33312,16 +33312,16 @@
         </is>
       </c>
       <c r="I419" s="14" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="J419" s="14" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="K419" s="15" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="L419" s="15" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="420" ht="14" customHeight="1">
@@ -33734,16 +33734,16 @@
         </is>
       </c>
       <c r="I426" s="14" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="J426" s="14" t="n">
-        <v>47.8</v>
+        <v>45.9</v>
       </c>
       <c r="K426" s="15" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="L426" s="15" t="n">
-        <v>4.07</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="427" ht="14" customHeight="1">
@@ -33904,16 +33904,16 @@
         </is>
       </c>
       <c r="I429" s="14" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="J429" s="14" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="K429" s="15" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="L429" s="15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="430" ht="14" customHeight="1">
@@ -33964,10 +33964,10 @@
         <v>6.4</v>
       </c>
       <c r="K430" s="15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="L430" s="15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="431" ht="14" customHeight="1">
@@ -34136,16 +34136,16 @@
         </is>
       </c>
       <c r="I433" s="14" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="J433" s="14" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="K433" s="15" t="n">
-        <v>4.47</v>
+        <v>4.43</v>
       </c>
       <c r="L433" s="15" t="n">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="434" ht="14" customHeight="1">
@@ -34252,16 +34252,16 @@
         </is>
       </c>
       <c r="I435" s="14" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="J435" s="14" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="K435" s="15" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="L435" s="15" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="436" ht="14" customHeight="1">
@@ -34306,16 +34306,16 @@
         </is>
       </c>
       <c r="I436" s="14" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J436" s="14" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K436" s="15" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="L436" s="15" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="437" ht="14" customHeight="1">
@@ -34363,13 +34363,13 @@
         <v>4.5</v>
       </c>
       <c r="J437" s="14" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="K437" s="15" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="L437" s="15" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="438" ht="14" customHeight="1">
@@ -34600,16 +34600,16 @@
         </is>
       </c>
       <c r="I441" s="14" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="J441" s="14" t="n">
-        <v>47.8</v>
+        <v>45.9</v>
       </c>
       <c r="K441" s="15" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="L441" s="15" t="n">
-        <v>4.07</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="442" ht="14" customHeight="1">
@@ -34716,16 +34716,16 @@
         </is>
       </c>
       <c r="I443" s="14" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="J443" s="14" t="n">
-        <v>31.7</v>
+        <v>30.9</v>
       </c>
       <c r="K443" s="15" t="n">
-        <v>3.73</v>
+        <v>3.64</v>
       </c>
       <c r="L443" s="15" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="444" ht="14" customHeight="1">
@@ -34780,10 +34780,10 @@
         </is>
       </c>
       <c r="K444" s="15" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="L444" s="15" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="445" ht="14" customHeight="1">
@@ -34838,10 +34838,10 @@
         </is>
       </c>
       <c r="K445" s="15" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="L445" s="15" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="446" ht="14" customHeight="1">
@@ -34896,10 +34896,10 @@
         </is>
       </c>
       <c r="K446" s="15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="L446" s="15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447" ht="14" customHeight="1">
@@ -35006,16 +35006,16 @@
         </is>
       </c>
       <c r="I448" s="14" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J448" s="14" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K448" s="15" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="L448" s="15" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="449" ht="14" customHeight="1">
@@ -35122,7 +35122,7 @@
         </is>
       </c>
       <c r="I450" s="14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J450" s="12" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         </is>
       </c>
       <c r="K450" s="15" t="n">
-        <v>3.71</v>
+        <v>3.59</v>
       </c>
       <c r="L450" s="12" t="inlineStr">
         <is>
@@ -35180,16 +35180,16 @@
         </is>
       </c>
       <c r="I451" s="14" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="J451" s="14" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="K451" s="15" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="L451" s="15" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="452" ht="14" customHeight="1">
@@ -35608,10 +35608,10 @@
         </is>
       </c>
       <c r="K458" s="15" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="L458" s="15" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="459" ht="14" customHeight="1">
@@ -35966,16 +35966,16 @@
         </is>
       </c>
       <c r="I464" s="14" t="n">
-        <v>12.7</v>
+        <v>12</v>
       </c>
       <c r="J464" s="14" t="n">
-        <v>22.4</v>
+        <v>21.1</v>
       </c>
       <c r="K464" s="15" t="n">
-        <v>4.45</v>
+        <v>4.19</v>
       </c>
       <c r="L464" s="15" t="n">
-        <v>4.45</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="465" ht="14" customHeight="1">
@@ -36330,16 +36330,16 @@
         </is>
       </c>
       <c r="I470" s="14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J470" s="14" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="K470" s="15" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="L470" s="15" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="471" ht="14" customHeight="1">
@@ -36394,10 +36394,10 @@
         </is>
       </c>
       <c r="K471" s="15" t="n">
-        <v>4.98</v>
+        <v>5.04</v>
       </c>
       <c r="L471" s="15" t="n">
-        <v>5.35</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="472" ht="14" customHeight="1">
@@ -36814,16 +36814,16 @@
         </is>
       </c>
       <c r="I478" s="14" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="J478" s="14" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="K478" s="15" t="n">
-        <v>4.81</v>
+        <v>4.79</v>
       </c>
       <c r="L478" s="15" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
     </row>
     <row r="479" ht="14" customHeight="1">
@@ -37188,10 +37188,10 @@
         </is>
       </c>
       <c r="K484" s="15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="L484" s="15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="485" ht="14" customHeight="1">
@@ -37427,13 +37427,13 @@
         </is>
       </c>
       <c r="J488" s="14" t="n">
-        <v>49.1</v>
+        <v>48.1</v>
       </c>
       <c r="K488" s="15" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="L488" s="15" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="489" ht="14" customHeight="1">
@@ -37488,10 +37488,10 @@
         </is>
       </c>
       <c r="K489" s="15" t="n">
-        <v>0.79</v>
+        <v>1.01</v>
       </c>
       <c r="L489" s="15" t="n">
-        <v>0.83</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="490" ht="14" customHeight="1">
@@ -37536,16 +37536,16 @@
         </is>
       </c>
       <c r="I490" s="14" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="J490" s="14" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="K490" s="15" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="L490" s="15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="491" ht="14" customHeight="1">

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -1168,16 +1168,16 @@
         </is>
       </c>
       <c r="N5" s="14" t="n">
-        <v>31.4</v>
+        <v>32.1</v>
       </c>
       <c r="O5" s="14" t="n">
         <v>8</v>
       </c>
       <c r="P5" s="15" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" s="15" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="N6" s="14" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="O6" s="14" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="P6" s="15" t="n">
-        <v>4.29</v>
+        <v>4.37</v>
       </c>
       <c r="Q6" s="15" t="n">
-        <v>4.77</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -1317,13 +1317,13 @@
         <v>9.699999999999999</v>
       </c>
       <c r="O7" s="14" t="n">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="P7" s="15" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="Q7" s="15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="N8" s="14" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="O8" s="14" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="P8" s="15" t="n">
-        <v>16.53</v>
+        <v>16.63</v>
       </c>
       <c r="Q8" s="12" t="inlineStr">
         <is>
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="N9" s="14" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="O9" s="14" t="n">
-        <v>35.4</v>
+        <v>34.9</v>
       </c>
       <c r="P9" s="15" t="n">
-        <v>11.19</v>
+        <v>11.05</v>
       </c>
       <c r="Q9" s="15" t="n">
-        <v>32.24</v>
+        <v>31.83</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
@@ -1535,16 +1535,16 @@
         </is>
       </c>
       <c r="N10" s="14" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="O10" s="14" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="P10" s="15" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="Q10" s="15" t="n">
-        <v>6.17</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="P11" s="15" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" s="15" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -1688,10 +1688,10 @@
         <v>8</v>
       </c>
       <c r="O12" s="14" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P12" s="15" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="Q12" s="12" t="inlineStr">
         <is>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="P13" s="15" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="Q13" s="15" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
@@ -1833,16 +1833,16 @@
         </is>
       </c>
       <c r="N14" s="14" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="O14" s="14" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="P14" s="15" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Q14" s="15" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="N16" s="14" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="O16" s="12" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="P16" s="15" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="Q16" s="12" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>1.22</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="N18" s="14" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="O18" s="14" t="n">
-        <v>59.1</v>
+        <v>58.3</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="Q18" s="12" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="P19" s="15" t="n">
-        <v>5.64</v>
+        <v>5.59</v>
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
@@ -2285,16 +2285,16 @@
         </is>
       </c>
       <c r="N20" s="14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" s="14" t="n">
         <v>10.8</v>
       </c>
       <c r="P20" s="15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q20" s="15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
@@ -2358,16 +2358,16 @@
         </is>
       </c>
       <c r="N21" s="14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O21" s="14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P21" s="15" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q21" s="15" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -2444,7 +2444,7 @@
         <v>1.33</v>
       </c>
       <c r="Q22" s="15" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
@@ -2508,16 +2508,16 @@
         </is>
       </c>
       <c r="N23" s="14" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O23" s="14" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="P23" s="15" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="Q23" s="15" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="N25" s="14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O25" s="14" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="P25" s="15" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="Q25" s="15" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="P27" s="15" t="n">
-        <v>4.64</v>
+        <v>4.73</v>
       </c>
       <c r="Q27" s="15" t="n">
-        <v>169.78</v>
+        <v>172.96</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
@@ -2885,16 +2885,16 @@
         </is>
       </c>
       <c r="N28" s="14" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="O28" s="14" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="P28" s="15" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q28" s="15" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="N29" s="14" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="P29" s="15" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="Q29" s="15" t="n">
-        <v>34.77</v>
+        <v>34.59</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="N30" s="14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O30" s="14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="P31" s="15" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Q31" s="15" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
@@ -3258,16 +3258,16 @@
         </is>
       </c>
       <c r="N33" s="14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O33" s="14" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="P33" s="15" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="Q33" s="15" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
@@ -3334,15 +3334,13 @@
         <v>4.4</v>
       </c>
       <c r="O34" s="14" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P34" s="15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Q34" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>1.19</v>
+      </c>
+      <c r="Q34" s="15" t="n">
+        <v>1.19</v>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
@@ -3419,7 +3417,7 @@
         <v>0.85</v>
       </c>
       <c r="Q35" s="15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
@@ -3556,16 +3554,16 @@
         </is>
       </c>
       <c r="N37" s="14" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="O37" s="14" t="n">
-        <v>27.1</v>
+        <v>27.6</v>
       </c>
       <c r="P37" s="15" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q37" s="15" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
@@ -3629,7 +3627,7 @@
         </is>
       </c>
       <c r="N38" s="14" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="O38" s="12" t="inlineStr">
         <is>
@@ -3706,16 +3704,16 @@
         </is>
       </c>
       <c r="N39" s="14" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="O39" s="14" t="n">
-        <v>35.8</v>
+        <v>36.2</v>
       </c>
       <c r="P39" s="15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="Q39" s="15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
@@ -3779,10 +3777,10 @@
         </is>
       </c>
       <c r="N40" s="14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O40" s="14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="P40" s="15" t="n">
         <v>0.34</v>
@@ -3862,7 +3860,7 @@
         </is>
       </c>
       <c r="P41" s="15" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="Q41" s="12" t="inlineStr">
         <is>
@@ -3931,16 +3929,16 @@
         </is>
       </c>
       <c r="N42" s="14" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="O42" s="14" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="P42" s="15" t="n">
-        <v>4.31</v>
+        <v>4.28</v>
       </c>
       <c r="Q42" s="15" t="n">
-        <v>6.03</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
@@ -4004,16 +4002,16 @@
         </is>
       </c>
       <c r="N43" s="14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O43" s="14" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="P43" s="15" t="n">
-        <v>5.32</v>
+        <v>5.41</v>
       </c>
       <c r="Q43" s="15" t="n">
-        <v>6.01</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
@@ -4077,16 +4075,16 @@
         </is>
       </c>
       <c r="N44" s="14" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="O44" s="14" t="n">
-        <v>28.5</v>
+        <v>28.1</v>
       </c>
       <c r="P44" s="15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q44" s="15" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
@@ -4150,16 +4148,16 @@
         </is>
       </c>
       <c r="N45" s="14" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="O45" s="14" t="n">
         <v>14.5</v>
       </c>
       <c r="P45" s="15" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="Q45" s="15" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
@@ -4231,7 +4229,7 @@
         </is>
       </c>
       <c r="P46" s="15" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q46" s="12" t="inlineStr">
         <is>
@@ -4373,16 +4371,16 @@
         </is>
       </c>
       <c r="N48" s="14" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="O48" s="14" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="P48" s="15" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="Q48" s="15" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
@@ -4456,10 +4454,10 @@
         </is>
       </c>
       <c r="P49" s="15" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q49" s="15" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
@@ -4479,7 +4477,7 @@
         </is>
       </c>
       <c r="D50" s="11" t="n">
-        <v>61.2</v>
+        <v>61</v>
       </c>
       <c r="E50" s="11" t="n">
         <v>4.3</v>
@@ -4523,13 +4521,13 @@
         </is>
       </c>
       <c r="N50" s="14" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="O50" s="14" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="P50" s="15" t="n">
-        <v>5.47</v>
+        <v>5.41</v>
       </c>
       <c r="Q50" s="12" t="inlineStr">
         <is>
@@ -4598,16 +4596,16 @@
         </is>
       </c>
       <c r="N51" s="14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O51" s="14" t="n">
-        <v>105.1</v>
+        <v>108.9</v>
       </c>
       <c r="P51" s="15" t="n">
-        <v>3.29</v>
+        <v>3.41</v>
       </c>
       <c r="Q51" s="15" t="n">
-        <v>170.85</v>
+        <v>177.06</v>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
@@ -4674,7 +4672,7 @@
         <v>4.9</v>
       </c>
       <c r="O52" s="14" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="P52" s="15" t="n">
         <v>3.06</v>
@@ -4754,10 +4752,10 @@
         </is>
       </c>
       <c r="P53" s="15" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Q53" s="15" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
@@ -4829,10 +4827,10 @@
         </is>
       </c>
       <c r="P54" s="15" t="n">
-        <v>9.609999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="Q54" s="15" t="n">
-        <v>18.74</v>
+        <v>17.31</v>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1">
@@ -4896,7 +4894,7 @@
         </is>
       </c>
       <c r="N55" s="14" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="O55" s="12" t="inlineStr">
         <is>
@@ -5056,10 +5054,10 @@
         <v>28.8</v>
       </c>
       <c r="P57" s="15" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="Q57" s="15" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
@@ -5123,16 +5121,16 @@
         </is>
       </c>
       <c r="N58" s="14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O58" s="14" t="n">
         <v>10.2</v>
       </c>
       <c r="P58" s="15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q58" s="15" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
@@ -5201,10 +5199,10 @@
         </is>
       </c>
       <c r="O59" s="14" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P59" s="15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Q59" s="12" t="inlineStr">
         <is>
@@ -5283,16 +5281,16 @@
         </is>
       </c>
       <c r="P60" s="15" t="n">
-        <v>14.72</v>
+        <v>14.5</v>
       </c>
       <c r="Q60" s="15" t="n">
-        <v>14.72</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -5302,26 +5300,26 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Everest Group, Ltd.</t>
+          <t>SLB N.V.</t>
         </is>
       </c>
       <c r="D61" s="11" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>3.4</v>
+        <v>10.1</v>
       </c>
       <c r="F61" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>2011</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>Meryl Hartzband</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="I61" s="13" t="inlineStr">
@@ -5334,9 +5332,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K61" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-01 (Award)</t>
+      <c r="K61" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L61" s="10" t="inlineStr">
@@ -5346,26 +5344,26 @@
       </c>
       <c r="M61" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N61" s="14" t="n">
-        <v>6.5</v>
+        <v>12.1</v>
       </c>
       <c r="O61" s="14" t="n">
-        <v>8</v>
+        <v>24.7</v>
       </c>
       <c r="P61" s="15" t="n">
-        <v>0.98</v>
+        <v>2.96</v>
       </c>
       <c r="Q61" s="15" t="n">
-        <v>1.08</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -5375,26 +5373,26 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>SLB N.V.</t>
+          <t>Everest Group, Ltd.</t>
         </is>
       </c>
       <c r="D62" s="11" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>10.1</v>
+        <v>3.4</v>
       </c>
       <c r="F62" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="10" t="inlineStr">
-        <is>
-          <t>2011</t>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>Meryl Hartzband</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
@@ -5407,9 +5405,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K62" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-01 (Award)</t>
         </is>
       </c>
       <c r="L62" s="10" t="inlineStr">
@@ -5419,20 +5417,20 @@
       </c>
       <c r="M62" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N62" s="14" t="n">
-        <v>12.2</v>
+        <v>6.5</v>
       </c>
       <c r="O62" s="14" t="n">
-        <v>25.1</v>
+        <v>7.9</v>
       </c>
       <c r="P62" s="15" t="n">
-        <v>3</v>
+        <v>0.97</v>
       </c>
       <c r="Q62" s="15" t="n">
-        <v>15.2</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
@@ -5513,7 +5511,7 @@
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>GLRE</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -5523,14 +5521,14 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Greenlight Capital Re, Ltd.</t>
+          <t>Amprius Technologies, Inc.</t>
         </is>
       </c>
       <c r="D64" s="11" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="F64" s="12" t="n">
         <v>1</v>
@@ -5542,7 +5540,7 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>Bryan Murphy</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="I64" s="13" t="inlineStr">
@@ -5555,9 +5553,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K64" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-07 (Award)</t>
+      <c r="K64" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L64" s="10" t="inlineStr">
@@ -5565,30 +5563,32 @@
           <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
-      <c r="M64" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M64" s="10" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N64" s="12" t="inlineStr">
         <is>
-          <t>net cash</t>
-        </is>
-      </c>
-      <c r="O64" s="14" t="n">
-        <v>10</v>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="O64" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="P64" s="15" t="n">
-        <v>0.71</v>
+        <v>11.16</v>
       </c>
       <c r="Q64" s="15" t="n">
-        <v>0.83</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>GLRE</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -5598,14 +5598,14 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Amprius Technologies, Inc.</t>
+          <t>Greenlight Capital Re, Ltd.</t>
         </is>
       </c>
       <c r="D65" s="11" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="F65" s="12" t="n">
         <v>1</v>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>Bryan Murphy</t>
         </is>
       </c>
       <c r="I65" s="13" t="inlineStr">
@@ -5625,12 +5625,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J65" s="13" t="n">
-        <v>1459212</v>
+      <c r="J65" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K65" s="10" t="inlineStr">
         <is>
-          <t>2026-06-15 (Sale)</t>
+          <t>2026-08-07 (Award)</t>
         </is>
       </c>
       <c r="L65" s="10" t="inlineStr">
@@ -5638,26 +5640,24 @@
           <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
-      <c r="M65" s="10" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="M65" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N65" s="12" t="inlineStr">
         <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="O65" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+          <t>net cash</t>
+        </is>
+      </c>
+      <c r="O65" s="14" t="n">
+        <v>9.9</v>
       </c>
       <c r="P65" s="15" t="n">
-        <v>10.82</v>
+        <v>0.71</v>
       </c>
       <c r="Q65" s="15" t="n">
-        <v>10.82</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="D66" s="11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E66" s="11" t="n">
         <v>2.3</v>
@@ -5796,13 +5796,13 @@
         </is>
       </c>
       <c r="N67" s="14" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="O67" s="14" t="n">
-        <v>46.3</v>
+        <v>47</v>
       </c>
       <c r="P67" s="15" t="n">
-        <v>53.17</v>
+        <v>54.02</v>
       </c>
       <c r="Q67" s="12" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -5823,14 +5823,14 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc.</t>
+          <t>Semtech Corporation</t>
         </is>
       </c>
       <c r="D68" s="11" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>4.1</v>
+        <v>7.3</v>
       </c>
       <c r="F68" s="12" t="n">
         <v>1</v>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>Miliana Pineda</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="I68" s="13" t="inlineStr">
@@ -5867,26 +5867,26 @@
       </c>
       <c r="M68" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N68" s="14" t="n">
-        <v>25.6</v>
+        <v>145.7</v>
       </c>
       <c r="O68" s="14" t="n">
-        <v>53.3</v>
+        <v>108.2</v>
       </c>
       <c r="P68" s="15" t="n">
-        <v>6.47</v>
+        <v>22.34</v>
       </c>
       <c r="Q68" s="15" t="n">
-        <v>6.62</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -5896,14 +5896,14 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Semtech Corporation</t>
+          <t>Dutch Bros Inc.</t>
         </is>
       </c>
       <c r="D69" s="11" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>7.3</v>
+        <v>4.1</v>
       </c>
       <c r="F69" s="12" t="n">
         <v>1</v>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>Miliana Pineda</t>
         </is>
       </c>
       <c r="I69" s="13" t="inlineStr">
@@ -5940,20 +5940,20 @@
       </c>
       <c r="M69" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N69" s="14" t="n">
-        <v>134.4</v>
+        <v>25.5</v>
       </c>
       <c r="O69" s="14" t="n">
-        <v>102</v>
+        <v>53.2</v>
       </c>
       <c r="P69" s="15" t="n">
-        <v>21.07</v>
+        <v>6.45</v>
       </c>
       <c r="Q69" s="15" t="n">
-        <v>69.81</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
@@ -6027,10 +6027,10 @@
         </is>
       </c>
       <c r="P70" s="15" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Q70" s="15" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="N71" s="14" t="n">
-        <v>23.1</v>
+        <v>23.5</v>
       </c>
       <c r="O71" s="12" t="inlineStr">
         <is>
@@ -6242,16 +6242,16 @@
         </is>
       </c>
       <c r="N73" s="14" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="O73" s="14" t="n">
-        <v>3987.7</v>
+        <v>3968.8</v>
       </c>
       <c r="P73" s="15" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="Q73" s="15" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="N75" s="14" t="n">
-        <v>149.2</v>
+        <v>147.7</v>
       </c>
       <c r="O75" s="12" t="inlineStr">
         <is>
@@ -6404,10 +6404,10 @@
         </is>
       </c>
       <c r="P75" s="15" t="n">
-        <v>4.44</v>
+        <v>4.39</v>
       </c>
       <c r="Q75" s="15" t="n">
-        <v>4.44</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
@@ -6477,10 +6477,10 @@
         <v>11.5</v>
       </c>
       <c r="P76" s="15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q76" s="15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
@@ -6544,16 +6544,16 @@
         </is>
       </c>
       <c r="N77" s="14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O77" s="14" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="P77" s="15" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q77" s="15" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
@@ -6688,16 +6688,16 @@
         </is>
       </c>
       <c r="N79" s="14" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="O79" s="14" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="P79" s="15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Q79" s="15" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="80" ht="14" customHeight="1">
@@ -6761,13 +6761,13 @@
         </is>
       </c>
       <c r="N80" s="14" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="O80" s="14" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P80" s="15" t="n">
-        <v>36.24</v>
+        <v>36.34</v>
       </c>
       <c r="Q80" s="12" t="inlineStr">
         <is>
@@ -6839,13 +6839,13 @@
         <v>1.5</v>
       </c>
       <c r="O81" s="14" t="n">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
       <c r="P81" s="15" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="Q81" s="15" t="n">
-        <v>6.92</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="82" ht="14" customHeight="1">
@@ -6909,16 +6909,16 @@
         </is>
       </c>
       <c r="N82" s="14" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="O82" s="14" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="P82" s="15" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Q82" s="15" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="83" ht="14" customHeight="1">
@@ -6991,7 +6991,7 @@
         <v>1.17</v>
       </c>
       <c r="Q83" s="15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="84" ht="14" customHeight="1">
@@ -7061,10 +7061,10 @@
         <v>5.2</v>
       </c>
       <c r="P84" s="15" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q84" s="15" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="85" ht="14" customHeight="1">
@@ -7128,16 +7128,16 @@
         </is>
       </c>
       <c r="N85" s="14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="O85" s="14" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="P85" s="15" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Q85" s="15" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="86" ht="14" customHeight="1">
@@ -7201,16 +7201,16 @@
         </is>
       </c>
       <c r="N86" s="14" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="O86" s="14" t="n">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
       <c r="P86" s="15" t="n">
-        <v>4.16</v>
+        <v>4</v>
       </c>
       <c r="Q86" s="15" t="n">
-        <v>6.85</v>
+        <v>6.58</v>
       </c>
     </row>
   </sheetData>
@@ -7411,16 +7411,16 @@
         </is>
       </c>
       <c r="K5" s="14" t="n">
-        <v>31.4</v>
+        <v>32.1</v>
       </c>
       <c r="L5" s="14" t="n">
         <v>8</v>
       </c>
       <c r="M5" s="15" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="N5" s="15" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -7471,16 +7471,16 @@
         </is>
       </c>
       <c r="K6" s="14" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="L6" s="14" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="M6" s="15" t="n">
-        <v>4.29</v>
+        <v>4.37</v>
       </c>
       <c r="N6" s="15" t="n">
-        <v>4.77</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="L7" s="14" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M7" s="15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N7" s="12" t="inlineStr">
         <is>
@@ -7598,13 +7598,13 @@
         <v>9.699999999999999</v>
       </c>
       <c r="L8" s="14" t="n">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="M8" s="15" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="N8" s="15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
@@ -7655,13 +7655,13 @@
         </is>
       </c>
       <c r="K9" s="14" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="M9" s="15" t="n">
-        <v>16.53</v>
+        <v>16.63</v>
       </c>
       <c r="N9" s="12" t="inlineStr">
         <is>
@@ -7717,16 +7717,16 @@
         </is>
       </c>
       <c r="K10" s="14" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="L10" s="14" t="n">
-        <v>35.4</v>
+        <v>34.9</v>
       </c>
       <c r="M10" s="15" t="n">
-        <v>11.19</v>
+        <v>11.05</v>
       </c>
       <c r="N10" s="15" t="n">
-        <v>32.24</v>
+        <v>31.83</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
@@ -7777,16 +7777,16 @@
         </is>
       </c>
       <c r="K11" s="14" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="M11" s="15" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="N11" s="15" t="n">
-        <v>6.17</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="M12" s="15" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="N12" s="15" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
@@ -8265,16 +8265,16 @@
         </is>
       </c>
       <c r="K18" s="14" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="L18" s="14" t="n">
-        <v>22.1</v>
+        <v>22.5</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>4.44</v>
+        <v>4.51</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>4.51</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
@@ -8401,16 +8401,16 @@
         </is>
       </c>
       <c r="K20" s="14" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="M20" s="15" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="N20" s="15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
@@ -8593,16 +8593,16 @@
         </is>
       </c>
       <c r="K23" s="14" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="M23" s="15" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="N23" s="15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
     </row>
   </sheetData>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="I5" s="14" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="K5" s="15" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
@@ -8831,16 +8831,16 @@
         </is>
       </c>
       <c r="I6" s="14" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="L6" s="15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -8881,16 +8881,16 @@
         </is>
       </c>
       <c r="I7" s="14" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="L7" s="15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
     </row>
   </sheetData>
@@ -9221,10 +9221,10 @@
         <v>8</v>
       </c>
       <c r="J5" s="14" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
@@ -9282,10 +9282,10 @@
         </is>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="L6" s="15" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -9328,46 +9328,46 @@
         </is>
       </c>
       <c r="I7" s="14" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="L7" s="15" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>W. Conn</t>
+          <t>Viral Patel</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Charter Communications</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>27.5</v>
+        <v>29.4</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -9380,29 +9380,27 @@
         </is>
       </c>
       <c r="I8" s="14" t="n">
-        <v>5.6</v>
+        <v>18.2</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>3</v>
+        <v>26.2</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>10.26</v>
+      </c>
+      <c r="L8" s="15" t="n">
+        <v>11.26</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Mary Kissel</t>
+          <t>W. Conn</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>Charter Communications</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -9417,11 +9415,11 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>25.3</v>
+        <v>27.5</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
@@ -9434,15 +9432,13 @@
         </is>
       </c>
       <c r="I9" s="14" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="J9" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>5.6</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>3</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
@@ -9453,31 +9449,31 @@
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Viral Patel</t>
+          <t>Mary Kissel</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -9490,16 +9486,20 @@
         </is>
       </c>
       <c r="I10" s="14" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>25.9</v>
+        <v>43.5</v>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="K10" s="15" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="L10" s="15" t="n">
-        <v>11.11</v>
+        <v>0.9</v>
+      </c>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
@@ -9542,16 +9542,16 @@
         </is>
       </c>
       <c r="I11" s="14" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -9603,7 +9603,7 @@
         <v>1.22</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
@@ -9646,13 +9646,13 @@
         </is>
       </c>
       <c r="I13" s="14" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="J13" s="14" t="n">
-        <v>59.1</v>
+        <v>58.3</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="K14" s="15" t="n">
-        <v>5.64</v>
+        <v>5.59</v>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
@@ -9758,16 +9758,16 @@
         </is>
       </c>
       <c r="I15" s="14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J15" s="14" t="n">
         <v>10.8</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="I16" s="14" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="K16" s="15" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
@@ -9864,16 +9864,16 @@
         </is>
       </c>
       <c r="I17" s="14" t="n">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="J17" s="14" t="n">
-        <v>35.6</v>
+        <v>36.2</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>5.79</v>
+        <v>5.88</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>8.15</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
@@ -9916,16 +9916,16 @@
         </is>
       </c>
       <c r="I18" s="14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
@@ -9981,7 +9981,7 @@
         <v>1.33</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
@@ -10035,7 +10035,7 @@
         <v>1.21</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
@@ -10078,16 +10078,16 @@
         </is>
       </c>
       <c r="I21" s="14" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J21" s="14" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="K21" s="15" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="L21" s="15" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="K22" s="15" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="L22" s="15" t="n">
-        <v>4.23</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
@@ -10240,16 +10240,16 @@
         </is>
       </c>
       <c r="I24" s="14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="K24" s="15" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="L24" s="15" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
@@ -10292,16 +10292,16 @@
         </is>
       </c>
       <c r="I25" s="14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="K25" s="15" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="L25" s="15" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
@@ -10344,16 +10344,16 @@
         </is>
       </c>
       <c r="I26" s="14" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K26" s="15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="L26" s="15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
@@ -10452,7 +10452,7 @@
         </is>
       </c>
       <c r="I28" s="14" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="K28" s="15" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="L28" s="15" t="n">
-        <v>34.77</v>
+        <v>34.59</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
@@ -10506,13 +10506,13 @@
         </is>
       </c>
       <c r="I29" s="14" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="I30" s="14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
@@ -10624,10 +10624,10 @@
         </is>
       </c>
       <c r="K31" s="15" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="L31" s="15" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
@@ -10722,13 +10722,13 @@
         </is>
       </c>
       <c r="I33" s="14" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>28.4</v>
+        <v>28.6</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
@@ -10786,10 +10786,10 @@
         </is>
       </c>
       <c r="K34" s="15" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="L34" s="15" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
@@ -10832,13 +10832,13 @@
         </is>
       </c>
       <c r="I35" s="14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J35" s="14" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="K35" s="15" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="I36" s="14" t="n">
-        <v>23.1</v>
+        <v>23.5</v>
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>1.8</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>14.16</v>
+        <v>13.8</v>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         </is>
       </c>
       <c r="K38" s="15" t="n">
-        <v>27.92</v>
+        <v>27.32</v>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>1.65</v>
       </c>
       <c r="L39" s="15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
@@ -11110,16 +11110,16 @@
         </is>
       </c>
       <c r="I40" s="14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J40" s="14" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="K40" s="15" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="L40" s="15" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
@@ -11162,7 +11162,7 @@
         </is>
       </c>
       <c r="I41" s="14" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="J41" s="14" t="n">
         <v>20.6</v>
@@ -11223,7 +11223,7 @@
         </is>
       </c>
       <c r="J42" s="14" t="n">
-        <v>51.8</v>
+        <v>52</v>
       </c>
       <c r="K42" s="15" t="n">
         <v>1.06</v>
@@ -11277,15 +11277,13 @@
         <v>4.4</v>
       </c>
       <c r="J43" s="14" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K43" s="15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="L43" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>1.19</v>
+      </c>
+      <c r="L43" s="15" t="n">
+        <v>1.19</v>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
@@ -11341,7 +11339,7 @@
         <v>0.85</v>
       </c>
       <c r="L44" s="15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
@@ -11389,7 +11387,7 @@
         </is>
       </c>
       <c r="J45" s="14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
@@ -11494,13 +11492,13 @@
         </is>
       </c>
       <c r="I47" s="14" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>16.53</v>
+        <v>16.63</v>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
@@ -11548,16 +11546,16 @@
         </is>
       </c>
       <c r="I48" s="14" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>27.1</v>
+        <v>27.6</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="L48" s="15" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
@@ -11600,16 +11598,16 @@
         </is>
       </c>
       <c r="I49" s="14" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="K49" s="15" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="L49" s="15" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
@@ -11652,7 +11650,7 @@
         </is>
       </c>
       <c r="I50" s="14" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
@@ -11708,7 +11706,7 @@
         </is>
       </c>
       <c r="I51" s="14" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="J51" s="12" t="inlineStr">
         <is>
@@ -11764,16 +11762,16 @@
         </is>
       </c>
       <c r="I52" s="14" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="J52" s="14" t="n">
-        <v>35.8</v>
+        <v>36.2</v>
       </c>
       <c r="K52" s="15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="L52" s="15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
@@ -11816,16 +11814,16 @@
         </is>
       </c>
       <c r="I53" s="14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J53" s="14" t="n">
-        <v>259</v>
+        <v>272.7</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>9.779999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="L53" s="15" t="n">
-        <v>9.779999999999999</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
@@ -11878,7 +11876,7 @@
         </is>
       </c>
       <c r="K54" s="15" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="L54" s="12" t="inlineStr">
         <is>
@@ -11926,27 +11924,27 @@
         </is>
       </c>
       <c r="I55" s="14" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="J55" s="14" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="K55" s="15" t="n">
-        <v>4.31</v>
+        <v>4.28</v>
       </c>
       <c r="L55" s="15" t="n">
-        <v>6.03</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Vuyo Kahla</t>
+          <t>Kent Yee</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Sasol</t>
+          <t>DXP Enterprises</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -11956,16 +11954,16 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>SSL</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
@@ -11978,27 +11976,29 @@
         </is>
       </c>
       <c r="I56" s="14" t="n">
-        <v>3.4</v>
+        <v>16.3</v>
       </c>
       <c r="J56" s="14" t="n">
-        <v>12.3</v>
+        <v>32.3</v>
       </c>
       <c r="K56" s="15" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="L56" s="15" t="n">
-        <v>0.93</v>
+        <v>5.53</v>
+      </c>
+      <c r="L56" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="14" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Kent Yee</t>
+          <t>Aviad Kaufman</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>DXP Enterprises</t>
+          <t>Kenon Holdings</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -12013,11 +12013,11 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
@@ -12030,24 +12030,22 @@
         </is>
       </c>
       <c r="I57" s="14" t="n">
-        <v>16.2</v>
+        <v>12.4</v>
       </c>
       <c r="J57" s="14" t="n">
-        <v>32.1</v>
+        <v>28.1</v>
       </c>
       <c r="K57" s="15" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="L57" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>2.12</v>
+      </c>
+      <c r="L57" s="15" t="n">
+        <v>2.17</v>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Aviad Kaufman</t>
+          <t>Idan Ofer</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -12075,36 +12073,36 @@
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>biography names the network</t>
+          <t>the tracked principal</t>
         </is>
       </c>
       <c r="I58" s="14" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="J58" s="14" t="n">
-        <v>28.5</v>
+        <v>28.1</v>
       </c>
       <c r="K58" s="15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="L58" s="15" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Idan Ofer</t>
+          <t>Charles Searle</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Kenon Holdings</t>
+          <t>Tencent Holdings</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -12119,44 +12117,44 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>TCEHY</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>the tracked principal</t>
+          <t>biography names the network</t>
         </is>
       </c>
       <c r="I59" s="14" t="n">
-        <v>12.5</v>
+        <v>10.7</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>28.5</v>
+        <v>14.5</v>
       </c>
       <c r="K59" s="15" t="n">
-        <v>2.14</v>
+        <v>2.97</v>
       </c>
       <c r="L59" s="15" t="n">
-        <v>2.2</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Charles Searle</t>
+          <t>Peter Loscher</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Tencent Holdings</t>
+          <t>Telefónica</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -12171,7 +12169,7 @@
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>TCEHY</t>
+          <t>TELFY</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
@@ -12188,27 +12186,31 @@
         </is>
       </c>
       <c r="I60" s="14" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J60" s="14" t="n">
-        <v>14.5</v>
+        <v>6</v>
+      </c>
+      <c r="J60" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="K60" s="15" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="L60" s="15" t="n">
-        <v>3.67</v>
+        <v>2.7</v>
+      </c>
+      <c r="L60" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Peter Loscher</t>
+          <t>Vuyo Kahla</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Telefónica</t>
+          <t>Sasol</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -12218,16 +12220,16 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>TELFY</t>
+          <t>SSL</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
@@ -12240,20 +12242,16 @@
         </is>
       </c>
       <c r="I61" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="J61" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>3.4</v>
+      </c>
+      <c r="J61" s="14" t="n">
+        <v>12.2</v>
       </c>
       <c r="K61" s="15" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="L61" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>0.91</v>
+      </c>
+      <c r="L61" s="15" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
@@ -12422,16 +12420,16 @@
         </is>
       </c>
       <c r="I64" s="14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J64" s="14" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="L64" s="15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
@@ -12905,13 +12903,13 @@
         <v>3.6</v>
       </c>
       <c r="J72" s="14" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="L72" s="15" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
@@ -12956,7 +12954,7 @@
         </is>
       </c>
       <c r="I73" s="14" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="J73" s="12" t="inlineStr">
         <is>
@@ -12964,7 +12962,7 @@
         </is>
       </c>
       <c r="K73" s="15" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
@@ -13024,10 +13022,10 @@
         </is>
       </c>
       <c r="K74" s="15" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="L74" s="15" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
@@ -13134,7 +13132,7 @@
         </is>
       </c>
       <c r="I76" s="14" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J76" s="14" t="n">
         <v>4.3</v>
@@ -13748,10 +13746,10 @@
         </is>
       </c>
       <c r="K86" s="15" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="L86" s="15" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="87" ht="14" customHeight="1">
@@ -14054,10 +14052,10 @@
         </is>
       </c>
       <c r="K91" s="15" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="L91" s="15" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="92" ht="14" customHeight="1">
@@ -14350,16 +14348,16 @@
         </is>
       </c>
       <c r="I96" s="14" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="J96" s="14" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="L96" s="15" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
@@ -14524,16 +14522,16 @@
         </is>
       </c>
       <c r="I99" s="14" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="J99" s="14" t="n">
-        <v>35.9</v>
+        <v>36.3</v>
       </c>
       <c r="K99" s="15" t="n">
-        <v>32.9</v>
+        <v>33.32</v>
       </c>
       <c r="L99" s="15" t="n">
-        <v>99.41</v>
+        <v>100.67</v>
       </c>
     </row>
     <row r="100" ht="14" customHeight="1">
@@ -15130,7 +15128,7 @@
         </is>
       </c>
       <c r="I109" s="14" t="n">
-        <v>202.5</v>
+        <v>216.6</v>
       </c>
       <c r="J109" s="12" t="inlineStr">
         <is>
@@ -15138,10 +15136,10 @@
         </is>
       </c>
       <c r="K109" s="15" t="n">
-        <v>5.61</v>
+        <v>5.76</v>
       </c>
       <c r="L109" s="15" t="n">
-        <v>5.62</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="110" ht="14" customHeight="1">
@@ -15192,7 +15190,7 @@
         <v>19.9</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="L110" s="12" t="inlineStr">
         <is>
@@ -15314,10 +15312,10 @@
         </is>
       </c>
       <c r="K112" s="15" t="n">
-        <v>5.67</v>
+        <v>5.82</v>
       </c>
       <c r="L112" s="15" t="n">
-        <v>5.67</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="113" ht="14" customHeight="1">
@@ -15672,16 +15670,16 @@
         </is>
       </c>
       <c r="I118" s="14" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="J118" s="14" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="L118" s="15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="119" ht="14" customHeight="1">
@@ -15974,7 +15972,7 @@
         </is>
       </c>
       <c r="I123" s="14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J123" s="12" t="inlineStr">
         <is>
@@ -15982,10 +15980,10 @@
         </is>
       </c>
       <c r="K123" s="15" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="L123" s="15" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="124" ht="14" customHeight="1">
@@ -16216,16 +16214,16 @@
         </is>
       </c>
       <c r="I127" s="14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J127" s="14" t="n">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="K127" s="15" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="L127" s="15" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="128" ht="14" customHeight="1">
@@ -16280,7 +16278,7 @@
         </is>
       </c>
       <c r="K128" s="15" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="L128" s="12" t="inlineStr">
         <is>
@@ -16950,13 +16948,13 @@
         </is>
       </c>
       <c r="I139" s="14" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="J139" s="14" t="n">
         <v>26.4</v>
       </c>
       <c r="K139" s="15" t="n">
-        <v>35.18</v>
+        <v>35.24</v>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
@@ -17071,13 +17069,13 @@
         <v>6.9</v>
       </c>
       <c r="J141" s="14" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K141" s="15" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="L141" s="15" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="142" ht="14" customHeight="1">
@@ -17246,16 +17244,16 @@
         </is>
       </c>
       <c r="I144" s="14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J144" s="14" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="L144" s="15" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="145" ht="14" customHeight="1">
@@ -17734,16 +17732,16 @@
         </is>
       </c>
       <c r="I152" s="14" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J152" s="14" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="L152" s="15" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="153" ht="14" customHeight="1">
@@ -17788,10 +17786,10 @@
         </is>
       </c>
       <c r="I153" s="14" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J153" s="14" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="K153" s="15" t="n">
         <v>0.86</v>
@@ -18278,10 +18276,10 @@
         </is>
       </c>
       <c r="K161" s="15" t="n">
-        <v>1.01</v>
+        <v>0.95</v>
       </c>
       <c r="L161" s="15" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="162" ht="14" customHeight="1">
@@ -19070,16 +19068,16 @@
         </is>
       </c>
       <c r="I174" s="14" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="J174" s="14" t="n">
-        <v>228</v>
+        <v>223.8</v>
       </c>
       <c r="K174" s="15" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="L174" s="15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="175" ht="14" customHeight="1">
@@ -19310,16 +19308,16 @@
         </is>
       </c>
       <c r="I178" s="14" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="J178" s="14" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="K178" s="15" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="L178" s="15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="179" ht="14" customHeight="1">
@@ -19426,16 +19424,16 @@
         </is>
       </c>
       <c r="I180" s="14" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J180" s="14" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="K180" s="15" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="L180" s="15" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="181" ht="14" customHeight="1">
@@ -19718,16 +19716,16 @@
         </is>
       </c>
       <c r="I185" s="14" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="J185" s="14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="K185" s="15" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="L185" s="15" t="n">
-        <v>5.37</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="186" ht="14" customHeight="1">
@@ -19770,16 +19768,16 @@
         </is>
       </c>
       <c r="I186" s="14" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="J186" s="14" t="n">
-        <v>17.3</v>
+        <v>16.7</v>
       </c>
       <c r="K186" s="15" t="n">
-        <v>4.1</v>
+        <v>3.96</v>
       </c>
       <c r="L186" s="15" t="n">
-        <v>211.22</v>
+        <v>203.59</v>
       </c>
     </row>
     <row r="187" ht="14" customHeight="1">
@@ -19822,16 +19820,16 @@
         </is>
       </c>
       <c r="I187" s="14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J187" s="14" t="n">
-        <v>105.1</v>
+        <v>108.9</v>
       </c>
       <c r="K187" s="15" t="n">
-        <v>3.29</v>
+        <v>3.41</v>
       </c>
       <c r="L187" s="15" t="n">
-        <v>170.85</v>
+        <v>177.06</v>
       </c>
     </row>
     <row r="188" ht="14" customHeight="1">
@@ -19874,16 +19872,16 @@
         </is>
       </c>
       <c r="I188" s="14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J188" s="14" t="n">
-        <v>105.1</v>
+        <v>108.9</v>
       </c>
       <c r="K188" s="15" t="n">
-        <v>3.29</v>
+        <v>3.41</v>
       </c>
       <c r="L188" s="15" t="n">
-        <v>170.85</v>
+        <v>177.06</v>
       </c>
     </row>
     <row r="189" ht="14" customHeight="1">
@@ -19929,7 +19927,7 @@
         <v>4.9</v>
       </c>
       <c r="J189" s="14" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="K189" s="15" t="n">
         <v>3.06</v>
@@ -19988,10 +19986,10 @@
         </is>
       </c>
       <c r="K190" s="15" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="L190" s="15" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="191" ht="14" customHeight="1">
@@ -20034,7 +20032,7 @@
         </is>
       </c>
       <c r="I191" s="14" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="J191" s="12" t="inlineStr">
         <is>
@@ -20152,10 +20150,10 @@
         <v>28.8</v>
       </c>
       <c r="K193" s="15" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="L193" s="15" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="194" ht="14" customHeight="1">
@@ -20204,10 +20202,10 @@
         <v>28.8</v>
       </c>
       <c r="K194" s="15" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="L194" s="15" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="195" ht="14" customHeight="1">
@@ -20256,10 +20254,10 @@
         <v>28.8</v>
       </c>
       <c r="K195" s="15" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="L195" s="15" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="196" ht="14" customHeight="1">
@@ -20308,10 +20306,10 @@
         <v>28.8</v>
       </c>
       <c r="K196" s="15" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="L196" s="15" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="197" ht="14" customHeight="1">
@@ -20360,10 +20358,10 @@
         <v>28.8</v>
       </c>
       <c r="K197" s="15" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="L197" s="15" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="198" ht="14" customHeight="1">
@@ -20412,10 +20410,10 @@
         <v>28.8</v>
       </c>
       <c r="K198" s="15" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="L198" s="15" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="199" ht="14" customHeight="1">
@@ -20464,10 +20462,10 @@
         <v>28.8</v>
       </c>
       <c r="K199" s="15" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="L199" s="15" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="200" ht="14" customHeight="1">
@@ -20516,10 +20514,10 @@
         <v>28.8</v>
       </c>
       <c r="K200" s="15" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="L200" s="15" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="201" ht="14" customHeight="1">
@@ -20568,10 +20566,10 @@
         <v>28.8</v>
       </c>
       <c r="K201" s="15" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="L201" s="15" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="202" ht="14" customHeight="1">
@@ -20620,10 +20618,10 @@
         <v>28.8</v>
       </c>
       <c r="K202" s="15" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="L202" s="15" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="203" ht="14" customHeight="1">
@@ -20672,10 +20670,10 @@
         <v>28.8</v>
       </c>
       <c r="K203" s="15" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="L203" s="15" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="204" ht="14" customHeight="1">
@@ -20728,10 +20726,10 @@
         </is>
       </c>
       <c r="K204" s="15" t="n">
-        <v>14.72</v>
+        <v>14.5</v>
       </c>
       <c r="L204" s="15" t="n">
-        <v>14.72</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="205" ht="14" customHeight="1">
@@ -20774,16 +20772,16 @@
         </is>
       </c>
       <c r="I205" s="14" t="n">
-        <v>19</v>
+        <v>19.7</v>
       </c>
       <c r="J205" s="14" t="n">
-        <v>39.8</v>
+        <v>41.3</v>
       </c>
       <c r="K205" s="15" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="L205" s="15" t="n">
-        <v>16.67</v>
+        <v>17.31</v>
       </c>
     </row>
     <row r="206" ht="14" customHeight="1">
@@ -20834,21 +20832,21 @@
         </is>
       </c>
       <c r="K206" s="15" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="L206" s="15" t="n">
-        <v>58.99</v>
+        <v>59.54</v>
       </c>
     </row>
     <row r="207" ht="14" customHeight="1">
       <c r="A207" s="10" t="inlineStr">
         <is>
-          <t>Kathleen Quirk</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>SLB (Other Energy Services</t>
         </is>
       </c>
       <c r="C207" s="10" t="inlineStr">
@@ -20863,11 +20861,11 @@
       </c>
       <c r="E207" s="9" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="F207" s="12" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="G207" s="10" t="inlineStr">
         <is>
@@ -20880,27 +20878,27 @@
         </is>
       </c>
       <c r="I207" s="14" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="J207" s="14" t="n">
-        <v>35.2</v>
+        <v>24.7</v>
       </c>
       <c r="K207" s="15" t="n">
-        <v>5.13</v>
+        <v>2.96</v>
       </c>
       <c r="L207" s="15" t="n">
-        <v>5.13</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="208" ht="14" customHeight="1">
       <c r="A208" s="10" t="inlineStr">
         <is>
-          <t>Meryl Hartzband</t>
+          <t>Kathleen Quirk</t>
         </is>
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>Everest Group (Hamilton</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="C208" s="10" t="inlineStr">
@@ -20915,44 +20913,44 @@
       </c>
       <c r="E208" s="9" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="F208" s="12" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G208" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H208" s="10" t="inlineStr">
+        <is>
+          <t>matched another way, usually an employer-name collision: not signal</t>
+        </is>
+      </c>
+      <c r="I208" s="14" t="n">
         <v>12.2</v>
       </c>
-      <c r="G208" s="10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H208" s="10" t="inlineStr">
-        <is>
-          <t>matched another way, usually an employer-name collision: not signal</t>
-        </is>
-      </c>
-      <c r="I208" s="14" t="n">
-        <v>6.5</v>
-      </c>
       <c r="J208" s="14" t="n">
-        <v>8</v>
+        <v>35.6</v>
       </c>
       <c r="K208" s="15" t="n">
-        <v>0.98</v>
+        <v>5.19</v>
       </c>
       <c r="L208" s="15" t="n">
-        <v>1.08</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="209" ht="14" customHeight="1">
       <c r="A209" s="10" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>Meryl Hartzband</t>
         </is>
       </c>
       <c r="B209" s="10" t="inlineStr">
         <is>
-          <t>SLB (Other Energy Services</t>
+          <t>Everest Group (Hamilton</t>
         </is>
       </c>
       <c r="C209" s="10" t="inlineStr">
@@ -20967,11 +20965,11 @@
       </c>
       <c r="E209" s="9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F209" s="12" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="G209" s="10" t="inlineStr">
         <is>
@@ -20984,16 +20982,16 @@
         </is>
       </c>
       <c r="I209" s="14" t="n">
-        <v>12.2</v>
+        <v>6.5</v>
       </c>
       <c r="J209" s="14" t="n">
-        <v>25.1</v>
+        <v>7.9</v>
       </c>
       <c r="K209" s="15" t="n">
-        <v>3</v>
+        <v>0.97</v>
       </c>
       <c r="L209" s="15" t="n">
-        <v>15.2</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="210" ht="14" customHeight="1">
@@ -21053,12 +21051,12 @@
     <row r="211" ht="14" customHeight="1">
       <c r="A211" s="10" t="inlineStr">
         <is>
-          <t>Bill Roeschlein</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="B211" s="10" t="inlineStr">
         <is>
-          <t>Tigo Energy</t>
+          <t>Amprius Technologies</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
@@ -21073,11 +21071,11 @@
       </c>
       <c r="E211" s="9" t="inlineStr">
         <is>
-          <t>TYGO</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="F211" s="12" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="G211" s="10" t="inlineStr">
         <is>
@@ -21089,28 +21087,32 @@
           <t>matched another way, usually an employer-name collision: not signal</t>
         </is>
       </c>
-      <c r="I211" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J211" s="14" t="n">
-        <v>6.2</v>
+      <c r="I211" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="J211" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="K211" s="15" t="n">
-        <v>1.52</v>
+        <v>11.16</v>
       </c>
       <c r="L211" s="15" t="n">
-        <v>2.19</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="212" ht="14" customHeight="1">
       <c r="A212" s="10" t="inlineStr">
         <is>
-          <t>Bryan Murphy</t>
+          <t>Bill Roeschlein</t>
         </is>
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>Greenlight Capital Re</t>
+          <t>Tigo Energy</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
@@ -21125,11 +21127,11 @@
       </c>
       <c r="E212" s="9" t="inlineStr">
         <is>
-          <t>GLRE</t>
+          <t>TYGO</t>
         </is>
       </c>
       <c r="F212" s="12" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="G212" s="10" t="inlineStr">
         <is>
@@ -21141,30 +21143,28 @@
           <t>matched another way, usually an employer-name collision: not signal</t>
         </is>
       </c>
-      <c r="I212" s="12" t="inlineStr">
-        <is>
-          <t>net cash</t>
-        </is>
+      <c r="I212" s="14" t="n">
+        <v>4.2</v>
       </c>
       <c r="J212" s="14" t="n">
-        <v>10</v>
+        <v>6.1</v>
       </c>
       <c r="K212" s="15" t="n">
-        <v>0.71</v>
+        <v>1.49</v>
       </c>
       <c r="L212" s="15" t="n">
-        <v>0.83</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="213" ht="14" customHeight="1">
       <c r="A213" s="10" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>Bryan Murphy</t>
         </is>
       </c>
       <c r="B213" s="10" t="inlineStr">
         <is>
-          <t>Amprius Technologies</t>
+          <t>Greenlight Capital Re</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
@@ -21179,11 +21179,11 @@
       </c>
       <c r="E213" s="9" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>GLRE</t>
         </is>
       </c>
       <c r="F213" s="12" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="G213" s="10" t="inlineStr">
         <is>
@@ -21197,19 +21197,17 @@
       </c>
       <c r="I213" s="12" t="inlineStr">
         <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="J213" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+          <t>net cash</t>
+        </is>
+      </c>
+      <c r="J213" s="14" t="n">
+        <v>9.9</v>
       </c>
       <c r="K213" s="15" t="n">
-        <v>10.82</v>
+        <v>0.71</v>
       </c>
       <c r="L213" s="15" t="n">
-        <v>10.82</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="214" ht="14" customHeight="1">
@@ -21299,7 +21297,7 @@
         </is>
       </c>
       <c r="F215" s="12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G215" s="10" t="inlineStr">
         <is>
@@ -21366,13 +21364,13 @@
         </is>
       </c>
       <c r="I216" s="14" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="J216" s="14" t="n">
-        <v>46.3</v>
+        <v>47</v>
       </c>
       <c r="K216" s="15" t="n">
-        <v>53.17</v>
+        <v>54.02</v>
       </c>
       <c r="L216" s="12" t="inlineStr">
         <is>
@@ -21420,27 +21418,27 @@
         </is>
       </c>
       <c r="I217" s="14" t="n">
-        <v>16.2</v>
+        <v>16.7</v>
       </c>
       <c r="J217" s="14" t="n">
-        <v>25.9</v>
+        <v>26.5</v>
       </c>
       <c r="K217" s="15" t="n">
-        <v>4.95</v>
+        <v>5.07</v>
       </c>
       <c r="L217" s="15" t="n">
-        <v>7.12</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="218" ht="14" customHeight="1">
       <c r="A218" s="10" t="inlineStr">
         <is>
-          <t>Miliana Pineda</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>Dutch Bros</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
@@ -21455,7 +21453,7 @@
       </c>
       <c r="E218" s="9" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="F218" s="12" t="n">
@@ -21472,27 +21470,27 @@
         </is>
       </c>
       <c r="I218" s="14" t="n">
-        <v>25.6</v>
+        <v>145.7</v>
       </c>
       <c r="J218" s="14" t="n">
-        <v>53.3</v>
+        <v>108.2</v>
       </c>
       <c r="K218" s="15" t="n">
-        <v>6.47</v>
+        <v>22.34</v>
       </c>
       <c r="L218" s="15" t="n">
-        <v>6.62</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="219" ht="14" customHeight="1">
       <c r="A219" s="10" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>Miliana Pineda</t>
         </is>
       </c>
       <c r="B219" s="10" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>Dutch Bros</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
@@ -21507,11 +21505,11 @@
       </c>
       <c r="E219" s="9" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="F219" s="12" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G219" s="10" t="inlineStr">
         <is>
@@ -21524,16 +21522,16 @@
         </is>
       </c>
       <c r="I219" s="14" t="n">
-        <v>134.4</v>
+        <v>25.5</v>
       </c>
       <c r="J219" s="14" t="n">
-        <v>102</v>
+        <v>53.2</v>
       </c>
       <c r="K219" s="15" t="n">
-        <v>21.07</v>
+        <v>6.45</v>
       </c>
       <c r="L219" s="15" t="n">
-        <v>69.81</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="220" ht="14" customHeight="1">
@@ -21586,10 +21584,10 @@
         </is>
       </c>
       <c r="K220" s="15" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="L220" s="15" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="221" ht="14" customHeight="1">
@@ -21632,13 +21630,13 @@
         </is>
       </c>
       <c r="I221" s="14" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="J221" s="14" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="K221" s="15" t="n">
-        <v>13.86</v>
+        <v>13.7</v>
       </c>
       <c r="L221" s="12" t="inlineStr">
         <is>
@@ -21746,10 +21744,10 @@
         <v>10.5</v>
       </c>
       <c r="K223" s="15" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="L223" s="15" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="224" ht="14" customHeight="1">
@@ -21896,16 +21894,16 @@
         </is>
       </c>
       <c r="I226" s="14" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="J226" s="14" t="n">
-        <v>3987.7</v>
+        <v>3968.8</v>
       </c>
       <c r="K226" s="15" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="L226" s="15" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="227" ht="14" customHeight="1">
@@ -21958,10 +21956,10 @@
         </is>
       </c>
       <c r="K227" s="15" t="n">
-        <v>4.47</v>
+        <v>4.59</v>
       </c>
       <c r="L227" s="15" t="n">
-        <v>97.22</v>
+        <v>99.86</v>
       </c>
     </row>
     <row r="228" ht="14" customHeight="1">
@@ -22004,7 +22002,7 @@
         </is>
       </c>
       <c r="I228" s="14" t="n">
-        <v>149.2</v>
+        <v>147.7</v>
       </c>
       <c r="J228" s="12" t="inlineStr">
         <is>
@@ -22012,10 +22010,10 @@
         </is>
       </c>
       <c r="K228" s="15" t="n">
-        <v>4.44</v>
+        <v>4.39</v>
       </c>
       <c r="L228" s="15" t="n">
-        <v>4.44</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="229" ht="14" customHeight="1">
@@ -22068,10 +22066,10 @@
         </is>
       </c>
       <c r="K229" s="15" t="n">
-        <v>13.35</v>
+        <v>13.58</v>
       </c>
       <c r="L229" s="15" t="n">
-        <v>14.71</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="230" ht="14" customHeight="1">
@@ -22114,16 +22112,16 @@
         </is>
       </c>
       <c r="I230" s="14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J230" s="14" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="K230" s="15" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="L230" s="15" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="231" ht="14" customHeight="1">
@@ -22218,7 +22216,7 @@
         </is>
       </c>
       <c r="I232" s="14" t="n">
-        <v>82.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="J232" s="12" t="inlineStr">
         <is>
@@ -22226,10 +22224,10 @@
         </is>
       </c>
       <c r="K232" s="15" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="L232" s="15" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="233" ht="14" customHeight="1">
@@ -22272,7 +22270,7 @@
         </is>
       </c>
       <c r="I233" s="14" t="n">
-        <v>82.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="J233" s="12" t="inlineStr">
         <is>
@@ -22280,10 +22278,10 @@
         </is>
       </c>
       <c r="K233" s="15" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="L233" s="15" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="234" ht="14" customHeight="1">
@@ -22326,16 +22324,16 @@
         </is>
       </c>
       <c r="I234" s="14" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="J234" s="14" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="K234" s="15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="L234" s="15" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="235" ht="14" customHeight="1">
@@ -22378,13 +22376,13 @@
         </is>
       </c>
       <c r="I235" s="14" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="J235" s="14" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="K235" s="15" t="n">
-        <v>36.24</v>
+        <v>36.34</v>
       </c>
       <c r="L235" s="12" t="inlineStr">
         <is>
@@ -22435,13 +22433,13 @@
         <v>1.5</v>
       </c>
       <c r="J236" s="14" t="n">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
       <c r="K236" s="15" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="L236" s="15" t="n">
-        <v>6.92</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="237" ht="14" customHeight="1">
@@ -22487,13 +22485,13 @@
         <v>1.5</v>
       </c>
       <c r="J237" s="14" t="n">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
       <c r="K237" s="15" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="L237" s="15" t="n">
-        <v>6.92</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="238" ht="14" customHeight="1">
@@ -22539,13 +22537,13 @@
         <v>1.5</v>
       </c>
       <c r="J238" s="14" t="n">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
       <c r="K238" s="15" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="L238" s="15" t="n">
-        <v>6.92</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="239" ht="14" customHeight="1">
@@ -22591,13 +22589,13 @@
         <v>1.5</v>
       </c>
       <c r="J239" s="14" t="n">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
       <c r="K239" s="15" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="L239" s="15" t="n">
-        <v>6.92</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="240" ht="14" customHeight="1">
@@ -22643,13 +22641,13 @@
         <v>1.5</v>
       </c>
       <c r="J240" s="14" t="n">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
       <c r="K240" s="15" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="L240" s="15" t="n">
-        <v>6.92</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="241" ht="14" customHeight="1">
@@ -22695,13 +22693,13 @@
         <v>1.5</v>
       </c>
       <c r="J241" s="14" t="n">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
       <c r="K241" s="15" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="L241" s="15" t="n">
-        <v>6.92</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="242" ht="14" customHeight="1">
@@ -22747,13 +22745,13 @@
         <v>1.5</v>
       </c>
       <c r="J242" s="14" t="n">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
       <c r="K242" s="15" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="L242" s="15" t="n">
-        <v>6.92</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="243" ht="14" customHeight="1">
@@ -22799,13 +22797,13 @@
         <v>1.5</v>
       </c>
       <c r="J243" s="14" t="n">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
       <c r="K243" s="15" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="L243" s="15" t="n">
-        <v>6.92</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="244" ht="14" customHeight="1">
@@ -22851,13 +22849,13 @@
         <v>1.5</v>
       </c>
       <c r="J244" s="14" t="n">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
       <c r="K244" s="15" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="L244" s="15" t="n">
-        <v>6.92</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="245" ht="14" customHeight="1">
@@ -22900,16 +22898,16 @@
         </is>
       </c>
       <c r="I245" s="14" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J245" s="14" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="K245" s="15" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="L245" s="15" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="246" ht="14" customHeight="1">
@@ -22961,7 +22959,7 @@
         <v>1.17</v>
       </c>
       <c r="L246" s="15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="247" ht="14" customHeight="1">
@@ -23010,10 +23008,10 @@
         <v>5.2</v>
       </c>
       <c r="K247" s="15" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L247" s="15" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="248" ht="14" customHeight="1">
@@ -23056,16 +23054,16 @@
         </is>
       </c>
       <c r="I248" s="14" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J248" s="14" t="n">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
       <c r="K248" s="15" t="n">
-        <v>4.16</v>
+        <v>4</v>
       </c>
       <c r="L248" s="15" t="n">
-        <v>6.85</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="249" ht="14" customHeight="1">
@@ -23416,16 +23414,16 @@
         </is>
       </c>
       <c r="I254" s="14" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="J254" s="14" t="n">
-        <v>45.9</v>
+        <v>47.9</v>
       </c>
       <c r="K254" s="15" t="n">
-        <v>3.28</v>
+        <v>3.43</v>
       </c>
       <c r="L254" s="15" t="n">
-        <v>3.91</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="255" ht="14" customHeight="1">
@@ -24650,10 +24648,10 @@
         </is>
       </c>
       <c r="K274" s="15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="L274" s="15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="275" ht="14" customHeight="1">
@@ -24760,10 +24758,10 @@
         </is>
       </c>
       <c r="I276" s="14" t="n">
-        <v>117.7</v>
+        <v>117.6</v>
       </c>
       <c r="J276" s="14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="K276" s="15" t="n">
         <v>0.22</v>
@@ -24817,13 +24815,13 @@
         <v>11.9</v>
       </c>
       <c r="J277" s="14" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="K277" s="15" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="L277" s="15" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="278" ht="14" customHeight="1">
@@ -25188,7 +25186,7 @@
         </is>
       </c>
       <c r="K283" s="15" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="L283" s="12" t="inlineStr">
         <is>
@@ -25238,16 +25236,16 @@
         </is>
       </c>
       <c r="I284" s="14" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J284" s="14" t="n">
-        <v>15.4</v>
+        <v>14.7</v>
       </c>
       <c r="K284" s="15" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="L284" s="15" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="285" ht="14" customHeight="1">
@@ -25550,10 +25548,10 @@
         </is>
       </c>
       <c r="K289" s="15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="L289" s="15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="290" ht="14" customHeight="1">
@@ -25608,10 +25606,10 @@
         </is>
       </c>
       <c r="K290" s="15" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="L290" s="15" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="291" ht="14" customHeight="1">
@@ -25661,13 +25659,13 @@
         </is>
       </c>
       <c r="J291" s="14" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="K291" s="15" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="L291" s="15" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="292" ht="14" customHeight="1">
@@ -25828,16 +25826,16 @@
         </is>
       </c>
       <c r="I294" s="14" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="J294" s="14" t="n">
-        <v>228</v>
+        <v>223.8</v>
       </c>
       <c r="K294" s="15" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="L294" s="15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="295" ht="14" customHeight="1">
@@ -25954,10 +25952,10 @@
         </is>
       </c>
       <c r="K296" s="15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="L296" s="15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="297" ht="14" customHeight="1">
@@ -26074,10 +26072,10 @@
         </is>
       </c>
       <c r="K298" s="15" t="n">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="L298" s="15" t="n">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="299" ht="14" customHeight="1">
@@ -26184,16 +26182,16 @@
         </is>
       </c>
       <c r="I300" s="14" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J300" s="14" t="n">
-        <v>15.4</v>
+        <v>14.7</v>
       </c>
       <c r="K300" s="15" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="L300" s="15" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="301" ht="14" customHeight="1">
@@ -26357,7 +26355,7 @@
         <v>12.4</v>
       </c>
       <c r="J303" s="14" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="K303" s="15" t="n">
         <v>2.47</v>
@@ -26906,10 +26904,10 @@
         </is>
       </c>
       <c r="K312" s="15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="L312" s="15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="313" ht="14" customHeight="1">
@@ -27026,10 +27024,10 @@
         </is>
       </c>
       <c r="K314" s="15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="L314" s="15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="315" ht="14" customHeight="1">
@@ -27074,16 +27072,16 @@
         </is>
       </c>
       <c r="I315" s="14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J315" s="14" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="K315" s="15" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="L315" s="15" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="316" ht="14" customHeight="1">
@@ -27138,10 +27136,10 @@
         </is>
       </c>
       <c r="K316" s="15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="L316" s="15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="317" ht="14" customHeight="1">
@@ -27258,10 +27256,10 @@
         </is>
       </c>
       <c r="K318" s="15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="L318" s="15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="319" ht="14" customHeight="1">
@@ -27316,10 +27314,10 @@
         </is>
       </c>
       <c r="K319" s="15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="L319" s="15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="320" ht="14" customHeight="1">
@@ -27364,16 +27362,16 @@
         </is>
       </c>
       <c r="I320" s="14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J320" s="14" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="K320" s="15" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="L320" s="15" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="321" ht="14" customHeight="1">
@@ -27790,16 +27788,16 @@
         </is>
       </c>
       <c r="I327" s="14" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="J327" s="14" t="n">
-        <v>21.1</v>
+        <v>22.8</v>
       </c>
       <c r="K327" s="15" t="n">
-        <v>4.19</v>
+        <v>4.51</v>
       </c>
       <c r="L327" s="15" t="n">
-        <v>4.19</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="328" ht="14" customHeight="1">
@@ -27916,10 +27914,10 @@
         </is>
       </c>
       <c r="K329" s="15" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="L329" s="15" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="330" ht="14" customHeight="1">
@@ -28150,16 +28148,16 @@
         </is>
       </c>
       <c r="I333" s="14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J333" s="14" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="K333" s="15" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="L333" s="15" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="334" ht="14" customHeight="1">
@@ -28204,16 +28202,16 @@
         </is>
       </c>
       <c r="I334" s="14" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="J334" s="14" t="n">
-        <v>228</v>
+        <v>223.8</v>
       </c>
       <c r="K334" s="15" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="L334" s="15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="335" ht="14" customHeight="1">
@@ -28754,16 +28752,16 @@
         </is>
       </c>
       <c r="I343" s="14" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J343" s="14" t="n">
-        <v>103.5</v>
+        <v>107.5</v>
       </c>
       <c r="K343" s="15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="L343" s="15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="344" ht="14" customHeight="1">
@@ -29164,16 +29162,16 @@
         </is>
       </c>
       <c r="I350" s="14" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="J350" s="14" t="n">
-        <v>228</v>
+        <v>223.8</v>
       </c>
       <c r="K350" s="15" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="L350" s="15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="351" ht="14" customHeight="1">
@@ -29223,13 +29221,13 @@
         </is>
       </c>
       <c r="J351" s="14" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="K351" s="15" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="L351" s="15" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="352" ht="14" customHeight="1">
@@ -29460,16 +29458,16 @@
         </is>
       </c>
       <c r="I355" s="14" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="J355" s="14" t="n">
-        <v>45.9</v>
+        <v>47.9</v>
       </c>
       <c r="K355" s="15" t="n">
-        <v>3.28</v>
+        <v>3.43</v>
       </c>
       <c r="L355" s="15" t="n">
-        <v>3.91</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="356" ht="14" customHeight="1">
@@ -29638,7 +29636,7 @@
         </is>
       </c>
       <c r="I358" s="14" t="n">
-        <v>110.6</v>
+        <v>114.5</v>
       </c>
       <c r="J358" s="12" t="inlineStr">
         <is>
@@ -29646,10 +29644,10 @@
         </is>
       </c>
       <c r="K358" s="15" t="n">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="L358" s="15" t="n">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="359" ht="14" customHeight="1">
@@ -30614,16 +30612,16 @@
         </is>
       </c>
       <c r="I374" s="14" t="n">
-        <v>17</v>
+        <v>16.3</v>
       </c>
       <c r="J374" s="14" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="K374" s="15" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="L374" s="15" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="375" ht="14" customHeight="1">
@@ -30908,16 +30906,16 @@
         </is>
       </c>
       <c r="I379" s="14" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="J379" s="14" t="n">
-        <v>228</v>
+        <v>223.8</v>
       </c>
       <c r="K379" s="15" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="L379" s="15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="380" ht="14" customHeight="1">
@@ -31086,16 +31084,16 @@
         </is>
       </c>
       <c r="I382" s="14" t="n">
-        <v>43.6</v>
+        <v>44.3</v>
       </c>
       <c r="J382" s="14" t="n">
-        <v>80.3</v>
+        <v>81.5</v>
       </c>
       <c r="K382" s="15" t="n">
-        <v>11.55</v>
+        <v>11.72</v>
       </c>
       <c r="L382" s="15" t="n">
-        <v>11.55</v>
+        <v>11.72</v>
       </c>
     </row>
     <row r="383" ht="14" customHeight="1">
@@ -31202,16 +31200,16 @@
         </is>
       </c>
       <c r="I384" s="14" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J384" s="14" t="n">
-        <v>103.5</v>
+        <v>107.5</v>
       </c>
       <c r="K384" s="15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="L384" s="15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="385" ht="14" customHeight="1">
@@ -31804,16 +31802,16 @@
         </is>
       </c>
       <c r="I394" s="14" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="J394" s="14" t="n">
-        <v>21.1</v>
+        <v>22.8</v>
       </c>
       <c r="K394" s="15" t="n">
-        <v>4.19</v>
+        <v>4.51</v>
       </c>
       <c r="L394" s="15" t="n">
-        <v>4.19</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="395" ht="14" customHeight="1">
@@ -31861,13 +31859,13 @@
         <v>3.1</v>
       </c>
       <c r="J395" s="14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K395" s="15" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="L395" s="15" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="396" ht="14" customHeight="1">
@@ -31912,16 +31910,16 @@
         </is>
       </c>
       <c r="I396" s="14" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="J396" s="14" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="K396" s="15" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="L396" s="15" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="397" ht="14" customHeight="1">
@@ -32400,16 +32398,16 @@
         </is>
       </c>
       <c r="I404" s="14" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="J404" s="14" t="n">
-        <v>228</v>
+        <v>223.8</v>
       </c>
       <c r="K404" s="15" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="L404" s="15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="405" ht="14" customHeight="1">
@@ -33194,7 +33192,7 @@
         </is>
       </c>
       <c r="I417" s="14" t="n">
-        <v>110.6</v>
+        <v>114.5</v>
       </c>
       <c r="J417" s="12" t="inlineStr">
         <is>
@@ -33202,10 +33200,10 @@
         </is>
       </c>
       <c r="K417" s="15" t="n">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="L417" s="15" t="n">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="418" ht="14" customHeight="1">
@@ -33315,7 +33313,7 @@
         <v>12.4</v>
       </c>
       <c r="J419" s="14" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="K419" s="15" t="n">
         <v>2.47</v>
@@ -33438,10 +33436,10 @@
         </is>
       </c>
       <c r="K421" s="15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="L421" s="15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="422" ht="14" customHeight="1">
@@ -33734,16 +33732,16 @@
         </is>
       </c>
       <c r="I426" s="14" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="J426" s="14" t="n">
-        <v>45.9</v>
+        <v>47.9</v>
       </c>
       <c r="K426" s="15" t="n">
-        <v>3.28</v>
+        <v>3.43</v>
       </c>
       <c r="L426" s="15" t="n">
-        <v>3.91</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="427" ht="14" customHeight="1">
@@ -33788,16 +33786,16 @@
         </is>
       </c>
       <c r="I427" s="14" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="J427" s="14" t="n">
-        <v>26.3</v>
+        <v>26.6</v>
       </c>
       <c r="K427" s="15" t="n">
-        <v>5.51</v>
+        <v>5.58</v>
       </c>
       <c r="L427" s="15" t="n">
-        <v>6.97</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="428" ht="14" customHeight="1">
@@ -33904,16 +33902,16 @@
         </is>
       </c>
       <c r="I429" s="14" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="J429" s="14" t="n">
-        <v>228</v>
+        <v>223.8</v>
       </c>
       <c r="K429" s="15" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="L429" s="15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="430" ht="14" customHeight="1">
@@ -33964,10 +33962,10 @@
         <v>6.4</v>
       </c>
       <c r="K430" s="15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="L430" s="15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="431" ht="14" customHeight="1">
@@ -34139,13 +34137,13 @@
         <v>13.7</v>
       </c>
       <c r="J433" s="14" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="K433" s="15" t="n">
-        <v>4.43</v>
+        <v>4.45</v>
       </c>
       <c r="L433" s="15" t="n">
-        <v>5.62</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="434" ht="14" customHeight="1">
@@ -34255,7 +34253,7 @@
         <v>12.4</v>
       </c>
       <c r="J435" s="14" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="K435" s="15" t="n">
         <v>2.47</v>
@@ -34360,16 +34358,16 @@
         </is>
       </c>
       <c r="I437" s="14" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J437" s="14" t="n">
-        <v>19.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K437" s="15" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="L437" s="15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="438" ht="14" customHeight="1">
@@ -34600,16 +34598,16 @@
         </is>
       </c>
       <c r="I441" s="14" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="J441" s="14" t="n">
-        <v>45.9</v>
+        <v>47.9</v>
       </c>
       <c r="K441" s="15" t="n">
-        <v>3.28</v>
+        <v>3.43</v>
       </c>
       <c r="L441" s="15" t="n">
-        <v>3.91</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="442" ht="14" customHeight="1">
@@ -34780,10 +34778,10 @@
         </is>
       </c>
       <c r="K444" s="15" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="L444" s="15" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="445" ht="14" customHeight="1">
@@ -34838,10 +34836,10 @@
         </is>
       </c>
       <c r="K445" s="15" t="n">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
       <c r="L445" s="15" t="n">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="446" ht="14" customHeight="1">
@@ -34896,10 +34894,10 @@
         </is>
       </c>
       <c r="K446" s="15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="L446" s="15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="447" ht="14" customHeight="1">
@@ -35183,7 +35181,7 @@
         <v>12.4</v>
       </c>
       <c r="J451" s="14" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="K451" s="15" t="n">
         <v>2.47</v>
@@ -35368,10 +35366,10 @@
         </is>
       </c>
       <c r="K454" s="15" t="n">
-        <v>9.48</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L454" s="15" t="n">
-        <v>9.48</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="455" ht="14" customHeight="1">
@@ -35608,10 +35606,10 @@
         </is>
       </c>
       <c r="K458" s="15" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="L458" s="15" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="459" ht="14" customHeight="1">
@@ -35966,16 +35964,16 @@
         </is>
       </c>
       <c r="I464" s="14" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="J464" s="14" t="n">
-        <v>21.1</v>
+        <v>22.8</v>
       </c>
       <c r="K464" s="15" t="n">
-        <v>4.19</v>
+        <v>4.51</v>
       </c>
       <c r="L464" s="15" t="n">
-        <v>4.19</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="465" ht="14" customHeight="1">
@@ -36330,16 +36328,16 @@
         </is>
       </c>
       <c r="I470" s="14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J470" s="14" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="K470" s="15" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="L470" s="15" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="471" ht="14" customHeight="1">
@@ -36394,10 +36392,10 @@
         </is>
       </c>
       <c r="K471" s="15" t="n">
-        <v>5.04</v>
+        <v>4.75</v>
       </c>
       <c r="L471" s="15" t="n">
-        <v>5.41</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="472" ht="14" customHeight="1">
@@ -37188,10 +37186,10 @@
         </is>
       </c>
       <c r="K484" s="15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="L484" s="15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="485" ht="14" customHeight="1">
@@ -37427,13 +37425,13 @@
         </is>
       </c>
       <c r="J488" s="14" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="K488" s="15" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="L488" s="15" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="489" ht="14" customHeight="1">
@@ -37488,10 +37486,10 @@
         </is>
       </c>
       <c r="K489" s="15" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="L489" s="15" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="490" ht="14" customHeight="1">
@@ -37536,16 +37534,16 @@
         </is>
       </c>
       <c r="I490" s="14" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="J490" s="14" t="n">
-        <v>228</v>
+        <v>223.8</v>
       </c>
       <c r="K490" s="15" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="L490" s="15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="491" ht="14" customHeight="1">

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -13,7 +13,8 @@
     <sheet name="Board Convergence" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Watchlist — Not in Universe" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Family Office &amp; SWF Map" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Network Roster Adds" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="New Insider Filings" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Network Roster Adds" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'README'!$1:$4</definedName>
@@ -27,8 +28,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Watchlist — Not in Universe'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Family Office &amp; SWF Map'!$A$4:$L$495</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Family Office &amp; SWF Map'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Network Roster Adds'!$A$4:$F$11</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Network Roster Adds'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'New Insider Filings'!$A$4:$I$35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'New Insider Filings'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Network Roster Adds'!$A$4:$F$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Network Roster Adds'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -538,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -719,207 +722,235 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>• 'Network Roster Adds' — investment firms found in the data and now tracked for holdings (context).</t>
+          <t>• 'New Insider Filings' — tracked people who filed an SEC Form 3 in the last 120 days: a new board seat,</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   officer role or 10% stake, live (the PitchBook searches date from September 2025). Confirmed when the</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Column definitions</t>
+          <t xml:space="preserve">   company is in the person's own profile; same-name filings are listed apart, beside the profile, to check.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>• Conf — linkage confidence: A = the tracked principal themselves; B = biography explicitly names</t>
+          <t>• 'Network Roster Adds' — investment firms found in the data and now tracked for holdings (context).</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   a searched network entity; C = matched the search some other way (often an employer-name collision) —</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">   treat C as noise. Convergence &amp; Watchlist only count A/B.</t>
+          <t>Column definitions</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>• Since — the seat's start year where the person's biography states it ('since 2018'); blank = unknown.</t>
+          <t>• Conf — linkage confidence: A = the tracked principal themselves; B = biography explicitly names</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>• Our Score / Smart$ n — this ticker's unified score and conviction-weighted 13F holder count from the</t>
+          <t xml:space="preserve">   a searched network entity; C = matched the search some other way (often an employer-name collision) —</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">   universe workbook (see its Legend for the full formula).</t>
+          <t xml:space="preserve">   treat C as noise. Convergence &amp; Watchlist only count A/B.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>• Dir Buys $ / Dir Sells $ — the connected directors' own open-market Form 4 trades at that company over</t>
+          <t>• Since — the seat's start year where the person's biography states it ('since 2018'); blank = unknown.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   12 months. Last Form 4 — their latest Form 4 of any kind (award, exercise, trade) in the last ~100 days:</t>
+          <t>• Our Score / Smart$ n — this ticker's unified score and conviction-weighted 13F holder count from the</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">   a recent one confirms the seat is live. Blank = none found (directors often file only around the AGM).</t>
+          <t xml:space="preserve">   universe workbook (see its Legend for the full formula).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>• Match (Family Office map) — C rows matched the search some other way, usually an employer-name</t>
+          <t>• Dir Buys $ / Dir Sells $ — the connected directors' own open-market Form 4 trades at that company over</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">   collision (Vulcan Materials' directors against Vulcan Inc., Paul Allen's vehicle): listed last, not signal.</t>
+          <t xml:space="preserve">   12 months. Last Form 4 — their latest Form 4 of any kind (award, exercise, trade) in the last ~100 days:</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   a recent one confirms the seat is live. Blank = none found (directors often file only around the AGM).</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Signal classification &amp; caveats</t>
+          <t>• Match (Family Office map) — C rows matched the search some other way, usually an employer-name</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>• OUTSIDE-director = a Board Member / Non-Exec / Advisor / Chairman who is NOT the company's CEO/founder.</t>
+          <t xml:space="preserve">   collision (Vulcan Materials' directors against Vulcan Inc., Paul Allen's vehicle): listed last, not signal.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Founder/CEO-on-own-board rows are labelled OPERATOR and excluded from the signal sheets.</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>• '(Former)' seats are flagged and excluded — only live placements count.</t>
+          <t>Signal classification &amp; caveats</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>• A person is 'network-connected' because their PitchBook biography ties them to a tracked titan / Sequoia /</t>
+          <t>• OUTSIDE-director = a Board Member / Non-Exec / Advisor / Chairman who is NOT the company's CEO/founder.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">   family-office; 'principal' rows are the tracked individual themselves.</t>
+          <t xml:space="preserve">   Founder/CEO-on-own-board rows are labelled OPERATOR and excluded from the signal sheets.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>• One of the five source files (2025-09-19) arrived truncated and unrecoverable; a same-author 2025-09-20</t>
+          <t>• '(Former)' seats are flagged and excluded — only live placements count.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">   search is present. Board data is a point-in-time snapshot (searches of September 2025), not a live feed:</t>
+          <t>• A person is 'network-connected' because their PitchBook biography ties them to a tracked titan / Sequoia /</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t xml:space="preserve">   family-office; 'principal' rows are the tracked individual themselves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>• One of the five source files (2025-09-19) arrived truncated and unrecoverable; a same-author 2025-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   search is present. Board data is a point-in-time snapshot (searches of September 2025), not a live feed:</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t xml:space="preserve">   seats may have ended since. Last Form 4 is the live check.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>CONTENTS — CLICK TO OPEN A SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Board Signal — In Universe</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Investor Board Seats</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Board Convergence</t>
         </is>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Watchlist — Not in Universe</t>
+          <t>Board Signal — In Universe</t>
         </is>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Family Office &amp; SWF Map</t>
+          <t>Investor Board Seats</t>
         </is>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Board Convergence</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Watchlist — Not in Universe</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Family Office &amp; SWF Map</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>New Insider Filings</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>Network Roster Adds</t>
         </is>
@@ -928,16 +959,17 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A54:B54"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId7"/>
   </hyperlinks>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1641,7 +1673,7 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>41</v>
+        <v>40.5</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>6.7</v>
@@ -2073,7 +2105,7 @@
     <row r="18" ht="14" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>SANA</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -2083,26 +2115,26 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Monro, Inc.</t>
+          <t>Sana Biotechnology, Inc.</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>20.4</v>
+        <v>21.3</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>2012</t>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Hope Woodhouse</t>
+          <t>Richard Mulligan</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
@@ -2115,9 +2147,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-11 (Award)</t>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L18" s="10" t="inlineStr">
@@ -2127,17 +2159,21 @@
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="N18" s="14" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="O18" s="14" t="n">
-        <v>58.3</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N18" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.72</v>
+        <v>5.59</v>
       </c>
       <c r="Q18" s="12" t="inlineStr">
         <is>
@@ -2148,7 +2184,7 @@
     <row r="19" ht="14" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>SANA</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -2158,26 +2194,26 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Sana Biotechnology, Inc.</t>
+          <t>Monro, Inc.</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>16.4</v>
+        <v>21.1</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>2012</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Richard Mulligan</t>
+          <t>Hope Woodhouse</t>
         </is>
       </c>
       <c r="I19" s="13" t="inlineStr">
@@ -2190,9 +2226,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-11 (Award)</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
@@ -2202,21 +2238,17 @@
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="N19" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="O19" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="N19" s="14" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="O19" s="14" t="n">
+        <v>58.3</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>5.59</v>
+        <v>0.72</v>
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
@@ -5004,7 +5036,7 @@
         </is>
       </c>
       <c r="D57" s="11" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="E57" s="11" t="n">
         <v>13.2</v>
@@ -9205,7 +9237,7 @@
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>41</v>
+        <v>40.5</v>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
@@ -9609,12 +9641,12 @@
     <row r="13" ht="14" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Hope Woodhouse</t>
+          <t>Richard Mulligan</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Monro</t>
+          <t>Sana Biotechnology</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -9629,11 +9661,11 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>SANA</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>20.4</v>
+        <v>21.3</v>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
@@ -9645,14 +9677,18 @@
           <t>biography names the network</t>
         </is>
       </c>
-      <c r="I13" s="14" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <v>58.3</v>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="K13" s="15" t="n">
-        <v>0.72</v>
+        <v>5.59</v>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
@@ -9663,12 +9699,12 @@
     <row r="14" ht="14" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Richard Mulligan</t>
+          <t>Hope Woodhouse</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Sana Biotechnology</t>
+          <t>Monro</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -9683,11 +9719,11 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>SANA</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>16.4</v>
+        <v>21.1</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
@@ -9699,18 +9735,14 @@
           <t>biography names the network</t>
         </is>
       </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+      <c r="I14" s="14" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>58.3</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>5.59</v>
+        <v>0.72</v>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
@@ -19703,7 +19735,7 @@
         </is>
       </c>
       <c r="F185" s="12" t="n">
-        <v>26.6</v>
+        <v>28.6</v>
       </c>
       <c r="G185" s="10" t="inlineStr">
         <is>
@@ -19731,12 +19763,12 @@
     <row r="186" ht="14" customHeight="1">
       <c r="A186" s="10" t="inlineStr">
         <is>
-          <t>Ashok Srivastava</t>
+          <t>Brandon Lewis</t>
         </is>
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Veon</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
@@ -19751,11 +19783,11 @@
       </c>
       <c r="E186" s="9" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>VEON</t>
         </is>
       </c>
       <c r="F186" s="12" t="n">
-        <v>26</v>
+        <v>25.4</v>
       </c>
       <c r="G186" s="10" t="inlineStr">
         <is>
@@ -19768,22 +19800,22 @@
         </is>
       </c>
       <c r="I186" s="14" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="J186" s="14" t="n">
-        <v>16.7</v>
+        <v>108.9</v>
       </c>
       <c r="K186" s="15" t="n">
-        <v>3.96</v>
+        <v>3.41</v>
       </c>
       <c r="L186" s="15" t="n">
-        <v>203.59</v>
+        <v>177.06</v>
       </c>
     </row>
     <row r="187" ht="14" customHeight="1">
       <c r="A187" s="10" t="inlineStr">
         <is>
-          <t>Brandon Lewis</t>
+          <t>Duncan Perry</t>
         </is>
       </c>
       <c r="B187" s="10" t="inlineStr">
@@ -19835,12 +19867,12 @@
     <row r="188" ht="14" customHeight="1">
       <c r="A188" s="10" t="inlineStr">
         <is>
-          <t>Duncan Perry</t>
+          <t>Kelly Osborne</t>
         </is>
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>Veon</t>
+          <t>Kinross Gold</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
@@ -19855,11 +19887,11 @@
       </c>
       <c r="E188" s="9" t="inlineStr">
         <is>
-          <t>VEON</t>
+          <t>KGC</t>
         </is>
       </c>
       <c r="F188" s="12" t="n">
-        <v>25.4</v>
+        <v>20.4</v>
       </c>
       <c r="G188" s="10" t="inlineStr">
         <is>
@@ -19872,27 +19904,27 @@
         </is>
       </c>
       <c r="I188" s="14" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J188" s="14" t="n">
-        <v>108.9</v>
+        <v>9.4</v>
       </c>
       <c r="K188" s="15" t="n">
-        <v>3.41</v>
+        <v>3.06</v>
       </c>
       <c r="L188" s="15" t="n">
-        <v>177.06</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="189" ht="14" customHeight="1">
       <c r="A189" s="10" t="inlineStr">
         <is>
-          <t>Kelly Osborne</t>
+          <t>Franz Humer</t>
         </is>
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>Kinross Gold</t>
+          <t>Allogene Therapeutics</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
@@ -19907,11 +19939,11 @@
       </c>
       <c r="E189" s="9" t="inlineStr">
         <is>
-          <t>KGC</t>
+          <t>ALLO</t>
         </is>
       </c>
       <c r="F189" s="12" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="G189" s="10" t="inlineStr">
         <is>
@@ -19923,28 +19955,32 @@
           <t>matched another way, usually an employer-name collision: not signal</t>
         </is>
       </c>
-      <c r="I189" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J189" s="14" t="n">
-        <v>9.4</v>
+      <c r="I189" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="J189" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="K189" s="15" t="n">
-        <v>3.06</v>
+        <v>1.24</v>
       </c>
       <c r="L189" s="15" t="n">
-        <v>3.06</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="190" ht="14" customHeight="1">
       <c r="A190" s="10" t="inlineStr">
         <is>
-          <t>Franz Humer</t>
+          <t>Pamala Kaufman</t>
         </is>
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>Allogene Therapeutics</t>
+          <t>Lindblad Expeditions Holdings</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
@@ -19959,11 +19995,11 @@
       </c>
       <c r="E190" s="9" t="inlineStr">
         <is>
-          <t>ALLO</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="F190" s="12" t="n">
-        <v>20.2</v>
+        <v>19.5</v>
       </c>
       <c r="G190" s="10" t="inlineStr">
         <is>
@@ -19975,32 +20011,34 @@
           <t>matched another way, usually an employer-name collision: not signal</t>
         </is>
       </c>
-      <c r="I190" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
+      <c r="I190" s="14" t="n">
+        <v>20.8</v>
       </c>
       <c r="J190" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="K190" s="15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="L190" s="15" t="n">
-        <v>1.24</v>
+      <c r="K190" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+      <c r="L190" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
       </c>
     </row>
     <row r="191" ht="14" customHeight="1">
       <c r="A191" s="10" t="inlineStr">
         <is>
-          <t>Pamala Kaufman</t>
+          <t>Danny Shepherd</t>
         </is>
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>Lindblad Expeditions Holdings</t>
+          <t>Beazer Homes USA</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
@@ -20015,7 +20053,7 @@
       </c>
       <c r="E191" s="9" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>BZH</t>
         </is>
       </c>
       <c r="F191" s="12" t="n">
@@ -20032,33 +20070,29 @@
         </is>
       </c>
       <c r="I191" s="14" t="n">
-        <v>20.8</v>
+        <v>39</v>
       </c>
       <c r="J191" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="K191" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
-      </c>
-      <c r="L191" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
+      <c r="K191" s="15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L191" s="15" t="n">
+        <v>0.78</v>
       </c>
     </row>
     <row r="192" ht="14" customHeight="1">
       <c r="A192" s="10" t="inlineStr">
         <is>
-          <t>Danny Shepherd</t>
+          <t>C. Wes Burton</t>
         </is>
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>Beazer Homes USA</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
@@ -20073,11 +20107,11 @@
       </c>
       <c r="E192" s="9" t="inlineStr">
         <is>
-          <t>BZH</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F192" s="12" t="n">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="G192" s="10" t="inlineStr">
         <is>
@@ -20090,24 +20124,22 @@
         </is>
       </c>
       <c r="I192" s="14" t="n">
-        <v>39</v>
-      </c>
-      <c r="J192" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>14.2</v>
+      </c>
+      <c r="J192" s="14" t="n">
+        <v>28.8</v>
       </c>
       <c r="K192" s="15" t="n">
-        <v>0.77</v>
+        <v>3.76</v>
       </c>
       <c r="L192" s="15" t="n">
-        <v>0.78</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="193" ht="14" customHeight="1">
       <c r="A193" s="10" t="inlineStr">
         <is>
-          <t>C. Wes Burton</t>
+          <t>Cynthia Hostetler</t>
         </is>
       </c>
       <c r="B193" s="10" t="inlineStr">
@@ -20131,7 +20163,7 @@
         </is>
       </c>
       <c r="F193" s="12" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="G193" s="10" t="inlineStr">
         <is>
@@ -20159,7 +20191,7 @@
     <row r="194" ht="14" customHeight="1">
       <c r="A194" s="10" t="inlineStr">
         <is>
-          <t>Cynthia Hostetler</t>
+          <t>David Clement</t>
         </is>
       </c>
       <c r="B194" s="10" t="inlineStr">
@@ -20183,7 +20215,7 @@
         </is>
       </c>
       <c r="F194" s="12" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="G194" s="10" t="inlineStr">
         <is>
@@ -20211,7 +20243,7 @@
     <row r="195" ht="14" customHeight="1">
       <c r="A195" s="10" t="inlineStr">
         <is>
-          <t>David Clement</t>
+          <t>Denson Franklin</t>
         </is>
       </c>
       <c r="B195" s="10" t="inlineStr">
@@ -20235,7 +20267,7 @@
         </is>
       </c>
       <c r="F195" s="12" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="G195" s="10" t="inlineStr">
         <is>
@@ -20263,7 +20295,7 @@
     <row r="196" ht="14" customHeight="1">
       <c r="A196" s="10" t="inlineStr">
         <is>
-          <t>Denson Franklin</t>
+          <t>George Willis</t>
         </is>
       </c>
       <c r="B196" s="10" t="inlineStr">
@@ -20287,7 +20319,7 @@
         </is>
       </c>
       <c r="F196" s="12" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="G196" s="10" t="inlineStr">
         <is>
@@ -20315,7 +20347,7 @@
     <row r="197" ht="14" customHeight="1">
       <c r="A197" s="10" t="inlineStr">
         <is>
-          <t>George Willis</t>
+          <t>J. Hill</t>
         </is>
       </c>
       <c r="B197" s="10" t="inlineStr">
@@ -20339,7 +20371,7 @@
         </is>
       </c>
       <c r="F197" s="12" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="G197" s="10" t="inlineStr">
         <is>
@@ -20367,7 +20399,7 @@
     <row r="198" ht="14" customHeight="1">
       <c r="A198" s="10" t="inlineStr">
         <is>
-          <t>J. Hill</t>
+          <t>J. Thomas Hill</t>
         </is>
       </c>
       <c r="B198" s="10" t="inlineStr">
@@ -20391,7 +20423,7 @@
         </is>
       </c>
       <c r="F198" s="12" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="G198" s="10" t="inlineStr">
         <is>
@@ -20419,7 +20451,7 @@
     <row r="199" ht="14" customHeight="1">
       <c r="A199" s="10" t="inlineStr">
         <is>
-          <t>J. Thomas Hill</t>
+          <t>Jerry Perkins</t>
         </is>
       </c>
       <c r="B199" s="10" t="inlineStr">
@@ -20443,7 +20475,7 @@
         </is>
       </c>
       <c r="F199" s="12" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="G199" s="10" t="inlineStr">
         <is>
@@ -20471,7 +20503,7 @@
     <row r="200" ht="14" customHeight="1">
       <c r="A200" s="10" t="inlineStr">
         <is>
-          <t>Jerry Perkins</t>
+          <t>Mark Warren</t>
         </is>
       </c>
       <c r="B200" s="10" t="inlineStr">
@@ -20495,7 +20527,7 @@
         </is>
       </c>
       <c r="F200" s="12" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="G200" s="10" t="inlineStr">
         <is>
@@ -20523,7 +20555,7 @@
     <row r="201" ht="14" customHeight="1">
       <c r="A201" s="10" t="inlineStr">
         <is>
-          <t>Mark Warren</t>
+          <t>Mary Carlisle</t>
         </is>
       </c>
       <c r="B201" s="10" t="inlineStr">
@@ -20547,7 +20579,7 @@
         </is>
       </c>
       <c r="F201" s="12" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="G201" s="10" t="inlineStr">
         <is>
@@ -20575,7 +20607,7 @@
     <row r="202" ht="14" customHeight="1">
       <c r="A202" s="10" t="inlineStr">
         <is>
-          <t>Mary Carlisle</t>
+          <t>Thomas Fanning</t>
         </is>
       </c>
       <c r="B202" s="10" t="inlineStr">
@@ -20599,7 +20631,7 @@
         </is>
       </c>
       <c r="F202" s="12" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="G202" s="10" t="inlineStr">
         <is>
@@ -20627,12 +20659,12 @@
     <row r="203" ht="14" customHeight="1">
       <c r="A203" s="10" t="inlineStr">
         <is>
-          <t>Thomas Fanning</t>
+          <t>Ashok Srivastava</t>
         </is>
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
@@ -20647,11 +20679,11 @@
       </c>
       <c r="E203" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="F203" s="12" t="n">
-        <v>18.9</v>
+        <v>18.1</v>
       </c>
       <c r="G203" s="10" t="inlineStr">
         <is>
@@ -20664,16 +20696,16 @@
         </is>
       </c>
       <c r="I203" s="14" t="n">
-        <v>14.2</v>
+        <v>11</v>
       </c>
       <c r="J203" s="14" t="n">
-        <v>28.8</v>
+        <v>16.7</v>
       </c>
       <c r="K203" s="15" t="n">
-        <v>3.76</v>
+        <v>3.96</v>
       </c>
       <c r="L203" s="15" t="n">
-        <v>9.77</v>
+        <v>203.59</v>
       </c>
     </row>
     <row r="204" ht="14" customHeight="1">
@@ -37874,6 +37906,1901 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:M35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="42.5" customWidth="1" min="2" max="2"/>
+    <col width="42.5" customWidth="1" min="3" max="3"/>
+    <col width="8.5" customWidth="1" min="4" max="4"/>
+    <col width="12.5" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="32.5" customWidth="1" min="7" max="7"/>
+    <col width="11.5" customWidth="1" min="8" max="8"/>
+    <col width="26.5" customWidth="1" min="9" max="9"/>
+    <col width="12.5" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="12.5" customWidth="1" min="12" max="12"/>
+    <col width="12.5" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>New Insider Filings — tracked people joining boards and companies (SEC Form 3)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>A Form 3 is filed within ten days of becoming a director, officer or 10% owner: the live version of the board seats the PitchBook searches recorded in September 2025. Last 120 days. Filers are matched to the tracked individuals by name, so a filing is CONFIRMED only when its company (or ticker) is in the person's own PitchBook profile; the rest share a name with a tracked person and are shown beside that person's profile to check — a CFO in Ohio is rarely the London banker of the same name. Role from the filing.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CONFIRMED — THE COMPANY IS IN THE PERSON'S OWN PROFILE — 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ROLE (FORM 3)</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>COMPANY</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>TICKER</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>THEIR PITCHBOOK PROFILE</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>NETWORK</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>OUR SCORE</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>FILED AS</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>P/TB</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Cynthia Hostetler</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Invesco Private Asset-Based Credit Fund</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Board Member at Vulcan Materials (Birmingham, AL)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Hostetler Cynthia Lynn</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Nathaniel Rothschild</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Snow Rothschild Acquisition Corp.</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>ISNR</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Executive Chairman at Volex (London, United Kingdom)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Titans &amp; Concentrated Managers</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>ROTHSCHILD NATHANIEL PVJ</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>SPAC</t>
+        </is>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>SPAC</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>SPAC</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>SPAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Duncan Perry</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>VEON Ltd.</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>VEON</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Board Member at Veon (Dubai, United Arab Emirates)</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Perry Duncan</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="L8" s="15" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="M8" s="15" t="n">
+        <v>177.06</v>
+      </c>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Brandon Lewis</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>VEON Ltd.</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>VEON</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Board Member at Veon (Dubai, United Arab Emirates)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Lewis Brandon K.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="M9" s="15" t="n">
+        <v>177.06</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SAME NAME AS A TRACKED PERSON — CHECK THE PROFILE MATCHES THE FILING — 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>ROLE (FORM 3)</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>COMPANY</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>TICKER</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>THEIR PITCHBOOK PROFILE</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>NETWORK</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>OUR SCORE</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>FILED AS</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>P/TB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="14" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Andrew Smith</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>MATRIX SERVICE CO</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>MTRX</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer, Finance &amp; Board Member at Playtech (London, United Kingdom)</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>SMITH ANDREW JOHN</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="L13" s="15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M13" s="15" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="14" ht="14" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Scott Gleason</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>SERA PROGNOSTICS, INC.</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>SERA</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Senior Vice President at Orasure Technologies (Bellaire, TX)</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Gleason Scott</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M14" s="15" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="15" ht="14" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Hassan Baqar</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>B-Scada, Inc.</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>SCDA</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Interim Chief Financial Officer at Insurance Income Strategies (Hamilton, Bermuda)</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Sequoia Network</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>BAQAR HASSAN</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="14" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Hassan Baqar</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>B-Scada, Inc.</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>SCDA</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Interim Chief Financial Officer at Insurance Income Strategies (Hamilton, Bermuda)</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Sequoia Network</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Baqar Hassan Sajjad</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="14" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Andrea Mollica</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Air Water Ventures Ltd</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>WATR</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Director at Royal Group (Abu Dhabi, United Arab Emirates)</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Gulf/Royal Family Offices</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Mollica Andrea</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="14" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Christopher Viehbacher</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Braveheart Bio, Inc.</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>BRVE</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer, President &amp; Board Member at Biogen (Cambridge, MA)</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Titans &amp; Concentrated Managers</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Viehbacher Christopher</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="14" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Cynthia Hostetler</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>ADI GLOBAL DISTRIBUTION INC.</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ADIG</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Board Member at Vulcan Materials (Birmingham, AL)</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Hostetler Cynthia Lynn</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="14" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>John Maxwell</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>TORTOISE ENERGY INFRASTRUCTURE CORP</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>TYG</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Board Member at Vulcan Industries (London (London, United Kingdom)</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>MAXWELL JOHN C III</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="14" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>David Jones</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Fidelity Private Credit Co II LLC</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>President, Chief Education Officer, Treasurer and Director at authID</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Jones David Blandford</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Cheng-Tie Chen</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>LightInTheBox Holding Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>LITB</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Vice President, Engineering (SoC Products) at Montage Technology</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Chen Cheng LOL</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K22" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+      <c r="M22" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="14" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Michael Jones</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>ProtoKinetix, Inc.</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>PKTX</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Co-Founder, Chief Executive Officer &amp; Board Member at Thrive Farmers (Roswell, GA)</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Sequoia Network</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Jones Michael Winston</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="14" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Roelof Botha</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>SPACE EXPLORATION TECHNOLOGIES CORP</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Partner, Seed/Early and Growth at Sequoia Capital (Menlo Park, CA)</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Sequoia Network</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>BOTHA ROELOF</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>450.4</v>
+      </c>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="L24" s="15" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="M24" s="15" t="n">
+        <v>7.51</v>
+      </c>
+    </row>
+    <row r="25" ht="14" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Derek Kan</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Fortinet, Inc.</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Board Member at Toll Brothers (Fort Washington, PA)</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Kan Derek T.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="L25" s="15" t="n">
+        <v>83.31</v>
+      </c>
+      <c r="M25" s="15" t="n">
+        <v>106.21</v>
+      </c>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>David Wilson</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Burke &amp; Herbert Financial Services Corp.</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>BHRB</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Founder, Owner &amp; Managing Director at Green Seed Group (Chicago, IL)</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Gulf/Royal Family Offices</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>WILSON DAVID</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L26" s="15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M26" s="15" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Elon Musk</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Director, CEO, CTO &amp; Chairman, 10% owner</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>SPACE EXPLORATION TECHNOLOGIES CORP</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Co-Founder, Board Member &amp; Chief Executive Officer at Tesla (Austin, TX)</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>Titans &amp; Concentrated Managers</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Musk Elon</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>450.4</v>
+      </c>
+      <c r="K27" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="L27" s="15" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="M27" s="15" t="n">
+        <v>7.51</v>
+      </c>
+    </row>
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>John Jackson</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>NATURAL GAS SERVICES GROUP INC</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>NGS</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Board Member, Chairman of Audit Committee &amp; Risk &amp; Member of Compliance Committee and Nominations Committee at Playtech</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>JACKSON JOHN EARL</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K28" s="14" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="L28" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M28" s="15" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Michael Smith</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Director, Chief Legal Officer</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>American Fusion, Inc.</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>AMFN</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Co-Founder, President, Chief Operating Officer &amp; Board Member at aspenify (Redwood City, CA)</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Sequoia Network</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Smith Michael Gregory</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="14" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Kevin Miller</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>EVP, CFO, Treasurer</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>UMH PROPERTIES, INC.</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>UMH</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer &amp; President at The Royal Group (Cicero, IL)</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Gulf/Royal Family Offices</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Miller Kevin S.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="L30" s="15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M30" s="15" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="31" ht="14" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Manish Bhatia</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Quantinuum Inc.</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>QNT</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer at Trident Group</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>BHATIA MANISH H</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="L31" s="15" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="M31" s="15" t="n">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Mary Kissel</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Cadre Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>CDRE</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Board Member at QXO (Greenwich, CT)</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Kissel Mary E.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="K32" s="14" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="L32" s="15" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M32" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="14" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Director, President, CEO and Director</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>FedEx Freight Holding Company, Inc.</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>FDXF</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer at SNI Companies (Jacksonville, FL)</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Gulf/Royal Family Offices</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Smith John Alan</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="K33" s="14" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+      <c r="M33" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Brandon Lewis</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Kyivstar Group Ltd.</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>KYIV</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>Board Member at Veon (Dubai, United Arab Emirates)</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Lewis Brandon K.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K34" s="14" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="L34" s="15" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M34" s="15" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="35" ht="14" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Duncan Perry</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Kyivstar Group Ltd.</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>KYIV</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>Board Member at Veon (Dubai, United Arab Emirates)</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Perry Duncan</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K35" s="14" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="L35" s="15" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M35" s="15" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:I35"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Watchlist — Not in Universe'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Family Office &amp; SWF Map'!$A$4:$L$495</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Family Office &amp; SWF Map'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'New Insider Filings'!$A$4:$I$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'New Insider Filings'!$A$4:$I$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'New Insider Filings'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Network Roster Adds'!$A$4:$F$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Network Roster Adds'!$1:$4</definedName>
@@ -3274,9 +3274,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K33" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-15 (Award)</t>
+      <c r="K33" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="D42" s="11" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E42" s="11" t="n">
         <v>2.1</v>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="D50" s="11" t="n">
-        <v>61</v>
+        <v>60.7</v>
       </c>
       <c r="E50" s="11" t="n">
         <v>4.3</v>
@@ -4716,7 +4716,7 @@
     <row r="53" ht="14" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>ALLO</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -4726,26 +4726,26 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Allogene Therapeutics, Inc.</t>
+          <t>Xometry, Inc.</t>
         </is>
       </c>
       <c r="D53" s="11" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="F53" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="10" t="inlineStr">
-        <is>
-          <t>2012</t>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>Franz Humer</t>
+          <t>Katharine Weymouth</t>
         </is>
       </c>
       <c r="I53" s="13" t="inlineStr">
@@ -4753,24 +4753,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J53" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J53" s="13" t="n">
+        <v>947668</v>
       </c>
       <c r="K53" s="10" t="inlineStr">
         <is>
-          <t>2026-06-18 (Award)</t>
+          <t>2026-08-31 (Exempt)</t>
         </is>
       </c>
       <c r="L53" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="M53" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N53" s="12" t="inlineStr">
@@ -4784,16 +4782,16 @@
         </is>
       </c>
       <c r="P53" s="15" t="n">
-        <v>1.24</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="Q53" s="15" t="n">
-        <v>1.24</v>
+        <v>17.31</v>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>ALLO</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -4803,26 +4801,26 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Xometry, Inc.</t>
+          <t>Allogene Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="D54" s="11" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="F54" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>2012</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>Katharine Weymouth</t>
+          <t>Franz Humer</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
@@ -4830,22 +4828,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J54" s="13" t="n">
-        <v>947668</v>
+      <c r="J54" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K54" s="10" t="inlineStr">
         <is>
-          <t>2026-08-31 (Exempt)</t>
+          <t>2026-06-18 (Award)</t>
         </is>
       </c>
       <c r="L54" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="M54" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N54" s="12" t="inlineStr">
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="P54" s="15" t="n">
-        <v>8.880000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="Q54" s="15" t="n">
-        <v>17.31</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1">
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="D55" s="11" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="E55" s="11" t="n">
         <v>2.6</v>
@@ -5336,7 +5336,7 @@
         </is>
       </c>
       <c r="D61" s="11" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="E61" s="11" t="n">
         <v>10.1</v>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="D65" s="11" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="E65" s="11" t="n">
         <v>1.2</v>
@@ -11943,7 +11943,7 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         </is>
       </c>
       <c r="F190" s="12" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="G190" s="10" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         </is>
       </c>
       <c r="F203" s="12" t="n">
-        <v>18.1</v>
+        <v>18.6</v>
       </c>
       <c r="G203" s="10" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         </is>
       </c>
       <c r="F207" s="12" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="G207" s="10" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         </is>
       </c>
       <c r="F208" s="12" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="G208" s="10" t="inlineStr">
         <is>
@@ -21139,12 +21139,12 @@
     <row r="212" ht="14" customHeight="1">
       <c r="A212" s="10" t="inlineStr">
         <is>
-          <t>Bill Roeschlein</t>
+          <t>Bryan Murphy</t>
         </is>
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>Tigo Energy</t>
+          <t>Greenlight Capital Re</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="E212" s="9" t="inlineStr">
         <is>
-          <t>TYGO</t>
+          <t>GLRE</t>
         </is>
       </c>
       <c r="F212" s="12" t="n">
@@ -21175,28 +21175,30 @@
           <t>matched another way, usually an employer-name collision: not signal</t>
         </is>
       </c>
-      <c r="I212" s="14" t="n">
-        <v>4.2</v>
+      <c r="I212" s="12" t="inlineStr">
+        <is>
+          <t>net cash</t>
+        </is>
       </c>
       <c r="J212" s="14" t="n">
-        <v>6.1</v>
+        <v>9.9</v>
       </c>
       <c r="K212" s="15" t="n">
-        <v>1.49</v>
+        <v>0.71</v>
       </c>
       <c r="L212" s="15" t="n">
-        <v>2.15</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="213" ht="14" customHeight="1">
       <c r="A213" s="10" t="inlineStr">
         <is>
-          <t>Bryan Murphy</t>
+          <t>Bill Roeschlein</t>
         </is>
       </c>
       <c r="B213" s="10" t="inlineStr">
         <is>
-          <t>Greenlight Capital Re</t>
+          <t>Tigo Energy</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
@@ -21211,11 +21213,11 @@
       </c>
       <c r="E213" s="9" t="inlineStr">
         <is>
-          <t>GLRE</t>
+          <t>TYGO</t>
         </is>
       </c>
       <c r="F213" s="12" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="G213" s="10" t="inlineStr">
         <is>
@@ -21227,19 +21229,17 @@
           <t>matched another way, usually an employer-name collision: not signal</t>
         </is>
       </c>
-      <c r="I213" s="12" t="inlineStr">
-        <is>
-          <t>net cash</t>
-        </is>
+      <c r="I213" s="14" t="n">
+        <v>4.2</v>
       </c>
       <c r="J213" s="14" t="n">
-        <v>9.9</v>
+        <v>6.1</v>
       </c>
       <c r="K213" s="15" t="n">
-        <v>0.71</v>
+        <v>1.49</v>
       </c>
       <c r="L213" s="15" t="n">
-        <v>0.82</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="214" ht="14" customHeight="1">
@@ -37906,7 +37906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -38287,7 +38287,7 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>SAME NAME AS A TRACKED PERSON — CHECK THE PROFILE MATCHES THE FILING — 23</t>
+          <t>SAME NAME AS A TRACKED PERSON — CHECK THE PROFILE MATCHES THE FILING — 20</t>
         </is>
       </c>
     </row>
@@ -38481,37 +38481,37 @@
     <row r="15" ht="14" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Hassan Baqar</t>
+          <t>Christopher Viehbacher</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>B-Scada, Inc.</t>
+          <t>Braveheart Bio, Inc.</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>SCDA</t>
+          <t>BRVE</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Interim Chief Financial Officer at Insurance Income Strategies (Hamilton, Bermuda)</t>
+          <t>Chief Executive Officer, President &amp; Board Member at Biogen (Cambridge, MA)</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Titans &amp; Concentrated Managers</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -38521,7 +38521,7 @@
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>BAQAR HASSAN</t>
+          <t>Viehbacher Christopher</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
@@ -38548,37 +38548,37 @@
     <row r="16" ht="14" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Hassan Baqar</t>
+          <t>Cynthia Hostetler</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>B-Scada, Inc.</t>
+          <t>ADI GLOBAL DISTRIBUTION INC.</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>SCDA</t>
+          <t>ADIG</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>Interim Chief Financial Officer at Insurance Income Strategies (Hamilton, Bermuda)</t>
+          <t>Board Member at Vulcan Materials (Birmingham, AL)</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -38588,7 +38588,7 @@
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>Baqar Hassan Sajjad</t>
+          <t>Hostetler Cynthia Lynn</t>
         </is>
       </c>
       <c r="J16" s="12" t="inlineStr">
@@ -38615,7 +38615,7 @@
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Andrea Mollica</t>
+          <t>David Jones</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -38625,27 +38625,27 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Air Water Ventures Ltd</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>WATR</t>
+          <t>Fidelity Private Credit Co II LLC</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>Director at Royal Group (Abu Dhabi, United Arab Emirates)</t>
+          <t>President, Chief Education Officer, Treasurer and Director at authID</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -38655,7 +38655,7 @@
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Mollica Andrea</t>
+          <t>Jones David Blandford</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
@@ -38682,74 +38682,64 @@
     <row r="18" ht="14" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Christopher Viehbacher</t>
+          <t>Mark Hudson</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>VP, Corporate Controller &amp; CAO</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Braveheart Bio, Inc.</t>
+          <t>MODINE MANUFACTURING CO</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>BRVE</t>
+          <t>MOD</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>Chief Executive Officer, President &amp; Board Member at Biogen (Cambridge, MA)</t>
+          <t>Chairman of the Council at Duchy of Lancaster</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Managers</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Gulf/Royal Family Offices</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>26.9</v>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>Viehbacher Christopher</t>
-        </is>
-      </c>
-      <c r="J18" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K18" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L18" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M18" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Hudson Mark D</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="L18" s="15" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="M18" s="15" t="n">
+        <v>14.73</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Cynthia Hostetler</t>
+          <t>Cheng-Tie Chen</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -38759,22 +38749,22 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>ADI GLOBAL DISTRIBUTION INC.</t>
+          <t>LightInTheBox Holding Co., Ltd.</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>ADIG</t>
+          <t>LITB</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>Board Member at Vulcan Materials (Birmingham, AL)</t>
+          <t>Vice President, Engineering (SoC Products) at Montage Technology</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -38782,41 +38772,35 @@
           <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H19" s="12" t="n">
+        <v>5</v>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>Hostetler Cynthia Lynn</t>
-        </is>
-      </c>
-      <c r="J19" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Chen Cheng LOL</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>3</v>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg equity</t>
         </is>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>John Maxwell</t>
+          <t>Michael Jones</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -38826,62 +38810,64 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>TORTOISE ENERGY INFRASTRUCTURE CORP</t>
+          <t>ProtoKinetix, Inc.</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>TYG</t>
+          <t>PKTX</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>Board Member at Vulcan Industries (London (London, United Kingdom)</t>
+          <t>Co-Founder, Chief Executive Officer &amp; Board Member at Thrive Farmers (Roswell, GA)</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>5.3</v>
+          <t>Sequoia Network</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>MAXWELL JOHN C III</t>
+          <t>Jones Michael Winston</t>
         </is>
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="12" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>David Jones</t>
+          <t>Roelof Botha</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -38891,64 +38877,56 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Fidelity Private Credit Co II LLC</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>SPACE EXPLORATION TECHNOLOGIES CORP</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>President, Chief Education Officer, Treasurer and Director at authID</t>
+          <t>Partner, Seed/Early and Growth at Sequoia Capital (Menlo Park, CA)</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Sequoia Network</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>27.9</v>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>Jones David Blandford</t>
-        </is>
-      </c>
-      <c r="J21" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>BOTHA ROELOF</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>450.4</v>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L21" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M21" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="L21" s="15" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="M21" s="15" t="n">
+        <v>7.51</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Cheng-Tie Chen</t>
+          <t>Derek Kan</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -38958,22 +38936,22 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>LightInTheBox Holding Co., Ltd.</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>LITB</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>Vice President, Engineering (SoC Products) at Montage Technology</t>
+          <t>Board Member at Toll Brothers (Fort Washington, PA)</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -38982,34 +38960,30 @@
         </is>
       </c>
       <c r="H22" s="12" t="n">
-        <v>5</v>
+        <v>-3.1</v>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Chen Cheng LOL</t>
+          <t>Kan Derek T.</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
-        <v>1.4</v>
+        <v>43.3</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
-      </c>
-      <c r="M22" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
+        <v>61.4</v>
+      </c>
+      <c r="L22" s="15" t="n">
+        <v>83.31</v>
+      </c>
+      <c r="M22" s="15" t="n">
+        <v>106.21</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Michael Jones</t>
+          <t>David Wilson</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -39019,69 +38993,59 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>ProtoKinetix, Inc.</t>
+          <t>Burke &amp; Herbert Financial Services Corp.</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>PKTX</t>
+          <t>BHRB</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>Co-Founder, Chief Executive Officer &amp; Board Member at Thrive Farmers (Roswell, GA)</t>
+          <t>Founder, Owner &amp; Managing Director at Green Seed Group (Chicago, IL)</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Gulf/Royal Family Offices</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>20.2</v>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>Jones Michael Winston</t>
-        </is>
-      </c>
-      <c r="J23" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K23" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>WILSON DAVID</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L23" s="15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M23" s="15" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Roelof Botha</t>
+          <t>Elon Musk</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Director, CEO, CTO &amp; Chairman, 10% owner</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -39096,17 +39060,17 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Partner, Seed/Early and Growth at Sequoia Capital (Menlo Park, CA)</t>
+          <t>Co-Founder, Board Member &amp; Chief Executive Officer at Tesla (Austin, TX)</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Titans &amp; Concentrated Managers</t>
         </is>
       </c>
       <c r="H24" s="12" t="n">
@@ -39114,7 +39078,7 @@
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>BOTHA ROELOF</t>
+          <t>Musk Elon</t>
         </is>
       </c>
       <c r="J24" s="14" t="n">
@@ -39135,7 +39099,7 @@
     <row r="25" ht="14" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Derek Kan</t>
+          <t>John Jackson</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -39145,22 +39109,22 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>NATURAL GAS SERVICES GROUP INC</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>Board Member at Toll Brothers (Fort Washington, PA)</t>
+          <t>Board Member, Chairman of Audit Committee &amp; Risk &amp; Member of Compliance Committee and Nominations Committee at Playtech</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -39169,146 +39133,154 @@
         </is>
       </c>
       <c r="H25" s="12" t="n">
-        <v>-3.1</v>
+        <v>10</v>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>Kan Derek T.</t>
+          <t>JACKSON JOHN EARL</t>
         </is>
       </c>
       <c r="J25" s="14" t="n">
-        <v>43.3</v>
+        <v>7.2</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>61.4</v>
+        <v>20.4</v>
       </c>
       <c r="L25" s="15" t="n">
-        <v>83.31</v>
+        <v>1.43</v>
       </c>
       <c r="M25" s="15" t="n">
-        <v>106.21</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>David Wilson</t>
+          <t>Michael Smith</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Director, Chief Legal Officer</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Burke &amp; Herbert Financial Services Corp.</t>
+          <t>American Fusion, Inc.</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>BHRB</t>
+          <t>AMFN</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>Founder, Owner &amp; Managing Director at Green Seed Group (Chicago, IL)</t>
+          <t>Co-Founder, President, Chief Operating Officer &amp; Board Member at aspenify (Redwood City, CA)</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="n">
-        <v>20.2</v>
+          <t>Sequoia Network</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>WILSON DAVID</t>
-        </is>
-      </c>
-      <c r="J26" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="K26" s="14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L26" s="15" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="M26" s="15" t="n">
-        <v>1.05</v>
+          <t>Smith Michael Gregory</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Elon Musk</t>
+          <t>Kevin Miller</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Director, CEO, CTO &amp; Chairman, 10% owner</t>
+          <t>EVP, CFO, Treasurer</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>SPACE EXPLORATION TECHNOLOGIES CORP</t>
+          <t>UMH PROPERTIES, INC.</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>SPCX</t>
+          <t>UMH</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>Co-Founder, Board Member &amp; Chief Executive Officer at Tesla (Austin, TX)</t>
+          <t>Chief Executive Officer &amp; President at The Royal Group (Cicero, IL)</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Managers</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="H27" s="12" t="n">
-        <v>27.9</v>
+        <v>20</v>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Musk Elon</t>
+          <t>Miller Kevin S.</t>
         </is>
       </c>
       <c r="J27" s="14" t="n">
-        <v>450.4</v>
-      </c>
-      <c r="K27" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="K27" s="14" t="n">
+        <v>84.8</v>
       </c>
       <c r="L27" s="15" t="n">
-        <v>6.75</v>
+        <v>1.46</v>
       </c>
       <c r="M27" s="15" t="n">
-        <v>7.51</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>John Jackson</t>
+          <t>Manish Bhatia</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -39318,22 +39290,22 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>NATURAL GAS SERVICES GROUP INC</t>
+          <t>Quantinuum Inc.</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>QNT</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>Board Member, Chairman of Audit Committee &amp; Risk &amp; Member of Compliance Committee and Nominations Committee at Playtech</t>
+          <t>Chief Financial Officer at Trident Group</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -39342,122 +39314,118 @@
         </is>
       </c>
       <c r="H28" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>JACKSON JOHN EARL</t>
-        </is>
-      </c>
-      <c r="J28" s="14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K28" s="14" t="n">
-        <v>20.4</v>
+          <t>BHATIA MANISH H</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="K28" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="L28" s="15" t="n">
-        <v>1.43</v>
+        <v>4.08</v>
       </c>
       <c r="M28" s="15" t="n">
-        <v>1.44</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Michael Smith</t>
+          <t>Mary Kissel</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Director, Chief Legal Officer</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>American Fusion, Inc.</t>
+          <t>Cadre Holdings, Inc.</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>AMFN</t>
+          <t>CDRE</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>Co-Founder, President, Chief Operating Officer &amp; Board Member at aspenify (Redwood City, CA)</t>
+          <t>Board Member at QXO (Greenwich, CT)</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>21.9</v>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Smith Michael Gregory</t>
-        </is>
-      </c>
-      <c r="J29" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K29" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L29" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Kissel Mary E.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="L29" s="15" t="n">
+        <v>3.23</v>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>neg TBV</t>
         </is>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Kevin Miller</t>
+          <t>John Smith</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>EVP, CFO, Treasurer</t>
+          <t>Director, President, CEO and Director</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>UMH PROPERTIES, INC.</t>
+          <t>FedEx Freight Holding Company, Inc.</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>UMH</t>
+          <t>FDXF</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Chief Executive Officer &amp; President at The Royal Group (Cicero, IL)</t>
+          <t>Chief Executive Officer at SNI Companies (Jacksonville, FL)</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -39466,30 +39434,34 @@
         </is>
       </c>
       <c r="H30" s="12" t="n">
-        <v>20</v>
+        <v>17.9</v>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>Miller Kevin S.</t>
+          <t>Smith John Alan</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
-        <v>16</v>
+        <v>25.5</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="L30" s="15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M30" s="15" t="n">
-        <v>1.46</v>
+        <v>30.2</v>
+      </c>
+      <c r="L30" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+      <c r="M30" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Manish Bhatia</t>
+          <t>Brandon Lewis</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -39499,22 +39471,22 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Quantinuum Inc.</t>
+          <t>Kyivstar Group Ltd.</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>QNT</t>
+          <t>KYIV</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>Chief Financial Officer at Trident Group</t>
+          <t>Board Member at Veon (Dubai, United Arab Emirates)</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -39523,34 +39495,30 @@
         </is>
       </c>
       <c r="H31" s="12" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>BHATIA MANISH H</t>
-        </is>
-      </c>
-      <c r="J31" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="K31" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+          <t>Lewis Brandon K.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>19.6</v>
       </c>
       <c r="L31" s="15" t="n">
-        <v>4.08</v>
+        <v>2.22</v>
       </c>
       <c r="M31" s="15" t="n">
-        <v>5.76</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Mary Kissel</t>
+          <t>Duncan Perry</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -39560,22 +39528,22 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Cadre Holdings, Inc.</t>
+          <t>Kyivstar Group Ltd.</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>CDRE</t>
+          <t>KYIV</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>Board Member at QXO (Greenwich, CT)</t>
+          <t>Board Member at Veon (Dubai, United Arab Emirates)</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -39584,205 +39552,28 @@
         </is>
       </c>
       <c r="H32" s="12" t="n">
-        <v>21.5</v>
+        <v>3.8</v>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>Kissel Mary E.</t>
+          <t>Perry Duncan</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
-        <v>16.2</v>
+        <v>5.9</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>30.1</v>
+        <v>19.6</v>
       </c>
       <c r="L32" s="15" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="M32" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="14" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>John Smith</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>Director, President, CEO and Director</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>FedEx Freight Holding Company, Inc.</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>FDXF</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>Chief Executive Officer at SNI Companies (Jacksonville, FL)</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>Gulf/Royal Family Offices</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>Smith John Alan</t>
-        </is>
-      </c>
-      <c r="J33" s="14" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="K33" s="14" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="L33" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
-      </c>
-      <c r="M33" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="14" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Brandon Lewis</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>Kyivstar Group Ltd.</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>KYIV</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>Board Member at Veon (Dubai, United Arab Emirates)</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>Billionaire/Oligarch Vehicles</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Lewis Brandon K.</t>
-        </is>
-      </c>
-      <c r="J34" s="14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K34" s="14" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="L34" s="15" t="n">
         <v>2.22</v>
       </c>
-      <c r="M34" s="15" t="n">
+      <c r="M32" s="15" t="n">
         <v>4.25</v>
       </c>
     </row>
-    <row r="35" ht="14" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Duncan Perry</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>Kyivstar Group Ltd.</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>KYIV</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>Board Member at Veon (Dubai, United Arab Emirates)</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>Billionaire/Oligarch Vehicles</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>Perry Duncan</t>
-        </is>
-      </c>
-      <c r="J35" s="14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K35" s="14" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="L35" s="15" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="M35" s="15" t="n">
-        <v>4.25</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:I35"/>
+  <autoFilter ref="A4:I32"/>
   <mergeCells count="4">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A11:I11"/>

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>6.6</v>
@@ -1273,16 +1273,16 @@
         </is>
       </c>
       <c r="N6" s="14" t="n">
-        <v>24.5</v>
+        <v>25.2</v>
       </c>
       <c r="O6" s="14" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="P6" s="15" t="n">
-        <v>4.28</v>
+        <v>4.48</v>
       </c>
       <c r="Q6" s="15" t="n">
-        <v>4.76</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -1346,16 +1346,16 @@
         </is>
       </c>
       <c r="N7" s="14" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="O7" s="14" t="n">
-        <v>27.3</v>
+        <v>27</v>
       </c>
       <c r="P7" s="15" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="Q7" s="15" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
@@ -1419,13 +1419,13 @@
         </is>
       </c>
       <c r="N8" s="14" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="O8" s="14" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="P8" s="15" t="n">
-        <v>16.87</v>
+        <v>16.7</v>
       </c>
       <c r="Q8" s="12" t="inlineStr">
         <is>
@@ -1494,16 +1494,16 @@
         </is>
       </c>
       <c r="N9" s="14" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="O9" s="14" t="n">
-        <v>34.4</v>
+        <v>35.8</v>
       </c>
       <c r="P9" s="15" t="n">
-        <v>10.88</v>
+        <v>11.33</v>
       </c>
       <c r="Q9" s="15" t="n">
-        <v>31.36</v>
+        <v>32.65</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
@@ -1570,13 +1570,13 @@
         <v>9</v>
       </c>
       <c r="O10" s="14" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P10" s="15" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
       <c r="Q10" s="15" t="n">
-        <v>6.17</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="P11" s="15" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" s="15" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>6.7</v>
@@ -1720,10 +1720,10 @@
         <v>8</v>
       </c>
       <c r="O12" s="14" t="n">
-        <v>16.1</v>
+        <v>16.4</v>
       </c>
       <c r="P12" s="15" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="Q12" s="12" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="P13" s="15" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q13" s="15" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
@@ -1865,16 +1865,16 @@
         </is>
       </c>
       <c r="N14" s="14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O14" s="14" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="P14" s="15" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Q14" s="15" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
@@ -1941,7 +1941,7 @@
         <v>5.5</v>
       </c>
       <c r="O15" s="14" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P15" s="15" t="n">
         <v>0.79</v>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="N16" s="14" t="n">
-        <v>42.3</v>
+        <v>43.7</v>
       </c>
       <c r="O16" s="12" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="P16" s="15" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="Q16" s="12" t="inlineStr">
         <is>
@@ -2093,13 +2093,13 @@
         <v>1.5</v>
       </c>
       <c r="O17" s="14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="E18" s="11" t="n">
         <v>3.1</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="P18" s="15" t="n">
-        <v>5.58</v>
+        <v>5.63</v>
       </c>
       <c r="Q18" s="12" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="E19" s="11" t="n">
         <v>3</v>
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="N19" s="14" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="O19" s="14" t="n">
-        <v>58.3</v>
+        <v>59.5</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
@@ -2317,16 +2317,16 @@
         </is>
       </c>
       <c r="N20" s="14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" s="14" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="P20" s="15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q20" s="15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
@@ -2390,16 +2390,16 @@
         </is>
       </c>
       <c r="N21" s="14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O21" s="14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P21" s="15" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="Q21" s="15" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="P22" s="15" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="Q22" s="15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
@@ -2540,16 +2540,16 @@
         </is>
       </c>
       <c r="N23" s="14" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="O23" s="14" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="P23" s="15" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="Q23" s="15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="O26" s="14" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="P26" s="15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Q26" s="12" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="P27" s="15" t="n">
-        <v>4.69</v>
+        <v>4.93</v>
       </c>
       <c r="Q27" s="15" t="n">
-        <v>171.53</v>
+        <v>180.6</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
@@ -2923,10 +2923,10 @@
         <v>16.6</v>
       </c>
       <c r="P28" s="15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q28" s="15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="P29" s="15" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="Q29" s="15" t="n">
-        <v>34.59</v>
+        <v>34.77</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
@@ -3065,10 +3065,10 @@
         </is>
       </c>
       <c r="N30" s="14" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="O30" s="14" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="P31" s="15" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="Q31" s="15" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
@@ -3223,10 +3223,10 @@
         <v>0.9</v>
       </c>
       <c r="P32" s="15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="Q32" s="15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="33" ht="14" customHeight="1">
@@ -3293,13 +3293,13 @@
         <v>5.2</v>
       </c>
       <c r="O33" s="14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="P33" s="15" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="Q33" s="15" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="P35" s="15" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="Q35" s="15" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
@@ -3588,16 +3588,16 @@
         </is>
       </c>
       <c r="N37" s="14" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="O37" s="14" t="n">
-        <v>27.4</v>
+        <v>27.7</v>
       </c>
       <c r="P37" s="15" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="Q37" s="15" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="P38" s="15" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="Q38" s="12" t="inlineStr">
         <is>
@@ -3738,16 +3738,16 @@
         </is>
       </c>
       <c r="N39" s="14" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="O39" s="14" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="P39" s="15" t="n">
-        <v>7.91</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q39" s="15" t="n">
-        <v>7.91</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="P41" s="15" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="Q41" s="12" t="inlineStr">
         <is>
@@ -3963,16 +3963,16 @@
         </is>
       </c>
       <c r="N42" s="14" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="O42" s="14" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="P42" s="15" t="n">
-        <v>4.08</v>
+        <v>4.17</v>
       </c>
       <c r="Q42" s="15" t="n">
-        <v>5.72</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="E43" s="11" t="n">
         <v>1.1</v>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="P43" s="15" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="Q43" s="15" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
@@ -4113,16 +4113,16 @@
         </is>
       </c>
       <c r="N44" s="14" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="O44" s="14" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="P44" s="15" t="n">
-        <v>5.35</v>
+        <v>5.48</v>
       </c>
       <c r="Q44" s="15" t="n">
-        <v>6.05</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
@@ -4186,16 +4186,16 @@
         </is>
       </c>
       <c r="N45" s="14" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="O45" s="14" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="P45" s="15" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="Q45" s="15" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
@@ -4259,16 +4259,16 @@
         </is>
       </c>
       <c r="N46" s="14" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="O46" s="14" t="n">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="P46" s="15" t="n">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="Q46" s="15" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="N47" s="14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="P47" s="15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q47" s="12" t="inlineStr">
         <is>
@@ -4409,16 +4409,16 @@
         </is>
       </c>
       <c r="N48" s="14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O48" s="14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="P48" s="15" t="n">
         <v>0.45</v>
       </c>
       <c r="Q48" s="15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
@@ -4482,16 +4482,16 @@
         </is>
       </c>
       <c r="N49" s="14" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="O49" s="14" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="P49" s="15" t="n">
-        <v>4.28</v>
+        <v>4.3</v>
       </c>
       <c r="Q49" s="15" t="n">
-        <v>4.28</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="D50" s="11" t="n">
-        <v>60.1</v>
+        <v>59.7</v>
       </c>
       <c r="E50" s="11" t="n">
         <v>4.3</v>
@@ -4555,13 +4555,13 @@
         </is>
       </c>
       <c r="N50" s="14" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="O50" s="14" t="n">
-        <v>29.7</v>
+        <v>29.4</v>
       </c>
       <c r="P50" s="15" t="n">
-        <v>5.36</v>
+        <v>5.3</v>
       </c>
       <c r="Q50" s="12" t="inlineStr">
         <is>
@@ -4630,16 +4630,16 @@
         </is>
       </c>
       <c r="N51" s="14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O51" s="14" t="n">
-        <v>108.7</v>
+        <v>115</v>
       </c>
       <c r="P51" s="15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q51" s="15" t="n">
-        <v>176.77</v>
+        <v>187.06</v>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="P52" s="15" t="n">
-        <v>9.17</v>
+        <v>9.44</v>
       </c>
       <c r="Q52" s="15" t="n">
-        <v>17.89</v>
+        <v>18.41</v>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
@@ -4784,10 +4784,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="P53" s="15" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="Q53" s="15" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
@@ -4835,9 +4835,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K54" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-18 (Award)</t>
+      <c r="K54" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L54" s="10" t="inlineStr">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="P54" s="15" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Q54" s="15" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1">
@@ -5085,7 +5085,7 @@
         <v>1.65</v>
       </c>
       <c r="Q57" s="15" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
@@ -5159,16 +5159,16 @@
         </is>
       </c>
       <c r="P58" s="15" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="Q58" s="15" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>CMPS</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -5178,26 +5178,26 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Lindblad Expeditions Holdings, Inc.</t>
+          <t>COMPASS Pathways plc</t>
         </is>
       </c>
       <c r="D59" s="11" t="n">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="F59" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G59" s="10" t="inlineStr">
-        <is>
-          <t>2022</t>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>Pamala Kaufman</t>
+          <t>Annalisa Jenkins</t>
         </is>
       </c>
       <c r="I59" s="13" t="inlineStr">
@@ -5210,9 +5210,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K59" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-08 (Award)</t>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L59" s="10" t="inlineStr">
@@ -5222,32 +5222,30 @@
       </c>
       <c r="M59" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="N59" s="14" t="n">
-        <v>23.2</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N59" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
       </c>
       <c r="O59" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="P59" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
-      </c>
-      <c r="Q59" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
+      <c r="P59" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q59" s="15" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -5257,26 +5255,26 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>COMPASS Pathways plc</t>
+          <t>SLB N.V.</t>
         </is>
       </c>
       <c r="D60" s="11" t="n">
-        <v>16.2</v>
+        <v>14.9</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>4.6</v>
+        <v>10.1</v>
       </c>
       <c r="F60" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>2011</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>Annalisa Jenkins</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="I60" s="13" t="inlineStr">
@@ -5301,30 +5299,26 @@
       </c>
       <c r="M60" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="N60" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="O60" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N60" s="14" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="O60" s="14" t="n">
+        <v>23.4</v>
       </c>
       <c r="P60" s="15" t="n">
-        <v>13.78</v>
+        <v>2.79</v>
       </c>
       <c r="Q60" s="15" t="n">
-        <v>13.78</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -5334,26 +5328,26 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>SLB N.V.</t>
+          <t>Lindblad Expeditions Holdings, Inc.</t>
         </is>
       </c>
       <c r="D61" s="11" t="n">
-        <v>14.9</v>
+        <v>13.8</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>10.1</v>
+        <v>2.6</v>
       </c>
       <c r="F61" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>Pamala Kaufman</t>
         </is>
       </c>
       <c r="I61" s="13" t="inlineStr">
@@ -5366,9 +5360,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K61" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K61" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-08 (Award)</t>
         </is>
       </c>
       <c r="L61" s="10" t="inlineStr">
@@ -5378,20 +5372,26 @@
       </c>
       <c r="M61" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N61" s="14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O61" s="14" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="P61" s="15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q61" s="15" t="n">
-        <v>14.2</v>
+        <v>25.2</v>
+      </c>
+      <c r="O61" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="P61" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+      <c r="Q61" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
@@ -5461,10 +5461,10 @@
         <v>7.8</v>
       </c>
       <c r="P62" s="15" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="Q62" s="15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="P65" s="15" t="n">
-        <v>11.05</v>
+        <v>11.23</v>
       </c>
       <c r="Q65" s="15" t="n">
-        <v>11.05</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
@@ -5762,13 +5762,13 @@
         </is>
       </c>
       <c r="O66" s="14" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="P66" s="15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="Q66" s="15" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
@@ -5907,16 +5907,16 @@
         </is>
       </c>
       <c r="N68" s="14" t="n">
-        <v>143.2</v>
+        <v>160.8</v>
       </c>
       <c r="O68" s="14" t="n">
-        <v>107.6</v>
+        <v>121.1</v>
       </c>
       <c r="P68" s="15" t="n">
-        <v>22.22</v>
+        <v>25</v>
       </c>
       <c r="Q68" s="15" t="n">
-        <v>73.62</v>
+        <v>82.84</v>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
@@ -5980,16 +5980,16 @@
         </is>
       </c>
       <c r="N69" s="14" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="O69" s="14" t="n">
-        <v>53.6</v>
+        <v>54.1</v>
       </c>
       <c r="P69" s="15" t="n">
-        <v>6.5</v>
+        <v>6.57</v>
       </c>
       <c r="Q69" s="15" t="n">
-        <v>6.66</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="N70" s="14" t="n">
-        <v>23.3</v>
+        <v>24.5</v>
       </c>
       <c r="O70" s="12" t="inlineStr">
         <is>
@@ -6201,13 +6201,13 @@
         </is>
       </c>
       <c r="N72" s="14" t="n">
-        <v>40.1</v>
+        <v>39.9</v>
       </c>
       <c r="O72" s="14" t="n">
-        <v>3926.4</v>
+        <v>3917</v>
       </c>
       <c r="P72" s="15" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="Q72" s="15" t="n">
         <v>0.9399999999999999</v>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="D74" s="11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="E74" s="11" t="n">
         <v>2.7</v>
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="N74" s="14" t="n">
-        <v>18.6</v>
+        <v>19.1</v>
       </c>
       <c r="O74" s="14" t="n">
-        <v>45.9</v>
+        <v>47.1</v>
       </c>
       <c r="P74" s="15" t="n">
-        <v>52.8</v>
+        <v>54.13</v>
       </c>
       <c r="Q74" s="12" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="N75" s="14" t="n">
-        <v>144.5</v>
+        <v>143.1</v>
       </c>
       <c r="O75" s="12" t="inlineStr">
         <is>
@@ -6438,10 +6438,10 @@
         </is>
       </c>
       <c r="P75" s="15" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
       <c r="Q75" s="15" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
@@ -6505,16 +6505,16 @@
         </is>
       </c>
       <c r="N76" s="14" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="O76" s="14" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="P76" s="15" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Q76" s="15" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
@@ -6578,16 +6578,16 @@
         </is>
       </c>
       <c r="N77" s="14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O77" s="14" t="n">
         <v>10.4</v>
       </c>
       <c r="P77" s="15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q77" s="15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
@@ -6649,16 +6649,16 @@
         </is>
       </c>
       <c r="N78" s="14" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="O78" s="14" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="P78" s="15" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="Q78" s="15" t="n">
-        <v>3.57</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="79" ht="14" customHeight="1">
@@ -6722,16 +6722,16 @@
         </is>
       </c>
       <c r="N79" s="14" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="O79" s="14" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="P79" s="15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Q79" s="15" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="80" ht="14" customHeight="1">
@@ -6795,13 +6795,13 @@
         </is>
       </c>
       <c r="N80" s="14" t="n">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="O80" s="14" t="n">
-        <v>19.3</v>
+        <v>20.1</v>
       </c>
       <c r="P80" s="15" t="n">
-        <v>35.14</v>
+        <v>36.49</v>
       </c>
       <c r="Q80" s="12" t="inlineStr">
         <is>
@@ -6873,13 +6873,13 @@
         <v>1.5</v>
       </c>
       <c r="O81" s="14" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="P81" s="15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Q81" s="15" t="n">
-        <v>6.55</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="82" ht="14" customHeight="1">
@@ -6943,22 +6943,22 @@
         </is>
       </c>
       <c r="N82" s="14" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="O82" s="14" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="P82" s="15" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Q82" s="15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="83" ht="14" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -6968,26 +6968,26 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group Ltd</t>
+          <t>Sprouts Farmers Market, Inc.</t>
         </is>
       </c>
       <c r="D83" s="11" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="F83" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G83" s="10" t="inlineStr">
-        <is>
-          <t>2022</t>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Douglas Rauch</t>
         </is>
       </c>
       <c r="I83" s="13" t="inlineStr">
@@ -7010,28 +7010,28 @@
           <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
-      <c r="M83" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M83" s="10" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N83" s="14" t="n">
-        <v>5.6</v>
+        <v>7.9</v>
       </c>
       <c r="O83" s="14" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="P83" s="15" t="n">
-        <v>1.13</v>
+        <v>4.12</v>
       </c>
       <c r="Q83" s="15" t="n">
-        <v>1.28</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="84" ht="14" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -7041,26 +7041,26 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Danaos Corporation</t>
+          <t>Woodside Energy Group Ltd</t>
         </is>
       </c>
       <c r="D84" s="11" t="n">
         <v>1.4</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F84" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="I84" s="13" t="inlineStr">
@@ -7080,31 +7080,31 @@
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
-        </is>
-      </c>
-      <c r="M84" s="10" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>Billionaire/Oligarch Vehicles</t>
+        </is>
+      </c>
+      <c r="M84" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N84" s="14" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="O84" s="14" t="n">
-        <v>5.2</v>
+        <v>13.4</v>
       </c>
       <c r="P84" s="15" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="Q84" s="15" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="85" ht="14" customHeight="1">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>SFM</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
@@ -7114,26 +7114,26 @@
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market, Inc.</t>
+          <t>Danaos Corporation</t>
         </is>
       </c>
       <c r="D85" s="11" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="F85" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G85" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>2005</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>Douglas Rauch</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="I85" s="13" t="inlineStr">
@@ -7153,25 +7153,25 @@
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="M85" s="10" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N85" s="14" t="n">
-        <v>8.1</v>
+        <v>4.2</v>
       </c>
       <c r="O85" s="14" t="n">
-        <v>12.6</v>
+        <v>5.5</v>
       </c>
       <c r="P85" s="15" t="n">
-        <v>4.15</v>
+        <v>0.73</v>
       </c>
       <c r="Q85" s="15" t="n">
-        <v>6.85</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="86" ht="14" customHeight="1">
@@ -7235,16 +7235,16 @@
         </is>
       </c>
       <c r="N86" s="14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O86" s="14" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="P86" s="15" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Q86" s="15" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
     </row>
   </sheetData>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>6.6</v>
@@ -7505,16 +7505,16 @@
         </is>
       </c>
       <c r="K6" s="14" t="n">
-        <v>24.5</v>
+        <v>25.2</v>
       </c>
       <c r="L6" s="14" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="M6" s="15" t="n">
-        <v>4.28</v>
+        <v>4.48</v>
       </c>
       <c r="N6" s="15" t="n">
-        <v>4.76</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -7629,16 +7629,16 @@
         </is>
       </c>
       <c r="K8" s="14" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="L8" s="14" t="n">
-        <v>27.3</v>
+        <v>27</v>
       </c>
       <c r="M8" s="15" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="N8" s="15" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
@@ -7689,13 +7689,13 @@
         </is>
       </c>
       <c r="K9" s="14" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="M9" s="15" t="n">
-        <v>16.87</v>
+        <v>16.7</v>
       </c>
       <c r="N9" s="12" t="inlineStr">
         <is>
@@ -7751,16 +7751,16 @@
         </is>
       </c>
       <c r="K10" s="14" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="L10" s="14" t="n">
-        <v>34.4</v>
+        <v>35.8</v>
       </c>
       <c r="M10" s="15" t="n">
-        <v>10.88</v>
+        <v>11.33</v>
       </c>
       <c r="N10" s="15" t="n">
-        <v>31.36</v>
+        <v>32.65</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
@@ -7814,13 +7814,13 @@
         <v>9</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="M11" s="15" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
       <c r="N11" s="15" t="n">
-        <v>6.17</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -7881,10 +7881,10 @@
         </is>
       </c>
       <c r="M12" s="15" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="N12" s="15" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
@@ -8299,16 +8299,16 @@
         </is>
       </c>
       <c r="K18" s="14" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="L18" s="14" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>4.36</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
@@ -8435,16 +8435,16 @@
         </is>
       </c>
       <c r="K20" s="14" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="M20" s="15" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="N20" s="15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
@@ -8499,16 +8499,16 @@
         </is>
       </c>
       <c r="K21" s="14" t="n">
-        <v>28.4</v>
+        <v>31.4</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>41.5</v>
+        <v>45.5</v>
       </c>
       <c r="M21" s="15" t="n">
-        <v>8.619999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="N21" s="15" t="n">
-        <v>8.630000000000001</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -8563,16 +8563,16 @@
         </is>
       </c>
       <c r="K22" s="14" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="L22" s="14" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="M22" s="15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="N22" s="15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
@@ -8627,16 +8627,16 @@
         </is>
       </c>
       <c r="K23" s="14" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="M23" s="15" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="N23" s="15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
     </row>
   </sheetData>
@@ -8819,7 +8819,7 @@
         </is>
       </c>
       <c r="K5" s="15" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
@@ -8865,16 +8865,16 @@
         </is>
       </c>
       <c r="I6" s="14" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="L6" s="15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -8915,16 +8915,16 @@
         </is>
       </c>
       <c r="I7" s="14" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L7" s="15" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
@@ -9255,10 +9255,10 @@
         <v>8</v>
       </c>
       <c r="J5" s="14" t="n">
-        <v>16.1</v>
+        <v>16.4</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
@@ -9316,10 +9316,10 @@
         </is>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L6" s="15" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -9362,16 +9362,16 @@
         </is>
       </c>
       <c r="I7" s="14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="L7" s="15" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
@@ -9414,16 +9414,16 @@
         </is>
       </c>
       <c r="I8" s="14" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>24.9</v>
+        <v>25.5</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>9.74</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="L8" s="15" t="n">
-        <v>10.7</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
@@ -9469,7 +9469,7 @@
         <v>5.5</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>0.79</v>
@@ -9520,7 +9520,7 @@
         </is>
       </c>
       <c r="I10" s="14" t="n">
-        <v>42.3</v>
+        <v>43.7</v>
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
@@ -9576,16 +9576,16 @@
         </is>
       </c>
       <c r="I11" s="14" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -9631,13 +9631,13 @@
         <v>1.5</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="K13" s="15" t="n">
-        <v>5.58</v>
+        <v>5.63</v>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
@@ -9738,13 +9738,13 @@
         </is>
       </c>
       <c r="I14" s="14" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="J14" s="14" t="n">
-        <v>58.3</v>
+        <v>59.5</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
@@ -9792,16 +9792,16 @@
         </is>
       </c>
       <c r="I15" s="14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
@@ -9844,7 +9844,7 @@
         </is>
       </c>
       <c r="I16" s="14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
@@ -9852,10 +9852,10 @@
         </is>
       </c>
       <c r="K16" s="15" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
@@ -9898,16 +9898,16 @@
         </is>
       </c>
       <c r="I17" s="14" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="J17" s="14" t="n">
-        <v>36.2</v>
+        <v>37.5</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>5.88</v>
+        <v>6.1</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>8.279999999999999</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
@@ -9950,16 +9950,16 @@
         </is>
       </c>
       <c r="I18" s="14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="K19" s="15" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
@@ -10058,16 +10058,16 @@
         </is>
       </c>
       <c r="I20" s="14" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
@@ -10110,7 +10110,7 @@
         </is>
       </c>
       <c r="I21" s="14" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="K21" s="15" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="L21" s="15" t="n">
-        <v>4.21</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="I26" s="14" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="J26" s="14" t="n">
         <v>4.2</v>
@@ -10430,7 +10430,7 @@
         </is>
       </c>
       <c r="I27" s="14" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         </is>
       </c>
       <c r="K27" s="15" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
@@ -10449,12 +10449,12 @@
     <row r="28" ht="14" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Jeffrey Fox</t>
+          <t>Kenneth Gunderman</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Westrock Coffee</t>
+          <t>Uniti Group (Financial Services</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -10469,11 +10469,11 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>WEST</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
@@ -10486,29 +10486,29 @@
         </is>
       </c>
       <c r="I28" s="14" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="J28" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+        <v>4.5</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>1.7</v>
       </c>
       <c r="K28" s="15" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="L28" s="15" t="n">
-        <v>34.59</v>
+        <v>13.12</v>
+      </c>
+      <c r="L28" s="12" t="inlineStr">
+        <is>
+          <t>neg TBV</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>David Allen</t>
+          <t>Jeffrey Fox</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Westrock Coffee</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>WEST</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
@@ -10540,29 +10540,29 @@
         </is>
       </c>
       <c r="I29" s="14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="J29" s="14" t="n">
-        <v>21.1</v>
+        <v>24.4</v>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="K29" s="15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L29" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>3.26</v>
+      </c>
+      <c r="L29" s="15" t="n">
+        <v>34.77</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Brian Corvese</t>
+          <t>David Allen</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Agenus</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -10577,11 +10577,11 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
@@ -10594,31 +10594,29 @@
         </is>
       </c>
       <c r="I30" s="14" t="n">
-        <v>2.8</v>
+        <v>14.7</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K30" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
+        <v>21.3</v>
+      </c>
+      <c r="K30" s="15" t="n">
+        <v>2.21</v>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>neg equity</t>
+          <t>neg TBV</t>
         </is>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Darwin Green</t>
+          <t>Brian Corvese</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Contango ORE</t>
+          <t>Agenus</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -10628,16 +10626,16 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>CTGO</t>
+          <t>AGEN</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
@@ -10650,29 +10648,31 @@
         </is>
       </c>
       <c r="I31" s="14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J31" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="K31" s="15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L31" s="15" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Stephen Gunther</t>
+          <t>Darwin Green</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Shoulder Innovations</t>
+          <t>Contango ORE</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -10687,11 +10687,11 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>CTGO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
@@ -10703,10 +10703,8 @@
           <t>biography names the network</t>
         </is>
       </c>
-      <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
+      <c r="I32" s="14" t="n">
+        <v>6.6</v>
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
@@ -10714,21 +10712,21 @@
         </is>
       </c>
       <c r="K32" s="15" t="n">
-        <v>3.15</v>
+        <v>0.92</v>
       </c>
       <c r="L32" s="15" t="n">
-        <v>3.15</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="33" ht="14" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>R. Cox</t>
+          <t>Stephen Gunther</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Terex</t>
+          <t>Shoulder Innovations</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -10738,16 +10736,16 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
@@ -10759,30 +10757,32 @@
           <t>biography names the network</t>
         </is>
       </c>
-      <c r="I33" s="14" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="J33" s="14" t="n">
-        <v>26.4</v>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
       </c>
       <c r="K33" s="15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="L33" s="12" t="inlineStr">
-        <is>
-          <t>neg TBV</t>
-        </is>
+        <v>3.18</v>
+      </c>
+      <c r="L33" s="15" t="n">
+        <v>3.18</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Randle Reece</t>
+          <t>R. Cox</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>AMN Healthcare Services</t>
+          <t>Terex</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -10797,11 +10797,11 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>AMN</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
@@ -10814,13 +10814,13 @@
         </is>
       </c>
       <c r="I34" s="14" t="n">
-        <v>5.2</v>
+        <v>19.7</v>
       </c>
       <c r="J34" s="14" t="n">
-        <v>13.3</v>
+        <v>28.1</v>
       </c>
       <c r="K34" s="15" t="n">
-        <v>1.89</v>
+        <v>1.29</v>
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
@@ -10831,12 +10831,12 @@
     <row r="35" ht="14" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>John Campbell</t>
+          <t>Randle Reece</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Porch Group</t>
+          <t>AMN Healthcare Services</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -10851,11 +10851,11 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>AMN</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
@@ -10868,17 +10868,13 @@
         </is>
       </c>
       <c r="I35" s="14" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="J35" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="K35" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
+        <v>5.3</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="K35" s="15" t="n">
+        <v>1.93</v>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
@@ -10889,12 +10885,12 @@
     <row r="36" ht="14" customHeight="1">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Kenneth Gunderman</t>
+          <t>John Campbell</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Uniti Group (Financial Services</t>
+          <t>Porch Group</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -10909,11 +10905,11 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
@@ -10926,13 +10922,17 @@
         </is>
       </c>
       <c r="I36" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J36" s="14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K36" s="15" t="n">
-        <v>13.12</v>
+        <v>24.5</v>
+      </c>
+      <c r="J36" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="K36" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
       </c>
       <c r="L36" s="12" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         </is>
       </c>
       <c r="K37" s="15" t="n">
-        <v>26.04</v>
+        <v>26.89</v>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
@@ -11042,10 +11042,10 @@
         <v>0.9</v>
       </c>
       <c r="K38" s="15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="L38" s="15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1">
@@ -11098,10 +11098,10 @@
         </is>
       </c>
       <c r="K39" s="15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L39" s="15" t="n">
         <v>1.56</v>
-      </c>
-      <c r="L39" s="15" t="n">
-        <v>1.57</v>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
@@ -11147,13 +11147,13 @@
         <v>5.2</v>
       </c>
       <c r="J40" s="14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K40" s="15" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="L40" s="15" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="I41" s="14" t="n">
-        <v>52.2</v>
+        <v>52</v>
       </c>
       <c r="J41" s="14" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
@@ -11257,10 +11257,10 @@
         </is>
       </c>
       <c r="J42" s="14" t="n">
-        <v>52</v>
+        <v>52.3</v>
       </c>
       <c r="K42" s="15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
@@ -11372,10 +11372,10 @@
         </is>
       </c>
       <c r="K44" s="15" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="L44" s="15" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
@@ -11423,7 +11423,7 @@
         </is>
       </c>
       <c r="J45" s="14" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
@@ -11528,13 +11528,13 @@
         </is>
       </c>
       <c r="I47" s="14" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>16.87</v>
+        <v>16.7</v>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
@@ -11582,16 +11582,16 @@
         </is>
       </c>
       <c r="I48" s="14" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>27.4</v>
+        <v>27.7</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="L48" s="15" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
@@ -11634,16 +11634,16 @@
         </is>
       </c>
       <c r="I49" s="14" t="n">
-        <v>24.1</v>
+        <v>24.8</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>29</v>
+        <v>29.8</v>
       </c>
       <c r="K49" s="15" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="L49" s="15" t="n">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
@@ -11694,7 +11694,7 @@
         </is>
       </c>
       <c r="K50" s="15" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="L50" s="12" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="K51" s="15" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
@@ -11798,16 +11798,16 @@
         </is>
       </c>
       <c r="I52" s="14" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="J52" s="14" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="K52" s="15" t="n">
-        <v>7.91</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L52" s="15" t="n">
-        <v>7.91</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
@@ -11850,16 +11850,16 @@
         </is>
       </c>
       <c r="I53" s="14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J53" s="14" t="n">
-        <v>270.2</v>
+        <v>267.3</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="L53" s="15" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
@@ -11912,7 +11912,7 @@
         </is>
       </c>
       <c r="K54" s="15" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="L54" s="12" t="inlineStr">
         <is>
@@ -11960,16 +11960,16 @@
         </is>
       </c>
       <c r="I55" s="14" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="J55" s="14" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="K55" s="15" t="n">
-        <v>4.08</v>
+        <v>4.17</v>
       </c>
       <c r="L55" s="15" t="n">
-        <v>5.72</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
@@ -12012,13 +12012,13 @@
         </is>
       </c>
       <c r="I56" s="14" t="n">
-        <v>15.6</v>
+        <v>16.3</v>
       </c>
       <c r="J56" s="14" t="n">
-        <v>30.4</v>
+        <v>31.7</v>
       </c>
       <c r="K56" s="15" t="n">
-        <v>5.2</v>
+        <v>5.43</v>
       </c>
       <c r="L56" s="12" t="inlineStr">
         <is>
@@ -12066,16 +12066,16 @@
         </is>
       </c>
       <c r="I57" s="14" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="J57" s="14" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="K57" s="15" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="L57" s="15" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
@@ -12118,16 +12118,16 @@
         </is>
       </c>
       <c r="I58" s="14" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="J58" s="14" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="K58" s="15" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="L58" s="15" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
@@ -12170,16 +12170,16 @@
         </is>
       </c>
       <c r="I59" s="14" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="K59" s="15" t="n">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="L59" s="15" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1">
@@ -12222,7 +12222,7 @@
         </is>
       </c>
       <c r="I60" s="14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J60" s="12" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         </is>
       </c>
       <c r="K60" s="15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L60" s="12" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
@@ -12281,13 +12281,13 @@
         <v>3.4</v>
       </c>
       <c r="J61" s="14" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="K61" s="15" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="L61" s="15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
@@ -12456,16 +12456,16 @@
         </is>
       </c>
       <c r="I64" s="14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J64" s="14" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="L64" s="15" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
@@ -12942,10 +12942,10 @@
         <v>7</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="L72" s="15" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
@@ -12998,7 +12998,7 @@
         </is>
       </c>
       <c r="K73" s="15" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>0.4</v>
       </c>
       <c r="L74" s="15" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
@@ -13411,13 +13411,13 @@
         <v>17</v>
       </c>
       <c r="J80" s="14" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="K80" s="15" t="n">
         <v>0.46</v>
       </c>
       <c r="L80" s="15" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="81" ht="14" customHeight="1">
@@ -13782,10 +13782,10 @@
         </is>
       </c>
       <c r="K86" s="15" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="L86" s="15" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="87" ht="14" customHeight="1">
@@ -14088,10 +14088,10 @@
         </is>
       </c>
       <c r="K91" s="15" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="L91" s="15" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="92" ht="14" customHeight="1">
@@ -14384,16 +14384,16 @@
         </is>
       </c>
       <c r="I96" s="14" t="n">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="J96" s="14" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="L96" s="15" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="I99" s="14" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="J99" s="14" t="n">
-        <v>36.7</v>
+        <v>36.4</v>
       </c>
       <c r="K99" s="15" t="n">
-        <v>33.67</v>
+        <v>33.36</v>
       </c>
       <c r="L99" s="15" t="n">
-        <v>101.74</v>
+        <v>100.79</v>
       </c>
     </row>
     <row r="100" ht="14" customHeight="1">
@@ -14930,10 +14930,10 @@
         </is>
       </c>
       <c r="K105" s="15" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="L105" s="15" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="106" ht="14" customHeight="1">
@@ -15164,7 +15164,7 @@
         </is>
       </c>
       <c r="I109" s="14" t="n">
-        <v>195.2</v>
+        <v>194.1</v>
       </c>
       <c r="J109" s="12" t="inlineStr">
         <is>
@@ -15172,10 +15172,10 @@
         </is>
       </c>
       <c r="K109" s="15" t="n">
-        <v>5.48</v>
+        <v>5.47</v>
       </c>
       <c r="L109" s="15" t="n">
-        <v>5.49</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="110" ht="14" customHeight="1">
@@ -15223,10 +15223,10 @@
         <v>8.6</v>
       </c>
       <c r="J110" s="14" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="L110" s="12" t="inlineStr">
         <is>
@@ -15348,10 +15348,10 @@
         </is>
       </c>
       <c r="K112" s="15" t="n">
-        <v>5.2</v>
+        <v>5.17</v>
       </c>
       <c r="L112" s="15" t="n">
-        <v>5.2</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="113" ht="14" customHeight="1">
@@ -15706,16 +15706,16 @@
         </is>
       </c>
       <c r="I118" s="14" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="J118" s="14" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L118" s="15" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="119" ht="14" customHeight="1">
@@ -16008,7 +16008,7 @@
         </is>
       </c>
       <c r="I123" s="14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J123" s="12" t="inlineStr">
         <is>
@@ -16016,10 +16016,10 @@
         </is>
       </c>
       <c r="K123" s="15" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="L123" s="15" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="124" ht="14" customHeight="1">
@@ -16250,16 +16250,16 @@
         </is>
       </c>
       <c r="I127" s="14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J127" s="14" t="n">
-        <v>17.6</v>
+        <v>17.3</v>
       </c>
       <c r="K127" s="15" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="L127" s="15" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="128" ht="14" customHeight="1">
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="K128" s="15" t="n">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="L128" s="12" t="inlineStr">
         <is>
@@ -16984,13 +16984,13 @@
         </is>
       </c>
       <c r="I139" s="14" t="n">
-        <v>22.2</v>
+        <v>21.8</v>
       </c>
       <c r="J139" s="14" t="n">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="K139" s="15" t="n">
-        <v>35.35</v>
+        <v>34.66</v>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
@@ -17105,13 +17105,13 @@
         <v>7</v>
       </c>
       <c r="J141" s="14" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K141" s="15" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="L141" s="15" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="142" ht="14" customHeight="1">
@@ -17768,16 +17768,16 @@
         </is>
       </c>
       <c r="I152" s="14" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J152" s="14" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="L152" s="15" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="153" ht="14" customHeight="1">
@@ -17828,7 +17828,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K153" s="15" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="L153" s="15" t="n">
         <v>0.83</v>
@@ -17876,16 +17876,16 @@
         </is>
       </c>
       <c r="I154" s="14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J154" s="14" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="L154" s="15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="155" ht="14" customHeight="1">
@@ -18312,10 +18312,10 @@
         </is>
       </c>
       <c r="K161" s="15" t="n">
-        <v>0.74</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L161" s="15" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="162" ht="14" customHeight="1">
@@ -19104,16 +19104,16 @@
         </is>
       </c>
       <c r="I174" s="14" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="J174" s="14" t="n">
-        <v>220.1</v>
+        <v>223.2</v>
       </c>
       <c r="K174" s="15" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="L174" s="15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="175" ht="14" customHeight="1">
@@ -19344,16 +19344,16 @@
         </is>
       </c>
       <c r="I178" s="14" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="J178" s="14" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="K178" s="15" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L178" s="15" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="179" ht="14" customHeight="1">
@@ -19460,16 +19460,16 @@
         </is>
       </c>
       <c r="I180" s="14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J180" s="14" t="n">
         <v>10.6</v>
       </c>
       <c r="K180" s="15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="L180" s="15" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="181" ht="14" customHeight="1">
@@ -19638,16 +19638,16 @@
         </is>
       </c>
       <c r="I183" s="14" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="J183" s="14" t="n">
-        <v>35.4</v>
+        <v>36.2</v>
       </c>
       <c r="K183" s="15" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="L183" s="15" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="184" ht="14" customHeight="1">
@@ -19739,7 +19739,7 @@
         </is>
       </c>
       <c r="F185" s="12" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="G185" s="10" t="inlineStr">
         <is>
@@ -19755,13 +19755,13 @@
         <v>6.8</v>
       </c>
       <c r="J185" s="14" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="K185" s="15" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="L185" s="15" t="n">
-        <v>5.4</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="186" ht="14" customHeight="1">
@@ -19804,16 +19804,16 @@
         </is>
       </c>
       <c r="I186" s="14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J186" s="14" t="n">
-        <v>108.7</v>
+        <v>115</v>
       </c>
       <c r="K186" s="15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L186" s="15" t="n">
-        <v>176.77</v>
+        <v>187.06</v>
       </c>
     </row>
     <row r="187" ht="14" customHeight="1">
@@ -19856,16 +19856,16 @@
         </is>
       </c>
       <c r="I187" s="14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J187" s="14" t="n">
-        <v>108.7</v>
+        <v>115</v>
       </c>
       <c r="K187" s="15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L187" s="15" t="n">
-        <v>176.77</v>
+        <v>187.06</v>
       </c>
     </row>
     <row r="188" ht="14" customHeight="1">
@@ -19914,10 +19914,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="K188" s="15" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L188" s="15" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="189" ht="14" customHeight="1">
@@ -19970,10 +19970,10 @@
         </is>
       </c>
       <c r="K189" s="15" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="L189" s="15" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="190" ht="14" customHeight="1">
@@ -20642,27 +20642,27 @@
         </is>
       </c>
       <c r="I202" s="14" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="J202" s="14" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="K202" s="15" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="L202" s="15" t="n">
-        <v>203.23</v>
+        <v>207.19</v>
       </c>
     </row>
     <row r="203" ht="14" customHeight="1">
       <c r="A203" s="10" t="inlineStr">
         <is>
-          <t>Pamala Kaufman</t>
+          <t>Annalisa Jenkins</t>
         </is>
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>Lindblad Expeditions Holdings</t>
+          <t>COMPASS Pathways</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
@@ -20677,11 +20677,11 @@
       </c>
       <c r="E203" s="9" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>CMPS</t>
         </is>
       </c>
       <c r="F203" s="12" t="n">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="G203" s="10" t="inlineStr">
         <is>
@@ -20693,34 +20693,32 @@
           <t>matched another way, usually an employer-name collision: not signal</t>
         </is>
       </c>
-      <c r="I203" s="14" t="n">
-        <v>23.2</v>
+      <c r="I203" s="12" t="inlineStr">
+        <is>
+          <t>neg EBITDA</t>
+        </is>
       </c>
       <c r="J203" s="12" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="K203" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
-      </c>
-      <c r="L203" s="12" t="inlineStr">
-        <is>
-          <t>neg equity</t>
-        </is>
+      <c r="K203" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="L203" s="15" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="204" ht="14" customHeight="1">
       <c r="A204" s="10" t="inlineStr">
         <is>
-          <t>Annalisa Jenkins</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>COMPASS Pathways</t>
+          <t>SLB (Other Energy Services</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
@@ -20735,11 +20733,11 @@
       </c>
       <c r="E204" s="9" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="F204" s="12" t="n">
-        <v>16.2</v>
+        <v>14.9</v>
       </c>
       <c r="G204" s="10" t="inlineStr">
         <is>
@@ -20751,32 +20749,28 @@
           <t>matched another way, usually an employer-name collision: not signal</t>
         </is>
       </c>
-      <c r="I204" s="12" t="inlineStr">
-        <is>
-          <t>neg EBITDA</t>
-        </is>
-      </c>
-      <c r="J204" s="12" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
+      <c r="I204" s="14" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J204" s="14" t="n">
+        <v>23.4</v>
       </c>
       <c r="K204" s="15" t="n">
-        <v>13.78</v>
+        <v>2.79</v>
       </c>
       <c r="L204" s="15" t="n">
-        <v>13.78</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="205" ht="14" customHeight="1">
       <c r="A205" s="10" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>Pamala Kaufman</t>
         </is>
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
-          <t>SLB (Other Energy Services</t>
+          <t>Lindblad Expeditions Holdings</t>
         </is>
       </c>
       <c r="C205" s="10" t="inlineStr">
@@ -20791,11 +20785,11 @@
       </c>
       <c r="E205" s="9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="F205" s="12" t="n">
-        <v>14.9</v>
+        <v>13.8</v>
       </c>
       <c r="G205" s="10" t="inlineStr">
         <is>
@@ -20808,16 +20802,22 @@
         </is>
       </c>
       <c r="I205" s="14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J205" s="14" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="K205" s="15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L205" s="15" t="n">
-        <v>14.2</v>
+        <v>25.2</v>
+      </c>
+      <c r="J205" s="12" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="K205" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
+      </c>
+      <c r="L205" s="12" t="inlineStr">
+        <is>
+          <t>neg equity</t>
+        </is>
       </c>
     </row>
     <row r="206" ht="14" customHeight="1">
@@ -20860,7 +20860,7 @@
         </is>
       </c>
       <c r="I206" s="14" t="n">
-        <v>39.8</v>
+        <v>40.6</v>
       </c>
       <c r="J206" s="12" t="inlineStr">
         <is>
@@ -20868,10 +20868,10 @@
         </is>
       </c>
       <c r="K206" s="15" t="n">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="L206" s="15" t="n">
-        <v>59.24</v>
+        <v>61.07</v>
       </c>
     </row>
     <row r="207" ht="14" customHeight="1">
@@ -20914,16 +20914,16 @@
         </is>
       </c>
       <c r="I207" s="14" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="J207" s="14" t="n">
-        <v>37.4</v>
+        <v>39.5</v>
       </c>
       <c r="K207" s="15" t="n">
-        <v>3.24</v>
+        <v>3.42</v>
       </c>
       <c r="L207" s="15" t="n">
-        <v>15.68</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="208" ht="14" customHeight="1">
@@ -20966,16 +20966,16 @@
         </is>
       </c>
       <c r="I208" s="14" t="n">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="J208" s="14" t="n">
-        <v>34.5</v>
+        <v>35.9</v>
       </c>
       <c r="K208" s="15" t="n">
-        <v>5.02</v>
+        <v>5.22</v>
       </c>
       <c r="L208" s="15" t="n">
-        <v>5.02</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="209" ht="14" customHeight="1">
@@ -21024,10 +21024,10 @@
         <v>7.8</v>
       </c>
       <c r="K209" s="15" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="L209" s="15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="210" ht="14" customHeight="1">
@@ -21134,10 +21134,10 @@
         </is>
       </c>
       <c r="K211" s="15" t="n">
-        <v>11.05</v>
+        <v>11.23</v>
       </c>
       <c r="L211" s="15" t="n">
-        <v>11.05</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="212" ht="14" customHeight="1">
@@ -21245,13 +21245,13 @@
         </is>
       </c>
       <c r="J213" s="14" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="K213" s="15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="L213" s="15" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="214" ht="14" customHeight="1">
@@ -21348,16 +21348,16 @@
         </is>
       </c>
       <c r="I215" s="14" t="n">
-        <v>16.4</v>
+        <v>15.8</v>
       </c>
       <c r="J215" s="14" t="n">
-        <v>26.3</v>
+        <v>25.4</v>
       </c>
       <c r="K215" s="15" t="n">
-        <v>5.04</v>
+        <v>4.87</v>
       </c>
       <c r="L215" s="15" t="n">
-        <v>7.24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="216" ht="14" customHeight="1">
@@ -21400,16 +21400,16 @@
         </is>
       </c>
       <c r="I216" s="14" t="n">
-        <v>143.2</v>
+        <v>160.8</v>
       </c>
       <c r="J216" s="14" t="n">
-        <v>107.6</v>
+        <v>121.1</v>
       </c>
       <c r="K216" s="15" t="n">
-        <v>22.22</v>
+        <v>25</v>
       </c>
       <c r="L216" s="15" t="n">
-        <v>73.62</v>
+        <v>82.84</v>
       </c>
     </row>
     <row r="217" ht="14" customHeight="1">
@@ -21452,16 +21452,16 @@
         </is>
       </c>
       <c r="I217" s="14" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="J217" s="14" t="n">
-        <v>53.6</v>
+        <v>54.1</v>
       </c>
       <c r="K217" s="15" t="n">
-        <v>6.5</v>
+        <v>6.57</v>
       </c>
       <c r="L217" s="15" t="n">
-        <v>6.66</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="218" ht="14" customHeight="1">
@@ -21514,10 +21514,10 @@
         </is>
       </c>
       <c r="K218" s="15" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="L218" s="15" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="219" ht="14" customHeight="1">
@@ -21560,13 +21560,13 @@
         </is>
       </c>
       <c r="I219" s="14" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J219" s="14" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="K219" s="15" t="n">
-        <v>13.37</v>
+        <v>13.18</v>
       </c>
       <c r="L219" s="12" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="I220" s="14" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="J220" s="12" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>0.51</v>
       </c>
       <c r="L220" s="15" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="221" ht="14" customHeight="1">
@@ -21671,13 +21671,13 @@
         <v>6.3</v>
       </c>
       <c r="J221" s="14" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="K221" s="15" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="L221" s="15" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="222" ht="14" customHeight="1">
@@ -21824,13 +21824,13 @@
         </is>
       </c>
       <c r="I224" s="14" t="n">
-        <v>40.1</v>
+        <v>39.9</v>
       </c>
       <c r="J224" s="14" t="n">
-        <v>3926.4</v>
+        <v>3917</v>
       </c>
       <c r="K224" s="15" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="L224" s="15" t="n">
         <v>0.9399999999999999</v>
@@ -21879,13 +21879,13 @@
         <v>4.4</v>
       </c>
       <c r="J225" s="14" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="K225" s="15" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="L225" s="15" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="226" ht="14" customHeight="1">
@@ -21938,10 +21938,10 @@
         </is>
       </c>
       <c r="K226" s="15" t="n">
-        <v>4.3</v>
+        <v>4.43</v>
       </c>
       <c r="L226" s="15" t="n">
-        <v>93.48999999999999</v>
+        <v>96.31999999999999</v>
       </c>
     </row>
     <row r="227" ht="14" customHeight="1">
@@ -21971,7 +21971,7 @@
         </is>
       </c>
       <c r="F227" s="12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G227" s="10" t="inlineStr">
         <is>
@@ -21984,13 +21984,13 @@
         </is>
       </c>
       <c r="I227" s="14" t="n">
-        <v>18.6</v>
+        <v>19.1</v>
       </c>
       <c r="J227" s="14" t="n">
-        <v>45.9</v>
+        <v>47.1</v>
       </c>
       <c r="K227" s="15" t="n">
-        <v>52.8</v>
+        <v>54.13</v>
       </c>
       <c r="L227" s="12" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         </is>
       </c>
       <c r="I228" s="14" t="n">
-        <v>144.5</v>
+        <v>143.1</v>
       </c>
       <c r="J228" s="12" t="inlineStr">
         <is>
@@ -22046,10 +22046,10 @@
         </is>
       </c>
       <c r="K228" s="15" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
       <c r="L228" s="15" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="229" ht="14" customHeight="1">
@@ -22102,10 +22102,10 @@
         </is>
       </c>
       <c r="K229" s="15" t="n">
-        <v>13.92</v>
+        <v>15.18</v>
       </c>
       <c r="L229" s="15" t="n">
-        <v>15.33</v>
+        <v>16.72</v>
       </c>
     </row>
     <row r="230" ht="14" customHeight="1">
@@ -22148,16 +22148,16 @@
         </is>
       </c>
       <c r="I230" s="14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J230" s="14" t="n">
         <v>10.4</v>
       </c>
       <c r="K230" s="15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="L230" s="15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="231" ht="14" customHeight="1">
@@ -22200,16 +22200,16 @@
         </is>
       </c>
       <c r="I231" s="14" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J231" s="14" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="K231" s="15" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="L231" s="15" t="n">
-        <v>3.57</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="232" ht="14" customHeight="1">
@@ -22252,7 +22252,7 @@
         </is>
       </c>
       <c r="I232" s="14" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="J232" s="12" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         </is>
       </c>
       <c r="I233" s="14" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="J233" s="12" t="inlineStr">
         <is>
@@ -22360,16 +22360,16 @@
         </is>
       </c>
       <c r="I234" s="14" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="J234" s="14" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="K234" s="15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="L234" s="15" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="235" ht="14" customHeight="1">
@@ -22412,13 +22412,13 @@
         </is>
       </c>
       <c r="I235" s="14" t="n">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="J235" s="14" t="n">
-        <v>19.3</v>
+        <v>20.1</v>
       </c>
       <c r="K235" s="15" t="n">
-        <v>35.14</v>
+        <v>36.49</v>
       </c>
       <c r="L235" s="12" t="inlineStr">
         <is>
@@ -22469,13 +22469,13 @@
         <v>1.5</v>
       </c>
       <c r="J236" s="14" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="K236" s="15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="L236" s="15" t="n">
-        <v>6.55</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="237" ht="14" customHeight="1">
@@ -22521,13 +22521,13 @@
         <v>1.5</v>
       </c>
       <c r="J237" s="14" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="K237" s="15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="L237" s="15" t="n">
-        <v>6.55</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="238" ht="14" customHeight="1">
@@ -22573,13 +22573,13 @@
         <v>1.5</v>
       </c>
       <c r="J238" s="14" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="K238" s="15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="L238" s="15" t="n">
-        <v>6.55</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="239" ht="14" customHeight="1">
@@ -22625,13 +22625,13 @@
         <v>1.5</v>
       </c>
       <c r="J239" s="14" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="K239" s="15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="L239" s="15" t="n">
-        <v>6.55</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="240" ht="14" customHeight="1">
@@ -22677,13 +22677,13 @@
         <v>1.5</v>
       </c>
       <c r="J240" s="14" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="K240" s="15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="L240" s="15" t="n">
-        <v>6.55</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="241" ht="14" customHeight="1">
@@ -22729,13 +22729,13 @@
         <v>1.5</v>
       </c>
       <c r="J241" s="14" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="K241" s="15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="L241" s="15" t="n">
-        <v>6.55</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="242" ht="14" customHeight="1">
@@ -22781,13 +22781,13 @@
         <v>1.5</v>
       </c>
       <c r="J242" s="14" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="K242" s="15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="L242" s="15" t="n">
-        <v>6.55</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="243" ht="14" customHeight="1">
@@ -22833,13 +22833,13 @@
         <v>1.5</v>
       </c>
       <c r="J243" s="14" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="K243" s="15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="L243" s="15" t="n">
-        <v>6.55</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="244" ht="14" customHeight="1">
@@ -22885,13 +22885,13 @@
         <v>1.5</v>
       </c>
       <c r="J244" s="14" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="K244" s="15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="L244" s="15" t="n">
-        <v>6.55</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="245" ht="14" customHeight="1">
@@ -22934,27 +22934,27 @@
         </is>
       </c>
       <c r="I245" s="14" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J245" s="14" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="K245" s="15" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="L245" s="15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="246" ht="14" customHeight="1">
       <c r="A246" s="10" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Douglas Rauch</t>
         </is>
       </c>
       <c r="B246" s="10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Sprouts Farmers Market</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
@@ -22969,11 +22969,11 @@
       </c>
       <c r="E246" s="9" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="F246" s="12" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="G246" s="10" t="inlineStr">
         <is>
@@ -22986,27 +22986,27 @@
         </is>
       </c>
       <c r="I246" s="14" t="n">
-        <v>5.6</v>
+        <v>7.9</v>
       </c>
       <c r="J246" s="14" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="K246" s="15" t="n">
-        <v>1.13</v>
+        <v>4.12</v>
       </c>
       <c r="L246" s="15" t="n">
-        <v>1.28</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="247" ht="14" customHeight="1">
       <c r="A247" s="10" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="B247" s="10" t="inlineStr">
         <is>
-          <t>Danaos</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
@@ -23016,12 +23016,12 @@
       </c>
       <c r="D247" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offices</t>
+          <t>Billionaire/Oligarch Vehicles</t>
         </is>
       </c>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="F247" s="12" t="n">
@@ -23038,27 +23038,27 @@
         </is>
       </c>
       <c r="I247" s="14" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="J247" s="14" t="n">
-        <v>5.2</v>
+        <v>13.4</v>
       </c>
       <c r="K247" s="15" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="L247" s="15" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="248" ht="14" customHeight="1">
       <c r="A248" s="10" t="inlineStr">
         <is>
-          <t>Douglas Rauch</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="B248" s="10" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market</t>
+          <t>Danaos</t>
         </is>
       </c>
       <c r="C248" s="10" t="inlineStr">
@@ -23068,16 +23068,16 @@
       </c>
       <c r="D248" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Vehicles</t>
+          <t>Gulf/Royal Family Offices</t>
         </is>
       </c>
       <c r="E248" s="9" t="inlineStr">
         <is>
-          <t>SFM</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F248" s="12" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="G248" s="10" t="inlineStr">
         <is>
@@ -23090,16 +23090,16 @@
         </is>
       </c>
       <c r="I248" s="14" t="n">
-        <v>8.1</v>
+        <v>4.2</v>
       </c>
       <c r="J248" s="14" t="n">
-        <v>12.6</v>
+        <v>5.5</v>
       </c>
       <c r="K248" s="15" t="n">
-        <v>4.15</v>
+        <v>0.73</v>
       </c>
       <c r="L248" s="15" t="n">
-        <v>6.85</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="249" ht="14" customHeight="1">
@@ -23278,10 +23278,10 @@
         </is>
       </c>
       <c r="K251" s="15" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="L251" s="15" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="252" ht="14" customHeight="1">
@@ -23450,16 +23450,16 @@
         </is>
       </c>
       <c r="I254" s="14" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="J254" s="14" t="n">
-        <v>46.9</v>
+        <v>45.5</v>
       </c>
       <c r="K254" s="15" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L254" s="15" t="n">
-        <v>3.99</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="255" ht="14" customHeight="1">
@@ -23879,10 +23879,10 @@
         <v>18.9</v>
       </c>
       <c r="J261" s="14" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="K261" s="15" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="L261" s="15" t="n">
         <v>0.42</v>
@@ -24687,7 +24687,7 @@
         <v>0.29</v>
       </c>
       <c r="L274" s="15" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="275" ht="14" customHeight="1">
@@ -24794,13 +24794,13 @@
         </is>
       </c>
       <c r="I276" s="14" t="n">
-        <v>117</v>
+        <v>116.8</v>
       </c>
       <c r="J276" s="14" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="K276" s="15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="L276" s="15" t="n">
         <v>0.21</v>
@@ -24848,16 +24848,16 @@
         </is>
       </c>
       <c r="I277" s="14" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="J277" s="14" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="K277" s="15" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="L277" s="15" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="278" ht="14" customHeight="1">
@@ -25222,7 +25222,7 @@
         </is>
       </c>
       <c r="K283" s="15" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="L283" s="12" t="inlineStr">
         <is>
@@ -25272,13 +25272,13 @@
         </is>
       </c>
       <c r="I284" s="14" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J284" s="14" t="n">
         <v>14</v>
       </c>
       <c r="K284" s="15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="L284" s="15" t="n">
         <v>1.97</v>
@@ -25587,7 +25587,7 @@
         <v>0.29</v>
       </c>
       <c r="L289" s="15" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="290" ht="14" customHeight="1">
@@ -25642,10 +25642,10 @@
         </is>
       </c>
       <c r="K290" s="15" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="L290" s="15" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="291" ht="14" customHeight="1">
@@ -25695,13 +25695,13 @@
         </is>
       </c>
       <c r="J291" s="14" t="n">
-        <v>43.6</v>
+        <v>44.4</v>
       </c>
       <c r="K291" s="15" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="L291" s="15" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="292" ht="14" customHeight="1">
@@ -25808,16 +25808,16 @@
         </is>
       </c>
       <c r="I293" s="14" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="J293" s="14" t="n">
-        <v>19.1</v>
+        <v>18.7</v>
       </c>
       <c r="K293" s="15" t="n">
-        <v>4.83</v>
+        <v>4.74</v>
       </c>
       <c r="L293" s="15" t="n">
-        <v>5.04</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="294" ht="14" customHeight="1">
@@ -25862,16 +25862,16 @@
         </is>
       </c>
       <c r="I294" s="14" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="J294" s="14" t="n">
-        <v>220.1</v>
+        <v>223.2</v>
       </c>
       <c r="K294" s="15" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="L294" s="15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="295" ht="14" customHeight="1">
@@ -25991,7 +25991,7 @@
         <v>0.29</v>
       </c>
       <c r="L296" s="15" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="297" ht="14" customHeight="1">
@@ -26218,13 +26218,13 @@
         </is>
       </c>
       <c r="I300" s="14" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J300" s="14" t="n">
         <v>14</v>
       </c>
       <c r="K300" s="15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="L300" s="15" t="n">
         <v>1.97</v>
@@ -26277,13 +26277,13 @@
         </is>
       </c>
       <c r="J301" s="14" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="K301" s="15" t="n">
-        <v>3.5</v>
+        <v>3.19</v>
       </c>
       <c r="L301" s="15" t="n">
-        <v>3.5</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="302" ht="14" customHeight="1">
@@ -26394,10 +26394,10 @@
         <v>28.5</v>
       </c>
       <c r="K303" s="15" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="L303" s="15" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="304" ht="14" customHeight="1">
@@ -26504,16 +26504,16 @@
         </is>
       </c>
       <c r="I305" s="14" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="J305" s="14" t="n">
         <v>18</v>
       </c>
       <c r="K305" s="15" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="L305" s="15" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="306" ht="14" customHeight="1">
@@ -26940,10 +26940,10 @@
         </is>
       </c>
       <c r="K312" s="15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="L312" s="15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="313" ht="14" customHeight="1">
@@ -27063,7 +27063,7 @@
         <v>0.29</v>
       </c>
       <c r="L314" s="15" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="315" ht="14" customHeight="1">
@@ -27175,7 +27175,7 @@
         <v>0.29</v>
       </c>
       <c r="L316" s="15" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="317" ht="14" customHeight="1">
@@ -27295,7 +27295,7 @@
         <v>0.29</v>
       </c>
       <c r="L318" s="15" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="319" ht="14" customHeight="1">
@@ -27350,10 +27350,10 @@
         </is>
       </c>
       <c r="K319" s="15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="L319" s="15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="320" ht="14" customHeight="1">
@@ -27824,16 +27824,16 @@
         </is>
       </c>
       <c r="I327" s="14" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="J327" s="14" t="n">
         <v>20.9</v>
       </c>
       <c r="K327" s="15" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="L327" s="15" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="328" ht="14" customHeight="1">
@@ -27950,10 +27950,10 @@
         </is>
       </c>
       <c r="K329" s="15" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="L329" s="15" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="330" ht="14" customHeight="1">
@@ -28238,16 +28238,16 @@
         </is>
       </c>
       <c r="I334" s="14" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="J334" s="14" t="n">
-        <v>220.1</v>
+        <v>223.2</v>
       </c>
       <c r="K334" s="15" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="L334" s="15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="335" ht="14" customHeight="1">
@@ -28788,10 +28788,10 @@
         </is>
       </c>
       <c r="I343" s="14" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J343" s="14" t="n">
-        <v>104.8</v>
+        <v>105.2</v>
       </c>
       <c r="K343" s="15" t="n">
         <v>0.57</v>
@@ -28904,16 +28904,16 @@
         </is>
       </c>
       <c r="I345" s="14" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="J345" s="14" t="n">
         <v>18</v>
       </c>
       <c r="K345" s="15" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="L345" s="15" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="346" ht="14" customHeight="1">
@@ -29020,16 +29020,16 @@
         </is>
       </c>
       <c r="I347" s="14" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="J347" s="14" t="n">
         <v>18</v>
       </c>
       <c r="K347" s="15" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="L347" s="15" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="348" ht="14" customHeight="1">
@@ -29198,16 +29198,16 @@
         </is>
       </c>
       <c r="I350" s="14" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="J350" s="14" t="n">
-        <v>220.1</v>
+        <v>223.2</v>
       </c>
       <c r="K350" s="15" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="L350" s="15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="351" ht="14" customHeight="1">
@@ -29257,13 +29257,13 @@
         </is>
       </c>
       <c r="J351" s="14" t="n">
-        <v>43.6</v>
+        <v>44.4</v>
       </c>
       <c r="K351" s="15" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="L351" s="15" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="352" ht="14" customHeight="1">
@@ -29494,16 +29494,16 @@
         </is>
       </c>
       <c r="I355" s="14" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="J355" s="14" t="n">
-        <v>46.9</v>
+        <v>45.5</v>
       </c>
       <c r="K355" s="15" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L355" s="15" t="n">
-        <v>3.99</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="356" ht="14" customHeight="1">
@@ -29672,7 +29672,7 @@
         </is>
       </c>
       <c r="I358" s="14" t="n">
-        <v>126</v>
+        <v>123.1</v>
       </c>
       <c r="J358" s="12" t="inlineStr">
         <is>
@@ -29680,10 +29680,10 @@
         </is>
       </c>
       <c r="K358" s="15" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="L358" s="15" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="359" ht="14" customHeight="1">
@@ -29972,7 +29972,7 @@
         </is>
       </c>
       <c r="I363" s="14" t="n">
-        <v>365.5</v>
+        <v>375</v>
       </c>
       <c r="J363" s="12" t="inlineStr">
         <is>
@@ -29980,10 +29980,10 @@
         </is>
       </c>
       <c r="K363" s="15" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="L363" s="15" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="364" ht="14" customHeight="1">
@@ -30648,16 +30648,16 @@
         </is>
       </c>
       <c r="I374" s="14" t="n">
-        <v>15</v>
+        <v>14.3</v>
       </c>
       <c r="J374" s="14" t="n">
-        <v>45</v>
+        <v>43.3</v>
       </c>
       <c r="K374" s="15" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="L374" s="15" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="375" ht="14" customHeight="1">
@@ -30942,16 +30942,16 @@
         </is>
       </c>
       <c r="I379" s="14" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="J379" s="14" t="n">
-        <v>220.1</v>
+        <v>223.2</v>
       </c>
       <c r="K379" s="15" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="L379" s="15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="380" ht="14" customHeight="1">
@@ -31123,7 +31123,7 @@
         <v>44.2</v>
       </c>
       <c r="J382" s="14" t="n">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K382" s="15" t="n">
         <v>11.71</v>
@@ -31236,10 +31236,10 @@
         </is>
       </c>
       <c r="I384" s="14" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J384" s="14" t="n">
-        <v>104.8</v>
+        <v>105.2</v>
       </c>
       <c r="K384" s="15" t="n">
         <v>0.57</v>
@@ -31838,16 +31838,16 @@
         </is>
       </c>
       <c r="I394" s="14" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="J394" s="14" t="n">
         <v>20.9</v>
       </c>
       <c r="K394" s="15" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="L394" s="15" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="395" ht="14" customHeight="1">
@@ -31895,13 +31895,13 @@
         <v>3.1</v>
       </c>
       <c r="J395" s="14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K395" s="15" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="L395" s="15" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="396" ht="14" customHeight="1">
@@ -31952,10 +31952,10 @@
         <v>16.8</v>
       </c>
       <c r="K396" s="15" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="L396" s="15" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="397" ht="14" customHeight="1">
@@ -32434,16 +32434,16 @@
         </is>
       </c>
       <c r="I404" s="14" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="J404" s="14" t="n">
-        <v>220.1</v>
+        <v>223.2</v>
       </c>
       <c r="K404" s="15" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="L404" s="15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="405" ht="14" customHeight="1">
@@ -33228,7 +33228,7 @@
         </is>
       </c>
       <c r="I417" s="14" t="n">
-        <v>126</v>
+        <v>123.1</v>
       </c>
       <c r="J417" s="12" t="inlineStr">
         <is>
@@ -33236,10 +33236,10 @@
         </is>
       </c>
       <c r="K417" s="15" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="L417" s="15" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="418" ht="14" customHeight="1">
@@ -33352,10 +33352,10 @@
         <v>28.5</v>
       </c>
       <c r="K419" s="15" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="L419" s="15" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="420" ht="14" customHeight="1">
@@ -33472,10 +33472,10 @@
         </is>
       </c>
       <c r="K421" s="15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="L421" s="15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="422" ht="14" customHeight="1">
@@ -33768,16 +33768,16 @@
         </is>
       </c>
       <c r="I426" s="14" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="J426" s="14" t="n">
-        <v>46.9</v>
+        <v>45.5</v>
       </c>
       <c r="K426" s="15" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L426" s="15" t="n">
-        <v>3.99</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="427" ht="14" customHeight="1">
@@ -33822,16 +33822,16 @@
         </is>
       </c>
       <c r="I427" s="14" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="J427" s="14" t="n">
-        <v>26.2</v>
+        <v>26.6</v>
       </c>
       <c r="K427" s="15" t="n">
-        <v>5.49</v>
+        <v>5.58</v>
       </c>
       <c r="L427" s="15" t="n">
-        <v>6.94</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="428" ht="14" customHeight="1">
@@ -33938,16 +33938,16 @@
         </is>
       </c>
       <c r="I429" s="14" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="J429" s="14" t="n">
-        <v>220.1</v>
+        <v>223.2</v>
       </c>
       <c r="K429" s="15" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="L429" s="15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="430" ht="14" customHeight="1">
@@ -33998,10 +33998,10 @@
         <v>6.2</v>
       </c>
       <c r="K430" s="15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="L430" s="15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="431" ht="14" customHeight="1">
@@ -34170,7 +34170,7 @@
         </is>
       </c>
       <c r="I433" s="14" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J433" s="14" t="n">
         <v>19.7</v>
@@ -34179,7 +34179,7 @@
         <v>4.39</v>
       </c>
       <c r="L433" s="15" t="n">
-        <v>5.56</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="434" ht="14" customHeight="1">
@@ -34292,10 +34292,10 @@
         <v>28.5</v>
       </c>
       <c r="K435" s="15" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="L435" s="15" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="436" ht="14" customHeight="1">
@@ -34340,16 +34340,16 @@
         </is>
       </c>
       <c r="I436" s="14" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J436" s="14" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K436" s="15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="L436" s="15" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="437" ht="14" customHeight="1">
@@ -34397,13 +34397,13 @@
         <v>2.4</v>
       </c>
       <c r="J437" s="14" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="K437" s="15" t="n">
         <v>0.96</v>
       </c>
       <c r="L437" s="15" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="438" ht="14" customHeight="1">
@@ -34634,16 +34634,16 @@
         </is>
       </c>
       <c r="I441" s="14" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="J441" s="14" t="n">
-        <v>46.9</v>
+        <v>45.5</v>
       </c>
       <c r="K441" s="15" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L441" s="15" t="n">
-        <v>3.99</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="442" ht="14" customHeight="1">
@@ -34750,16 +34750,16 @@
         </is>
       </c>
       <c r="I443" s="14" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="J443" s="14" t="n">
-        <v>30.4</v>
+        <v>30.8</v>
       </c>
       <c r="K443" s="15" t="n">
-        <v>3.58</v>
+        <v>3.63</v>
       </c>
       <c r="L443" s="15" t="n">
-        <v>3.59</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="444" ht="14" customHeight="1">
@@ -34814,10 +34814,10 @@
         </is>
       </c>
       <c r="K444" s="15" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="L444" s="15" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="445" ht="14" customHeight="1">
@@ -34872,10 +34872,10 @@
         </is>
       </c>
       <c r="K445" s="15" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="L445" s="15" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="446" ht="14" customHeight="1">
@@ -34930,10 +34930,10 @@
         </is>
       </c>
       <c r="K446" s="15" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="L446" s="15" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="447" ht="14" customHeight="1">
@@ -35040,16 +35040,16 @@
         </is>
       </c>
       <c r="I448" s="14" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J448" s="14" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K448" s="15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="L448" s="15" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="449" ht="14" customHeight="1">
@@ -35164,7 +35164,7 @@
         </is>
       </c>
       <c r="K450" s="15" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="L450" s="12" t="inlineStr">
         <is>
@@ -35220,10 +35220,10 @@
         <v>28.5</v>
       </c>
       <c r="K451" s="15" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="L451" s="15" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="452" ht="14" customHeight="1">
@@ -35402,10 +35402,10 @@
         </is>
       </c>
       <c r="K454" s="15" t="n">
-        <v>9.48</v>
+        <v>11.2</v>
       </c>
       <c r="L454" s="15" t="n">
-        <v>9.48</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="455" ht="14" customHeight="1">
@@ -35460,10 +35460,10 @@
         </is>
       </c>
       <c r="K455" s="15" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="L455" s="15" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="456" ht="14" customHeight="1">
@@ -35642,10 +35642,10 @@
         </is>
       </c>
       <c r="K458" s="15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="L458" s="15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="459" ht="14" customHeight="1">
@@ -36000,16 +36000,16 @@
         </is>
       </c>
       <c r="I464" s="14" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="J464" s="14" t="n">
         <v>20.9</v>
       </c>
       <c r="K464" s="15" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="L464" s="15" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="465" ht="14" customHeight="1">
@@ -36428,10 +36428,10 @@
         </is>
       </c>
       <c r="K471" s="15" t="n">
-        <v>5.79</v>
+        <v>5.56</v>
       </c>
       <c r="L471" s="15" t="n">
-        <v>6.22</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="472" ht="14" customHeight="1">
@@ -36848,16 +36848,16 @@
         </is>
       </c>
       <c r="I478" s="14" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="J478" s="14" t="n">
-        <v>19.1</v>
+        <v>18.7</v>
       </c>
       <c r="K478" s="15" t="n">
-        <v>4.83</v>
+        <v>4.74</v>
       </c>
       <c r="L478" s="15" t="n">
-        <v>5.04</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="479" ht="14" customHeight="1">
@@ -37225,7 +37225,7 @@
         <v>0.29</v>
       </c>
       <c r="L484" s="15" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="485" ht="14" customHeight="1">
@@ -37461,13 +37461,13 @@
         </is>
       </c>
       <c r="J488" s="14" t="n">
-        <v>43.6</v>
+        <v>44.4</v>
       </c>
       <c r="K488" s="15" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="L488" s="15" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="489" ht="14" customHeight="1">
@@ -37522,10 +37522,10 @@
         </is>
       </c>
       <c r="K489" s="15" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="L489" s="15" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="490" ht="14" customHeight="1">
@@ -37570,16 +37570,16 @@
         </is>
       </c>
       <c r="I490" s="14" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="J490" s="14" t="n">
-        <v>220.1</v>
+        <v>223.2</v>
       </c>
       <c r="K490" s="15" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="L490" s="15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="491" ht="14" customHeight="1">
@@ -38360,7 +38360,7 @@
         </is>
       </c>
       <c r="J12" s="14" t="n">
-        <v>9.6</v>
+        <v>12.2</v>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
@@ -38368,10 +38368,10 @@
         </is>
       </c>
       <c r="L12" s="15" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
@@ -38429,10 +38429,10 @@
         </is>
       </c>
       <c r="L13" s="15" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
@@ -38443,7 +38443,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -38478,7 +38478,7 @@
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>BAQAR HASSAN</t>
+          <t>Baqar Hassan Sajjad</t>
         </is>
       </c>
       <c r="J14" s="12" t="inlineStr">
@@ -38510,7 +38510,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -38545,7 +38545,7 @@
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>Baqar Hassan Sajjad</t>
+          <t>BAQAR HASSAN</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
@@ -38939,7 +38939,7 @@
         </is>
       </c>
       <c r="H21" s="12" t="n">
-        <v>29.5</v>
+        <v>30</v>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
@@ -38947,16 +38947,16 @@
         </is>
       </c>
       <c r="J21" s="14" t="n">
-        <v>34.7</v>
+        <v>33.6</v>
       </c>
       <c r="K21" s="14" t="n">
-        <v>70.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="L21" s="15" t="n">
-        <v>8.41</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M21" s="15" t="n">
-        <v>13.95</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -39004,10 +39004,10 @@
         </is>
       </c>
       <c r="J22" s="14" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
@@ -39132,7 +39132,7 @@
         </is>
       </c>
       <c r="J24" s="14" t="n">
-        <v>369.5</v>
+        <v>566.6</v>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
@@ -39140,10 +39140,10 @@
         </is>
       </c>
       <c r="L24" s="15" t="n">
-        <v>6.95</v>
+        <v>7.26</v>
       </c>
       <c r="M24" s="15" t="n">
-        <v>7.74</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
@@ -39183,7 +39183,7 @@
         </is>
       </c>
       <c r="H25" s="12" t="n">
-        <v>-3.1</v>
+        <v>-2.6</v>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
@@ -39191,16 +39191,16 @@
         </is>
       </c>
       <c r="J25" s="14" t="n">
-        <v>44.5</v>
+        <v>45.4</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>62.5</v>
+        <v>63.8</v>
       </c>
       <c r="L25" s="15" t="n">
-        <v>84.81</v>
+        <v>86.62</v>
       </c>
       <c r="M25" s="15" t="n">
-        <v>108.13</v>
+        <v>110.43</v>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
@@ -39240,7 +39240,7 @@
         </is>
       </c>
       <c r="H26" s="12" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
@@ -39248,16 +39248,16 @@
         </is>
       </c>
       <c r="J26" s="14" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="L26" s="15" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="M26" s="15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
@@ -39305,7 +39305,7 @@
         </is>
       </c>
       <c r="J27" s="14" t="n">
-        <v>369.5</v>
+        <v>566.6</v>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
@@ -39313,10 +39313,10 @@
         </is>
       </c>
       <c r="L27" s="15" t="n">
-        <v>6.95</v>
+        <v>7.26</v>
       </c>
       <c r="M27" s="15" t="n">
-        <v>7.74</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
@@ -39364,16 +39364,16 @@
         </is>
       </c>
       <c r="J28" s="14" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>19.9</v>
+        <v>20.6</v>
       </c>
       <c r="L28" s="15" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M28" s="15" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
@@ -39488,16 +39488,16 @@
         </is>
       </c>
       <c r="J30" s="14" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>85.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="L30" s="15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M30" s="15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
@@ -39506,9 +39506,9 @@
           <t>Manish Bhatia</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
